--- a/attached_assets/gantt_template.xlsx
+++ b/attached_assets/gantt_template.xlsx
@@ -66,9 +66,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,26 +400,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R250"/>
-  <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="25.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="30.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,10 +464,10 @@
       <c r="B2" t="str">
         <v>PHASE • Design &amp; Approvals</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D2" s="1" t="str">
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
@@ -518,10 +497,10 @@
       <c r="M2" t="str">
         <v/>
       </c>
-      <c r="N2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O2" s="1" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
@@ -541,11 +520,8 @@
       <c r="B3" t="str">
         <v>Client Brief &amp; Scope</v>
       </c>
-      <c r="C3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D3" s="1">
-        <f>IF(AND(C3&lt;&gt;"",E3&lt;&gt;""),C3+E3-1,"")</f>
+      <c r="C3" t="str">
+        <v/>
       </c>
       <c r="E3">
         <v>2</v>
@@ -574,11 +550,8 @@
       <c r="M3" t="str">
         <v/>
       </c>
-      <c r="N3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O3" s="1">
-        <f>IF(AND(N3&lt;&gt;"",E3&lt;&gt;""),N3+E3-1,"")</f>
+      <c r="N3" t="str">
+        <v/>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -597,11 +570,8 @@
       <c r="B4" t="str">
         <v>Schematic Drawings (Overall)</v>
       </c>
-      <c r="C4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D4" s="1">
-        <f>IF(AND(C4&lt;&gt;"",E4&lt;&gt;""),C4+E4-1,"")</f>
+      <c r="C4" t="str">
+        <v/>
       </c>
       <c r="E4">
         <v>5</v>
@@ -630,11 +600,8 @@
       <c r="M4" t="str">
         <v/>
       </c>
-      <c r="N4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O4" s="1">
-        <f>IF(AND(N4&lt;&gt;"",E4&lt;&gt;""),N4+E4-1,"")</f>
+      <c r="N4" t="str">
+        <v/>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -653,11 +620,8 @@
       <c r="B5" t="str">
         <v>Working Drawings (Overall)</v>
       </c>
-      <c r="C5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D5" s="1">
-        <f>IF(AND(C5&lt;&gt;"",E5&lt;&gt;""),C5+E5-1,"")</f>
+      <c r="C5" t="str">
+        <v/>
       </c>
       <c r="E5">
         <v>7</v>
@@ -686,11 +650,8 @@
       <c r="M5" t="str">
         <v/>
       </c>
-      <c r="N5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O5" s="1">
-        <f>IF(AND(N5&lt;&gt;"",E5&lt;&gt;""),N5+E5-1,"")</f>
+      <c r="N5" t="str">
+        <v/>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -709,11 +670,8 @@
       <c r="B6" t="str">
         <v>Finishes Board &amp; Samples (Overall)</v>
       </c>
-      <c r="C6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D6" s="1">
-        <f>IF(AND(C6&lt;&gt;"",E6&lt;&gt;""),C6+E6-1,"")</f>
+      <c r="C6" t="str">
+        <v/>
       </c>
       <c r="E6">
         <v>3</v>
@@ -742,11 +700,8 @@
       <c r="M6" t="str">
         <v/>
       </c>
-      <c r="N6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O6" s="1">
-        <f>IF(AND(N6&lt;&gt;"",E6&lt;&gt;""),N6+E6-1,"")</f>
+      <c r="N6" t="str">
+        <v/>
       </c>
       <c r="P6" t="str">
         <v/>
@@ -765,11 +720,8 @@
       <c r="B7" t="str">
         <v>Client Sign‑off (Drawings &amp; Finishes)</v>
       </c>
-      <c r="C7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="1">
-        <f>IF(AND(C7&lt;&gt;"",E7&lt;&gt;""),C7+E7-1,"")</f>
+      <c r="C7" t="str">
+        <v/>
       </c>
       <c r="E7">
         <v>1</v>
@@ -798,11 +750,8 @@
       <c r="M7" t="str">
         <v/>
       </c>
-      <c r="N7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O7" s="1">
-        <f>IF(AND(N7&lt;&gt;"",E7&lt;&gt;""),N7+E7-1,"")</f>
+      <c r="N7" t="str">
+        <v/>
       </c>
       <c r="P7" t="str">
         <v/>
@@ -821,10 +770,10 @@
       <c r="B8" t="str">
         <v>PHASE • Vendor Evaluation → Quotes → Finalisation → Work Orders</v>
       </c>
-      <c r="C8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D8" s="1" t="str">
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
@@ -854,10 +803,10 @@
       <c r="M8" t="str">
         <v/>
       </c>
-      <c r="N8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O8" s="1" t="str">
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
@@ -877,10 +826,10 @@
       <c r="B9" t="str">
         <v>PACKAGE • Civil</v>
       </c>
-      <c r="C9" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D9" s="1" t="str">
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
@@ -910,10 +859,10 @@
       <c r="M9" t="str">
         <v/>
       </c>
-      <c r="N9" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O9" s="1" t="str">
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
         <v/>
       </c>
       <c r="P9" t="str">
@@ -933,11 +882,8 @@
       <c r="B10" t="str">
         <v>Civil: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C10" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D10" s="1">
-        <f>IF(AND(C10&lt;&gt;"",E10&lt;&gt;""),C10+E10-1,"")</f>
+      <c r="C10" t="str">
+        <v/>
       </c>
       <c r="E10">
         <v>3</v>
@@ -966,11 +912,8 @@
       <c r="M10" t="str">
         <v/>
       </c>
-      <c r="N10" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O10" s="1">
-        <f>IF(AND(N10&lt;&gt;"",E10&lt;&gt;""),N10+E10-1,"")</f>
+      <c r="N10" t="str">
+        <v/>
       </c>
       <c r="P10" t="str">
         <v/>
@@ -989,11 +932,8 @@
       <c r="B11" t="str">
         <v>Civil: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C11" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D11" s="1">
-        <f>IF(AND(C11&lt;&gt;"",E11&lt;&gt;""),C11+E11-1,"")</f>
+      <c r="C11" t="str">
+        <v/>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1022,11 +962,8 @@
       <c r="M11" t="str">
         <v/>
       </c>
-      <c r="N11" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O11" s="1">
-        <f>IF(AND(N11&lt;&gt;"",E11&lt;&gt;""),N11+E11-1,"")</f>
+      <c r="N11" t="str">
+        <v/>
       </c>
       <c r="P11" t="str">
         <v/>
@@ -1045,11 +982,8 @@
       <c r="B12" t="str">
         <v>Civil: RFQs Issued</v>
       </c>
-      <c r="C12" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D12" s="1">
-        <f>IF(AND(C12&lt;&gt;"",E12&lt;&gt;""),C12+E12-1,"")</f>
+      <c r="C12" t="str">
+        <v/>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1078,11 +1012,8 @@
       <c r="M12" t="str">
         <v/>
       </c>
-      <c r="N12" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O12" s="1">
-        <f>IF(AND(N12&lt;&gt;"",E12&lt;&gt;""),N12+E12-1,"")</f>
+      <c r="N12" t="str">
+        <v/>
       </c>
       <c r="P12" t="str">
         <v/>
@@ -1101,11 +1032,8 @@
       <c r="B13" t="str">
         <v>Civil: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D13" s="1">
-        <f>IF(AND(C13&lt;&gt;"",E13&lt;&gt;""),C13+E13-1,"")</f>
+      <c r="C13" t="str">
+        <v/>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1134,11 +1062,8 @@
       <c r="M13" t="str">
         <v/>
       </c>
-      <c r="N13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O13" s="1">
-        <f>IF(AND(N13&lt;&gt;"",E13&lt;&gt;""),N13+E13-1,"")</f>
+      <c r="N13" t="str">
+        <v/>
       </c>
       <c r="P13" t="str">
         <v/>
@@ -1157,11 +1082,8 @@
       <c r="B14" t="str">
         <v>Civil: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D14" s="1">
-        <f>IF(AND(C14&lt;&gt;"",E14&lt;&gt;""),C14+E14-1,"")</f>
+      <c r="C14" t="str">
+        <v/>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1190,11 +1112,8 @@
       <c r="M14" t="str">
         <v/>
       </c>
-      <c r="N14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O14" s="1">
-        <f>IF(AND(N14&lt;&gt;"",E14&lt;&gt;""),N14+E14-1,"")</f>
+      <c r="N14" t="str">
+        <v/>
       </c>
       <c r="P14" t="str">
         <v/>
@@ -1213,11 +1132,8 @@
       <c r="B15" t="str">
         <v>Civil: Vendor Finalisation</v>
       </c>
-      <c r="C15" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D15" s="1">
-        <f>IF(AND(C15&lt;&gt;"",E15&lt;&gt;""),C15+E15-1,"")</f>
+      <c r="C15" t="str">
+        <v/>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1246,11 +1162,8 @@
       <c r="M15" t="str">
         <v/>
       </c>
-      <c r="N15" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O15" s="1">
-        <f>IF(AND(N15&lt;&gt;"",E15&lt;&gt;""),N15+E15-1,"")</f>
+      <c r="N15" t="str">
+        <v/>
       </c>
       <c r="P15" t="str">
         <v/>
@@ -1269,11 +1182,8 @@
       <c r="B16" t="str">
         <v>Civil: Work Order / PO Release</v>
       </c>
-      <c r="C16" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D16" s="1">
-        <f>IF(AND(C16&lt;&gt;"",E16&lt;&gt;""),C16+E16-1,"")</f>
+      <c r="C16" t="str">
+        <v/>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1302,11 +1212,8 @@
       <c r="M16" t="str">
         <v/>
       </c>
-      <c r="N16" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O16" s="1">
-        <f>IF(AND(N16&lt;&gt;"",E16&lt;&gt;""),N16+E16-1,"")</f>
+      <c r="N16" t="str">
+        <v/>
       </c>
       <c r="P16" t="str">
         <v/>
@@ -1325,10 +1232,10 @@
       <c r="B17" t="str">
         <v>PACKAGE • Electricals</v>
       </c>
-      <c r="C17" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D17" s="1" t="str">
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
@@ -1358,10 +1265,10 @@
       <c r="M17" t="str">
         <v/>
       </c>
-      <c r="N17" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O17" s="1" t="str">
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
         <v/>
       </c>
       <c r="P17" t="str">
@@ -1381,11 +1288,8 @@
       <c r="B18" t="str">
         <v>Electricals: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C18" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D18" s="1">
-        <f>IF(AND(C18&lt;&gt;"",E18&lt;&gt;""),C18+E18-1,"")</f>
+      <c r="C18" t="str">
+        <v/>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1414,11 +1318,8 @@
       <c r="M18" t="str">
         <v/>
       </c>
-      <c r="N18" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O18" s="1">
-        <f>IF(AND(N18&lt;&gt;"",E18&lt;&gt;""),N18+E18-1,"")</f>
+      <c r="N18" t="str">
+        <v/>
       </c>
       <c r="P18" t="str">
         <v/>
@@ -1437,11 +1338,8 @@
       <c r="B19" t="str">
         <v>Electricals: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C19" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D19" s="1">
-        <f>IF(AND(C19&lt;&gt;"",E19&lt;&gt;""),C19+E19-1,"")</f>
+      <c r="C19" t="str">
+        <v/>
       </c>
       <c r="E19">
         <v>2</v>
@@ -1470,11 +1368,8 @@
       <c r="M19" t="str">
         <v/>
       </c>
-      <c r="N19" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O19" s="1">
-        <f>IF(AND(N19&lt;&gt;"",E19&lt;&gt;""),N19+E19-1,"")</f>
+      <c r="N19" t="str">
+        <v/>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -1493,11 +1388,8 @@
       <c r="B20" t="str">
         <v>Electricals: RFQs Issued</v>
       </c>
-      <c r="C20" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D20" s="1">
-        <f>IF(AND(C20&lt;&gt;"",E20&lt;&gt;""),C20+E20-1,"")</f>
+      <c r="C20" t="str">
+        <v/>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1526,11 +1418,8 @@
       <c r="M20" t="str">
         <v/>
       </c>
-      <c r="N20" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O20" s="1">
-        <f>IF(AND(N20&lt;&gt;"",E20&lt;&gt;""),N20+E20-1,"")</f>
+      <c r="N20" t="str">
+        <v/>
       </c>
       <c r="P20" t="str">
         <v/>
@@ -1549,11 +1438,8 @@
       <c r="B21" t="str">
         <v>Electricals: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C21" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D21" s="1">
-        <f>IF(AND(C21&lt;&gt;"",E21&lt;&gt;""),C21+E21-1,"")</f>
+      <c r="C21" t="str">
+        <v/>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1582,11 +1468,8 @@
       <c r="M21" t="str">
         <v/>
       </c>
-      <c r="N21" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O21" s="1">
-        <f>IF(AND(N21&lt;&gt;"",E21&lt;&gt;""),N21+E21-1,"")</f>
+      <c r="N21" t="str">
+        <v/>
       </c>
       <c r="P21" t="str">
         <v/>
@@ -1605,11 +1488,8 @@
       <c r="B22" t="str">
         <v>Electricals: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C22" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D22" s="1">
-        <f>IF(AND(C22&lt;&gt;"",E22&lt;&gt;""),C22+E22-1,"")</f>
+      <c r="C22" t="str">
+        <v/>
       </c>
       <c r="E22">
         <v>2</v>
@@ -1638,11 +1518,8 @@
       <c r="M22" t="str">
         <v/>
       </c>
-      <c r="N22" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O22" s="1">
-        <f>IF(AND(N22&lt;&gt;"",E22&lt;&gt;""),N22+E22-1,"")</f>
+      <c r="N22" t="str">
+        <v/>
       </c>
       <c r="P22" t="str">
         <v/>
@@ -1661,11 +1538,8 @@
       <c r="B23" t="str">
         <v>Electricals: Vendor Finalisation</v>
       </c>
-      <c r="C23" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D23" s="1">
-        <f>IF(AND(C23&lt;&gt;"",E23&lt;&gt;""),C23+E23-1,"")</f>
+      <c r="C23" t="str">
+        <v/>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1694,11 +1568,8 @@
       <c r="M23" t="str">
         <v/>
       </c>
-      <c r="N23" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O23" s="1">
-        <f>IF(AND(N23&lt;&gt;"",E23&lt;&gt;""),N23+E23-1,"")</f>
+      <c r="N23" t="str">
+        <v/>
       </c>
       <c r="P23" t="str">
         <v/>
@@ -1717,11 +1588,8 @@
       <c r="B24" t="str">
         <v>Electricals: Work Order / PO Release</v>
       </c>
-      <c r="C24" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D24" s="1">
-        <f>IF(AND(C24&lt;&gt;"",E24&lt;&gt;""),C24+E24-1,"")</f>
+      <c r="C24" t="str">
+        <v/>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1750,11 +1618,8 @@
       <c r="M24" t="str">
         <v/>
       </c>
-      <c r="N24" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O24" s="1">
-        <f>IF(AND(N24&lt;&gt;"",E24&lt;&gt;""),N24+E24-1,"")</f>
+      <c r="N24" t="str">
+        <v/>
       </c>
       <c r="P24" t="str">
         <v/>
@@ -1773,10 +1638,10 @@
       <c r="B25" t="str">
         <v>PACKAGE • Plumbing</v>
       </c>
-      <c r="C25" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D25" s="1" t="str">
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25" t="str">
@@ -1806,10 +1671,10 @@
       <c r="M25" t="str">
         <v/>
       </c>
-      <c r="N25" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O25" s="1" t="str">
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
         <v/>
       </c>
       <c r="P25" t="str">
@@ -1829,11 +1694,8 @@
       <c r="B26" t="str">
         <v>Plumbing: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C26" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D26" s="1">
-        <f>IF(AND(C26&lt;&gt;"",E26&lt;&gt;""),C26+E26-1,"")</f>
+      <c r="C26" t="str">
+        <v/>
       </c>
       <c r="E26">
         <v>3</v>
@@ -1862,11 +1724,8 @@
       <c r="M26" t="str">
         <v/>
       </c>
-      <c r="N26" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O26" s="1">
-        <f>IF(AND(N26&lt;&gt;"",E26&lt;&gt;""),N26+E26-1,"")</f>
+      <c r="N26" t="str">
+        <v/>
       </c>
       <c r="P26" t="str">
         <v/>
@@ -1885,11 +1744,8 @@
       <c r="B27" t="str">
         <v>Plumbing: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C27" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D27" s="1">
-        <f>IF(AND(C27&lt;&gt;"",E27&lt;&gt;""),C27+E27-1,"")</f>
+      <c r="C27" t="str">
+        <v/>
       </c>
       <c r="E27">
         <v>2</v>
@@ -1918,11 +1774,8 @@
       <c r="M27" t="str">
         <v/>
       </c>
-      <c r="N27" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O27" s="1">
-        <f>IF(AND(N27&lt;&gt;"",E27&lt;&gt;""),N27+E27-1,"")</f>
+      <c r="N27" t="str">
+        <v/>
       </c>
       <c r="P27" t="str">
         <v/>
@@ -1941,11 +1794,8 @@
       <c r="B28" t="str">
         <v>Plumbing: RFQs Issued</v>
       </c>
-      <c r="C28" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D28" s="1">
-        <f>IF(AND(C28&lt;&gt;"",E28&lt;&gt;""),C28+E28-1,"")</f>
+      <c r="C28" t="str">
+        <v/>
       </c>
       <c r="E28">
         <v>2</v>
@@ -1974,11 +1824,8 @@
       <c r="M28" t="str">
         <v/>
       </c>
-      <c r="N28" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O28" s="1">
-        <f>IF(AND(N28&lt;&gt;"",E28&lt;&gt;""),N28+E28-1,"")</f>
+      <c r="N28" t="str">
+        <v/>
       </c>
       <c r="P28" t="str">
         <v/>
@@ -1997,11 +1844,8 @@
       <c r="B29" t="str">
         <v>Plumbing: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C29" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D29" s="1">
-        <f>IF(AND(C29&lt;&gt;"",E29&lt;&gt;""),C29+E29-1,"")</f>
+      <c r="C29" t="str">
+        <v/>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2030,11 +1874,8 @@
       <c r="M29" t="str">
         <v/>
       </c>
-      <c r="N29" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O29" s="1">
-        <f>IF(AND(N29&lt;&gt;"",E29&lt;&gt;""),N29+E29-1,"")</f>
+      <c r="N29" t="str">
+        <v/>
       </c>
       <c r="P29" t="str">
         <v/>
@@ -2053,11 +1894,8 @@
       <c r="B30" t="str">
         <v>Plumbing: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C30" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D30" s="1">
-        <f>IF(AND(C30&lt;&gt;"",E30&lt;&gt;""),C30+E30-1,"")</f>
+      <c r="C30" t="str">
+        <v/>
       </c>
       <c r="E30">
         <v>2</v>
@@ -2086,11 +1924,8 @@
       <c r="M30" t="str">
         <v/>
       </c>
-      <c r="N30" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O30" s="1">
-        <f>IF(AND(N30&lt;&gt;"",E30&lt;&gt;""),N30+E30-1,"")</f>
+      <c r="N30" t="str">
+        <v/>
       </c>
       <c r="P30" t="str">
         <v/>
@@ -2109,11 +1944,8 @@
       <c r="B31" t="str">
         <v>Plumbing: Vendor Finalisation</v>
       </c>
-      <c r="C31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D31" s="1">
-        <f>IF(AND(C31&lt;&gt;"",E31&lt;&gt;""),C31+E31-1,"")</f>
+      <c r="C31" t="str">
+        <v/>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2142,11 +1974,8 @@
       <c r="M31" t="str">
         <v/>
       </c>
-      <c r="N31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O31" s="1">
-        <f>IF(AND(N31&lt;&gt;"",E31&lt;&gt;""),N31+E31-1,"")</f>
+      <c r="N31" t="str">
+        <v/>
       </c>
       <c r="P31" t="str">
         <v/>
@@ -2165,11 +1994,8 @@
       <c r="B32" t="str">
         <v>Plumbing: Work Order / PO Release</v>
       </c>
-      <c r="C32" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D32" s="1">
-        <f>IF(AND(C32&lt;&gt;"",E32&lt;&gt;""),C32+E32-1,"")</f>
+      <c r="C32" t="str">
+        <v/>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2198,11 +2024,8 @@
       <c r="M32" t="str">
         <v/>
       </c>
-      <c r="N32" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O32" s="1">
-        <f>IF(AND(N32&lt;&gt;"",E32&lt;&gt;""),N32+E32-1,"")</f>
+      <c r="N32" t="str">
+        <v/>
       </c>
       <c r="P32" t="str">
         <v/>
@@ -2221,10 +2044,10 @@
       <c r="B33" t="str">
         <v>PACKAGE • Kitchens</v>
       </c>
-      <c r="C33" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D33" s="1" t="str">
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
         <v/>
       </c>
       <c r="E33" t="str">
@@ -2254,10 +2077,10 @@
       <c r="M33" t="str">
         <v/>
       </c>
-      <c r="N33" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O33" s="1" t="str">
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
         <v/>
       </c>
       <c r="P33" t="str">
@@ -2277,11 +2100,8 @@
       <c r="B34" t="str">
         <v>Kitchens: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C34" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D34" s="1">
-        <f>IF(AND(C34&lt;&gt;"",E34&lt;&gt;""),C34+E34-1,"")</f>
+      <c r="C34" t="str">
+        <v/>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2310,11 +2130,8 @@
       <c r="M34" t="str">
         <v/>
       </c>
-      <c r="N34" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O34" s="1">
-        <f>IF(AND(N34&lt;&gt;"",E34&lt;&gt;""),N34+E34-1,"")</f>
+      <c r="N34" t="str">
+        <v/>
       </c>
       <c r="P34" t="str">
         <v/>
@@ -2333,11 +2150,8 @@
       <c r="B35" t="str">
         <v>Kitchens: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C35" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D35" s="1">
-        <f>IF(AND(C35&lt;&gt;"",E35&lt;&gt;""),C35+E35-1,"")</f>
+      <c r="C35" t="str">
+        <v/>
       </c>
       <c r="E35">
         <v>2</v>
@@ -2366,11 +2180,8 @@
       <c r="M35" t="str">
         <v/>
       </c>
-      <c r="N35" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O35" s="1">
-        <f>IF(AND(N35&lt;&gt;"",E35&lt;&gt;""),N35+E35-1,"")</f>
+      <c r="N35" t="str">
+        <v/>
       </c>
       <c r="P35" t="str">
         <v/>
@@ -2389,11 +2200,8 @@
       <c r="B36" t="str">
         <v>Kitchens: RFQs Issued</v>
       </c>
-      <c r="C36" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D36" s="1">
-        <f>IF(AND(C36&lt;&gt;"",E36&lt;&gt;""),C36+E36-1,"")</f>
+      <c r="C36" t="str">
+        <v/>
       </c>
       <c r="E36">
         <v>2</v>
@@ -2422,11 +2230,8 @@
       <c r="M36" t="str">
         <v/>
       </c>
-      <c r="N36" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O36" s="1">
-        <f>IF(AND(N36&lt;&gt;"",E36&lt;&gt;""),N36+E36-1,"")</f>
+      <c r="N36" t="str">
+        <v/>
       </c>
       <c r="P36" t="str">
         <v/>
@@ -2445,11 +2250,8 @@
       <c r="B37" t="str">
         <v>Kitchens: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C37" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D37" s="1">
-        <f>IF(AND(C37&lt;&gt;"",E37&lt;&gt;""),C37+E37-1,"")</f>
+      <c r="C37" t="str">
+        <v/>
       </c>
       <c r="E37">
         <v>3</v>
@@ -2478,11 +2280,8 @@
       <c r="M37" t="str">
         <v/>
       </c>
-      <c r="N37" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O37" s="1">
-        <f>IF(AND(N37&lt;&gt;"",E37&lt;&gt;""),N37+E37-1,"")</f>
+      <c r="N37" t="str">
+        <v/>
       </c>
       <c r="P37" t="str">
         <v/>
@@ -2501,11 +2300,8 @@
       <c r="B38" t="str">
         <v>Kitchens: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C38" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D38" s="1">
-        <f>IF(AND(C38&lt;&gt;"",E38&lt;&gt;""),C38+E38-1,"")</f>
+      <c r="C38" t="str">
+        <v/>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2534,11 +2330,8 @@
       <c r="M38" t="str">
         <v/>
       </c>
-      <c r="N38" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O38" s="1">
-        <f>IF(AND(N38&lt;&gt;"",E38&lt;&gt;""),N38+E38-1,"")</f>
+      <c r="N38" t="str">
+        <v/>
       </c>
       <c r="P38" t="str">
         <v/>
@@ -2557,11 +2350,8 @@
       <c r="B39" t="str">
         <v>Kitchens: Vendor Finalisation</v>
       </c>
-      <c r="C39" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D39" s="1">
-        <f>IF(AND(C39&lt;&gt;"",E39&lt;&gt;""),C39+E39-1,"")</f>
+      <c r="C39" t="str">
+        <v/>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2590,11 +2380,8 @@
       <c r="M39" t="str">
         <v/>
       </c>
-      <c r="N39" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O39" s="1">
-        <f>IF(AND(N39&lt;&gt;"",E39&lt;&gt;""),N39+E39-1,"")</f>
+      <c r="N39" t="str">
+        <v/>
       </c>
       <c r="P39" t="str">
         <v/>
@@ -2613,11 +2400,8 @@
       <c r="B40" t="str">
         <v>Kitchens: Work Order / PO Release</v>
       </c>
-      <c r="C40" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D40" s="1">
-        <f>IF(AND(C40&lt;&gt;"",E40&lt;&gt;""),C40+E40-1,"")</f>
+      <c r="C40" t="str">
+        <v/>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2646,11 +2430,8 @@
       <c r="M40" t="str">
         <v/>
       </c>
-      <c r="N40" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O40" s="1">
-        <f>IF(AND(N40&lt;&gt;"",E40&lt;&gt;""),N40+E40-1,"")</f>
+      <c r="N40" t="str">
+        <v/>
       </c>
       <c r="P40" t="str">
         <v/>
@@ -2669,10 +2450,10 @@
       <c r="B41" t="str">
         <v>PACKAGE • Bathrooms</v>
       </c>
-      <c r="C41" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D41" s="1" t="str">
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
@@ -2702,10 +2483,10 @@
       <c r="M41" t="str">
         <v/>
       </c>
-      <c r="N41" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O41" s="1" t="str">
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
         <v/>
       </c>
       <c r="P41" t="str">
@@ -2725,11 +2506,8 @@
       <c r="B42" t="str">
         <v>Bathrooms: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C42" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D42" s="1">
-        <f>IF(AND(C42&lt;&gt;"",E42&lt;&gt;""),C42+E42-1,"")</f>
+      <c r="C42" t="str">
+        <v/>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2758,11 +2536,8 @@
       <c r="M42" t="str">
         <v/>
       </c>
-      <c r="N42" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O42" s="1">
-        <f>IF(AND(N42&lt;&gt;"",E42&lt;&gt;""),N42+E42-1,"")</f>
+      <c r="N42" t="str">
+        <v/>
       </c>
       <c r="P42" t="str">
         <v/>
@@ -2781,11 +2556,8 @@
       <c r="B43" t="str">
         <v>Bathrooms: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C43" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D43" s="1">
-        <f>IF(AND(C43&lt;&gt;"",E43&lt;&gt;""),C43+E43-1,"")</f>
+      <c r="C43" t="str">
+        <v/>
       </c>
       <c r="E43">
         <v>2</v>
@@ -2814,11 +2586,8 @@
       <c r="M43" t="str">
         <v/>
       </c>
-      <c r="N43" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O43" s="1">
-        <f>IF(AND(N43&lt;&gt;"",E43&lt;&gt;""),N43+E43-1,"")</f>
+      <c r="N43" t="str">
+        <v/>
       </c>
       <c r="P43" t="str">
         <v/>
@@ -2837,11 +2606,8 @@
       <c r="B44" t="str">
         <v>Bathrooms: RFQs Issued</v>
       </c>
-      <c r="C44" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D44" s="1">
-        <f>IF(AND(C44&lt;&gt;"",E44&lt;&gt;""),C44+E44-1,"")</f>
+      <c r="C44" t="str">
+        <v/>
       </c>
       <c r="E44">
         <v>2</v>
@@ -2870,11 +2636,8 @@
       <c r="M44" t="str">
         <v/>
       </c>
-      <c r="N44" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O44" s="1">
-        <f>IF(AND(N44&lt;&gt;"",E44&lt;&gt;""),N44+E44-1,"")</f>
+      <c r="N44" t="str">
+        <v/>
       </c>
       <c r="P44" t="str">
         <v/>
@@ -2893,11 +2656,8 @@
       <c r="B45" t="str">
         <v>Bathrooms: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C45" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D45" s="1">
-        <f>IF(AND(C45&lt;&gt;"",E45&lt;&gt;""),C45+E45-1,"")</f>
+      <c r="C45" t="str">
+        <v/>
       </c>
       <c r="E45">
         <v>3</v>
@@ -2926,11 +2686,8 @@
       <c r="M45" t="str">
         <v/>
       </c>
-      <c r="N45" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O45" s="1">
-        <f>IF(AND(N45&lt;&gt;"",E45&lt;&gt;""),N45+E45-1,"")</f>
+      <c r="N45" t="str">
+        <v/>
       </c>
       <c r="P45" t="str">
         <v/>
@@ -2949,11 +2706,8 @@
       <c r="B46" t="str">
         <v>Bathrooms: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C46" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D46" s="1">
-        <f>IF(AND(C46&lt;&gt;"",E46&lt;&gt;""),C46+E46-1,"")</f>
+      <c r="C46" t="str">
+        <v/>
       </c>
       <c r="E46">
         <v>2</v>
@@ -2982,11 +2736,8 @@
       <c r="M46" t="str">
         <v/>
       </c>
-      <c r="N46" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O46" s="1">
-        <f>IF(AND(N46&lt;&gt;"",E46&lt;&gt;""),N46+E46-1,"")</f>
+      <c r="N46" t="str">
+        <v/>
       </c>
       <c r="P46" t="str">
         <v/>
@@ -3005,11 +2756,8 @@
       <c r="B47" t="str">
         <v>Bathrooms: Vendor Finalisation</v>
       </c>
-      <c r="C47" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D47" s="1">
-        <f>IF(AND(C47&lt;&gt;"",E47&lt;&gt;""),C47+E47-1,"")</f>
+      <c r="C47" t="str">
+        <v/>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3038,11 +2786,8 @@
       <c r="M47" t="str">
         <v/>
       </c>
-      <c r="N47" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O47" s="1">
-        <f>IF(AND(N47&lt;&gt;"",E47&lt;&gt;""),N47+E47-1,"")</f>
+      <c r="N47" t="str">
+        <v/>
       </c>
       <c r="P47" t="str">
         <v/>
@@ -3061,11 +2806,8 @@
       <c r="B48" t="str">
         <v>Bathrooms: Work Order / PO Release</v>
       </c>
-      <c r="C48" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D48" s="1">
-        <f>IF(AND(C48&lt;&gt;"",E48&lt;&gt;""),C48+E48-1,"")</f>
+      <c r="C48" t="str">
+        <v/>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3094,11 +2836,8 @@
       <c r="M48" t="str">
         <v/>
       </c>
-      <c r="N48" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O48" s="1">
-        <f>IF(AND(N48&lt;&gt;"",E48&lt;&gt;""),N48+E48-1,"")</f>
+      <c r="N48" t="str">
+        <v/>
       </c>
       <c r="P48" t="str">
         <v/>
@@ -3117,10 +2856,10 @@
       <c r="B49" t="str">
         <v>PACKAGE • Audio</v>
       </c>
-      <c r="C49" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D49" s="1" t="str">
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49" t="str">
@@ -3150,10 +2889,10 @@
       <c r="M49" t="str">
         <v/>
       </c>
-      <c r="N49" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O49" s="1" t="str">
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
         <v/>
       </c>
       <c r="P49" t="str">
@@ -3173,11 +2912,8 @@
       <c r="B50" t="str">
         <v>Audio: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C50" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D50" s="1">
-        <f>IF(AND(C50&lt;&gt;"",E50&lt;&gt;""),C50+E50-1,"")</f>
+      <c r="C50" t="str">
+        <v/>
       </c>
       <c r="E50">
         <v>3</v>
@@ -3206,11 +2942,8 @@
       <c r="M50" t="str">
         <v/>
       </c>
-      <c r="N50" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O50" s="1">
-        <f>IF(AND(N50&lt;&gt;"",E50&lt;&gt;""),N50+E50-1,"")</f>
+      <c r="N50" t="str">
+        <v/>
       </c>
       <c r="P50" t="str">
         <v/>
@@ -3229,11 +2962,8 @@
       <c r="B51" t="str">
         <v>Audio: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C51" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D51" s="1">
-        <f>IF(AND(C51&lt;&gt;"",E51&lt;&gt;""),C51+E51-1,"")</f>
+      <c r="C51" t="str">
+        <v/>
       </c>
       <c r="E51">
         <v>2</v>
@@ -3262,11 +2992,8 @@
       <c r="M51" t="str">
         <v/>
       </c>
-      <c r="N51" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O51" s="1">
-        <f>IF(AND(N51&lt;&gt;"",E51&lt;&gt;""),N51+E51-1,"")</f>
+      <c r="N51" t="str">
+        <v/>
       </c>
       <c r="P51" t="str">
         <v/>
@@ -3285,11 +3012,8 @@
       <c r="B52" t="str">
         <v>Audio: RFQs Issued</v>
       </c>
-      <c r="C52" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="1">
-        <f>IF(AND(C52&lt;&gt;"",E52&lt;&gt;""),C52+E52-1,"")</f>
+      <c r="C52" t="str">
+        <v/>
       </c>
       <c r="E52">
         <v>2</v>
@@ -3318,11 +3042,8 @@
       <c r="M52" t="str">
         <v/>
       </c>
-      <c r="N52" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O52" s="1">
-        <f>IF(AND(N52&lt;&gt;"",E52&lt;&gt;""),N52+E52-1,"")</f>
+      <c r="N52" t="str">
+        <v/>
       </c>
       <c r="P52" t="str">
         <v/>
@@ -3341,11 +3062,8 @@
       <c r="B53" t="str">
         <v>Audio: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C53" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D53" s="1">
-        <f>IF(AND(C53&lt;&gt;"",E53&lt;&gt;""),C53+E53-1,"")</f>
+      <c r="C53" t="str">
+        <v/>
       </c>
       <c r="E53">
         <v>3</v>
@@ -3374,11 +3092,8 @@
       <c r="M53" t="str">
         <v/>
       </c>
-      <c r="N53" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O53" s="1">
-        <f>IF(AND(N53&lt;&gt;"",E53&lt;&gt;""),N53+E53-1,"")</f>
+      <c r="N53" t="str">
+        <v/>
       </c>
       <c r="P53" t="str">
         <v/>
@@ -3397,11 +3112,8 @@
       <c r="B54" t="str">
         <v>Audio: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C54" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D54" s="1">
-        <f>IF(AND(C54&lt;&gt;"",E54&lt;&gt;""),C54+E54-1,"")</f>
+      <c r="C54" t="str">
+        <v/>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3430,11 +3142,8 @@
       <c r="M54" t="str">
         <v/>
       </c>
-      <c r="N54" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O54" s="1">
-        <f>IF(AND(N54&lt;&gt;"",E54&lt;&gt;""),N54+E54-1,"")</f>
+      <c r="N54" t="str">
+        <v/>
       </c>
       <c r="P54" t="str">
         <v/>
@@ -3453,11 +3162,8 @@
       <c r="B55" t="str">
         <v>Audio: Vendor Finalisation</v>
       </c>
-      <c r="C55" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D55" s="1">
-        <f>IF(AND(C55&lt;&gt;"",E55&lt;&gt;""),C55+E55-1,"")</f>
+      <c r="C55" t="str">
+        <v/>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3486,11 +3192,8 @@
       <c r="M55" t="str">
         <v/>
       </c>
-      <c r="N55" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O55" s="1">
-        <f>IF(AND(N55&lt;&gt;"",E55&lt;&gt;""),N55+E55-1,"")</f>
+      <c r="N55" t="str">
+        <v/>
       </c>
       <c r="P55" t="str">
         <v/>
@@ -3509,11 +3212,8 @@
       <c r="B56" t="str">
         <v>Audio: Work Order / PO Release</v>
       </c>
-      <c r="C56" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D56" s="1">
-        <f>IF(AND(C56&lt;&gt;"",E56&lt;&gt;""),C56+E56-1,"")</f>
+      <c r="C56" t="str">
+        <v/>
       </c>
       <c r="E56">
         <v>1</v>
@@ -3542,11 +3242,8 @@
       <c r="M56" t="str">
         <v/>
       </c>
-      <c r="N56" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O56" s="1">
-        <f>IF(AND(N56&lt;&gt;"",E56&lt;&gt;""),N56+E56-1,"")</f>
+      <c r="N56" t="str">
+        <v/>
       </c>
       <c r="P56" t="str">
         <v/>
@@ -3565,10 +3262,10 @@
       <c r="B57" t="str">
         <v>PACKAGE • Automation</v>
       </c>
-      <c r="C57" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D57" s="1" t="str">
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57" t="str">
@@ -3598,10 +3295,10 @@
       <c r="M57" t="str">
         <v/>
       </c>
-      <c r="N57" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O57" s="1" t="str">
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v/>
       </c>
       <c r="P57" t="str">
@@ -3621,11 +3318,8 @@
       <c r="B58" t="str">
         <v>Automation: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C58" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D58" s="1">
-        <f>IF(AND(C58&lt;&gt;"",E58&lt;&gt;""),C58+E58-1,"")</f>
+      <c r="C58" t="str">
+        <v/>
       </c>
       <c r="E58">
         <v>3</v>
@@ -3654,11 +3348,8 @@
       <c r="M58" t="str">
         <v/>
       </c>
-      <c r="N58" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O58" s="1">
-        <f>IF(AND(N58&lt;&gt;"",E58&lt;&gt;""),N58+E58-1,"")</f>
+      <c r="N58" t="str">
+        <v/>
       </c>
       <c r="P58" t="str">
         <v/>
@@ -3677,11 +3368,8 @@
       <c r="B59" t="str">
         <v>Automation: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C59" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D59" s="1">
-        <f>IF(AND(C59&lt;&gt;"",E59&lt;&gt;""),C59+E59-1,"")</f>
+      <c r="C59" t="str">
+        <v/>
       </c>
       <c r="E59">
         <v>2</v>
@@ -3710,11 +3398,8 @@
       <c r="M59" t="str">
         <v/>
       </c>
-      <c r="N59" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O59" s="1">
-        <f>IF(AND(N59&lt;&gt;"",E59&lt;&gt;""),N59+E59-1,"")</f>
+      <c r="N59" t="str">
+        <v/>
       </c>
       <c r="P59" t="str">
         <v/>
@@ -3733,11 +3418,8 @@
       <c r="B60" t="str">
         <v>Automation: RFQs Issued</v>
       </c>
-      <c r="C60" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D60" s="1">
-        <f>IF(AND(C60&lt;&gt;"",E60&lt;&gt;""),C60+E60-1,"")</f>
+      <c r="C60" t="str">
+        <v/>
       </c>
       <c r="E60">
         <v>2</v>
@@ -3766,11 +3448,8 @@
       <c r="M60" t="str">
         <v/>
       </c>
-      <c r="N60" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O60" s="1">
-        <f>IF(AND(N60&lt;&gt;"",E60&lt;&gt;""),N60+E60-1,"")</f>
+      <c r="N60" t="str">
+        <v/>
       </c>
       <c r="P60" t="str">
         <v/>
@@ -3789,11 +3468,8 @@
       <c r="B61" t="str">
         <v>Automation: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C61" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D61" s="1">
-        <f>IF(AND(C61&lt;&gt;"",E61&lt;&gt;""),C61+E61-1,"")</f>
+      <c r="C61" t="str">
+        <v/>
       </c>
       <c r="E61">
         <v>3</v>
@@ -3822,11 +3498,8 @@
       <c r="M61" t="str">
         <v/>
       </c>
-      <c r="N61" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O61" s="1">
-        <f>IF(AND(N61&lt;&gt;"",E61&lt;&gt;""),N61+E61-1,"")</f>
+      <c r="N61" t="str">
+        <v/>
       </c>
       <c r="P61" t="str">
         <v/>
@@ -3845,11 +3518,8 @@
       <c r="B62" t="str">
         <v>Automation: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C62" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D62" s="1">
-        <f>IF(AND(C62&lt;&gt;"",E62&lt;&gt;""),C62+E62-1,"")</f>
+      <c r="C62" t="str">
+        <v/>
       </c>
       <c r="E62">
         <v>2</v>
@@ -3878,11 +3548,8 @@
       <c r="M62" t="str">
         <v/>
       </c>
-      <c r="N62" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O62" s="1">
-        <f>IF(AND(N62&lt;&gt;"",E62&lt;&gt;""),N62+E62-1,"")</f>
+      <c r="N62" t="str">
+        <v/>
       </c>
       <c r="P62" t="str">
         <v/>
@@ -3901,11 +3568,8 @@
       <c r="B63" t="str">
         <v>Automation: Vendor Finalisation</v>
       </c>
-      <c r="C63" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D63" s="1">
-        <f>IF(AND(C63&lt;&gt;"",E63&lt;&gt;""),C63+E63-1,"")</f>
+      <c r="C63" t="str">
+        <v/>
       </c>
       <c r="E63">
         <v>1</v>
@@ -3934,11 +3598,8 @@
       <c r="M63" t="str">
         <v/>
       </c>
-      <c r="N63" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O63" s="1">
-        <f>IF(AND(N63&lt;&gt;"",E63&lt;&gt;""),N63+E63-1,"")</f>
+      <c r="N63" t="str">
+        <v/>
       </c>
       <c r="P63" t="str">
         <v/>
@@ -3957,11 +3618,8 @@
       <c r="B64" t="str">
         <v>Automation: Work Order / PO Release</v>
       </c>
-      <c r="C64" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D64" s="1">
-        <f>IF(AND(C64&lt;&gt;"",E64&lt;&gt;""),C64+E64-1,"")</f>
+      <c r="C64" t="str">
+        <v/>
       </c>
       <c r="E64">
         <v>1</v>
@@ -3990,11 +3648,8 @@
       <c r="M64" t="str">
         <v/>
       </c>
-      <c r="N64" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O64" s="1">
-        <f>IF(AND(N64&lt;&gt;"",E64&lt;&gt;""),N64+E64-1,"")</f>
+      <c r="N64" t="str">
+        <v/>
       </c>
       <c r="P64" t="str">
         <v/>
@@ -4013,10 +3668,10 @@
       <c r="B65" t="str">
         <v>PACKAGE • Lighting</v>
       </c>
-      <c r="C65" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D65" s="1" t="str">
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
         <v/>
       </c>
       <c r="E65" t="str">
@@ -4046,10 +3701,10 @@
       <c r="M65" t="str">
         <v/>
       </c>
-      <c r="N65" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O65" s="1" t="str">
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
         <v/>
       </c>
       <c r="P65" t="str">
@@ -4069,11 +3724,8 @@
       <c r="B66" t="str">
         <v>Lighting: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C66" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D66" s="1">
-        <f>IF(AND(C66&lt;&gt;"",E66&lt;&gt;""),C66+E66-1,"")</f>
+      <c r="C66" t="str">
+        <v/>
       </c>
       <c r="E66">
         <v>3</v>
@@ -4102,11 +3754,8 @@
       <c r="M66" t="str">
         <v/>
       </c>
-      <c r="N66" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O66" s="1">
-        <f>IF(AND(N66&lt;&gt;"",E66&lt;&gt;""),N66+E66-1,"")</f>
+      <c r="N66" t="str">
+        <v/>
       </c>
       <c r="P66" t="str">
         <v/>
@@ -4125,11 +3774,8 @@
       <c r="B67" t="str">
         <v>Lighting: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C67" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D67" s="1">
-        <f>IF(AND(C67&lt;&gt;"",E67&lt;&gt;""),C67+E67-1,"")</f>
+      <c r="C67" t="str">
+        <v/>
       </c>
       <c r="E67">
         <v>2</v>
@@ -4158,11 +3804,8 @@
       <c r="M67" t="str">
         <v/>
       </c>
-      <c r="N67" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O67" s="1">
-        <f>IF(AND(N67&lt;&gt;"",E67&lt;&gt;""),N67+E67-1,"")</f>
+      <c r="N67" t="str">
+        <v/>
       </c>
       <c r="P67" t="str">
         <v/>
@@ -4181,11 +3824,8 @@
       <c r="B68" t="str">
         <v>Lighting: RFQs Issued</v>
       </c>
-      <c r="C68" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D68" s="1">
-        <f>IF(AND(C68&lt;&gt;"",E68&lt;&gt;""),C68+E68-1,"")</f>
+      <c r="C68" t="str">
+        <v/>
       </c>
       <c r="E68">
         <v>2</v>
@@ -4214,11 +3854,8 @@
       <c r="M68" t="str">
         <v/>
       </c>
-      <c r="N68" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O68" s="1">
-        <f>IF(AND(N68&lt;&gt;"",E68&lt;&gt;""),N68+E68-1,"")</f>
+      <c r="N68" t="str">
+        <v/>
       </c>
       <c r="P68" t="str">
         <v/>
@@ -4237,11 +3874,8 @@
       <c r="B69" t="str">
         <v>Lighting: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C69" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D69" s="1">
-        <f>IF(AND(C69&lt;&gt;"",E69&lt;&gt;""),C69+E69-1,"")</f>
+      <c r="C69" t="str">
+        <v/>
       </c>
       <c r="E69">
         <v>3</v>
@@ -4270,11 +3904,8 @@
       <c r="M69" t="str">
         <v/>
       </c>
-      <c r="N69" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O69" s="1">
-        <f>IF(AND(N69&lt;&gt;"",E69&lt;&gt;""),N69+E69-1,"")</f>
+      <c r="N69" t="str">
+        <v/>
       </c>
       <c r="P69" t="str">
         <v/>
@@ -4293,11 +3924,8 @@
       <c r="B70" t="str">
         <v>Lighting: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C70" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D70" s="1">
-        <f>IF(AND(C70&lt;&gt;"",E70&lt;&gt;""),C70+E70-1,"")</f>
+      <c r="C70" t="str">
+        <v/>
       </c>
       <c r="E70">
         <v>2</v>
@@ -4326,11 +3954,8 @@
       <c r="M70" t="str">
         <v/>
       </c>
-      <c r="N70" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O70" s="1">
-        <f>IF(AND(N70&lt;&gt;"",E70&lt;&gt;""),N70+E70-1,"")</f>
+      <c r="N70" t="str">
+        <v/>
       </c>
       <c r="P70" t="str">
         <v/>
@@ -4349,11 +3974,8 @@
       <c r="B71" t="str">
         <v>Lighting: Vendor Finalisation</v>
       </c>
-      <c r="C71" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D71" s="1">
-        <f>IF(AND(C71&lt;&gt;"",E71&lt;&gt;""),C71+E71-1,"")</f>
+      <c r="C71" t="str">
+        <v/>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4382,11 +4004,8 @@
       <c r="M71" t="str">
         <v/>
       </c>
-      <c r="N71" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O71" s="1">
-        <f>IF(AND(N71&lt;&gt;"",E71&lt;&gt;""),N71+E71-1,"")</f>
+      <c r="N71" t="str">
+        <v/>
       </c>
       <c r="P71" t="str">
         <v/>
@@ -4405,11 +4024,8 @@
       <c r="B72" t="str">
         <v>Lighting: Work Order / PO Release</v>
       </c>
-      <c r="C72" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D72" s="1">
-        <f>IF(AND(C72&lt;&gt;"",E72&lt;&gt;""),C72+E72-1,"")</f>
+      <c r="C72" t="str">
+        <v/>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4438,11 +4054,8 @@
       <c r="M72" t="str">
         <v/>
       </c>
-      <c r="N72" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O72" s="1">
-        <f>IF(AND(N72&lt;&gt;"",E72&lt;&gt;""),N72+E72-1,"")</f>
+      <c r="N72" t="str">
+        <v/>
       </c>
       <c r="P72" t="str">
         <v/>
@@ -4461,10 +4074,10 @@
       <c r="B73" t="str">
         <v>PACKAGE • HVAC</v>
       </c>
-      <c r="C73" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D73" s="1" t="str">
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
         <v/>
       </c>
       <c r="E73" t="str">
@@ -4494,10 +4107,10 @@
       <c r="M73" t="str">
         <v/>
       </c>
-      <c r="N73" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O73" s="1" t="str">
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
         <v/>
       </c>
       <c r="P73" t="str">
@@ -4517,11 +4130,8 @@
       <c r="B74" t="str">
         <v>HVAC: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C74" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D74" s="1">
-        <f>IF(AND(C74&lt;&gt;"",E74&lt;&gt;""),C74+E74-1,"")</f>
+      <c r="C74" t="str">
+        <v/>
       </c>
       <c r="E74">
         <v>3</v>
@@ -4550,11 +4160,8 @@
       <c r="M74" t="str">
         <v/>
       </c>
-      <c r="N74" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O74" s="1">
-        <f>IF(AND(N74&lt;&gt;"",E74&lt;&gt;""),N74+E74-1,"")</f>
+      <c r="N74" t="str">
+        <v/>
       </c>
       <c r="P74" t="str">
         <v/>
@@ -4573,11 +4180,8 @@
       <c r="B75" t="str">
         <v>HVAC: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C75" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D75" s="1">
-        <f>IF(AND(C75&lt;&gt;"",E75&lt;&gt;""),C75+E75-1,"")</f>
+      <c r="C75" t="str">
+        <v/>
       </c>
       <c r="E75">
         <v>2</v>
@@ -4606,11 +4210,8 @@
       <c r="M75" t="str">
         <v/>
       </c>
-      <c r="N75" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O75" s="1">
-        <f>IF(AND(N75&lt;&gt;"",E75&lt;&gt;""),N75+E75-1,"")</f>
+      <c r="N75" t="str">
+        <v/>
       </c>
       <c r="P75" t="str">
         <v/>
@@ -4629,11 +4230,8 @@
       <c r="B76" t="str">
         <v>HVAC: RFQs Issued</v>
       </c>
-      <c r="C76" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D76" s="1">
-        <f>IF(AND(C76&lt;&gt;"",E76&lt;&gt;""),C76+E76-1,"")</f>
+      <c r="C76" t="str">
+        <v/>
       </c>
       <c r="E76">
         <v>2</v>
@@ -4662,11 +4260,8 @@
       <c r="M76" t="str">
         <v/>
       </c>
-      <c r="N76" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O76" s="1">
-        <f>IF(AND(N76&lt;&gt;"",E76&lt;&gt;""),N76+E76-1,"")</f>
+      <c r="N76" t="str">
+        <v/>
       </c>
       <c r="P76" t="str">
         <v/>
@@ -4685,11 +4280,8 @@
       <c r="B77" t="str">
         <v>HVAC: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C77" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D77" s="1">
-        <f>IF(AND(C77&lt;&gt;"",E77&lt;&gt;""),C77+E77-1,"")</f>
+      <c r="C77" t="str">
+        <v/>
       </c>
       <c r="E77">
         <v>3</v>
@@ -4718,11 +4310,8 @@
       <c r="M77" t="str">
         <v/>
       </c>
-      <c r="N77" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O77" s="1">
-        <f>IF(AND(N77&lt;&gt;"",E77&lt;&gt;""),N77+E77-1,"")</f>
+      <c r="N77" t="str">
+        <v/>
       </c>
       <c r="P77" t="str">
         <v/>
@@ -4741,11 +4330,8 @@
       <c r="B78" t="str">
         <v>HVAC: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C78" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D78" s="1">
-        <f>IF(AND(C78&lt;&gt;"",E78&lt;&gt;""),C78+E78-1,"")</f>
+      <c r="C78" t="str">
+        <v/>
       </c>
       <c r="E78">
         <v>2</v>
@@ -4774,11 +4360,8 @@
       <c r="M78" t="str">
         <v/>
       </c>
-      <c r="N78" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O78" s="1">
-        <f>IF(AND(N78&lt;&gt;"",E78&lt;&gt;""),N78+E78-1,"")</f>
+      <c r="N78" t="str">
+        <v/>
       </c>
       <c r="P78" t="str">
         <v/>
@@ -4797,11 +4380,8 @@
       <c r="B79" t="str">
         <v>HVAC: Vendor Finalisation</v>
       </c>
-      <c r="C79" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D79" s="1">
-        <f>IF(AND(C79&lt;&gt;"",E79&lt;&gt;""),C79+E79-1,"")</f>
+      <c r="C79" t="str">
+        <v/>
       </c>
       <c r="E79">
         <v>1</v>
@@ -4830,11 +4410,8 @@
       <c r="M79" t="str">
         <v/>
       </c>
-      <c r="N79" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O79" s="1">
-        <f>IF(AND(N79&lt;&gt;"",E79&lt;&gt;""),N79+E79-1,"")</f>
+      <c r="N79" t="str">
+        <v/>
       </c>
       <c r="P79" t="str">
         <v/>
@@ -4853,11 +4430,8 @@
       <c r="B80" t="str">
         <v>HVAC: Work Order / PO Release</v>
       </c>
-      <c r="C80" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D80" s="1">
-        <f>IF(AND(C80&lt;&gt;"",E80&lt;&gt;""),C80+E80-1,"")</f>
+      <c r="C80" t="str">
+        <v/>
       </c>
       <c r="E80">
         <v>1</v>
@@ -4886,11 +4460,8 @@
       <c r="M80" t="str">
         <v/>
       </c>
-      <c r="N80" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O80" s="1">
-        <f>IF(AND(N80&lt;&gt;"",E80&lt;&gt;""),N80+E80-1,"")</f>
+      <c r="N80" t="str">
+        <v/>
       </c>
       <c r="P80" t="str">
         <v/>
@@ -4909,10 +4480,10 @@
       <c r="B81" t="str">
         <v>PACKAGE • Doors &amp; Windows</v>
       </c>
-      <c r="C81" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D81" s="1" t="str">
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
         <v/>
       </c>
       <c r="E81" t="str">
@@ -4942,10 +4513,10 @@
       <c r="M81" t="str">
         <v/>
       </c>
-      <c r="N81" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O81" s="1" t="str">
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
         <v/>
       </c>
       <c r="P81" t="str">
@@ -4965,11 +4536,8 @@
       <c r="B82" t="str">
         <v>Doors &amp; Windows: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C82" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D82" s="1">
-        <f>IF(AND(C82&lt;&gt;"",E82&lt;&gt;""),C82+E82-1,"")</f>
+      <c r="C82" t="str">
+        <v/>
       </c>
       <c r="E82">
         <v>3</v>
@@ -4998,11 +4566,8 @@
       <c r="M82" t="str">
         <v/>
       </c>
-      <c r="N82" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O82" s="1">
-        <f>IF(AND(N82&lt;&gt;"",E82&lt;&gt;""),N82+E82-1,"")</f>
+      <c r="N82" t="str">
+        <v/>
       </c>
       <c r="P82" t="str">
         <v/>
@@ -5021,11 +4586,8 @@
       <c r="B83" t="str">
         <v>Doors &amp; Windows: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C83" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D83" s="1">
-        <f>IF(AND(C83&lt;&gt;"",E83&lt;&gt;""),C83+E83-1,"")</f>
+      <c r="C83" t="str">
+        <v/>
       </c>
       <c r="E83">
         <v>2</v>
@@ -5054,11 +4616,8 @@
       <c r="M83" t="str">
         <v/>
       </c>
-      <c r="N83" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O83" s="1">
-        <f>IF(AND(N83&lt;&gt;"",E83&lt;&gt;""),N83+E83-1,"")</f>
+      <c r="N83" t="str">
+        <v/>
       </c>
       <c r="P83" t="str">
         <v/>
@@ -5077,11 +4636,8 @@
       <c r="B84" t="str">
         <v>Doors &amp; Windows: RFQs Issued</v>
       </c>
-      <c r="C84" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D84" s="1">
-        <f>IF(AND(C84&lt;&gt;"",E84&lt;&gt;""),C84+E84-1,"")</f>
+      <c r="C84" t="str">
+        <v/>
       </c>
       <c r="E84">
         <v>2</v>
@@ -5110,11 +4666,8 @@
       <c r="M84" t="str">
         <v/>
       </c>
-      <c r="N84" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O84" s="1">
-        <f>IF(AND(N84&lt;&gt;"",E84&lt;&gt;""),N84+E84-1,"")</f>
+      <c r="N84" t="str">
+        <v/>
       </c>
       <c r="P84" t="str">
         <v/>
@@ -5133,11 +4686,8 @@
       <c r="B85" t="str">
         <v>Doors &amp; Windows: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C85" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D85" s="1">
-        <f>IF(AND(C85&lt;&gt;"",E85&lt;&gt;""),C85+E85-1,"")</f>
+      <c r="C85" t="str">
+        <v/>
       </c>
       <c r="E85">
         <v>3</v>
@@ -5166,11 +4716,8 @@
       <c r="M85" t="str">
         <v/>
       </c>
-      <c r="N85" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O85" s="1">
-        <f>IF(AND(N85&lt;&gt;"",E85&lt;&gt;""),N85+E85-1,"")</f>
+      <c r="N85" t="str">
+        <v/>
       </c>
       <c r="P85" t="str">
         <v/>
@@ -5189,11 +4736,8 @@
       <c r="B86" t="str">
         <v>Doors &amp; Windows: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C86" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D86" s="1">
-        <f>IF(AND(C86&lt;&gt;"",E86&lt;&gt;""),C86+E86-1,"")</f>
+      <c r="C86" t="str">
+        <v/>
       </c>
       <c r="E86">
         <v>2</v>
@@ -5222,11 +4766,8 @@
       <c r="M86" t="str">
         <v/>
       </c>
-      <c r="N86" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O86" s="1">
-        <f>IF(AND(N86&lt;&gt;"",E86&lt;&gt;""),N86+E86-1,"")</f>
+      <c r="N86" t="str">
+        <v/>
       </c>
       <c r="P86" t="str">
         <v/>
@@ -5245,11 +4786,8 @@
       <c r="B87" t="str">
         <v>Doors &amp; Windows: Vendor Finalisation</v>
       </c>
-      <c r="C87" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D87" s="1">
-        <f>IF(AND(C87&lt;&gt;"",E87&lt;&gt;""),C87+E87-1,"")</f>
+      <c r="C87" t="str">
+        <v/>
       </c>
       <c r="E87">
         <v>1</v>
@@ -5278,11 +4816,8 @@
       <c r="M87" t="str">
         <v/>
       </c>
-      <c r="N87" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O87" s="1">
-        <f>IF(AND(N87&lt;&gt;"",E87&lt;&gt;""),N87+E87-1,"")</f>
+      <c r="N87" t="str">
+        <v/>
       </c>
       <c r="P87" t="str">
         <v/>
@@ -5301,11 +4836,8 @@
       <c r="B88" t="str">
         <v>Doors &amp; Windows: Work Order / PO Release</v>
       </c>
-      <c r="C88" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D88" s="1">
-        <f>IF(AND(C88&lt;&gt;"",E88&lt;&gt;""),C88+E88-1,"")</f>
+      <c r="C88" t="str">
+        <v/>
       </c>
       <c r="E88">
         <v>1</v>
@@ -5334,11 +4866,8 @@
       <c r="M88" t="str">
         <v/>
       </c>
-      <c r="N88" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O88" s="1">
-        <f>IF(AND(N88&lt;&gt;"",E88&lt;&gt;""),N88+E88-1,"")</f>
+      <c r="N88" t="str">
+        <v/>
       </c>
       <c r="P88" t="str">
         <v/>
@@ -5357,10 +4886,10 @@
       <c r="B89" t="str">
         <v>PACKAGE • Wall Finishes</v>
       </c>
-      <c r="C89" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D89" s="1" t="str">
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
         <v/>
       </c>
       <c r="E89" t="str">
@@ -5390,10 +4919,10 @@
       <c r="M89" t="str">
         <v/>
       </c>
-      <c r="N89" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O89" s="1" t="str">
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
         <v/>
       </c>
       <c r="P89" t="str">
@@ -5413,11 +4942,8 @@
       <c r="B90" t="str">
         <v>Wall Finishes: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C90" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D90" s="1">
-        <f>IF(AND(C90&lt;&gt;"",E90&lt;&gt;""),C90+E90-1,"")</f>
+      <c r="C90" t="str">
+        <v/>
       </c>
       <c r="E90">
         <v>3</v>
@@ -5446,11 +4972,8 @@
       <c r="M90" t="str">
         <v/>
       </c>
-      <c r="N90" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O90" s="1">
-        <f>IF(AND(N90&lt;&gt;"",E90&lt;&gt;""),N90+E90-1,"")</f>
+      <c r="N90" t="str">
+        <v/>
       </c>
       <c r="P90" t="str">
         <v/>
@@ -5469,11 +4992,8 @@
       <c r="B91" t="str">
         <v>Wall Finishes: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C91" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D91" s="1">
-        <f>IF(AND(C91&lt;&gt;"",E91&lt;&gt;""),C91+E91-1,"")</f>
+      <c r="C91" t="str">
+        <v/>
       </c>
       <c r="E91">
         <v>2</v>
@@ -5502,11 +5022,8 @@
       <c r="M91" t="str">
         <v/>
       </c>
-      <c r="N91" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O91" s="1">
-        <f>IF(AND(N91&lt;&gt;"",E91&lt;&gt;""),N91+E91-1,"")</f>
+      <c r="N91" t="str">
+        <v/>
       </c>
       <c r="P91" t="str">
         <v/>
@@ -5525,11 +5042,8 @@
       <c r="B92" t="str">
         <v>Wall Finishes: RFQs Issued</v>
       </c>
-      <c r="C92" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D92" s="1">
-        <f>IF(AND(C92&lt;&gt;"",E92&lt;&gt;""),C92+E92-1,"")</f>
+      <c r="C92" t="str">
+        <v/>
       </c>
       <c r="E92">
         <v>2</v>
@@ -5558,11 +5072,8 @@
       <c r="M92" t="str">
         <v/>
       </c>
-      <c r="N92" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O92" s="1">
-        <f>IF(AND(N92&lt;&gt;"",E92&lt;&gt;""),N92+E92-1,"")</f>
+      <c r="N92" t="str">
+        <v/>
       </c>
       <c r="P92" t="str">
         <v/>
@@ -5581,11 +5092,8 @@
       <c r="B93" t="str">
         <v>Wall Finishes: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C93" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D93" s="1">
-        <f>IF(AND(C93&lt;&gt;"",E93&lt;&gt;""),C93+E93-1,"")</f>
+      <c r="C93" t="str">
+        <v/>
       </c>
       <c r="E93">
         <v>3</v>
@@ -5614,11 +5122,8 @@
       <c r="M93" t="str">
         <v/>
       </c>
-      <c r="N93" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O93" s="1">
-        <f>IF(AND(N93&lt;&gt;"",E93&lt;&gt;""),N93+E93-1,"")</f>
+      <c r="N93" t="str">
+        <v/>
       </c>
       <c r="P93" t="str">
         <v/>
@@ -5637,11 +5142,8 @@
       <c r="B94" t="str">
         <v>Wall Finishes: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C94" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D94" s="1">
-        <f>IF(AND(C94&lt;&gt;"",E94&lt;&gt;""),C94+E94-1,"")</f>
+      <c r="C94" t="str">
+        <v/>
       </c>
       <c r="E94">
         <v>2</v>
@@ -5670,11 +5172,8 @@
       <c r="M94" t="str">
         <v/>
       </c>
-      <c r="N94" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O94" s="1">
-        <f>IF(AND(N94&lt;&gt;"",E94&lt;&gt;""),N94+E94-1,"")</f>
+      <c r="N94" t="str">
+        <v/>
       </c>
       <c r="P94" t="str">
         <v/>
@@ -5693,11 +5192,8 @@
       <c r="B95" t="str">
         <v>Wall Finishes: Vendor Finalisation</v>
       </c>
-      <c r="C95" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D95" s="1">
-        <f>IF(AND(C95&lt;&gt;"",E95&lt;&gt;""),C95+E95-1,"")</f>
+      <c r="C95" t="str">
+        <v/>
       </c>
       <c r="E95">
         <v>1</v>
@@ -5726,11 +5222,8 @@
       <c r="M95" t="str">
         <v/>
       </c>
-      <c r="N95" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O95" s="1">
-        <f>IF(AND(N95&lt;&gt;"",E95&lt;&gt;""),N95+E95-1,"")</f>
+      <c r="N95" t="str">
+        <v/>
       </c>
       <c r="P95" t="str">
         <v/>
@@ -5749,11 +5242,8 @@
       <c r="B96" t="str">
         <v>Wall Finishes: Work Order / PO Release</v>
       </c>
-      <c r="C96" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D96" s="1">
-        <f>IF(AND(C96&lt;&gt;"",E96&lt;&gt;""),C96+E96-1,"")</f>
+      <c r="C96" t="str">
+        <v/>
       </c>
       <c r="E96">
         <v>1</v>
@@ -5782,11 +5272,8 @@
       <c r="M96" t="str">
         <v/>
       </c>
-      <c r="N96" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O96" s="1">
-        <f>IF(AND(N96&lt;&gt;"",E96&lt;&gt;""),N96+E96-1,"")</f>
+      <c r="N96" t="str">
+        <v/>
       </c>
       <c r="P96" t="str">
         <v/>
@@ -5805,10 +5292,10 @@
       <c r="B97" t="str">
         <v>PACKAGE • Furnishing</v>
       </c>
-      <c r="C97" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D97" s="1" t="str">
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97" t="str">
         <v/>
       </c>
       <c r="E97" t="str">
@@ -5838,10 +5325,10 @@
       <c r="M97" t="str">
         <v/>
       </c>
-      <c r="N97" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O97" s="1" t="str">
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
         <v/>
       </c>
       <c r="P97" t="str">
@@ -5861,11 +5348,8 @@
       <c r="B98" t="str">
         <v>Furnishing: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C98" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D98" s="1">
-        <f>IF(AND(C98&lt;&gt;"",E98&lt;&gt;""),C98+E98-1,"")</f>
+      <c r="C98" t="str">
+        <v/>
       </c>
       <c r="E98">
         <v>3</v>
@@ -5894,11 +5378,8 @@
       <c r="M98" t="str">
         <v/>
       </c>
-      <c r="N98" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O98" s="1">
-        <f>IF(AND(N98&lt;&gt;"",E98&lt;&gt;""),N98+E98-1,"")</f>
+      <c r="N98" t="str">
+        <v/>
       </c>
       <c r="P98" t="str">
         <v/>
@@ -5917,11 +5398,8 @@
       <c r="B99" t="str">
         <v>Furnishing: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C99" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D99" s="1">
-        <f>IF(AND(C99&lt;&gt;"",E99&lt;&gt;""),C99+E99-1,"")</f>
+      <c r="C99" t="str">
+        <v/>
       </c>
       <c r="E99">
         <v>2</v>
@@ -5950,11 +5428,8 @@
       <c r="M99" t="str">
         <v/>
       </c>
-      <c r="N99" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O99" s="1">
-        <f>IF(AND(N99&lt;&gt;"",E99&lt;&gt;""),N99+E99-1,"")</f>
+      <c r="N99" t="str">
+        <v/>
       </c>
       <c r="P99" t="str">
         <v/>
@@ -5973,11 +5448,8 @@
       <c r="B100" t="str">
         <v>Furnishing: RFQs Issued</v>
       </c>
-      <c r="C100" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D100" s="1">
-        <f>IF(AND(C100&lt;&gt;"",E100&lt;&gt;""),C100+E100-1,"")</f>
+      <c r="C100" t="str">
+        <v/>
       </c>
       <c r="E100">
         <v>2</v>
@@ -6006,11 +5478,8 @@
       <c r="M100" t="str">
         <v/>
       </c>
-      <c r="N100" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O100" s="1">
-        <f>IF(AND(N100&lt;&gt;"",E100&lt;&gt;""),N100+E100-1,"")</f>
+      <c r="N100" t="str">
+        <v/>
       </c>
       <c r="P100" t="str">
         <v/>
@@ -6029,11 +5498,8 @@
       <c r="B101" t="str">
         <v>Furnishing: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C101" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D101" s="1">
-        <f>IF(AND(C101&lt;&gt;"",E101&lt;&gt;""),C101+E101-1,"")</f>
+      <c r="C101" t="str">
+        <v/>
       </c>
       <c r="E101">
         <v>3</v>
@@ -6062,11 +5528,8 @@
       <c r="M101" t="str">
         <v/>
       </c>
-      <c r="N101" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O101" s="1">
-        <f>IF(AND(N101&lt;&gt;"",E101&lt;&gt;""),N101+E101-1,"")</f>
+      <c r="N101" t="str">
+        <v/>
       </c>
       <c r="P101" t="str">
         <v/>
@@ -6085,11 +5548,8 @@
       <c r="B102" t="str">
         <v>Furnishing: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C102" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D102" s="1">
-        <f>IF(AND(C102&lt;&gt;"",E102&lt;&gt;""),C102+E102-1,"")</f>
+      <c r="C102" t="str">
+        <v/>
       </c>
       <c r="E102">
         <v>2</v>
@@ -6118,11 +5578,8 @@
       <c r="M102" t="str">
         <v/>
       </c>
-      <c r="N102" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O102" s="1">
-        <f>IF(AND(N102&lt;&gt;"",E102&lt;&gt;""),N102+E102-1,"")</f>
+      <c r="N102" t="str">
+        <v/>
       </c>
       <c r="P102" t="str">
         <v/>
@@ -6141,11 +5598,8 @@
       <c r="B103" t="str">
         <v>Furnishing: Vendor Finalisation</v>
       </c>
-      <c r="C103" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D103" s="1">
-        <f>IF(AND(C103&lt;&gt;"",E103&lt;&gt;""),C103+E103-1,"")</f>
+      <c r="C103" t="str">
+        <v/>
       </c>
       <c r="E103">
         <v>1</v>
@@ -6174,11 +5628,8 @@
       <c r="M103" t="str">
         <v/>
       </c>
-      <c r="N103" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O103" s="1">
-        <f>IF(AND(N103&lt;&gt;"",E103&lt;&gt;""),N103+E103-1,"")</f>
+      <c r="N103" t="str">
+        <v/>
       </c>
       <c r="P103" t="str">
         <v/>
@@ -6197,11 +5648,8 @@
       <c r="B104" t="str">
         <v>Furnishing: Work Order / PO Release</v>
       </c>
-      <c r="C104" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D104" s="1">
-        <f>IF(AND(C104&lt;&gt;"",E104&lt;&gt;""),C104+E104-1,"")</f>
+      <c r="C104" t="str">
+        <v/>
       </c>
       <c r="E104">
         <v>1</v>
@@ -6230,11 +5678,8 @@
       <c r="M104" t="str">
         <v/>
       </c>
-      <c r="N104" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O104" s="1">
-        <f>IF(AND(N104&lt;&gt;"",E104&lt;&gt;""),N104+E104-1,"")</f>
+      <c r="N104" t="str">
+        <v/>
       </c>
       <c r="P104" t="str">
         <v/>
@@ -6253,10 +5698,10 @@
       <c r="B105" t="str">
         <v>PACKAGE • Soft Furnishing</v>
       </c>
-      <c r="C105" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D105" s="1" t="str">
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
         <v/>
       </c>
       <c r="E105" t="str">
@@ -6286,10 +5731,10 @@
       <c r="M105" t="str">
         <v/>
       </c>
-      <c r="N105" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O105" s="1" t="str">
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
         <v/>
       </c>
       <c r="P105" t="str">
@@ -6309,11 +5754,8 @@
       <c r="B106" t="str">
         <v>Soft Furnishing: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C106" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D106" s="1">
-        <f>IF(AND(C106&lt;&gt;"",E106&lt;&gt;""),C106+E106-1,"")</f>
+      <c r="C106" t="str">
+        <v/>
       </c>
       <c r="E106">
         <v>3</v>
@@ -6342,11 +5784,8 @@
       <c r="M106" t="str">
         <v/>
       </c>
-      <c r="N106" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O106" s="1">
-        <f>IF(AND(N106&lt;&gt;"",E106&lt;&gt;""),N106+E106-1,"")</f>
+      <c r="N106" t="str">
+        <v/>
       </c>
       <c r="P106" t="str">
         <v/>
@@ -6365,11 +5804,8 @@
       <c r="B107" t="str">
         <v>Soft Furnishing: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C107" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D107" s="1">
-        <f>IF(AND(C107&lt;&gt;"",E107&lt;&gt;""),C107+E107-1,"")</f>
+      <c r="C107" t="str">
+        <v/>
       </c>
       <c r="E107">
         <v>2</v>
@@ -6398,11 +5834,8 @@
       <c r="M107" t="str">
         <v/>
       </c>
-      <c r="N107" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O107" s="1">
-        <f>IF(AND(N107&lt;&gt;"",E107&lt;&gt;""),N107+E107-1,"")</f>
+      <c r="N107" t="str">
+        <v/>
       </c>
       <c r="P107" t="str">
         <v/>
@@ -6421,11 +5854,8 @@
       <c r="B108" t="str">
         <v>Soft Furnishing: RFQs Issued</v>
       </c>
-      <c r="C108" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D108" s="1">
-        <f>IF(AND(C108&lt;&gt;"",E108&lt;&gt;""),C108+E108-1,"")</f>
+      <c r="C108" t="str">
+        <v/>
       </c>
       <c r="E108">
         <v>2</v>
@@ -6454,11 +5884,8 @@
       <c r="M108" t="str">
         <v/>
       </c>
-      <c r="N108" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O108" s="1">
-        <f>IF(AND(N108&lt;&gt;"",E108&lt;&gt;""),N108+E108-1,"")</f>
+      <c r="N108" t="str">
+        <v/>
       </c>
       <c r="P108" t="str">
         <v/>
@@ -6477,11 +5904,8 @@
       <c r="B109" t="str">
         <v>Soft Furnishing: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C109" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D109" s="1">
-        <f>IF(AND(C109&lt;&gt;"",E109&lt;&gt;""),C109+E109-1,"")</f>
+      <c r="C109" t="str">
+        <v/>
       </c>
       <c r="E109">
         <v>3</v>
@@ -6510,11 +5934,8 @@
       <c r="M109" t="str">
         <v/>
       </c>
-      <c r="N109" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O109" s="1">
-        <f>IF(AND(N109&lt;&gt;"",E109&lt;&gt;""),N109+E109-1,"")</f>
+      <c r="N109" t="str">
+        <v/>
       </c>
       <c r="P109" t="str">
         <v/>
@@ -6533,11 +5954,8 @@
       <c r="B110" t="str">
         <v>Soft Furnishing: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C110" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D110" s="1">
-        <f>IF(AND(C110&lt;&gt;"",E110&lt;&gt;""),C110+E110-1,"")</f>
+      <c r="C110" t="str">
+        <v/>
       </c>
       <c r="E110">
         <v>2</v>
@@ -6566,11 +5984,8 @@
       <c r="M110" t="str">
         <v/>
       </c>
-      <c r="N110" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O110" s="1">
-        <f>IF(AND(N110&lt;&gt;"",E110&lt;&gt;""),N110+E110-1,"")</f>
+      <c r="N110" t="str">
+        <v/>
       </c>
       <c r="P110" t="str">
         <v/>
@@ -6589,11 +6004,8 @@
       <c r="B111" t="str">
         <v>Soft Furnishing: Vendor Finalisation</v>
       </c>
-      <c r="C111" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D111" s="1">
-        <f>IF(AND(C111&lt;&gt;"",E111&lt;&gt;""),C111+E111-1,"")</f>
+      <c r="C111" t="str">
+        <v/>
       </c>
       <c r="E111">
         <v>1</v>
@@ -6622,11 +6034,8 @@
       <c r="M111" t="str">
         <v/>
       </c>
-      <c r="N111" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O111" s="1">
-        <f>IF(AND(N111&lt;&gt;"",E111&lt;&gt;""),N111+E111-1,"")</f>
+      <c r="N111" t="str">
+        <v/>
       </c>
       <c r="P111" t="str">
         <v/>
@@ -6645,11 +6054,8 @@
       <c r="B112" t="str">
         <v>Soft Furnishing: Work Order / PO Release</v>
       </c>
-      <c r="C112" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D112" s="1">
-        <f>IF(AND(C112&lt;&gt;"",E112&lt;&gt;""),C112+E112-1,"")</f>
+      <c r="C112" t="str">
+        <v/>
       </c>
       <c r="E112">
         <v>1</v>
@@ -6678,11 +6084,8 @@
       <c r="M112" t="str">
         <v/>
       </c>
-      <c r="N112" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O112" s="1">
-        <f>IF(AND(N112&lt;&gt;"",E112&lt;&gt;""),N112+E112-1,"")</f>
+      <c r="N112" t="str">
+        <v/>
       </c>
       <c r="P112" t="str">
         <v/>
@@ -6701,10 +6104,10 @@
       <c r="B113" t="str">
         <v>PACKAGE • Appliances</v>
       </c>
-      <c r="C113" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D113" s="1" t="str">
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
         <v/>
       </c>
       <c r="E113" t="str">
@@ -6734,10 +6137,10 @@
       <c r="M113" t="str">
         <v/>
       </c>
-      <c r="N113" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O113" s="1" t="str">
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
         <v/>
       </c>
       <c r="P113" t="str">
@@ -6757,11 +6160,8 @@
       <c r="B114" t="str">
         <v>Appliances: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C114" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D114" s="1">
-        <f>IF(AND(C114&lt;&gt;"",E114&lt;&gt;""),C114+E114-1,"")</f>
+      <c r="C114" t="str">
+        <v/>
       </c>
       <c r="E114">
         <v>3</v>
@@ -6790,11 +6190,8 @@
       <c r="M114" t="str">
         <v/>
       </c>
-      <c r="N114" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O114" s="1">
-        <f>IF(AND(N114&lt;&gt;"",E114&lt;&gt;""),N114+E114-1,"")</f>
+      <c r="N114" t="str">
+        <v/>
       </c>
       <c r="P114" t="str">
         <v/>
@@ -6813,11 +6210,8 @@
       <c r="B115" t="str">
         <v>Appliances: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C115" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D115" s="1">
-        <f>IF(AND(C115&lt;&gt;"",E115&lt;&gt;""),C115+E115-1,"")</f>
+      <c r="C115" t="str">
+        <v/>
       </c>
       <c r="E115">
         <v>2</v>
@@ -6846,11 +6240,8 @@
       <c r="M115" t="str">
         <v/>
       </c>
-      <c r="N115" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O115" s="1">
-        <f>IF(AND(N115&lt;&gt;"",E115&lt;&gt;""),N115+E115-1,"")</f>
+      <c r="N115" t="str">
+        <v/>
       </c>
       <c r="P115" t="str">
         <v/>
@@ -6869,11 +6260,8 @@
       <c r="B116" t="str">
         <v>Appliances: RFQs Issued</v>
       </c>
-      <c r="C116" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D116" s="1">
-        <f>IF(AND(C116&lt;&gt;"",E116&lt;&gt;""),C116+E116-1,"")</f>
+      <c r="C116" t="str">
+        <v/>
       </c>
       <c r="E116">
         <v>2</v>
@@ -6902,11 +6290,8 @@
       <c r="M116" t="str">
         <v/>
       </c>
-      <c r="N116" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O116" s="1">
-        <f>IF(AND(N116&lt;&gt;"",E116&lt;&gt;""),N116+E116-1,"")</f>
+      <c r="N116" t="str">
+        <v/>
       </c>
       <c r="P116" t="str">
         <v/>
@@ -6925,11 +6310,8 @@
       <c r="B117" t="str">
         <v>Appliances: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C117" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D117" s="1">
-        <f>IF(AND(C117&lt;&gt;"",E117&lt;&gt;""),C117+E117-1,"")</f>
+      <c r="C117" t="str">
+        <v/>
       </c>
       <c r="E117">
         <v>3</v>
@@ -6958,11 +6340,8 @@
       <c r="M117" t="str">
         <v/>
       </c>
-      <c r="N117" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O117" s="1">
-        <f>IF(AND(N117&lt;&gt;"",E117&lt;&gt;""),N117+E117-1,"")</f>
+      <c r="N117" t="str">
+        <v/>
       </c>
       <c r="P117" t="str">
         <v/>
@@ -6981,11 +6360,8 @@
       <c r="B118" t="str">
         <v>Appliances: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C118" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D118" s="1">
-        <f>IF(AND(C118&lt;&gt;"",E118&lt;&gt;""),C118+E118-1,"")</f>
+      <c r="C118" t="str">
+        <v/>
       </c>
       <c r="E118">
         <v>2</v>
@@ -7014,11 +6390,8 @@
       <c r="M118" t="str">
         <v/>
       </c>
-      <c r="N118" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O118" s="1">
-        <f>IF(AND(N118&lt;&gt;"",E118&lt;&gt;""),N118+E118-1,"")</f>
+      <c r="N118" t="str">
+        <v/>
       </c>
       <c r="P118" t="str">
         <v/>
@@ -7037,11 +6410,8 @@
       <c r="B119" t="str">
         <v>Appliances: Vendor Finalisation</v>
       </c>
-      <c r="C119" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D119" s="1">
-        <f>IF(AND(C119&lt;&gt;"",E119&lt;&gt;""),C119+E119-1,"")</f>
+      <c r="C119" t="str">
+        <v/>
       </c>
       <c r="E119">
         <v>1</v>
@@ -7070,11 +6440,8 @@
       <c r="M119" t="str">
         <v/>
       </c>
-      <c r="N119" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O119" s="1">
-        <f>IF(AND(N119&lt;&gt;"",E119&lt;&gt;""),N119+E119-1,"")</f>
+      <c r="N119" t="str">
+        <v/>
       </c>
       <c r="P119" t="str">
         <v/>
@@ -7093,11 +6460,8 @@
       <c r="B120" t="str">
         <v>Appliances: Work Order / PO Release</v>
       </c>
-      <c r="C120" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D120" s="1">
-        <f>IF(AND(C120&lt;&gt;"",E120&lt;&gt;""),C120+E120-1,"")</f>
+      <c r="C120" t="str">
+        <v/>
       </c>
       <c r="E120">
         <v>1</v>
@@ -7126,11 +6490,8 @@
       <c r="M120" t="str">
         <v/>
       </c>
-      <c r="N120" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O120" s="1">
-        <f>IF(AND(N120&lt;&gt;"",E120&lt;&gt;""),N120+E120-1,"")</f>
+      <c r="N120" t="str">
+        <v/>
       </c>
       <c r="P120" t="str">
         <v/>
@@ -7149,10 +6510,10 @@
       <c r="B121" t="str">
         <v>PACKAGE • Flooring</v>
       </c>
-      <c r="C121" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D121" s="1" t="str">
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
         <v/>
       </c>
       <c r="E121" t="str">
@@ -7182,10 +6543,10 @@
       <c r="M121" t="str">
         <v/>
       </c>
-      <c r="N121" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O121" s="1" t="str">
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
         <v/>
       </c>
       <c r="P121" t="str">
@@ -7205,11 +6566,8 @@
       <c r="B122" t="str">
         <v>Flooring: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C122" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D122" s="1">
-        <f>IF(AND(C122&lt;&gt;"",E122&lt;&gt;""),C122+E122-1,"")</f>
+      <c r="C122" t="str">
+        <v/>
       </c>
       <c r="E122">
         <v>3</v>
@@ -7238,11 +6596,8 @@
       <c r="M122" t="str">
         <v/>
       </c>
-      <c r="N122" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O122" s="1">
-        <f>IF(AND(N122&lt;&gt;"",E122&lt;&gt;""),N122+E122-1,"")</f>
+      <c r="N122" t="str">
+        <v/>
       </c>
       <c r="P122" t="str">
         <v/>
@@ -7261,11 +6616,8 @@
       <c r="B123" t="str">
         <v>Flooring: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C123" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D123" s="1">
-        <f>IF(AND(C123&lt;&gt;"",E123&lt;&gt;""),C123+E123-1,"")</f>
+      <c r="C123" t="str">
+        <v/>
       </c>
       <c r="E123">
         <v>2</v>
@@ -7294,11 +6646,8 @@
       <c r="M123" t="str">
         <v/>
       </c>
-      <c r="N123" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O123" s="1">
-        <f>IF(AND(N123&lt;&gt;"",E123&lt;&gt;""),N123+E123-1,"")</f>
+      <c r="N123" t="str">
+        <v/>
       </c>
       <c r="P123" t="str">
         <v/>
@@ -7317,11 +6666,8 @@
       <c r="B124" t="str">
         <v>Flooring: RFQs Issued</v>
       </c>
-      <c r="C124" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D124" s="1">
-        <f>IF(AND(C124&lt;&gt;"",E124&lt;&gt;""),C124+E124-1,"")</f>
+      <c r="C124" t="str">
+        <v/>
       </c>
       <c r="E124">
         <v>2</v>
@@ -7350,11 +6696,8 @@
       <c r="M124" t="str">
         <v/>
       </c>
-      <c r="N124" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O124" s="1">
-        <f>IF(AND(N124&lt;&gt;"",E124&lt;&gt;""),N124+E124-1,"")</f>
+      <c r="N124" t="str">
+        <v/>
       </c>
       <c r="P124" t="str">
         <v/>
@@ -7373,11 +6716,8 @@
       <c r="B125" t="str">
         <v>Flooring: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C125" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D125" s="1">
-        <f>IF(AND(C125&lt;&gt;"",E125&lt;&gt;""),C125+E125-1,"")</f>
+      <c r="C125" t="str">
+        <v/>
       </c>
       <c r="E125">
         <v>3</v>
@@ -7406,11 +6746,8 @@
       <c r="M125" t="str">
         <v/>
       </c>
-      <c r="N125" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O125" s="1">
-        <f>IF(AND(N125&lt;&gt;"",E125&lt;&gt;""),N125+E125-1,"")</f>
+      <c r="N125" t="str">
+        <v/>
       </c>
       <c r="P125" t="str">
         <v/>
@@ -7429,11 +6766,8 @@
       <c r="B126" t="str">
         <v>Flooring: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C126" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D126" s="1">
-        <f>IF(AND(C126&lt;&gt;"",E126&lt;&gt;""),C126+E126-1,"")</f>
+      <c r="C126" t="str">
+        <v/>
       </c>
       <c r="E126">
         <v>2</v>
@@ -7462,11 +6796,8 @@
       <c r="M126" t="str">
         <v/>
       </c>
-      <c r="N126" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O126" s="1">
-        <f>IF(AND(N126&lt;&gt;"",E126&lt;&gt;""),N126+E126-1,"")</f>
+      <c r="N126" t="str">
+        <v/>
       </c>
       <c r="P126" t="str">
         <v/>
@@ -7485,11 +6816,8 @@
       <c r="B127" t="str">
         <v>Flooring: Vendor Finalisation</v>
       </c>
-      <c r="C127" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D127" s="1">
-        <f>IF(AND(C127&lt;&gt;"",E127&lt;&gt;""),C127+E127-1,"")</f>
+      <c r="C127" t="str">
+        <v/>
       </c>
       <c r="E127">
         <v>1</v>
@@ -7518,11 +6846,8 @@
       <c r="M127" t="str">
         <v/>
       </c>
-      <c r="N127" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O127" s="1">
-        <f>IF(AND(N127&lt;&gt;"",E127&lt;&gt;""),N127+E127-1,"")</f>
+      <c r="N127" t="str">
+        <v/>
       </c>
       <c r="P127" t="str">
         <v/>
@@ -7541,11 +6866,8 @@
       <c r="B128" t="str">
         <v>Flooring: Work Order / PO Release</v>
       </c>
-      <c r="C128" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D128" s="1">
-        <f>IF(AND(C128&lt;&gt;"",E128&lt;&gt;""),C128+E128-1,"")</f>
+      <c r="C128" t="str">
+        <v/>
       </c>
       <c r="E128">
         <v>1</v>
@@ -7574,11 +6896,8 @@
       <c r="M128" t="str">
         <v/>
       </c>
-      <c r="N128" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O128" s="1">
-        <f>IF(AND(N128&lt;&gt;"",E128&lt;&gt;""),N128+E128-1,"")</f>
+      <c r="N128" t="str">
+        <v/>
       </c>
       <c r="P128" t="str">
         <v/>
@@ -7597,10 +6916,10 @@
       <c r="B129" t="str">
         <v>PACKAGE • Carpentry</v>
       </c>
-      <c r="C129" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D129" s="1" t="str">
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
         <v/>
       </c>
       <c r="E129" t="str">
@@ -7630,10 +6949,10 @@
       <c r="M129" t="str">
         <v/>
       </c>
-      <c r="N129" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O129" s="1" t="str">
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
         <v/>
       </c>
       <c r="P129" t="str">
@@ -7653,11 +6972,8 @@
       <c r="B130" t="str">
         <v>Carpentry: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C130" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D130" s="1">
-        <f>IF(AND(C130&lt;&gt;"",E130&lt;&gt;""),C130+E130-1,"")</f>
+      <c r="C130" t="str">
+        <v/>
       </c>
       <c r="E130">
         <v>3</v>
@@ -7686,11 +7002,8 @@
       <c r="M130" t="str">
         <v/>
       </c>
-      <c r="N130" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O130" s="1">
-        <f>IF(AND(N130&lt;&gt;"",E130&lt;&gt;""),N130+E130-1,"")</f>
+      <c r="N130" t="str">
+        <v/>
       </c>
       <c r="P130" t="str">
         <v/>
@@ -7709,11 +7022,8 @@
       <c r="B131" t="str">
         <v>Carpentry: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C131" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D131" s="1">
-        <f>IF(AND(C131&lt;&gt;"",E131&lt;&gt;""),C131+E131-1,"")</f>
+      <c r="C131" t="str">
+        <v/>
       </c>
       <c r="E131">
         <v>2</v>
@@ -7742,11 +7052,8 @@
       <c r="M131" t="str">
         <v/>
       </c>
-      <c r="N131" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O131" s="1">
-        <f>IF(AND(N131&lt;&gt;"",E131&lt;&gt;""),N131+E131-1,"")</f>
+      <c r="N131" t="str">
+        <v/>
       </c>
       <c r="P131" t="str">
         <v/>
@@ -7765,11 +7072,8 @@
       <c r="B132" t="str">
         <v>Carpentry: RFQs Issued</v>
       </c>
-      <c r="C132" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D132" s="1">
-        <f>IF(AND(C132&lt;&gt;"",E132&lt;&gt;""),C132+E132-1,"")</f>
+      <c r="C132" t="str">
+        <v/>
       </c>
       <c r="E132">
         <v>2</v>
@@ -7798,11 +7102,8 @@
       <c r="M132" t="str">
         <v/>
       </c>
-      <c r="N132" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O132" s="1">
-        <f>IF(AND(N132&lt;&gt;"",E132&lt;&gt;""),N132+E132-1,"")</f>
+      <c r="N132" t="str">
+        <v/>
       </c>
       <c r="P132" t="str">
         <v/>
@@ -7821,11 +7122,8 @@
       <c r="B133" t="str">
         <v>Carpentry: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C133" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D133" s="1">
-        <f>IF(AND(C133&lt;&gt;"",E133&lt;&gt;""),C133+E133-1,"")</f>
+      <c r="C133" t="str">
+        <v/>
       </c>
       <c r="E133">
         <v>3</v>
@@ -7854,11 +7152,8 @@
       <c r="M133" t="str">
         <v/>
       </c>
-      <c r="N133" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O133" s="1">
-        <f>IF(AND(N133&lt;&gt;"",E133&lt;&gt;""),N133+E133-1,"")</f>
+      <c r="N133" t="str">
+        <v/>
       </c>
       <c r="P133" t="str">
         <v/>
@@ -7877,11 +7172,8 @@
       <c r="B134" t="str">
         <v>Carpentry: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C134" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D134" s="1">
-        <f>IF(AND(C134&lt;&gt;"",E134&lt;&gt;""),C134+E134-1,"")</f>
+      <c r="C134" t="str">
+        <v/>
       </c>
       <c r="E134">
         <v>2</v>
@@ -7910,11 +7202,8 @@
       <c r="M134" t="str">
         <v/>
       </c>
-      <c r="N134" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O134" s="1">
-        <f>IF(AND(N134&lt;&gt;"",E134&lt;&gt;""),N134+E134-1,"")</f>
+      <c r="N134" t="str">
+        <v/>
       </c>
       <c r="P134" t="str">
         <v/>
@@ -7933,11 +7222,8 @@
       <c r="B135" t="str">
         <v>Carpentry: Vendor Finalisation</v>
       </c>
-      <c r="C135" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D135" s="1">
-        <f>IF(AND(C135&lt;&gt;"",E135&lt;&gt;""),C135+E135-1,"")</f>
+      <c r="C135" t="str">
+        <v/>
       </c>
       <c r="E135">
         <v>1</v>
@@ -7966,11 +7252,8 @@
       <c r="M135" t="str">
         <v/>
       </c>
-      <c r="N135" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O135" s="1">
-        <f>IF(AND(N135&lt;&gt;"",E135&lt;&gt;""),N135+E135-1,"")</f>
+      <c r="N135" t="str">
+        <v/>
       </c>
       <c r="P135" t="str">
         <v/>
@@ -7989,11 +7272,8 @@
       <c r="B136" t="str">
         <v>Carpentry: Work Order / PO Release</v>
       </c>
-      <c r="C136" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D136" s="1">
-        <f>IF(AND(C136&lt;&gt;"",E136&lt;&gt;""),C136+E136-1,"")</f>
+      <c r="C136" t="str">
+        <v/>
       </c>
       <c r="E136">
         <v>1</v>
@@ -8022,11 +7302,8 @@
       <c r="M136" t="str">
         <v/>
       </c>
-      <c r="N136" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O136" s="1">
-        <f>IF(AND(N136&lt;&gt;"",E136&lt;&gt;""),N136+E136-1,"")</f>
+      <c r="N136" t="str">
+        <v/>
       </c>
       <c r="P136" t="str">
         <v/>
@@ -8045,10 +7322,10 @@
       <c r="B137" t="str">
         <v>PHASE • Execution (Category-wise)</v>
       </c>
-      <c r="C137" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D137" s="1" t="str">
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137" t="str">
         <v/>
       </c>
       <c r="E137" t="str">
@@ -8078,10 +7355,10 @@
       <c r="M137" t="str">
         <v/>
       </c>
-      <c r="N137" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O137" s="1" t="str">
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
         <v/>
       </c>
       <c r="P137" t="str">
@@ -8101,10 +7378,10 @@
       <c r="B138" t="str">
         <v>EXECUTE • Civil</v>
       </c>
-      <c r="C138" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D138" s="1" t="str">
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138" t="str">
         <v/>
       </c>
       <c r="E138" t="str">
@@ -8134,10 +7411,10 @@
       <c r="M138" t="str">
         <v/>
       </c>
-      <c r="N138" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O138" s="1" t="str">
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
         <v/>
       </c>
       <c r="P138" t="str">
@@ -8157,11 +7434,8 @@
       <c r="B139" t="str">
         <v>Civil: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C139" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D139" s="1">
-        <f>IF(AND(C139&lt;&gt;"",E139&lt;&gt;""),C139+E139-1,"")</f>
+      <c r="C139" t="str">
+        <v/>
       </c>
       <c r="E139">
         <v>2</v>
@@ -8190,11 +7464,8 @@
       <c r="M139" t="str">
         <v/>
       </c>
-      <c r="N139" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O139" s="1">
-        <f>IF(AND(N139&lt;&gt;"",E139&lt;&gt;""),N139+E139-1,"")</f>
+      <c r="N139" t="str">
+        <v/>
       </c>
       <c r="P139" t="str">
         <v/>
@@ -8213,11 +7484,8 @@
       <c r="B140" t="str">
         <v>Civil: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C140" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D140" s="1">
-        <f>IF(AND(C140&lt;&gt;"",E140&lt;&gt;""),C140+E140-1,"")</f>
+      <c r="C140" t="str">
+        <v/>
       </c>
       <c r="E140">
         <v>7</v>
@@ -8246,11 +7514,8 @@
       <c r="M140" t="str">
         <v/>
       </c>
-      <c r="N140" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O140" s="1">
-        <f>IF(AND(N140&lt;&gt;"",E140&lt;&gt;""),N140+E140-1,"")</f>
+      <c r="N140" t="str">
+        <v/>
       </c>
       <c r="P140" t="str">
         <v/>
@@ -8269,11 +7534,8 @@
       <c r="B141" t="str">
         <v>Civil: Delivery to Site</v>
       </c>
-      <c r="C141" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D141" s="1">
-        <f>IF(AND(C141&lt;&gt;"",E141&lt;&gt;""),C141+E141-1,"")</f>
+      <c r="C141" t="str">
+        <v/>
       </c>
       <c r="E141">
         <v>1</v>
@@ -8302,11 +7564,8 @@
       <c r="M141" t="str">
         <v/>
       </c>
-      <c r="N141" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O141" s="1">
-        <f>IF(AND(N141&lt;&gt;"",E141&lt;&gt;""),N141+E141-1,"")</f>
+      <c r="N141" t="str">
+        <v/>
       </c>
       <c r="P141" t="str">
         <v/>
@@ -8325,11 +7584,8 @@
       <c r="B142" t="str">
         <v>Civil: Installation / Execution</v>
       </c>
-      <c r="C142" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D142" s="1">
-        <f>IF(AND(C142&lt;&gt;"",E142&lt;&gt;""),C142+E142-1,"")</f>
+      <c r="C142" t="str">
+        <v/>
       </c>
       <c r="E142">
         <v>5</v>
@@ -8358,11 +7614,8 @@
       <c r="M142" t="str">
         <v/>
       </c>
-      <c r="N142" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O142" s="1">
-        <f>IF(AND(N142&lt;&gt;"",E142&lt;&gt;""),N142+E142-1,"")</f>
+      <c r="N142" t="str">
+        <v/>
       </c>
       <c r="P142" t="str">
         <v/>
@@ -8381,11 +7634,8 @@
       <c r="B143" t="str">
         <v>Civil: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C143" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D143" s="1">
-        <f>IF(AND(C143&lt;&gt;"",E143&lt;&gt;""),C143+E143-1,"")</f>
+      <c r="C143" t="str">
+        <v/>
       </c>
       <c r="E143">
         <v>2</v>
@@ -8414,11 +7664,8 @@
       <c r="M143" t="str">
         <v/>
       </c>
-      <c r="N143" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O143" s="1">
-        <f>IF(AND(N143&lt;&gt;"",E143&lt;&gt;""),N143+E143-1,"")</f>
+      <c r="N143" t="str">
+        <v/>
       </c>
       <c r="P143" t="str">
         <v/>
@@ -8437,10 +7684,10 @@
       <c r="B144" t="str">
         <v>EXECUTE • Electricals</v>
       </c>
-      <c r="C144" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D144" s="1" t="str">
+      <c r="C144" t="str">
+        <v/>
+      </c>
+      <c r="D144" t="str">
         <v/>
       </c>
       <c r="E144" t="str">
@@ -8470,10 +7717,10 @@
       <c r="M144" t="str">
         <v/>
       </c>
-      <c r="N144" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O144" s="1" t="str">
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
         <v/>
       </c>
       <c r="P144" t="str">
@@ -8493,11 +7740,8 @@
       <c r="B145" t="str">
         <v>Electricals: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C145" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D145" s="1">
-        <f>IF(AND(C145&lt;&gt;"",E145&lt;&gt;""),C145+E145-1,"")</f>
+      <c r="C145" t="str">
+        <v/>
       </c>
       <c r="E145">
         <v>2</v>
@@ -8526,11 +7770,8 @@
       <c r="M145" t="str">
         <v/>
       </c>
-      <c r="N145" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O145" s="1">
-        <f>IF(AND(N145&lt;&gt;"",E145&lt;&gt;""),N145+E145-1,"")</f>
+      <c r="N145" t="str">
+        <v/>
       </c>
       <c r="P145" t="str">
         <v/>
@@ -8549,11 +7790,8 @@
       <c r="B146" t="str">
         <v>Electricals: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C146" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D146" s="1">
-        <f>IF(AND(C146&lt;&gt;"",E146&lt;&gt;""),C146+E146-1,"")</f>
+      <c r="C146" t="str">
+        <v/>
       </c>
       <c r="E146">
         <v>7</v>
@@ -8582,11 +7820,8 @@
       <c r="M146" t="str">
         <v/>
       </c>
-      <c r="N146" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O146" s="1">
-        <f>IF(AND(N146&lt;&gt;"",E146&lt;&gt;""),N146+E146-1,"")</f>
+      <c r="N146" t="str">
+        <v/>
       </c>
       <c r="P146" t="str">
         <v/>
@@ -8605,11 +7840,8 @@
       <c r="B147" t="str">
         <v>Electricals: Delivery to Site</v>
       </c>
-      <c r="C147" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D147" s="1">
-        <f>IF(AND(C147&lt;&gt;"",E147&lt;&gt;""),C147+E147-1,"")</f>
+      <c r="C147" t="str">
+        <v/>
       </c>
       <c r="E147">
         <v>1</v>
@@ -8638,11 +7870,8 @@
       <c r="M147" t="str">
         <v/>
       </c>
-      <c r="N147" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O147" s="1">
-        <f>IF(AND(N147&lt;&gt;"",E147&lt;&gt;""),N147+E147-1,"")</f>
+      <c r="N147" t="str">
+        <v/>
       </c>
       <c r="P147" t="str">
         <v/>
@@ -8661,11 +7890,8 @@
       <c r="B148" t="str">
         <v>Electricals: Installation / Execution</v>
       </c>
-      <c r="C148" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D148" s="1">
-        <f>IF(AND(C148&lt;&gt;"",E148&lt;&gt;""),C148+E148-1,"")</f>
+      <c r="C148" t="str">
+        <v/>
       </c>
       <c r="E148">
         <v>5</v>
@@ -8694,11 +7920,8 @@
       <c r="M148" t="str">
         <v/>
       </c>
-      <c r="N148" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O148" s="1">
-        <f>IF(AND(N148&lt;&gt;"",E148&lt;&gt;""),N148+E148-1,"")</f>
+      <c r="N148" t="str">
+        <v/>
       </c>
       <c r="P148" t="str">
         <v/>
@@ -8717,11 +7940,8 @@
       <c r="B149" t="str">
         <v>Electricals: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C149" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D149" s="1">
-        <f>IF(AND(C149&lt;&gt;"",E149&lt;&gt;""),C149+E149-1,"")</f>
+      <c r="C149" t="str">
+        <v/>
       </c>
       <c r="E149">
         <v>2</v>
@@ -8750,11 +7970,8 @@
       <c r="M149" t="str">
         <v/>
       </c>
-      <c r="N149" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O149" s="1">
-        <f>IF(AND(N149&lt;&gt;"",E149&lt;&gt;""),N149+E149-1,"")</f>
+      <c r="N149" t="str">
+        <v/>
       </c>
       <c r="P149" t="str">
         <v/>
@@ -8773,10 +7990,10 @@
       <c r="B150" t="str">
         <v>EXECUTE • Plumbing</v>
       </c>
-      <c r="C150" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D150" s="1" t="str">
+      <c r="C150" t="str">
+        <v/>
+      </c>
+      <c r="D150" t="str">
         <v/>
       </c>
       <c r="E150" t="str">
@@ -8806,10 +8023,10 @@
       <c r="M150" t="str">
         <v/>
       </c>
-      <c r="N150" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O150" s="1" t="str">
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
         <v/>
       </c>
       <c r="P150" t="str">
@@ -8829,11 +8046,8 @@
       <c r="B151" t="str">
         <v>Plumbing: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C151" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D151" s="1">
-        <f>IF(AND(C151&lt;&gt;"",E151&lt;&gt;""),C151+E151-1,"")</f>
+      <c r="C151" t="str">
+        <v/>
       </c>
       <c r="E151">
         <v>2</v>
@@ -8862,11 +8076,8 @@
       <c r="M151" t="str">
         <v/>
       </c>
-      <c r="N151" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O151" s="1">
-        <f>IF(AND(N151&lt;&gt;"",E151&lt;&gt;""),N151+E151-1,"")</f>
+      <c r="N151" t="str">
+        <v/>
       </c>
       <c r="P151" t="str">
         <v/>
@@ -8885,11 +8096,8 @@
       <c r="B152" t="str">
         <v>Plumbing: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C152" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D152" s="1">
-        <f>IF(AND(C152&lt;&gt;"",E152&lt;&gt;""),C152+E152-1,"")</f>
+      <c r="C152" t="str">
+        <v/>
       </c>
       <c r="E152">
         <v>7</v>
@@ -8918,11 +8126,8 @@
       <c r="M152" t="str">
         <v/>
       </c>
-      <c r="N152" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O152" s="1">
-        <f>IF(AND(N152&lt;&gt;"",E152&lt;&gt;""),N152+E152-1,"")</f>
+      <c r="N152" t="str">
+        <v/>
       </c>
       <c r="P152" t="str">
         <v/>
@@ -8941,11 +8146,8 @@
       <c r="B153" t="str">
         <v>Plumbing: Delivery to Site</v>
       </c>
-      <c r="C153" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D153" s="1">
-        <f>IF(AND(C153&lt;&gt;"",E153&lt;&gt;""),C153+E153-1,"")</f>
+      <c r="C153" t="str">
+        <v/>
       </c>
       <c r="E153">
         <v>1</v>
@@ -8974,11 +8176,8 @@
       <c r="M153" t="str">
         <v/>
       </c>
-      <c r="N153" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O153" s="1">
-        <f>IF(AND(N153&lt;&gt;"",E153&lt;&gt;""),N153+E153-1,"")</f>
+      <c r="N153" t="str">
+        <v/>
       </c>
       <c r="P153" t="str">
         <v/>
@@ -8997,11 +8196,8 @@
       <c r="B154" t="str">
         <v>Plumbing: Installation / Execution</v>
       </c>
-      <c r="C154" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D154" s="1">
-        <f>IF(AND(C154&lt;&gt;"",E154&lt;&gt;""),C154+E154-1,"")</f>
+      <c r="C154" t="str">
+        <v/>
       </c>
       <c r="E154">
         <v>5</v>
@@ -9030,11 +8226,8 @@
       <c r="M154" t="str">
         <v/>
       </c>
-      <c r="N154" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O154" s="1">
-        <f>IF(AND(N154&lt;&gt;"",E154&lt;&gt;""),N154+E154-1,"")</f>
+      <c r="N154" t="str">
+        <v/>
       </c>
       <c r="P154" t="str">
         <v/>
@@ -9053,11 +8246,8 @@
       <c r="B155" t="str">
         <v>Plumbing: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C155" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D155" s="1">
-        <f>IF(AND(C155&lt;&gt;"",E155&lt;&gt;""),C155+E155-1,"")</f>
+      <c r="C155" t="str">
+        <v/>
       </c>
       <c r="E155">
         <v>2</v>
@@ -9086,11 +8276,8 @@
       <c r="M155" t="str">
         <v/>
       </c>
-      <c r="N155" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O155" s="1">
-        <f>IF(AND(N155&lt;&gt;"",E155&lt;&gt;""),N155+E155-1,"")</f>
+      <c r="N155" t="str">
+        <v/>
       </c>
       <c r="P155" t="str">
         <v/>
@@ -9109,10 +8296,10 @@
       <c r="B156" t="str">
         <v>EXECUTE • Kitchens</v>
       </c>
-      <c r="C156" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D156" s="1" t="str">
+      <c r="C156" t="str">
+        <v/>
+      </c>
+      <c r="D156" t="str">
         <v/>
       </c>
       <c r="E156" t="str">
@@ -9142,10 +8329,10 @@
       <c r="M156" t="str">
         <v/>
       </c>
-      <c r="N156" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O156" s="1" t="str">
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
         <v/>
       </c>
       <c r="P156" t="str">
@@ -9165,11 +8352,8 @@
       <c r="B157" t="str">
         <v>Kitchens: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C157" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D157" s="1">
-        <f>IF(AND(C157&lt;&gt;"",E157&lt;&gt;""),C157+E157-1,"")</f>
+      <c r="C157" t="str">
+        <v/>
       </c>
       <c r="E157">
         <v>2</v>
@@ -9198,11 +8382,8 @@
       <c r="M157" t="str">
         <v/>
       </c>
-      <c r="N157" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O157" s="1">
-        <f>IF(AND(N157&lt;&gt;"",E157&lt;&gt;""),N157+E157-1,"")</f>
+      <c r="N157" t="str">
+        <v/>
       </c>
       <c r="P157" t="str">
         <v/>
@@ -9221,11 +8402,8 @@
       <c r="B158" t="str">
         <v>Kitchens: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C158" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D158" s="1">
-        <f>IF(AND(C158&lt;&gt;"",E158&lt;&gt;""),C158+E158-1,"")</f>
+      <c r="C158" t="str">
+        <v/>
       </c>
       <c r="E158">
         <v>7</v>
@@ -9254,11 +8432,8 @@
       <c r="M158" t="str">
         <v/>
       </c>
-      <c r="N158" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O158" s="1">
-        <f>IF(AND(N158&lt;&gt;"",E158&lt;&gt;""),N158+E158-1,"")</f>
+      <c r="N158" t="str">
+        <v/>
       </c>
       <c r="P158" t="str">
         <v/>
@@ -9277,11 +8452,8 @@
       <c r="B159" t="str">
         <v>Kitchens: Delivery to Site</v>
       </c>
-      <c r="C159" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D159" s="1">
-        <f>IF(AND(C159&lt;&gt;"",E159&lt;&gt;""),C159+E159-1,"")</f>
+      <c r="C159" t="str">
+        <v/>
       </c>
       <c r="E159">
         <v>1</v>
@@ -9310,11 +8482,8 @@
       <c r="M159" t="str">
         <v/>
       </c>
-      <c r="N159" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O159" s="1">
-        <f>IF(AND(N159&lt;&gt;"",E159&lt;&gt;""),N159+E159-1,"")</f>
+      <c r="N159" t="str">
+        <v/>
       </c>
       <c r="P159" t="str">
         <v/>
@@ -9333,11 +8502,8 @@
       <c r="B160" t="str">
         <v>Kitchens: Installation / Execution</v>
       </c>
-      <c r="C160" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D160" s="1">
-        <f>IF(AND(C160&lt;&gt;"",E160&lt;&gt;""),C160+E160-1,"")</f>
+      <c r="C160" t="str">
+        <v/>
       </c>
       <c r="E160">
         <v>5</v>
@@ -9366,11 +8532,8 @@
       <c r="M160" t="str">
         <v/>
       </c>
-      <c r="N160" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O160" s="1">
-        <f>IF(AND(N160&lt;&gt;"",E160&lt;&gt;""),N160+E160-1,"")</f>
+      <c r="N160" t="str">
+        <v/>
       </c>
       <c r="P160" t="str">
         <v/>
@@ -9389,11 +8552,8 @@
       <c r="B161" t="str">
         <v>Kitchens: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C161" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D161" s="1">
-        <f>IF(AND(C161&lt;&gt;"",E161&lt;&gt;""),C161+E161-1,"")</f>
+      <c r="C161" t="str">
+        <v/>
       </c>
       <c r="E161">
         <v>2</v>
@@ -9422,11 +8582,8 @@
       <c r="M161" t="str">
         <v/>
       </c>
-      <c r="N161" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O161" s="1">
-        <f>IF(AND(N161&lt;&gt;"",E161&lt;&gt;""),N161+E161-1,"")</f>
+      <c r="N161" t="str">
+        <v/>
       </c>
       <c r="P161" t="str">
         <v/>
@@ -9445,10 +8602,10 @@
       <c r="B162" t="str">
         <v>EXECUTE • Bathrooms</v>
       </c>
-      <c r="C162" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D162" s="1" t="str">
+      <c r="C162" t="str">
+        <v/>
+      </c>
+      <c r="D162" t="str">
         <v/>
       </c>
       <c r="E162" t="str">
@@ -9478,10 +8635,10 @@
       <c r="M162" t="str">
         <v/>
       </c>
-      <c r="N162" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O162" s="1" t="str">
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
         <v/>
       </c>
       <c r="P162" t="str">
@@ -9501,11 +8658,8 @@
       <c r="B163" t="str">
         <v>Bathrooms: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C163" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D163" s="1">
-        <f>IF(AND(C163&lt;&gt;"",E163&lt;&gt;""),C163+E163-1,"")</f>
+      <c r="C163" t="str">
+        <v/>
       </c>
       <c r="E163">
         <v>2</v>
@@ -9534,11 +8688,8 @@
       <c r="M163" t="str">
         <v/>
       </c>
-      <c r="N163" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O163" s="1">
-        <f>IF(AND(N163&lt;&gt;"",E163&lt;&gt;""),N163+E163-1,"")</f>
+      <c r="N163" t="str">
+        <v/>
       </c>
       <c r="P163" t="str">
         <v/>
@@ -9557,11 +8708,8 @@
       <c r="B164" t="str">
         <v>Bathrooms: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C164" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D164" s="1">
-        <f>IF(AND(C164&lt;&gt;"",E164&lt;&gt;""),C164+E164-1,"")</f>
+      <c r="C164" t="str">
+        <v/>
       </c>
       <c r="E164">
         <v>7</v>
@@ -9590,11 +8738,8 @@
       <c r="M164" t="str">
         <v/>
       </c>
-      <c r="N164" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O164" s="1">
-        <f>IF(AND(N164&lt;&gt;"",E164&lt;&gt;""),N164+E164-1,"")</f>
+      <c r="N164" t="str">
+        <v/>
       </c>
       <c r="P164" t="str">
         <v/>
@@ -9613,11 +8758,8 @@
       <c r="B165" t="str">
         <v>Bathrooms: Delivery to Site</v>
       </c>
-      <c r="C165" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D165" s="1">
-        <f>IF(AND(C165&lt;&gt;"",E165&lt;&gt;""),C165+E165-1,"")</f>
+      <c r="C165" t="str">
+        <v/>
       </c>
       <c r="E165">
         <v>1</v>
@@ -9646,11 +8788,8 @@
       <c r="M165" t="str">
         <v/>
       </c>
-      <c r="N165" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O165" s="1">
-        <f>IF(AND(N165&lt;&gt;"",E165&lt;&gt;""),N165+E165-1,"")</f>
+      <c r="N165" t="str">
+        <v/>
       </c>
       <c r="P165" t="str">
         <v/>
@@ -9669,11 +8808,8 @@
       <c r="B166" t="str">
         <v>Bathrooms: Installation / Execution</v>
       </c>
-      <c r="C166" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D166" s="1">
-        <f>IF(AND(C166&lt;&gt;"",E166&lt;&gt;""),C166+E166-1,"")</f>
+      <c r="C166" t="str">
+        <v/>
       </c>
       <c r="E166">
         <v>5</v>
@@ -9702,11 +8838,8 @@
       <c r="M166" t="str">
         <v/>
       </c>
-      <c r="N166" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O166" s="1">
-        <f>IF(AND(N166&lt;&gt;"",E166&lt;&gt;""),N166+E166-1,"")</f>
+      <c r="N166" t="str">
+        <v/>
       </c>
       <c r="P166" t="str">
         <v/>
@@ -9725,11 +8858,8 @@
       <c r="B167" t="str">
         <v>Bathrooms: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C167" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D167" s="1">
-        <f>IF(AND(C167&lt;&gt;"",E167&lt;&gt;""),C167+E167-1,"")</f>
+      <c r="C167" t="str">
+        <v/>
       </c>
       <c r="E167">
         <v>2</v>
@@ -9758,11 +8888,8 @@
       <c r="M167" t="str">
         <v/>
       </c>
-      <c r="N167" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O167" s="1">
-        <f>IF(AND(N167&lt;&gt;"",E167&lt;&gt;""),N167+E167-1,"")</f>
+      <c r="N167" t="str">
+        <v/>
       </c>
       <c r="P167" t="str">
         <v/>
@@ -9781,10 +8908,10 @@
       <c r="B168" t="str">
         <v>EXECUTE • Audio</v>
       </c>
-      <c r="C168" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D168" s="1" t="str">
+      <c r="C168" t="str">
+        <v/>
+      </c>
+      <c r="D168" t="str">
         <v/>
       </c>
       <c r="E168" t="str">
@@ -9814,10 +8941,10 @@
       <c r="M168" t="str">
         <v/>
       </c>
-      <c r="N168" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O168" s="1" t="str">
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
         <v/>
       </c>
       <c r="P168" t="str">
@@ -9837,11 +8964,8 @@
       <c r="B169" t="str">
         <v>Audio: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C169" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D169" s="1">
-        <f>IF(AND(C169&lt;&gt;"",E169&lt;&gt;""),C169+E169-1,"")</f>
+      <c r="C169" t="str">
+        <v/>
       </c>
       <c r="E169">
         <v>2</v>
@@ -9870,11 +8994,8 @@
       <c r="M169" t="str">
         <v/>
       </c>
-      <c r="N169" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O169" s="1">
-        <f>IF(AND(N169&lt;&gt;"",E169&lt;&gt;""),N169+E169-1,"")</f>
+      <c r="N169" t="str">
+        <v/>
       </c>
       <c r="P169" t="str">
         <v/>
@@ -9893,11 +9014,8 @@
       <c r="B170" t="str">
         <v>Audio: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C170" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D170" s="1">
-        <f>IF(AND(C170&lt;&gt;"",E170&lt;&gt;""),C170+E170-1,"")</f>
+      <c r="C170" t="str">
+        <v/>
       </c>
       <c r="E170">
         <v>7</v>
@@ -9926,11 +9044,8 @@
       <c r="M170" t="str">
         <v/>
       </c>
-      <c r="N170" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O170" s="1">
-        <f>IF(AND(N170&lt;&gt;"",E170&lt;&gt;""),N170+E170-1,"")</f>
+      <c r="N170" t="str">
+        <v/>
       </c>
       <c r="P170" t="str">
         <v/>
@@ -9949,11 +9064,8 @@
       <c r="B171" t="str">
         <v>Audio: Delivery to Site</v>
       </c>
-      <c r="C171" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D171" s="1">
-        <f>IF(AND(C171&lt;&gt;"",E171&lt;&gt;""),C171+E171-1,"")</f>
+      <c r="C171" t="str">
+        <v/>
       </c>
       <c r="E171">
         <v>1</v>
@@ -9982,11 +9094,8 @@
       <c r="M171" t="str">
         <v/>
       </c>
-      <c r="N171" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O171" s="1">
-        <f>IF(AND(N171&lt;&gt;"",E171&lt;&gt;""),N171+E171-1,"")</f>
+      <c r="N171" t="str">
+        <v/>
       </c>
       <c r="P171" t="str">
         <v/>
@@ -10005,11 +9114,8 @@
       <c r="B172" t="str">
         <v>Audio: Installation / Execution</v>
       </c>
-      <c r="C172" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D172" s="1">
-        <f>IF(AND(C172&lt;&gt;"",E172&lt;&gt;""),C172+E172-1,"")</f>
+      <c r="C172" t="str">
+        <v/>
       </c>
       <c r="E172">
         <v>5</v>
@@ -10038,11 +9144,8 @@
       <c r="M172" t="str">
         <v/>
       </c>
-      <c r="N172" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O172" s="1">
-        <f>IF(AND(N172&lt;&gt;"",E172&lt;&gt;""),N172+E172-1,"")</f>
+      <c r="N172" t="str">
+        <v/>
       </c>
       <c r="P172" t="str">
         <v/>
@@ -10061,11 +9164,8 @@
       <c r="B173" t="str">
         <v>Audio: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C173" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D173" s="1">
-        <f>IF(AND(C173&lt;&gt;"",E173&lt;&gt;""),C173+E173-1,"")</f>
+      <c r="C173" t="str">
+        <v/>
       </c>
       <c r="E173">
         <v>2</v>
@@ -10094,11 +9194,8 @@
       <c r="M173" t="str">
         <v/>
       </c>
-      <c r="N173" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O173" s="1">
-        <f>IF(AND(N173&lt;&gt;"",E173&lt;&gt;""),N173+E173-1,"")</f>
+      <c r="N173" t="str">
+        <v/>
       </c>
       <c r="P173" t="str">
         <v/>
@@ -10117,10 +9214,10 @@
       <c r="B174" t="str">
         <v>EXECUTE • Automation</v>
       </c>
-      <c r="C174" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D174" s="1" t="str">
+      <c r="C174" t="str">
+        <v/>
+      </c>
+      <c r="D174" t="str">
         <v/>
       </c>
       <c r="E174" t="str">
@@ -10150,10 +9247,10 @@
       <c r="M174" t="str">
         <v/>
       </c>
-      <c r="N174" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O174" s="1" t="str">
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
         <v/>
       </c>
       <c r="P174" t="str">
@@ -10173,11 +9270,8 @@
       <c r="B175" t="str">
         <v>Automation: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C175" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D175" s="1">
-        <f>IF(AND(C175&lt;&gt;"",E175&lt;&gt;""),C175+E175-1,"")</f>
+      <c r="C175" t="str">
+        <v/>
       </c>
       <c r="E175">
         <v>2</v>
@@ -10206,11 +9300,8 @@
       <c r="M175" t="str">
         <v/>
       </c>
-      <c r="N175" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O175" s="1">
-        <f>IF(AND(N175&lt;&gt;"",E175&lt;&gt;""),N175+E175-1,"")</f>
+      <c r="N175" t="str">
+        <v/>
       </c>
       <c r="P175" t="str">
         <v/>
@@ -10229,11 +9320,8 @@
       <c r="B176" t="str">
         <v>Automation: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C176" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D176" s="1">
-        <f>IF(AND(C176&lt;&gt;"",E176&lt;&gt;""),C176+E176-1,"")</f>
+      <c r="C176" t="str">
+        <v/>
       </c>
       <c r="E176">
         <v>7</v>
@@ -10262,11 +9350,8 @@
       <c r="M176" t="str">
         <v/>
       </c>
-      <c r="N176" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O176" s="1">
-        <f>IF(AND(N176&lt;&gt;"",E176&lt;&gt;""),N176+E176-1,"")</f>
+      <c r="N176" t="str">
+        <v/>
       </c>
       <c r="P176" t="str">
         <v/>
@@ -10285,11 +9370,8 @@
       <c r="B177" t="str">
         <v>Automation: Delivery to Site</v>
       </c>
-      <c r="C177" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D177" s="1">
-        <f>IF(AND(C177&lt;&gt;"",E177&lt;&gt;""),C177+E177-1,"")</f>
+      <c r="C177" t="str">
+        <v/>
       </c>
       <c r="E177">
         <v>1</v>
@@ -10318,11 +9400,8 @@
       <c r="M177" t="str">
         <v/>
       </c>
-      <c r="N177" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O177" s="1">
-        <f>IF(AND(N177&lt;&gt;"",E177&lt;&gt;""),N177+E177-1,"")</f>
+      <c r="N177" t="str">
+        <v/>
       </c>
       <c r="P177" t="str">
         <v/>
@@ -10341,11 +9420,8 @@
       <c r="B178" t="str">
         <v>Automation: Installation / Execution</v>
       </c>
-      <c r="C178" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D178" s="1">
-        <f>IF(AND(C178&lt;&gt;"",E178&lt;&gt;""),C178+E178-1,"")</f>
+      <c r="C178" t="str">
+        <v/>
       </c>
       <c r="E178">
         <v>5</v>
@@ -10374,11 +9450,8 @@
       <c r="M178" t="str">
         <v/>
       </c>
-      <c r="N178" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O178" s="1">
-        <f>IF(AND(N178&lt;&gt;"",E178&lt;&gt;""),N178+E178-1,"")</f>
+      <c r="N178" t="str">
+        <v/>
       </c>
       <c r="P178" t="str">
         <v/>
@@ -10397,11 +9470,8 @@
       <c r="B179" t="str">
         <v>Automation: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C179" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D179" s="1">
-        <f>IF(AND(C179&lt;&gt;"",E179&lt;&gt;""),C179+E179-1,"")</f>
+      <c r="C179" t="str">
+        <v/>
       </c>
       <c r="E179">
         <v>2</v>
@@ -10430,11 +9500,8 @@
       <c r="M179" t="str">
         <v/>
       </c>
-      <c r="N179" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O179" s="1">
-        <f>IF(AND(N179&lt;&gt;"",E179&lt;&gt;""),N179+E179-1,"")</f>
+      <c r="N179" t="str">
+        <v/>
       </c>
       <c r="P179" t="str">
         <v/>
@@ -10453,10 +9520,10 @@
       <c r="B180" t="str">
         <v>EXECUTE • Lighting</v>
       </c>
-      <c r="C180" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D180" s="1" t="str">
+      <c r="C180" t="str">
+        <v/>
+      </c>
+      <c r="D180" t="str">
         <v/>
       </c>
       <c r="E180" t="str">
@@ -10486,10 +9553,10 @@
       <c r="M180" t="str">
         <v/>
       </c>
-      <c r="N180" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O180" s="1" t="str">
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
         <v/>
       </c>
       <c r="P180" t="str">
@@ -10509,11 +9576,8 @@
       <c r="B181" t="str">
         <v>Lighting: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C181" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D181" s="1">
-        <f>IF(AND(C181&lt;&gt;"",E181&lt;&gt;""),C181+E181-1,"")</f>
+      <c r="C181" t="str">
+        <v/>
       </c>
       <c r="E181">
         <v>2</v>
@@ -10542,11 +9606,8 @@
       <c r="M181" t="str">
         <v/>
       </c>
-      <c r="N181" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O181" s="1">
-        <f>IF(AND(N181&lt;&gt;"",E181&lt;&gt;""),N181+E181-1,"")</f>
+      <c r="N181" t="str">
+        <v/>
       </c>
       <c r="P181" t="str">
         <v/>
@@ -10565,11 +9626,8 @@
       <c r="B182" t="str">
         <v>Lighting: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C182" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D182" s="1">
-        <f>IF(AND(C182&lt;&gt;"",E182&lt;&gt;""),C182+E182-1,"")</f>
+      <c r="C182" t="str">
+        <v/>
       </c>
       <c r="E182">
         <v>7</v>
@@ -10598,11 +9656,8 @@
       <c r="M182" t="str">
         <v/>
       </c>
-      <c r="N182" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O182" s="1">
-        <f>IF(AND(N182&lt;&gt;"",E182&lt;&gt;""),N182+E182-1,"")</f>
+      <c r="N182" t="str">
+        <v/>
       </c>
       <c r="P182" t="str">
         <v/>
@@ -10621,11 +9676,8 @@
       <c r="B183" t="str">
         <v>Lighting: Delivery to Site</v>
       </c>
-      <c r="C183" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D183" s="1">
-        <f>IF(AND(C183&lt;&gt;"",E183&lt;&gt;""),C183+E183-1,"")</f>
+      <c r="C183" t="str">
+        <v/>
       </c>
       <c r="E183">
         <v>1</v>
@@ -10654,11 +9706,8 @@
       <c r="M183" t="str">
         <v/>
       </c>
-      <c r="N183" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O183" s="1">
-        <f>IF(AND(N183&lt;&gt;"",E183&lt;&gt;""),N183+E183-1,"")</f>
+      <c r="N183" t="str">
+        <v/>
       </c>
       <c r="P183" t="str">
         <v/>
@@ -10677,11 +9726,8 @@
       <c r="B184" t="str">
         <v>Lighting: Installation / Execution</v>
       </c>
-      <c r="C184" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D184" s="1">
-        <f>IF(AND(C184&lt;&gt;"",E184&lt;&gt;""),C184+E184-1,"")</f>
+      <c r="C184" t="str">
+        <v/>
       </c>
       <c r="E184">
         <v>5</v>
@@ -10710,11 +9756,8 @@
       <c r="M184" t="str">
         <v/>
       </c>
-      <c r="N184" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O184" s="1">
-        <f>IF(AND(N184&lt;&gt;"",E184&lt;&gt;""),N184+E184-1,"")</f>
+      <c r="N184" t="str">
+        <v/>
       </c>
       <c r="P184" t="str">
         <v/>
@@ -10733,11 +9776,8 @@
       <c r="B185" t="str">
         <v>Lighting: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C185" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D185" s="1">
-        <f>IF(AND(C185&lt;&gt;"",E185&lt;&gt;""),C185+E185-1,"")</f>
+      <c r="C185" t="str">
+        <v/>
       </c>
       <c r="E185">
         <v>2</v>
@@ -10766,11 +9806,8 @@
       <c r="M185" t="str">
         <v/>
       </c>
-      <c r="N185" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O185" s="1">
-        <f>IF(AND(N185&lt;&gt;"",E185&lt;&gt;""),N185+E185-1,"")</f>
+      <c r="N185" t="str">
+        <v/>
       </c>
       <c r="P185" t="str">
         <v/>
@@ -10789,10 +9826,10 @@
       <c r="B186" t="str">
         <v>EXECUTE • HVAC</v>
       </c>
-      <c r="C186" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D186" s="1" t="str">
+      <c r="C186" t="str">
+        <v/>
+      </c>
+      <c r="D186" t="str">
         <v/>
       </c>
       <c r="E186" t="str">
@@ -10822,10 +9859,10 @@
       <c r="M186" t="str">
         <v/>
       </c>
-      <c r="N186" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O186" s="1" t="str">
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
         <v/>
       </c>
       <c r="P186" t="str">
@@ -10845,11 +9882,8 @@
       <c r="B187" t="str">
         <v>HVAC: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C187" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D187" s="1">
-        <f>IF(AND(C187&lt;&gt;"",E187&lt;&gt;""),C187+E187-1,"")</f>
+      <c r="C187" t="str">
+        <v/>
       </c>
       <c r="E187">
         <v>2</v>
@@ -10878,11 +9912,8 @@
       <c r="M187" t="str">
         <v/>
       </c>
-      <c r="N187" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O187" s="1">
-        <f>IF(AND(N187&lt;&gt;"",E187&lt;&gt;""),N187+E187-1,"")</f>
+      <c r="N187" t="str">
+        <v/>
       </c>
       <c r="P187" t="str">
         <v/>
@@ -10901,11 +9932,8 @@
       <c r="B188" t="str">
         <v>HVAC: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C188" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D188" s="1">
-        <f>IF(AND(C188&lt;&gt;"",E188&lt;&gt;""),C188+E188-1,"")</f>
+      <c r="C188" t="str">
+        <v/>
       </c>
       <c r="E188">
         <v>7</v>
@@ -10934,11 +9962,8 @@
       <c r="M188" t="str">
         <v/>
       </c>
-      <c r="N188" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O188" s="1">
-        <f>IF(AND(N188&lt;&gt;"",E188&lt;&gt;""),N188+E188-1,"")</f>
+      <c r="N188" t="str">
+        <v/>
       </c>
       <c r="P188" t="str">
         <v/>
@@ -10957,11 +9982,8 @@
       <c r="B189" t="str">
         <v>HVAC: Delivery to Site</v>
       </c>
-      <c r="C189" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D189" s="1">
-        <f>IF(AND(C189&lt;&gt;"",E189&lt;&gt;""),C189+E189-1,"")</f>
+      <c r="C189" t="str">
+        <v/>
       </c>
       <c r="E189">
         <v>1</v>
@@ -10990,11 +10012,8 @@
       <c r="M189" t="str">
         <v/>
       </c>
-      <c r="N189" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O189" s="1">
-        <f>IF(AND(N189&lt;&gt;"",E189&lt;&gt;""),N189+E189-1,"")</f>
+      <c r="N189" t="str">
+        <v/>
       </c>
       <c r="P189" t="str">
         <v/>
@@ -11013,11 +10032,8 @@
       <c r="B190" t="str">
         <v>HVAC: Installation / Execution</v>
       </c>
-      <c r="C190" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D190" s="1">
-        <f>IF(AND(C190&lt;&gt;"",E190&lt;&gt;""),C190+E190-1,"")</f>
+      <c r="C190" t="str">
+        <v/>
       </c>
       <c r="E190">
         <v>5</v>
@@ -11046,11 +10062,8 @@
       <c r="M190" t="str">
         <v/>
       </c>
-      <c r="N190" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O190" s="1">
-        <f>IF(AND(N190&lt;&gt;"",E190&lt;&gt;""),N190+E190-1,"")</f>
+      <c r="N190" t="str">
+        <v/>
       </c>
       <c r="P190" t="str">
         <v/>
@@ -11069,11 +10082,8 @@
       <c r="B191" t="str">
         <v>HVAC: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C191" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D191" s="1">
-        <f>IF(AND(C191&lt;&gt;"",E191&lt;&gt;""),C191+E191-1,"")</f>
+      <c r="C191" t="str">
+        <v/>
       </c>
       <c r="E191">
         <v>2</v>
@@ -11102,11 +10112,8 @@
       <c r="M191" t="str">
         <v/>
       </c>
-      <c r="N191" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O191" s="1">
-        <f>IF(AND(N191&lt;&gt;"",E191&lt;&gt;""),N191+E191-1,"")</f>
+      <c r="N191" t="str">
+        <v/>
       </c>
       <c r="P191" t="str">
         <v/>
@@ -11125,10 +10132,10 @@
       <c r="B192" t="str">
         <v>EXECUTE • Doors &amp; Windows</v>
       </c>
-      <c r="C192" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D192" s="1" t="str">
+      <c r="C192" t="str">
+        <v/>
+      </c>
+      <c r="D192" t="str">
         <v/>
       </c>
       <c r="E192" t="str">
@@ -11158,10 +10165,10 @@
       <c r="M192" t="str">
         <v/>
       </c>
-      <c r="N192" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O192" s="1" t="str">
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
         <v/>
       </c>
       <c r="P192" t="str">
@@ -11181,11 +10188,8 @@
       <c r="B193" t="str">
         <v>Doors &amp; Windows: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C193" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D193" s="1">
-        <f>IF(AND(C193&lt;&gt;"",E193&lt;&gt;""),C193+E193-1,"")</f>
+      <c r="C193" t="str">
+        <v/>
       </c>
       <c r="E193">
         <v>2</v>
@@ -11214,11 +10218,8 @@
       <c r="M193" t="str">
         <v/>
       </c>
-      <c r="N193" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O193" s="1">
-        <f>IF(AND(N193&lt;&gt;"",E193&lt;&gt;""),N193+E193-1,"")</f>
+      <c r="N193" t="str">
+        <v/>
       </c>
       <c r="P193" t="str">
         <v/>
@@ -11237,11 +10238,8 @@
       <c r="B194" t="str">
         <v>Doors &amp; Windows: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C194" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D194" s="1">
-        <f>IF(AND(C194&lt;&gt;"",E194&lt;&gt;""),C194+E194-1,"")</f>
+      <c r="C194" t="str">
+        <v/>
       </c>
       <c r="E194">
         <v>7</v>
@@ -11270,11 +10268,8 @@
       <c r="M194" t="str">
         <v/>
       </c>
-      <c r="N194" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O194" s="1">
-        <f>IF(AND(N194&lt;&gt;"",E194&lt;&gt;""),N194+E194-1,"")</f>
+      <c r="N194" t="str">
+        <v/>
       </c>
       <c r="P194" t="str">
         <v/>
@@ -11293,11 +10288,8 @@
       <c r="B195" t="str">
         <v>Doors &amp; Windows: Delivery to Site</v>
       </c>
-      <c r="C195" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D195" s="1">
-        <f>IF(AND(C195&lt;&gt;"",E195&lt;&gt;""),C195+E195-1,"")</f>
+      <c r="C195" t="str">
+        <v/>
       </c>
       <c r="E195">
         <v>1</v>
@@ -11326,11 +10318,8 @@
       <c r="M195" t="str">
         <v/>
       </c>
-      <c r="N195" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O195" s="1">
-        <f>IF(AND(N195&lt;&gt;"",E195&lt;&gt;""),N195+E195-1,"")</f>
+      <c r="N195" t="str">
+        <v/>
       </c>
       <c r="P195" t="str">
         <v/>
@@ -11349,11 +10338,8 @@
       <c r="B196" t="str">
         <v>Doors &amp; Windows: Installation / Execution</v>
       </c>
-      <c r="C196" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D196" s="1">
-        <f>IF(AND(C196&lt;&gt;"",E196&lt;&gt;""),C196+E196-1,"")</f>
+      <c r="C196" t="str">
+        <v/>
       </c>
       <c r="E196">
         <v>5</v>
@@ -11382,11 +10368,8 @@
       <c r="M196" t="str">
         <v/>
       </c>
-      <c r="N196" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O196" s="1">
-        <f>IF(AND(N196&lt;&gt;"",E196&lt;&gt;""),N196+E196-1,"")</f>
+      <c r="N196" t="str">
+        <v/>
       </c>
       <c r="P196" t="str">
         <v/>
@@ -11405,11 +10388,8 @@
       <c r="B197" t="str">
         <v>Doors &amp; Windows: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C197" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D197" s="1">
-        <f>IF(AND(C197&lt;&gt;"",E197&lt;&gt;""),C197+E197-1,"")</f>
+      <c r="C197" t="str">
+        <v/>
       </c>
       <c r="E197">
         <v>2</v>
@@ -11438,11 +10418,8 @@
       <c r="M197" t="str">
         <v/>
       </c>
-      <c r="N197" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O197" s="1">
-        <f>IF(AND(N197&lt;&gt;"",E197&lt;&gt;""),N197+E197-1,"")</f>
+      <c r="N197" t="str">
+        <v/>
       </c>
       <c r="P197" t="str">
         <v/>
@@ -11461,10 +10438,10 @@
       <c r="B198" t="str">
         <v>EXECUTE • Wall Finishes</v>
       </c>
-      <c r="C198" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D198" s="1" t="str">
+      <c r="C198" t="str">
+        <v/>
+      </c>
+      <c r="D198" t="str">
         <v/>
       </c>
       <c r="E198" t="str">
@@ -11494,10 +10471,10 @@
       <c r="M198" t="str">
         <v/>
       </c>
-      <c r="N198" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O198" s="1" t="str">
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
         <v/>
       </c>
       <c r="P198" t="str">
@@ -11517,11 +10494,8 @@
       <c r="B199" t="str">
         <v>Wall Finishes: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C199" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D199" s="1">
-        <f>IF(AND(C199&lt;&gt;"",E199&lt;&gt;""),C199+E199-1,"")</f>
+      <c r="C199" t="str">
+        <v/>
       </c>
       <c r="E199">
         <v>2</v>
@@ -11550,11 +10524,8 @@
       <c r="M199" t="str">
         <v/>
       </c>
-      <c r="N199" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O199" s="1">
-        <f>IF(AND(N199&lt;&gt;"",E199&lt;&gt;""),N199+E199-1,"")</f>
+      <c r="N199" t="str">
+        <v/>
       </c>
       <c r="P199" t="str">
         <v/>
@@ -11573,11 +10544,8 @@
       <c r="B200" t="str">
         <v>Wall Finishes: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C200" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D200" s="1">
-        <f>IF(AND(C200&lt;&gt;"",E200&lt;&gt;""),C200+E200-1,"")</f>
+      <c r="C200" t="str">
+        <v/>
       </c>
       <c r="E200">
         <v>7</v>
@@ -11606,11 +10574,8 @@
       <c r="M200" t="str">
         <v/>
       </c>
-      <c r="N200" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O200" s="1">
-        <f>IF(AND(N200&lt;&gt;"",E200&lt;&gt;""),N200+E200-1,"")</f>
+      <c r="N200" t="str">
+        <v/>
       </c>
       <c r="P200" t="str">
         <v/>
@@ -11629,11 +10594,8 @@
       <c r="B201" t="str">
         <v>Wall Finishes: Delivery to Site</v>
       </c>
-      <c r="C201" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D201" s="1">
-        <f>IF(AND(C201&lt;&gt;"",E201&lt;&gt;""),C201+E201-1,"")</f>
+      <c r="C201" t="str">
+        <v/>
       </c>
       <c r="E201">
         <v>1</v>
@@ -11662,11 +10624,8 @@
       <c r="M201" t="str">
         <v/>
       </c>
-      <c r="N201" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O201" s="1">
-        <f>IF(AND(N201&lt;&gt;"",E201&lt;&gt;""),N201+E201-1,"")</f>
+      <c r="N201" t="str">
+        <v/>
       </c>
       <c r="P201" t="str">
         <v/>
@@ -11685,11 +10644,8 @@
       <c r="B202" t="str">
         <v>Wall Finishes: Installation / Execution</v>
       </c>
-      <c r="C202" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D202" s="1">
-        <f>IF(AND(C202&lt;&gt;"",E202&lt;&gt;""),C202+E202-1,"")</f>
+      <c r="C202" t="str">
+        <v/>
       </c>
       <c r="E202">
         <v>5</v>
@@ -11718,11 +10674,8 @@
       <c r="M202" t="str">
         <v/>
       </c>
-      <c r="N202" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O202" s="1">
-        <f>IF(AND(N202&lt;&gt;"",E202&lt;&gt;""),N202+E202-1,"")</f>
+      <c r="N202" t="str">
+        <v/>
       </c>
       <c r="P202" t="str">
         <v/>
@@ -11741,11 +10694,8 @@
       <c r="B203" t="str">
         <v>Wall Finishes: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C203" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D203" s="1">
-        <f>IF(AND(C203&lt;&gt;"",E203&lt;&gt;""),C203+E203-1,"")</f>
+      <c r="C203" t="str">
+        <v/>
       </c>
       <c r="E203">
         <v>2</v>
@@ -11774,11 +10724,8 @@
       <c r="M203" t="str">
         <v/>
       </c>
-      <c r="N203" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O203" s="1">
-        <f>IF(AND(N203&lt;&gt;"",E203&lt;&gt;""),N203+E203-1,"")</f>
+      <c r="N203" t="str">
+        <v/>
       </c>
       <c r="P203" t="str">
         <v/>
@@ -11797,10 +10744,10 @@
       <c r="B204" t="str">
         <v>EXECUTE • Furnishing</v>
       </c>
-      <c r="C204" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D204" s="1" t="str">
+      <c r="C204" t="str">
+        <v/>
+      </c>
+      <c r="D204" t="str">
         <v/>
       </c>
       <c r="E204" t="str">
@@ -11830,10 +10777,10 @@
       <c r="M204" t="str">
         <v/>
       </c>
-      <c r="N204" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O204" s="1" t="str">
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
         <v/>
       </c>
       <c r="P204" t="str">
@@ -11853,11 +10800,8 @@
       <c r="B205" t="str">
         <v>Furnishing: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C205" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D205" s="1">
-        <f>IF(AND(C205&lt;&gt;"",E205&lt;&gt;""),C205+E205-1,"")</f>
+      <c r="C205" t="str">
+        <v/>
       </c>
       <c r="E205">
         <v>2</v>
@@ -11886,11 +10830,8 @@
       <c r="M205" t="str">
         <v/>
       </c>
-      <c r="N205" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O205" s="1">
-        <f>IF(AND(N205&lt;&gt;"",E205&lt;&gt;""),N205+E205-1,"")</f>
+      <c r="N205" t="str">
+        <v/>
       </c>
       <c r="P205" t="str">
         <v/>
@@ -11909,11 +10850,8 @@
       <c r="B206" t="str">
         <v>Furnishing: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C206" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D206" s="1">
-        <f>IF(AND(C206&lt;&gt;"",E206&lt;&gt;""),C206+E206-1,"")</f>
+      <c r="C206" t="str">
+        <v/>
       </c>
       <c r="E206">
         <v>7</v>
@@ -11942,11 +10880,8 @@
       <c r="M206" t="str">
         <v/>
       </c>
-      <c r="N206" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O206" s="1">
-        <f>IF(AND(N206&lt;&gt;"",E206&lt;&gt;""),N206+E206-1,"")</f>
+      <c r="N206" t="str">
+        <v/>
       </c>
       <c r="P206" t="str">
         <v/>
@@ -11965,11 +10900,8 @@
       <c r="B207" t="str">
         <v>Furnishing: Delivery to Site</v>
       </c>
-      <c r="C207" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D207" s="1">
-        <f>IF(AND(C207&lt;&gt;"",E207&lt;&gt;""),C207+E207-1,"")</f>
+      <c r="C207" t="str">
+        <v/>
       </c>
       <c r="E207">
         <v>1</v>
@@ -11998,11 +10930,8 @@
       <c r="M207" t="str">
         <v/>
       </c>
-      <c r="N207" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O207" s="1">
-        <f>IF(AND(N207&lt;&gt;"",E207&lt;&gt;""),N207+E207-1,"")</f>
+      <c r="N207" t="str">
+        <v/>
       </c>
       <c r="P207" t="str">
         <v/>
@@ -12021,11 +10950,8 @@
       <c r="B208" t="str">
         <v>Furnishing: Installation / Execution</v>
       </c>
-      <c r="C208" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D208" s="1">
-        <f>IF(AND(C208&lt;&gt;"",E208&lt;&gt;""),C208+E208-1,"")</f>
+      <c r="C208" t="str">
+        <v/>
       </c>
       <c r="E208">
         <v>5</v>
@@ -12054,11 +10980,8 @@
       <c r="M208" t="str">
         <v/>
       </c>
-      <c r="N208" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O208" s="1">
-        <f>IF(AND(N208&lt;&gt;"",E208&lt;&gt;""),N208+E208-1,"")</f>
+      <c r="N208" t="str">
+        <v/>
       </c>
       <c r="P208" t="str">
         <v/>
@@ -12077,11 +11000,8 @@
       <c r="B209" t="str">
         <v>Furnishing: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C209" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D209" s="1">
-        <f>IF(AND(C209&lt;&gt;"",E209&lt;&gt;""),C209+E209-1,"")</f>
+      <c r="C209" t="str">
+        <v/>
       </c>
       <c r="E209">
         <v>2</v>
@@ -12110,11 +11030,8 @@
       <c r="M209" t="str">
         <v/>
       </c>
-      <c r="N209" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O209" s="1">
-        <f>IF(AND(N209&lt;&gt;"",E209&lt;&gt;""),N209+E209-1,"")</f>
+      <c r="N209" t="str">
+        <v/>
       </c>
       <c r="P209" t="str">
         <v/>
@@ -12133,10 +11050,10 @@
       <c r="B210" t="str">
         <v>EXECUTE • Soft Furnishing</v>
       </c>
-      <c r="C210" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D210" s="1" t="str">
+      <c r="C210" t="str">
+        <v/>
+      </c>
+      <c r="D210" t="str">
         <v/>
       </c>
       <c r="E210" t="str">
@@ -12166,10 +11083,10 @@
       <c r="M210" t="str">
         <v/>
       </c>
-      <c r="N210" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O210" s="1" t="str">
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
         <v/>
       </c>
       <c r="P210" t="str">
@@ -12189,11 +11106,8 @@
       <c r="B211" t="str">
         <v>Soft Furnishing: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C211" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D211" s="1">
-        <f>IF(AND(C211&lt;&gt;"",E211&lt;&gt;""),C211+E211-1,"")</f>
+      <c r="C211" t="str">
+        <v/>
       </c>
       <c r="E211">
         <v>2</v>
@@ -12222,11 +11136,8 @@
       <c r="M211" t="str">
         <v/>
       </c>
-      <c r="N211" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O211" s="1">
-        <f>IF(AND(N211&lt;&gt;"",E211&lt;&gt;""),N211+E211-1,"")</f>
+      <c r="N211" t="str">
+        <v/>
       </c>
       <c r="P211" t="str">
         <v/>
@@ -12245,11 +11156,8 @@
       <c r="B212" t="str">
         <v>Soft Furnishing: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C212" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D212" s="1">
-        <f>IF(AND(C212&lt;&gt;"",E212&lt;&gt;""),C212+E212-1,"")</f>
+      <c r="C212" t="str">
+        <v/>
       </c>
       <c r="E212">
         <v>7</v>
@@ -12278,11 +11186,8 @@
       <c r="M212" t="str">
         <v/>
       </c>
-      <c r="N212" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O212" s="1">
-        <f>IF(AND(N212&lt;&gt;"",E212&lt;&gt;""),N212+E212-1,"")</f>
+      <c r="N212" t="str">
+        <v/>
       </c>
       <c r="P212" t="str">
         <v/>
@@ -12301,11 +11206,8 @@
       <c r="B213" t="str">
         <v>Soft Furnishing: Delivery to Site</v>
       </c>
-      <c r="C213" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D213" s="1">
-        <f>IF(AND(C213&lt;&gt;"",E213&lt;&gt;""),C213+E213-1,"")</f>
+      <c r="C213" t="str">
+        <v/>
       </c>
       <c r="E213">
         <v>1</v>
@@ -12334,11 +11236,8 @@
       <c r="M213" t="str">
         <v/>
       </c>
-      <c r="N213" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O213" s="1">
-        <f>IF(AND(N213&lt;&gt;"",E213&lt;&gt;""),N213+E213-1,"")</f>
+      <c r="N213" t="str">
+        <v/>
       </c>
       <c r="P213" t="str">
         <v/>
@@ -12357,11 +11256,8 @@
       <c r="B214" t="str">
         <v>Soft Furnishing: Installation / Execution</v>
       </c>
-      <c r="C214" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D214" s="1">
-        <f>IF(AND(C214&lt;&gt;"",E214&lt;&gt;""),C214+E214-1,"")</f>
+      <c r="C214" t="str">
+        <v/>
       </c>
       <c r="E214">
         <v>5</v>
@@ -12390,11 +11286,8 @@
       <c r="M214" t="str">
         <v/>
       </c>
-      <c r="N214" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O214" s="1">
-        <f>IF(AND(N214&lt;&gt;"",E214&lt;&gt;""),N214+E214-1,"")</f>
+      <c r="N214" t="str">
+        <v/>
       </c>
       <c r="P214" t="str">
         <v/>
@@ -12413,11 +11306,8 @@
       <c r="B215" t="str">
         <v>Soft Furnishing: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C215" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D215" s="1">
-        <f>IF(AND(C215&lt;&gt;"",E215&lt;&gt;""),C215+E215-1,"")</f>
+      <c r="C215" t="str">
+        <v/>
       </c>
       <c r="E215">
         <v>2</v>
@@ -12446,11 +11336,8 @@
       <c r="M215" t="str">
         <v/>
       </c>
-      <c r="N215" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O215" s="1">
-        <f>IF(AND(N215&lt;&gt;"",E215&lt;&gt;""),N215+E215-1,"")</f>
+      <c r="N215" t="str">
+        <v/>
       </c>
       <c r="P215" t="str">
         <v/>
@@ -12469,10 +11356,10 @@
       <c r="B216" t="str">
         <v>EXECUTE • Appliances</v>
       </c>
-      <c r="C216" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D216" s="1" t="str">
+      <c r="C216" t="str">
+        <v/>
+      </c>
+      <c r="D216" t="str">
         <v/>
       </c>
       <c r="E216" t="str">
@@ -12502,10 +11389,10 @@
       <c r="M216" t="str">
         <v/>
       </c>
-      <c r="N216" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O216" s="1" t="str">
+      <c r="N216" t="str">
+        <v/>
+      </c>
+      <c r="O216" t="str">
         <v/>
       </c>
       <c r="P216" t="str">
@@ -12525,11 +11412,8 @@
       <c r="B217" t="str">
         <v>Appliances: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C217" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D217" s="1">
-        <f>IF(AND(C217&lt;&gt;"",E217&lt;&gt;""),C217+E217-1,"")</f>
+      <c r="C217" t="str">
+        <v/>
       </c>
       <c r="E217">
         <v>2</v>
@@ -12558,11 +11442,8 @@
       <c r="M217" t="str">
         <v/>
       </c>
-      <c r="N217" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O217" s="1">
-        <f>IF(AND(N217&lt;&gt;"",E217&lt;&gt;""),N217+E217-1,"")</f>
+      <c r="N217" t="str">
+        <v/>
       </c>
       <c r="P217" t="str">
         <v/>
@@ -12581,11 +11462,8 @@
       <c r="B218" t="str">
         <v>Appliances: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C218" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D218" s="1">
-        <f>IF(AND(C218&lt;&gt;"",E218&lt;&gt;""),C218+E218-1,"")</f>
+      <c r="C218" t="str">
+        <v/>
       </c>
       <c r="E218">
         <v>7</v>
@@ -12614,11 +11492,8 @@
       <c r="M218" t="str">
         <v/>
       </c>
-      <c r="N218" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O218" s="1">
-        <f>IF(AND(N218&lt;&gt;"",E218&lt;&gt;""),N218+E218-1,"")</f>
+      <c r="N218" t="str">
+        <v/>
       </c>
       <c r="P218" t="str">
         <v/>
@@ -12637,11 +11512,8 @@
       <c r="B219" t="str">
         <v>Appliances: Delivery to Site</v>
       </c>
-      <c r="C219" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D219" s="1">
-        <f>IF(AND(C219&lt;&gt;"",E219&lt;&gt;""),C219+E219-1,"")</f>
+      <c r="C219" t="str">
+        <v/>
       </c>
       <c r="E219">
         <v>1</v>
@@ -12670,11 +11542,8 @@
       <c r="M219" t="str">
         <v/>
       </c>
-      <c r="N219" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O219" s="1">
-        <f>IF(AND(N219&lt;&gt;"",E219&lt;&gt;""),N219+E219-1,"")</f>
+      <c r="N219" t="str">
+        <v/>
       </c>
       <c r="P219" t="str">
         <v/>
@@ -12693,11 +11562,8 @@
       <c r="B220" t="str">
         <v>Appliances: Installation / Execution</v>
       </c>
-      <c r="C220" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D220" s="1">
-        <f>IF(AND(C220&lt;&gt;"",E220&lt;&gt;""),C220+E220-1,"")</f>
+      <c r="C220" t="str">
+        <v/>
       </c>
       <c r="E220">
         <v>5</v>
@@ -12726,11 +11592,8 @@
       <c r="M220" t="str">
         <v/>
       </c>
-      <c r="N220" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O220" s="1">
-        <f>IF(AND(N220&lt;&gt;"",E220&lt;&gt;""),N220+E220-1,"")</f>
+      <c r="N220" t="str">
+        <v/>
       </c>
       <c r="P220" t="str">
         <v/>
@@ -12749,11 +11612,8 @@
       <c r="B221" t="str">
         <v>Appliances: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C221" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D221" s="1">
-        <f>IF(AND(C221&lt;&gt;"",E221&lt;&gt;""),C221+E221-1,"")</f>
+      <c r="C221" t="str">
+        <v/>
       </c>
       <c r="E221">
         <v>2</v>
@@ -12782,11 +11642,8 @@
       <c r="M221" t="str">
         <v/>
       </c>
-      <c r="N221" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O221" s="1">
-        <f>IF(AND(N221&lt;&gt;"",E221&lt;&gt;""),N221+E221-1,"")</f>
+      <c r="N221" t="str">
+        <v/>
       </c>
       <c r="P221" t="str">
         <v/>
@@ -12805,10 +11662,10 @@
       <c r="B222" t="str">
         <v>EXECUTE • Flooring</v>
       </c>
-      <c r="C222" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D222" s="1" t="str">
+      <c r="C222" t="str">
+        <v/>
+      </c>
+      <c r="D222" t="str">
         <v/>
       </c>
       <c r="E222" t="str">
@@ -12838,10 +11695,10 @@
       <c r="M222" t="str">
         <v/>
       </c>
-      <c r="N222" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O222" s="1" t="str">
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
         <v/>
       </c>
       <c r="P222" t="str">
@@ -12861,11 +11718,8 @@
       <c r="B223" t="str">
         <v>Flooring: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C223" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D223" s="1">
-        <f>IF(AND(C223&lt;&gt;"",E223&lt;&gt;""),C223+E223-1,"")</f>
+      <c r="C223" t="str">
+        <v/>
       </c>
       <c r="E223">
         <v>2</v>
@@ -12894,11 +11748,8 @@
       <c r="M223" t="str">
         <v/>
       </c>
-      <c r="N223" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O223" s="1">
-        <f>IF(AND(N223&lt;&gt;"",E223&lt;&gt;""),N223+E223-1,"")</f>
+      <c r="N223" t="str">
+        <v/>
       </c>
       <c r="P223" t="str">
         <v/>
@@ -12917,11 +11768,8 @@
       <c r="B224" t="str">
         <v>Flooring: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C224" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D224" s="1">
-        <f>IF(AND(C224&lt;&gt;"",E224&lt;&gt;""),C224+E224-1,"")</f>
+      <c r="C224" t="str">
+        <v/>
       </c>
       <c r="E224">
         <v>7</v>
@@ -12950,11 +11798,8 @@
       <c r="M224" t="str">
         <v/>
       </c>
-      <c r="N224" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O224" s="1">
-        <f>IF(AND(N224&lt;&gt;"",E224&lt;&gt;""),N224+E224-1,"")</f>
+      <c r="N224" t="str">
+        <v/>
       </c>
       <c r="P224" t="str">
         <v/>
@@ -12973,11 +11818,8 @@
       <c r="B225" t="str">
         <v>Flooring: Delivery to Site</v>
       </c>
-      <c r="C225" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D225" s="1">
-        <f>IF(AND(C225&lt;&gt;"",E225&lt;&gt;""),C225+E225-1,"")</f>
+      <c r="C225" t="str">
+        <v/>
       </c>
       <c r="E225">
         <v>1</v>
@@ -13006,11 +11848,8 @@
       <c r="M225" t="str">
         <v/>
       </c>
-      <c r="N225" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O225" s="1">
-        <f>IF(AND(N225&lt;&gt;"",E225&lt;&gt;""),N225+E225-1,"")</f>
+      <c r="N225" t="str">
+        <v/>
       </c>
       <c r="P225" t="str">
         <v/>
@@ -13029,11 +11868,8 @@
       <c r="B226" t="str">
         <v>Flooring: Installation / Execution</v>
       </c>
-      <c r="C226" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D226" s="1">
-        <f>IF(AND(C226&lt;&gt;"",E226&lt;&gt;""),C226+E226-1,"")</f>
+      <c r="C226" t="str">
+        <v/>
       </c>
       <c r="E226">
         <v>5</v>
@@ -13062,11 +11898,8 @@
       <c r="M226" t="str">
         <v/>
       </c>
-      <c r="N226" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O226" s="1">
-        <f>IF(AND(N226&lt;&gt;"",E226&lt;&gt;""),N226+E226-1,"")</f>
+      <c r="N226" t="str">
+        <v/>
       </c>
       <c r="P226" t="str">
         <v/>
@@ -13085,11 +11918,8 @@
       <c r="B227" t="str">
         <v>Flooring: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C227" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D227" s="1">
-        <f>IF(AND(C227&lt;&gt;"",E227&lt;&gt;""),C227+E227-1,"")</f>
+      <c r="C227" t="str">
+        <v/>
       </c>
       <c r="E227">
         <v>2</v>
@@ -13118,11 +11948,8 @@
       <c r="M227" t="str">
         <v/>
       </c>
-      <c r="N227" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O227" s="1">
-        <f>IF(AND(N227&lt;&gt;"",E227&lt;&gt;""),N227+E227-1,"")</f>
+      <c r="N227" t="str">
+        <v/>
       </c>
       <c r="P227" t="str">
         <v/>
@@ -13141,10 +11968,10 @@
       <c r="B228" t="str">
         <v>EXECUTE • Carpentry</v>
       </c>
-      <c r="C228" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D228" s="1" t="str">
+      <c r="C228" t="str">
+        <v/>
+      </c>
+      <c r="D228" t="str">
         <v/>
       </c>
       <c r="E228" t="str">
@@ -13174,10 +12001,10 @@
       <c r="M228" t="str">
         <v/>
       </c>
-      <c r="N228" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O228" s="1" t="str">
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
         <v/>
       </c>
       <c r="P228" t="str">
@@ -13197,11 +12024,8 @@
       <c r="B229" t="str">
         <v>Carpentry: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C229" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D229" s="1">
-        <f>IF(AND(C229&lt;&gt;"",E229&lt;&gt;""),C229+E229-1,"")</f>
+      <c r="C229" t="str">
+        <v/>
       </c>
       <c r="E229">
         <v>2</v>
@@ -13230,11 +12054,8 @@
       <c r="M229" t="str">
         <v/>
       </c>
-      <c r="N229" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O229" s="1">
-        <f>IF(AND(N229&lt;&gt;"",E229&lt;&gt;""),N229+E229-1,"")</f>
+      <c r="N229" t="str">
+        <v/>
       </c>
       <c r="P229" t="str">
         <v/>
@@ -13253,11 +12074,8 @@
       <c r="B230" t="str">
         <v>Carpentry: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C230" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D230" s="1">
-        <f>IF(AND(C230&lt;&gt;"",E230&lt;&gt;""),C230+E230-1,"")</f>
+      <c r="C230" t="str">
+        <v/>
       </c>
       <c r="E230">
         <v>7</v>
@@ -13286,11 +12104,8 @@
       <c r="M230" t="str">
         <v/>
       </c>
-      <c r="N230" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O230" s="1">
-        <f>IF(AND(N230&lt;&gt;"",E230&lt;&gt;""),N230+E230-1,"")</f>
+      <c r="N230" t="str">
+        <v/>
       </c>
       <c r="P230" t="str">
         <v/>
@@ -13309,11 +12124,8 @@
       <c r="B231" t="str">
         <v>Carpentry: Delivery to Site</v>
       </c>
-      <c r="C231" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D231" s="1">
-        <f>IF(AND(C231&lt;&gt;"",E231&lt;&gt;""),C231+E231-1,"")</f>
+      <c r="C231" t="str">
+        <v/>
       </c>
       <c r="E231">
         <v>1</v>
@@ -13342,11 +12154,8 @@
       <c r="M231" t="str">
         <v/>
       </c>
-      <c r="N231" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O231" s="1">
-        <f>IF(AND(N231&lt;&gt;"",E231&lt;&gt;""),N231+E231-1,"")</f>
+      <c r="N231" t="str">
+        <v/>
       </c>
       <c r="P231" t="str">
         <v/>
@@ -13365,11 +12174,8 @@
       <c r="B232" t="str">
         <v>Carpentry: Installation / Execution</v>
       </c>
-      <c r="C232" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D232" s="1">
-        <f>IF(AND(C232&lt;&gt;"",E232&lt;&gt;""),C232+E232-1,"")</f>
+      <c r="C232" t="str">
+        <v/>
       </c>
       <c r="E232">
         <v>5</v>
@@ -13398,11 +12204,8 @@
       <c r="M232" t="str">
         <v/>
       </c>
-      <c r="N232" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O232" s="1">
-        <f>IF(AND(N232&lt;&gt;"",E232&lt;&gt;""),N232+E232-1,"")</f>
+      <c r="N232" t="str">
+        <v/>
       </c>
       <c r="P232" t="str">
         <v/>
@@ -13421,11 +12224,8 @@
       <c r="B233" t="str">
         <v>Carpentry: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C233" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D233" s="1">
-        <f>IF(AND(C233&lt;&gt;"",E233&lt;&gt;""),C233+E233-1,"")</f>
+      <c r="C233" t="str">
+        <v/>
       </c>
       <c r="E233">
         <v>2</v>
@@ -13454,11 +12254,8 @@
       <c r="M233" t="str">
         <v/>
       </c>
-      <c r="N233" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O233" s="1">
-        <f>IF(AND(N233&lt;&gt;"",E233&lt;&gt;""),N233+E233-1,"")</f>
+      <c r="N233" t="str">
+        <v/>
       </c>
       <c r="P233" t="str">
         <v/>
@@ -13477,10 +12274,10 @@
       <c r="B234" t="str">
         <v>LINK • Flooring waits for Civil</v>
       </c>
-      <c r="C234" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D234" s="1" t="str">
+      <c r="C234" t="str">
+        <v/>
+      </c>
+      <c r="D234" t="str">
         <v/>
       </c>
       <c r="E234" t="str">
@@ -13510,10 +12307,10 @@
       <c r="M234" t="str">
         <v/>
       </c>
-      <c r="N234" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O234" s="1" t="str">
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
         <v/>
       </c>
       <c r="P234" t="str">
@@ -13533,10 +12330,10 @@
       <c r="B235" t="str">
         <v>LINK • Wall Finishes wait for Civil</v>
       </c>
-      <c r="C235" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D235" s="1" t="str">
+      <c r="C235" t="str">
+        <v/>
+      </c>
+      <c r="D235" t="str">
         <v/>
       </c>
       <c r="E235" t="str">
@@ -13566,10 +12363,10 @@
       <c r="M235" t="str">
         <v/>
       </c>
-      <c r="N235" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O235" s="1" t="str">
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
         <v/>
       </c>
       <c r="P235" t="str">
@@ -13589,10 +12386,10 @@
       <c r="B236" t="str">
         <v>LINK • Doors &amp; Windows wait for Civil</v>
       </c>
-      <c r="C236" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D236" s="1" t="str">
+      <c r="C236" t="str">
+        <v/>
+      </c>
+      <c r="D236" t="str">
         <v/>
       </c>
       <c r="E236" t="str">
@@ -13622,10 +12419,10 @@
       <c r="M236" t="str">
         <v/>
       </c>
-      <c r="N236" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O236" s="1" t="str">
+      <c r="N236" t="str">
+        <v/>
+      </c>
+      <c r="O236" t="str">
         <v/>
       </c>
       <c r="P236" t="str">
@@ -13645,10 +12442,10 @@
       <c r="B237" t="str">
         <v>LINK • Carpentry waits for Civil</v>
       </c>
-      <c r="C237" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D237" s="1" t="str">
+      <c r="C237" t="str">
+        <v/>
+      </c>
+      <c r="D237" t="str">
         <v/>
       </c>
       <c r="E237" t="str">
@@ -13678,10 +12475,10 @@
       <c r="M237" t="str">
         <v/>
       </c>
-      <c r="N237" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O237" s="1" t="str">
+      <c r="N237" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
         <v/>
       </c>
       <c r="P237" t="str">
@@ -13701,10 +12498,10 @@
       <c r="B238" t="str">
         <v>LINK • Lighting after Electricals</v>
       </c>
-      <c r="C238" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D238" s="1" t="str">
+      <c r="C238" t="str">
+        <v/>
+      </c>
+      <c r="D238" t="str">
         <v/>
       </c>
       <c r="E238" t="str">
@@ -13734,10 +12531,10 @@
       <c r="M238" t="str">
         <v/>
       </c>
-      <c r="N238" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O238" s="1" t="str">
+      <c r="N238" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
         <v/>
       </c>
       <c r="P238" t="str">
@@ -13757,10 +12554,10 @@
       <c r="B239" t="str">
         <v>LINK • Automation after Electricals</v>
       </c>
-      <c r="C239" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D239" s="1" t="str">
+      <c r="C239" t="str">
+        <v/>
+      </c>
+      <c r="D239" t="str">
         <v/>
       </c>
       <c r="E239" t="str">
@@ -13790,10 +12587,10 @@
       <c r="M239" t="str">
         <v/>
       </c>
-      <c r="N239" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O239" s="1" t="str">
+      <c r="N239" t="str">
+        <v/>
+      </c>
+      <c r="O239" t="str">
         <v/>
       </c>
       <c r="P239" t="str">
@@ -13813,10 +12610,10 @@
       <c r="B240" t="str">
         <v>LINK • Audio after Electricals</v>
       </c>
-      <c r="C240" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D240" s="1" t="str">
+      <c r="C240" t="str">
+        <v/>
+      </c>
+      <c r="D240" t="str">
         <v/>
       </c>
       <c r="E240" t="str">
@@ -13846,10 +12643,10 @@
       <c r="M240" t="str">
         <v/>
       </c>
-      <c r="N240" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O240" s="1" t="str">
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
         <v/>
       </c>
       <c r="P240" t="str">
@@ -13869,10 +12666,10 @@
       <c r="B241" t="str">
         <v>LINK • Kitchens after Plumbing</v>
       </c>
-      <c r="C241" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D241" s="1" t="str">
+      <c r="C241" t="str">
+        <v/>
+      </c>
+      <c r="D241" t="str">
         <v/>
       </c>
       <c r="E241" t="str">
@@ -13902,10 +12699,10 @@
       <c r="M241" t="str">
         <v/>
       </c>
-      <c r="N241" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O241" s="1" t="str">
+      <c r="N241" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
         <v/>
       </c>
       <c r="P241" t="str">
@@ -13925,10 +12722,10 @@
       <c r="B242" t="str">
         <v>LINK • Bathrooms after Plumbing</v>
       </c>
-      <c r="C242" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D242" s="1" t="str">
+      <c r="C242" t="str">
+        <v/>
+      </c>
+      <c r="D242" t="str">
         <v/>
       </c>
       <c r="E242" t="str">
@@ -13958,10 +12755,10 @@
       <c r="M242" t="str">
         <v/>
       </c>
-      <c r="N242" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O242" s="1" t="str">
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
         <v/>
       </c>
       <c r="P242" t="str">
@@ -13981,10 +12778,10 @@
       <c r="B243" t="str">
         <v>LINK • Appliances after Kitchens &amp; Electricals</v>
       </c>
-      <c r="C243" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D243" s="1" t="str">
+      <c r="C243" t="str">
+        <v/>
+      </c>
+      <c r="D243" t="str">
         <v/>
       </c>
       <c r="E243" t="str">
@@ -14014,10 +12811,10 @@
       <c r="M243" t="str">
         <v/>
       </c>
-      <c r="N243" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O243" s="1" t="str">
+      <c r="N243" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
         <v/>
       </c>
       <c r="P243" t="str">
@@ -14037,10 +12834,10 @@
       <c r="B244" t="str">
         <v>PHASE • Closeout &amp; Handover</v>
       </c>
-      <c r="C244" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D244" s="1" t="str">
+      <c r="C244" t="str">
+        <v/>
+      </c>
+      <c r="D244" t="str">
         <v/>
       </c>
       <c r="E244" t="str">
@@ -14070,10 +12867,10 @@
       <c r="M244" t="str">
         <v/>
       </c>
-      <c r="N244" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O244" s="1" t="str">
+      <c r="N244" t="str">
+        <v/>
+      </c>
+      <c r="O244" t="str">
         <v/>
       </c>
       <c r="P244" t="str">
@@ -14093,10 +12890,10 @@
       <c r="B245" t="str">
         <v>All Trades Complete – Declaration</v>
       </c>
-      <c r="C245" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D245" s="1" t="str">
+      <c r="C245" t="str">
+        <v/>
+      </c>
+      <c r="D245" t="str">
         <v/>
       </c>
       <c r="E245">
@@ -14126,10 +12923,10 @@
       <c r="M245" t="str">
         <v/>
       </c>
-      <c r="N245" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O245" s="1" t="str">
+      <c r="N245" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
         <v/>
       </c>
       <c r="P245" t="str">
@@ -14149,11 +12946,8 @@
       <c r="B246" t="str">
         <v>Snagging / Punch List</v>
       </c>
-      <c r="C246" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D246" s="1">
-        <f>IF(AND(C246&lt;&gt;"",E246&lt;&gt;""),C246+E246-1,"")</f>
+      <c r="C246" t="str">
+        <v/>
       </c>
       <c r="E246">
         <v>3</v>
@@ -14182,11 +12976,8 @@
       <c r="M246" t="str">
         <v/>
       </c>
-      <c r="N246" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O246" s="1">
-        <f>IF(AND(N246&lt;&gt;"",E246&lt;&gt;""),N246+E246-1,"")</f>
+      <c r="N246" t="str">
+        <v/>
       </c>
       <c r="P246" t="str">
         <v/>
@@ -14205,11 +12996,8 @@
       <c r="B247" t="str">
         <v>Rectification of Snags</v>
       </c>
-      <c r="C247" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D247" s="1">
-        <f>IF(AND(C247&lt;&gt;"",E247&lt;&gt;""),C247+E247-1,"")</f>
+      <c r="C247" t="str">
+        <v/>
       </c>
       <c r="E247">
         <v>5</v>
@@ -14238,11 +13026,8 @@
       <c r="M247" t="str">
         <v/>
       </c>
-      <c r="N247" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O247" s="1">
-        <f>IF(AND(N247&lt;&gt;"",E247&lt;&gt;""),N247+E247-1,"")</f>
+      <c r="N247" t="str">
+        <v/>
       </c>
       <c r="P247" t="str">
         <v/>
@@ -14261,11 +13046,8 @@
       <c r="B248" t="str">
         <v>Client Demo &amp; Acceptance</v>
       </c>
-      <c r="C248" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D248" s="1">
-        <f>IF(AND(C248&lt;&gt;"",E248&lt;&gt;""),C248+E248-1,"")</f>
+      <c r="C248" t="str">
+        <v/>
       </c>
       <c r="E248">
         <v>1</v>
@@ -14294,11 +13076,8 @@
       <c r="M248" t="str">
         <v/>
       </c>
-      <c r="N248" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O248" s="1">
-        <f>IF(AND(N248&lt;&gt;"",E248&lt;&gt;""),N248+E248-1,"")</f>
+      <c r="N248" t="str">
+        <v/>
       </c>
       <c r="P248" t="str">
         <v/>
@@ -14317,11 +13096,8 @@
       <c r="B249" t="str">
         <v>Practical Completion / Handover</v>
       </c>
-      <c r="C249" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D249" s="1">
-        <f>IF(AND(C249&lt;&gt;"",E249&lt;&gt;""),C249+E249-1,"")</f>
+      <c r="C249" t="str">
+        <v/>
       </c>
       <c r="E249">
         <v>1</v>
@@ -14350,11 +13126,8 @@
       <c r="M249" t="str">
         <v/>
       </c>
-      <c r="N249" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O249" s="1">
-        <f>IF(AND(N249&lt;&gt;"",E249&lt;&gt;""),N249+E249-1,"")</f>
+      <c r="N249" t="str">
+        <v/>
       </c>
       <c r="P249" t="str">
         <v/>
@@ -14373,11 +13146,8 @@
       <c r="B250" t="str">
         <v>As‑Built Docs &amp; O&amp;M Manuals</v>
       </c>
-      <c r="C250" s="1" t="str">
-        <v/>
-      </c>
-      <c r="D250" s="1">
-        <f>IF(AND(C250&lt;&gt;"",E250&lt;&gt;""),C250+E250-1,"")</f>
+      <c r="C250" t="str">
+        <v/>
       </c>
       <c r="E250">
         <v>5</v>
@@ -14406,11 +13176,8 @@
       <c r="M250" t="str">
         <v/>
       </c>
-      <c r="N250" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O250" s="1">
-        <f>IF(AND(N250&lt;&gt;"",E250&lt;&gt;""),N250+E250-1,"")</f>
+      <c r="N250" t="str">
+        <v/>
       </c>
       <c r="P250" t="str">
         <v/>
@@ -14432,11 +13199,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C79"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/attached_assets/gantt_template.xlsx
+++ b/attached_assets/gantt_template.xlsx
@@ -13198,7 +13198,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:E200"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13222,7 +13228,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. Enter Start Date in column C - Excel will show a calendar picker</v>
+        <v>2. Enter Start Date in column C - see "DATE ENTRY METHODS" below for calendar options</v>
       </c>
     </row>
     <row r="6">
@@ -13247,42 +13253,42 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TASK ORGANIZATION</v>
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>• PHASE headers organize major project phases (Outline Level 1)</v>
+        <v>DATE ENTRY METHODS - CHOOSE YOUR PREFERRED OPTION</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>• PACKAGE headers organize vendor categories (Outline Level 1)</v>
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>• Individual tasks under each package (Outline Level 2)</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>OPTION 1: KEYBOARD ENTRY (Built-in, Works Everywhere)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>PHASES INCLUDED</v>
+        <v>• Click any date cell and type: 2024-01-15 (YYYY-MM-DD format)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1. Design &amp; Approvals - Initial design phase with client approvals</v>
+        <v>• Or press Ctrl+; to insert today's date</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2. Vendor Evaluation → Quotes → Finalisation → Work Orders</v>
+        <v>• Simple and fast for experienced users</v>
       </c>
     </row>
     <row r="18">
@@ -13292,468 +13298,1154 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>PACKAGES INCLUDED</v>
+        <v>OPTION 2: VISUAL CALENDAR PICKER - RECOMMENDED ⭐</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>• Civil, Electricals, Plumbing, Kitchens, Bathrooms, Audio, Automation</v>
+        <v>For the best experience, install a free calendar add-in:</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>• Lighting, HVAC, Curtains, Furniture, Wardrobes, Flooring, Painting</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>• False Ceiling, Mirrors, Soft Furnishings, Décor, Upholstery, Storage</v>
+        <v>METHOD A: Randy's Date Picker (Works in Excel 2016/2019/2021/365, 32-bit &amp; 64-bit)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>• Each package follows the same workflow:</v>
+        <v>Step 1: Download the add-in</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">  1. Vendor Evaluation → 2. Meetings/Survey → 3. RFQs → 4. Quotes</v>
+        <v xml:space="preserve">        • Google search: "Randy Austin date picker Excel download"</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">  5. Comparison → 6. Finalisation → 7. Work Order</v>
+        <v xml:space="preserve">        • Or visit: https://bettersolutions.com/excel/date-picker/ (trusted source)</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v xml:space="preserve">        • Download the .xlam file (Excel add-in)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>AUTOMATIC DATE CALCULATION</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>• When you enter Start Date + Duration, Finish Date calculates automatically</v>
+        <v>Step 2: Install the add-in</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>• Formula: Finish = Start + Duration - 1 day</v>
+        <v xml:space="preserve">        • Open Excel</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>• Example: Start = Jan 1, Duration = 5 → Finish = Jan 5</v>
+        <v xml:space="preserve">        • File → Options → Add-ins</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>• Works for both actual dates and target dates</v>
+        <v xml:space="preserve">        • At bottom, select "Excel Add-ins" → Click "Go..."</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v xml:space="preserve">        • Click "Browse..." → Find your downloaded .xlam file</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DATE ENTRY WITH CALENDAR</v>
+        <v xml:space="preserve">        • Check the box next to "Randy's Date Picker" → Click OK</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>• Click any Start or Finish date cell</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>• Excel shows a calendar icon or date picker</v>
+        <v>Step 3: Use the calendar</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>• Select date from calendar or type YYYY-MM-DD (e.g., 2024-01-15)</v>
+        <v xml:space="preserve">        • Click any date cell in your template</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v xml:space="preserve">        • A floating calendar popup appears automatically</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>COLUMN REFERENCE</v>
+        <v xml:space="preserve">        • Click a date to insert it</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Column</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Description</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Notes</v>
+        <v xml:space="preserve">        • Works for all date columns (no configuration needed)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Task identifier (1-249)</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Pre-filled, do not change</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Task name</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Pre-filled with your project tasks</v>
+        <v>METHOD B: Kutools Date Picker (Commercial, Full-Featured)</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Start</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Start date (CALENDAR PICKER)</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Click for calendar, auto-calculates finish</v>
+        <v xml:space="preserve">        • Visit: https://www.extendoffice.com/product/kutools-for-excel.html</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Finish</v>
-      </c>
-      <c r="B43" t="str">
-        <v>End date (AUTO-CALCULATED)</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Auto: Start + Duration - 1</v>
+        <v xml:space="preserve">        • Free trial available, then $49 for permanent license</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Working days</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Pre-filled, adjust as needed</v>
+        <v xml:space="preserve">        • Includes 300+ Excel tools beyond just date picking</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>% Complete</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Progress (0-100)</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Update as work progresses</v>
+        <v xml:space="preserve">        • Calendar appears when clicking any date cell</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Predecessors</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Dependencies</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Pre-configured: TaskID(Type)</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Resource Names</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Assigned team</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Pre-filled: Designer, Client, Vendor, etc.</v>
+        <v>METHOD C: Built-in ActiveX Control (Legacy, 32-bit Excel Only)</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Status</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Current status</v>
-      </c>
-      <c r="C48" t="str">
-        <v>not_started, in_progress, completed, blocked</v>
+        <v xml:space="preserve">        ⚠️ Not recommended - doesn't work in 64-bit Excel</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Task priority</v>
-      </c>
-      <c r="C49" t="str">
-        <v>low, medium, high (auto-set for key tasks)</v>
+        <v xml:space="preserve">        • Enable Developer tab: File → Options → Customize Ribbon → Check "Developer"</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Approval Required</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Needs approval? (Y/N)</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Pre-set for approval tasks</v>
+        <v xml:space="preserve">        • Developer → Insert → More Controls</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Materials</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Required materials</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Optional</v>
+        <v xml:space="preserve">        • Select "Microsoft Date and Time Picker Control 6.0"</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Task owner</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Optional</v>
+        <v xml:space="preserve">        • Manually link to each cell (time-consuming for 249 tasks)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Target Start</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Planned start (CALENDAR)</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Optional planning dates</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Target Finish</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Planned finish (AUTO-CALC)</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Auto: Target Start + Duration - 1</v>
+        <v>COMPARISON: Which Method Should You Choose?</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Remarks</v>
+        <v>Method</v>
       </c>
       <c r="B55" t="str">
-        <v>Notes</v>
+        <v>Ease of Use</v>
       </c>
       <c r="C55" t="str">
-        <v>Pre-filled with milestones</v>
+        <v>64-bit Compatible</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Cost</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Recommendation</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Outline Level</v>
+        <v>Keyboard Entry</v>
       </c>
       <c r="B56" t="str">
-        <v>Hierarchy (1 or 2)</v>
+        <v>Easy</v>
       </c>
       <c r="C56" t="str">
-        <v>1=Phase/Package, 2=Task</v>
+        <v>Yes</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Free</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Good for quick edits</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Color</v>
+        <v>Randy's Picker</v>
       </c>
       <c r="B57" t="str">
-        <v>Task color</v>
+        <v>Very Easy</v>
       </c>
       <c r="C57" t="str">
-        <v>Optional hex code: #4A90E2</v>
+        <v>Yes</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Free</v>
+      </c>
+      <c r="E57" t="str">
+        <v>⭐ BEST for most users</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Kutools</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Very Easy</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D58" t="str">
+        <v>$49</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Best for power users</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>DEPENDENCY TYPES</v>
+        <v>ActiveX Control</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Difficult</v>
+      </c>
+      <c r="C59" t="str">
+        <v>No</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Free</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Avoid - outdated</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Format</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Meaning</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Example</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>TaskID(FS)</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Finish-to-Start (most common)</v>
-      </c>
-      <c r="C61" t="str">
-        <v>2(FS) = Task 2 finishes before this starts</v>
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>TaskID(SS)</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Start-to-Start</v>
-      </c>
-      <c r="C62" t="str">
-        <v>3(SS) = Task 3 starts before this starts</v>
+        <v>TASK ORGANIZATION</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>TaskID(FF)</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Finish-to-Finish</v>
-      </c>
-      <c r="C63" t="str">
-        <v>4(FF) = Task 4 finishes before this finishes</v>
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TaskID(SF)</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Start-to-Finish (rare)</v>
-      </c>
-      <c r="C64" t="str">
-        <v>5(SF) = Task 5 starts before this finishes</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>With lag</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Add delay</v>
-      </c>
-      <c r="C65" t="str">
-        <v>2(FS)+3 = Wait 3 days after Task 2 finishes</v>
+        <v>PHASES INCLUDED</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Multiple</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Comma-separated</v>
-      </c>
-      <c r="C66" t="str">
-        <v>4(FS),5(FS) = Wait for both 4 and 5</v>
+        <v>1. Design &amp; Approvals - Initial design phase with client approvals</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>2. Vendor Evaluation → Quotes → Finalisation → Work Orders</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>PRE-CONFIGURED DEPENDENCIES</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>All task dependencies are pre-configured based on typical project workflow</v>
+        <v>PACKAGES INCLUDED (20 Categories)</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Each package follows sequential steps with dependencies on previous steps</v>
+        <v>• Civil, Electricals, Plumbing, Kitchens, Bathrooms, Audio, Automation</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Cross-package dependencies link packages to design phase completion</v>
+        <v>• Lighting, HVAC, Curtains, Furniture, Wardrobes, Flooring, Painting</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>• False Ceiling, Mirrors, Soft Furnishings, Décor, Upholstery, Storage</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CRITICAL PATH ANALYSIS</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>After importing, the system will:</v>
+        <v>Each package follows the same 7-step workflow:</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>• Calculate Early Start (ES) and Early Finish (EF) for all tasks</v>
+        <v xml:space="preserve">  1. Vendor Evaluation (shortlist) → 2. Vendor Meetings / Site Survey</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>• Calculate Late Start (LS) and Late Finish (LF) for all tasks</v>
+        <v xml:space="preserve">  3. RFQs Issued → 4. Quotes Received &amp; Clarifications</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>• Identify critical tasks (zero float - must complete on time)</v>
+        <v xml:space="preserve">  5. Quote Comparison &amp; Negotiation → 6. Vendor Finalisation</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>• Show total project duration and critical path percentage</v>
+        <v xml:space="preserve">  7. Work Order / PO Release</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>• Detect circular dependencies and prevent import errors</v>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>HIERARCHY</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>• PHASE headers: Outline Level 1 (major project phases)</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>• PACKAGE headers: Outline Level 1 (vendor categories)</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>• Individual tasks: Outline Level 2 (specific activities)</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>AUTOMATIC DATE CALCULATIONS</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>• When you enter Start Date + Duration, Finish Date calculates automatically</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>• Formula: Finish = Start + Duration - 1 day</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>• Example: Start = Jan 1, Duration = 5 → Finish = Jan 5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>• Works for both Actual dates (C, D) and Target dates (N, O)</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>• You can override auto-calculated dates if needed</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>COLUMN REFERENCE (18 Columns)</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Column</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Description</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Task identifier (1-249)</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Pre-filled, do not change</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Task name</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Pre-filled with your project tasks</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Start</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Start date</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Use calendar picker or type YYYY-MM-DD</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Finish</v>
+      </c>
+      <c r="B103" t="str">
+        <v>End date (AUTO-CALC)</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Auto: Start + Duration - 1, can override</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Duration</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Working days</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Pre-filled, adjust as needed</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>% Complete</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Progress (0-100)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Update as work progresses</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Predecessors</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Dependencies</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Pre-configured: TaskID(Type)</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Resource Names</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Assigned team</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Designer, Client, Vendor, etc.</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Current status</v>
+      </c>
+      <c r="C108" t="str">
+        <v>not_started, in_progress, completed, blocked</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Task priority</v>
+      </c>
+      <c r="C109" t="str">
+        <v>low, medium, high (auto-set for key tasks)</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Approval Required</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Needs approval? (Y/N)</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Pre-set for approval tasks</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Materials</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Required materials</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Optional - add as needed</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Task owner name</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Optional - assign task owner</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Target Start</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Planned start</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Optional planning dates</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Target Finish</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Planned finish (AUTO-CALC)</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Auto: Target Start + Duration - 1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Milestones and special notes</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Outline Level</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Hierarchy (1 or 2)</v>
+      </c>
+      <c r="C116" t="str">
+        <v>1=Phase/Package, 2=Task</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Color</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Task color</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Optional hex code: #4A90E2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>DEPENDENCY TYPES (Critical Path Analysis)</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Format</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Meaning</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Example</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TaskID(FS)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Finish-to-Start</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Task finishes before this starts</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2(FS) = Wait for Task 2 to finish</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TaskID(SS)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Start-to-Start</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Task starts before this starts</v>
+      </c>
+      <c r="D125" t="str">
+        <v>3(SS) = Wait for Task 3 to start</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TaskID(FF)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Finish-to-Finish</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Task finishes before this finishes</v>
+      </c>
+      <c r="D126" t="str">
+        <v>4(FF) = Must finish with Task 4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TaskID(SF)</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Start-to-Finish</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Task starts before this finishes</v>
+      </c>
+      <c r="D127" t="str">
+        <v>5(SF) = Rare, special cases</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>With lag</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Add delay</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Wait extra days after dependency</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2(FS)+3 = 3 days after Task 2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Multiple</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Comma-separated</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Wait for multiple tasks</v>
+      </c>
+      <c r="D129" t="str">
+        <v>4(FS),5(FS) = Wait for both</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>PRE-CONFIGURED DEPENDENCIES</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>All task dependencies are pre-configured based on typical interior design workflow:</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>• Design phase tasks flow sequentially (Client Brief → Schematics → Working Drawings)</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>• Each package starts after Client Sign-off on drawings</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>• Within each package, tasks follow the 7-step workflow sequentially</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>• You can modify dependencies if your project workflow differs</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>CRITICAL PATH ANALYSIS (After Importing to PixelCraft Designer)</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>After importing this template into PixelCraft Designer, the system will:</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>✓ Calculate Early Start (ES) and Early Finish (EF) for all tasks</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>✓ Calculate Late Start (LS) and Late Finish (LF) for all tasks</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>✓ Identify critical tasks (zero float - must complete on time)</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>✓ Show total project duration in working days</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>✓ Display critical path percentage (% of tasks on critical path)</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>✓ Detect circular dependencies and prevent import errors</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>✓ Highlight critical tasks with visual badges</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>WHAT IS THE CRITICAL PATH?</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>The critical path is the longest sequence of dependent tasks that determines</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>the minimum project duration. Any delay in critical path tasks delays the</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>entire project. Tasks not on the critical path have "float" (slack time).</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>KEY METRICS:</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>• Total Float: How many days a task can be delayed without affecting project end</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>• Critical Tasks: Tasks with zero float (must complete on schedule)</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>• Project Duration: Earliest possible project completion date</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TIPS FOR BEST RESULTS</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>1. Install Randy's Date Picker first for easiest date entry</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>2. Start by filling in Start dates for the first few tasks</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>3. Let the Finish dates auto-calculate (they use the formula)</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>4. Adjust Duration values based on your project needs</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>5. Review pre-configured dependencies - modify if your workflow differs</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>6. Use Status column to track progress: not_started → in_progress → completed</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>7. Set Priority to "high" for time-sensitive or client-facing tasks</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>8. Import into PixelCraft Designer to see Critical Path Analysis</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>9. Download updated schedule from PixelCraft to get latest progress</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>10. Keep Approval Required tasks visible - they often become bottlenecks</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TROUBLESHOOTING</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Problem: Date validation message appears but no calendar</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Solution: You need to install a calendar add-in (see OPTION 2 above)</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Problem: Finish date not calculating automatically</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Solution: Make sure Start date AND Duration are both filled in</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Problem: Import fails with "circular dependency" error</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Solution: Check Predecessors column - a task cannot depend on itself or</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v xml:space="preserve">         create a loop (e.g., Task 5 → Task 10 → Task 5)</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Problem: Critical path shows 100% of tasks as critical</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Solution: Dependencies may be too strict - some packages could start in</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v xml:space="preserve">         parallel instead of sequentially</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Problem: Excel shows "####" in date columns</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Solution: Column is too narrow - double-click column border to auto-fit</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>For support with PixelCraft Designer system, contact your administrator</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/attached_assets/gantt_template.xlsx
+++ b/attached_assets/gantt_template.xlsx
@@ -400,6 +400,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R250"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1" hidden="true"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1" hidden="true"/>
+    <col min="12" max="12" width="25.83203125" customWidth="1" hidden="true"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1" hidden="true"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1" hidden="true"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1" hidden="true"/>
+    <col min="16" max="16" width="30.83203125" customWidth="1" hidden="true"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1" hidden="true"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1" hidden="true"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13199,12 +13219,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E200"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/attached_assets/gantt_template.xlsx
+++ b/attached_assets/gantt_template.xlsx
@@ -401,24 +401,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R250"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1" hidden="true"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1" hidden="true"/>
-    <col min="12" max="12" width="25.83203125" customWidth="1" hidden="true"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1" hidden="true"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1" hidden="true"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1" hidden="true"/>
-    <col min="16" max="16" width="30.83203125" customWidth="1" hidden="true"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1" hidden="true"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1" hidden="true"/>
+    <col min="1" max="1"/>
+    <col min="2" max="2"/>
+    <col min="3" max="3"/>
+    <col min="4" max="4"/>
+    <col min="5" max="5"/>
+    <col min="6" max="6"/>
+    <col min="7" max="7"/>
+    <col min="8" max="8"/>
+    <col min="9" max="9"/>
+    <col min="10" max="10"/>
+    <col min="11" max="11"/>
+    <col min="12" max="12"/>
+    <col min="13" max="13"/>
+    <col min="14" max="14"/>
+    <col min="15" max="15"/>
+    <col min="16" max="16"/>
+    <col min="17" max="17"/>
+    <col min="18" max="18"/>
+    <col min="19" max="19" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/attached_assets/gantt_template.xlsx
+++ b/attached_assets/gantt_template.xlsx
@@ -33,9 +33,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -401,25 +400,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R250"/>
   <cols>
-    <col min="1" max="1"/>
-    <col min="2" max="2"/>
-    <col min="3" max="3"/>
-    <col min="4" max="4"/>
-    <col min="5" max="5"/>
-    <col min="6" max="6"/>
-    <col min="7" max="7"/>
-    <col min="8" max="8"/>
-    <col min="9" max="9"/>
-    <col min="10" max="10"/>
-    <col min="11" max="11"/>
-    <col min="12" max="12"/>
-    <col min="13" max="13"/>
-    <col min="14" max="14"/>
-    <col min="15" max="15"/>
-    <col min="16" max="16"/>
-    <col min="17" max="17"/>
-    <col min="18" max="18"/>
-    <col min="19" max="19" width="100.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="30.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,6 +542,9 @@
       <c r="C3" t="str">
         <v/>
       </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
       <c r="E3">
         <v>2</v>
       </c>
@@ -572,6 +573,9 @@
         <v/>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
@@ -594,6 +598,9 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
       <c r="E4">
         <v>5</v>
       </c>
@@ -622,6 +629,9 @@
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v/>
       </c>
       <c r="P4" t="str">
@@ -644,6 +654,9 @@
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
       <c r="E5">
         <v>7</v>
       </c>
@@ -672,6 +685,9 @@
         <v/>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
@@ -694,6 +710,9 @@
       <c r="C6" t="str">
         <v/>
       </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
       <c r="E6">
         <v>3</v>
       </c>
@@ -722,6 +741,9 @@
         <v/>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
@@ -744,6 +766,9 @@
       <c r="C7" t="str">
         <v/>
       </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
       <c r="E7">
         <v>1</v>
       </c>
@@ -772,6 +797,9 @@
         <v/>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
@@ -906,6 +934,9 @@
       <c r="C10" t="str">
         <v/>
       </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
       <c r="E10">
         <v>3</v>
       </c>
@@ -934,6 +965,9 @@
         <v/>
       </c>
       <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
         <v/>
       </c>
       <c r="P10" t="str">
@@ -956,6 +990,9 @@
       <c r="C11" t="str">
         <v/>
       </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
       <c r="E11">
         <v>2</v>
       </c>
@@ -984,6 +1021,9 @@
         <v/>
       </c>
       <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
         <v/>
       </c>
       <c r="P11" t="str">
@@ -1006,6 +1046,9 @@
       <c r="C12" t="str">
         <v/>
       </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
       <c r="E12">
         <v>2</v>
       </c>
@@ -1034,6 +1077,9 @@
         <v/>
       </c>
       <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
         <v/>
       </c>
       <c r="P12" t="str">
@@ -1056,6 +1102,9 @@
       <c r="C13" t="str">
         <v/>
       </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
       <c r="E13">
         <v>3</v>
       </c>
@@ -1084,6 +1133,9 @@
         <v/>
       </c>
       <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
         <v/>
       </c>
       <c r="P13" t="str">
@@ -1106,6 +1158,9 @@
       <c r="C14" t="str">
         <v/>
       </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
       <c r="E14">
         <v>2</v>
       </c>
@@ -1134,6 +1189,9 @@
         <v/>
       </c>
       <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
         <v/>
       </c>
       <c r="P14" t="str">
@@ -1156,6 +1214,9 @@
       <c r="C15" t="str">
         <v/>
       </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
       <c r="E15">
         <v>1</v>
       </c>
@@ -1184,6 +1245,9 @@
         <v/>
       </c>
       <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
         <v/>
       </c>
       <c r="P15" t="str">
@@ -1206,6 +1270,9 @@
       <c r="C16" t="str">
         <v/>
       </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
       <c r="E16">
         <v>1</v>
       </c>
@@ -1234,6 +1301,9 @@
         <v/>
       </c>
       <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
         <v/>
       </c>
       <c r="P16" t="str">
@@ -1312,6 +1382,9 @@
       <c r="C18" t="str">
         <v/>
       </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
       <c r="E18">
         <v>3</v>
       </c>
@@ -1340,6 +1413,9 @@
         <v/>
       </c>
       <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
         <v/>
       </c>
       <c r="P18" t="str">
@@ -1362,6 +1438,9 @@
       <c r="C19" t="str">
         <v/>
       </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
       <c r="E19">
         <v>2</v>
       </c>
@@ -1390,6 +1469,9 @@
         <v/>
       </c>
       <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
         <v/>
       </c>
       <c r="P19" t="str">
@@ -1412,6 +1494,9 @@
       <c r="C20" t="str">
         <v/>
       </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
       <c r="E20">
         <v>2</v>
       </c>
@@ -1440,6 +1525,9 @@
         <v/>
       </c>
       <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
         <v/>
       </c>
       <c r="P20" t="str">
@@ -1462,6 +1550,9 @@
       <c r="C21" t="str">
         <v/>
       </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
       <c r="E21">
         <v>3</v>
       </c>
@@ -1490,6 +1581,9 @@
         <v/>
       </c>
       <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
         <v/>
       </c>
       <c r="P21" t="str">
@@ -1512,6 +1606,9 @@
       <c r="C22" t="str">
         <v/>
       </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
       <c r="E22">
         <v>2</v>
       </c>
@@ -1540,6 +1637,9 @@
         <v/>
       </c>
       <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
         <v/>
       </c>
       <c r="P22" t="str">
@@ -1562,6 +1662,9 @@
       <c r="C23" t="str">
         <v/>
       </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
       <c r="E23">
         <v>1</v>
       </c>
@@ -1590,6 +1693,9 @@
         <v/>
       </c>
       <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
         <v/>
       </c>
       <c r="P23" t="str">
@@ -1612,6 +1718,9 @@
       <c r="C24" t="str">
         <v/>
       </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
       <c r="E24">
         <v>1</v>
       </c>
@@ -1640,6 +1749,9 @@
         <v/>
       </c>
       <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
         <v/>
       </c>
       <c r="P24" t="str">
@@ -1718,6 +1830,9 @@
       <c r="C26" t="str">
         <v/>
       </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
       <c r="E26">
         <v>3</v>
       </c>
@@ -1746,6 +1861,9 @@
         <v/>
       </c>
       <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
         <v/>
       </c>
       <c r="P26" t="str">
@@ -1768,6 +1886,9 @@
       <c r="C27" t="str">
         <v/>
       </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
       <c r="E27">
         <v>2</v>
       </c>
@@ -1796,6 +1917,9 @@
         <v/>
       </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
         <v/>
       </c>
       <c r="P27" t="str">
@@ -1818,6 +1942,9 @@
       <c r="C28" t="str">
         <v/>
       </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
       <c r="E28">
         <v>2</v>
       </c>
@@ -1846,6 +1973,9 @@
         <v/>
       </c>
       <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
         <v/>
       </c>
       <c r="P28" t="str">
@@ -1868,6 +1998,9 @@
       <c r="C29" t="str">
         <v/>
       </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
       <c r="E29">
         <v>3</v>
       </c>
@@ -1896,6 +2029,9 @@
         <v/>
       </c>
       <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
         <v/>
       </c>
       <c r="P29" t="str">
@@ -1918,6 +2054,9 @@
       <c r="C30" t="str">
         <v/>
       </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
       <c r="E30">
         <v>2</v>
       </c>
@@ -1946,6 +2085,9 @@
         <v/>
       </c>
       <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
         <v/>
       </c>
       <c r="P30" t="str">
@@ -1968,6 +2110,9 @@
       <c r="C31" t="str">
         <v/>
       </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
       <c r="E31">
         <v>1</v>
       </c>
@@ -1996,6 +2141,9 @@
         <v/>
       </c>
       <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
         <v/>
       </c>
       <c r="P31" t="str">
@@ -2018,6 +2166,9 @@
       <c r="C32" t="str">
         <v/>
       </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
       <c r="E32">
         <v>1</v>
       </c>
@@ -2046,6 +2197,9 @@
         <v/>
       </c>
       <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
         <v/>
       </c>
       <c r="P32" t="str">
@@ -2124,6 +2278,9 @@
       <c r="C34" t="str">
         <v/>
       </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
       <c r="E34">
         <v>3</v>
       </c>
@@ -2152,6 +2309,9 @@
         <v/>
       </c>
       <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
         <v/>
       </c>
       <c r="P34" t="str">
@@ -2174,6 +2334,9 @@
       <c r="C35" t="str">
         <v/>
       </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
       <c r="E35">
         <v>2</v>
       </c>
@@ -2202,6 +2365,9 @@
         <v/>
       </c>
       <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
         <v/>
       </c>
       <c r="P35" t="str">
@@ -2224,6 +2390,9 @@
       <c r="C36" t="str">
         <v/>
       </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
       <c r="E36">
         <v>2</v>
       </c>
@@ -2252,6 +2421,9 @@
         <v/>
       </c>
       <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
         <v/>
       </c>
       <c r="P36" t="str">
@@ -2274,6 +2446,9 @@
       <c r="C37" t="str">
         <v/>
       </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
       <c r="E37">
         <v>3</v>
       </c>
@@ -2302,6 +2477,9 @@
         <v/>
       </c>
       <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
         <v/>
       </c>
       <c r="P37" t="str">
@@ -2324,6 +2502,9 @@
       <c r="C38" t="str">
         <v/>
       </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
       <c r="E38">
         <v>2</v>
       </c>
@@ -2352,6 +2533,9 @@
         <v/>
       </c>
       <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
         <v/>
       </c>
       <c r="P38" t="str">
@@ -2374,6 +2558,9 @@
       <c r="C39" t="str">
         <v/>
       </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
       <c r="E39">
         <v>1</v>
       </c>
@@ -2402,6 +2589,9 @@
         <v/>
       </c>
       <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
         <v/>
       </c>
       <c r="P39" t="str">
@@ -2424,6 +2614,9 @@
       <c r="C40" t="str">
         <v/>
       </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
       <c r="E40">
         <v>1</v>
       </c>
@@ -2452,6 +2645,9 @@
         <v/>
       </c>
       <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
         <v/>
       </c>
       <c r="P40" t="str">
@@ -2530,6 +2726,9 @@
       <c r="C42" t="str">
         <v/>
       </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
       <c r="E42">
         <v>3</v>
       </c>
@@ -2558,6 +2757,9 @@
         <v/>
       </c>
       <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
         <v/>
       </c>
       <c r="P42" t="str">
@@ -2580,6 +2782,9 @@
       <c r="C43" t="str">
         <v/>
       </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
       <c r="E43">
         <v>2</v>
       </c>
@@ -2608,6 +2813,9 @@
         <v/>
       </c>
       <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
         <v/>
       </c>
       <c r="P43" t="str">
@@ -2630,6 +2838,9 @@
       <c r="C44" t="str">
         <v/>
       </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
       <c r="E44">
         <v>2</v>
       </c>
@@ -2658,6 +2869,9 @@
         <v/>
       </c>
       <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
         <v/>
       </c>
       <c r="P44" t="str">
@@ -2680,6 +2894,9 @@
       <c r="C45" t="str">
         <v/>
       </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
       <c r="E45">
         <v>3</v>
       </c>
@@ -2708,6 +2925,9 @@
         <v/>
       </c>
       <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v/>
       </c>
       <c r="P45" t="str">
@@ -2730,6 +2950,9 @@
       <c r="C46" t="str">
         <v/>
       </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
       <c r="E46">
         <v>2</v>
       </c>
@@ -2758,6 +2981,9 @@
         <v/>
       </c>
       <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
         <v/>
       </c>
       <c r="P46" t="str">
@@ -2780,6 +3006,9 @@
       <c r="C47" t="str">
         <v/>
       </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
       <c r="E47">
         <v>1</v>
       </c>
@@ -2808,6 +3037,9 @@
         <v/>
       </c>
       <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
         <v/>
       </c>
       <c r="P47" t="str">
@@ -2830,6 +3062,9 @@
       <c r="C48" t="str">
         <v/>
       </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
       <c r="E48">
         <v>1</v>
       </c>
@@ -2858,6 +3093,9 @@
         <v/>
       </c>
       <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
         <v/>
       </c>
       <c r="P48" t="str">
@@ -2936,6 +3174,9 @@
       <c r="C50" t="str">
         <v/>
       </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
       <c r="E50">
         <v>3</v>
       </c>
@@ -2964,6 +3205,9 @@
         <v/>
       </c>
       <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v/>
       </c>
       <c r="P50" t="str">
@@ -2986,6 +3230,9 @@
       <c r="C51" t="str">
         <v/>
       </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
       <c r="E51">
         <v>2</v>
       </c>
@@ -3014,6 +3261,9 @@
         <v/>
       </c>
       <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
         <v/>
       </c>
       <c r="P51" t="str">
@@ -3036,6 +3286,9 @@
       <c r="C52" t="str">
         <v/>
       </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
       <c r="E52">
         <v>2</v>
       </c>
@@ -3064,6 +3317,9 @@
         <v/>
       </c>
       <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
         <v/>
       </c>
       <c r="P52" t="str">
@@ -3086,6 +3342,9 @@
       <c r="C53" t="str">
         <v/>
       </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
       <c r="E53">
         <v>3</v>
       </c>
@@ -3114,6 +3373,9 @@
         <v/>
       </c>
       <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
         <v/>
       </c>
       <c r="P53" t="str">
@@ -3136,6 +3398,9 @@
       <c r="C54" t="str">
         <v/>
       </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
       <c r="E54">
         <v>2</v>
       </c>
@@ -3164,6 +3429,9 @@
         <v/>
       </c>
       <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
         <v/>
       </c>
       <c r="P54" t="str">
@@ -3186,6 +3454,9 @@
       <c r="C55" t="str">
         <v/>
       </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
       <c r="E55">
         <v>1</v>
       </c>
@@ -3214,6 +3485,9 @@
         <v/>
       </c>
       <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
         <v/>
       </c>
       <c r="P55" t="str">
@@ -3236,6 +3510,9 @@
       <c r="C56" t="str">
         <v/>
       </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
       <c r="E56">
         <v>1</v>
       </c>
@@ -3264,6 +3541,9 @@
         <v/>
       </c>
       <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v/>
       </c>
       <c r="P56" t="str">
@@ -3342,6 +3622,9 @@
       <c r="C58" t="str">
         <v/>
       </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
       <c r="E58">
         <v>3</v>
       </c>
@@ -3370,6 +3653,9 @@
         <v/>
       </c>
       <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v/>
       </c>
       <c r="P58" t="str">
@@ -3392,6 +3678,9 @@
       <c r="C59" t="str">
         <v/>
       </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
       <c r="E59">
         <v>2</v>
       </c>
@@ -3420,6 +3709,9 @@
         <v/>
       </c>
       <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
         <v/>
       </c>
       <c r="P59" t="str">
@@ -3442,6 +3734,9 @@
       <c r="C60" t="str">
         <v/>
       </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
       <c r="E60">
         <v>2</v>
       </c>
@@ -3470,6 +3765,9 @@
         <v/>
       </c>
       <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
         <v/>
       </c>
       <c r="P60" t="str">
@@ -3492,6 +3790,9 @@
       <c r="C61" t="str">
         <v/>
       </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
       <c r="E61">
         <v>3</v>
       </c>
@@ -3520,6 +3821,9 @@
         <v/>
       </c>
       <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
         <v/>
       </c>
       <c r="P61" t="str">
@@ -3542,6 +3846,9 @@
       <c r="C62" t="str">
         <v/>
       </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
       <c r="E62">
         <v>2</v>
       </c>
@@ -3570,6 +3877,9 @@
         <v/>
       </c>
       <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
         <v/>
       </c>
       <c r="P62" t="str">
@@ -3592,6 +3902,9 @@
       <c r="C63" t="str">
         <v/>
       </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
       <c r="E63">
         <v>1</v>
       </c>
@@ -3620,6 +3933,9 @@
         <v/>
       </c>
       <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
         <v/>
       </c>
       <c r="P63" t="str">
@@ -3642,6 +3958,9 @@
       <c r="C64" t="str">
         <v/>
       </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
       <c r="E64">
         <v>1</v>
       </c>
@@ -3670,6 +3989,9 @@
         <v/>
       </c>
       <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
         <v/>
       </c>
       <c r="P64" t="str">
@@ -3748,6 +4070,9 @@
       <c r="C66" t="str">
         <v/>
       </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
       <c r="E66">
         <v>3</v>
       </c>
@@ -3776,6 +4101,9 @@
         <v/>
       </c>
       <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
         <v/>
       </c>
       <c r="P66" t="str">
@@ -3798,6 +4126,9 @@
       <c r="C67" t="str">
         <v/>
       </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
       <c r="E67">
         <v>2</v>
       </c>
@@ -3826,6 +4157,9 @@
         <v/>
       </c>
       <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
         <v/>
       </c>
       <c r="P67" t="str">
@@ -3848,6 +4182,9 @@
       <c r="C68" t="str">
         <v/>
       </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
       <c r="E68">
         <v>2</v>
       </c>
@@ -3876,6 +4213,9 @@
         <v/>
       </c>
       <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
         <v/>
       </c>
       <c r="P68" t="str">
@@ -3898,6 +4238,9 @@
       <c r="C69" t="str">
         <v/>
       </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
       <c r="E69">
         <v>3</v>
       </c>
@@ -3926,6 +4269,9 @@
         <v/>
       </c>
       <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
         <v/>
       </c>
       <c r="P69" t="str">
@@ -3948,6 +4294,9 @@
       <c r="C70" t="str">
         <v/>
       </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
       <c r="E70">
         <v>2</v>
       </c>
@@ -3976,6 +4325,9 @@
         <v/>
       </c>
       <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
         <v/>
       </c>
       <c r="P70" t="str">
@@ -3998,6 +4350,9 @@
       <c r="C71" t="str">
         <v/>
       </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
       <c r="E71">
         <v>1</v>
       </c>
@@ -4026,6 +4381,9 @@
         <v/>
       </c>
       <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
         <v/>
       </c>
       <c r="P71" t="str">
@@ -4048,6 +4406,9 @@
       <c r="C72" t="str">
         <v/>
       </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
       <c r="E72">
         <v>1</v>
       </c>
@@ -4076,6 +4437,9 @@
         <v/>
       </c>
       <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
         <v/>
       </c>
       <c r="P72" t="str">
@@ -4154,6 +4518,9 @@
       <c r="C74" t="str">
         <v/>
       </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
       <c r="E74">
         <v>3</v>
       </c>
@@ -4182,6 +4549,9 @@
         <v/>
       </c>
       <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
         <v/>
       </c>
       <c r="P74" t="str">
@@ -4204,6 +4574,9 @@
       <c r="C75" t="str">
         <v/>
       </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
       <c r="E75">
         <v>2</v>
       </c>
@@ -4232,6 +4605,9 @@
         <v/>
       </c>
       <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
         <v/>
       </c>
       <c r="P75" t="str">
@@ -4254,6 +4630,9 @@
       <c r="C76" t="str">
         <v/>
       </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
       <c r="E76">
         <v>2</v>
       </c>
@@ -4282,6 +4661,9 @@
         <v/>
       </c>
       <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
         <v/>
       </c>
       <c r="P76" t="str">
@@ -4304,6 +4686,9 @@
       <c r="C77" t="str">
         <v/>
       </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
       <c r="E77">
         <v>3</v>
       </c>
@@ -4332,6 +4717,9 @@
         <v/>
       </c>
       <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
         <v/>
       </c>
       <c r="P77" t="str">
@@ -4354,6 +4742,9 @@
       <c r="C78" t="str">
         <v/>
       </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
       <c r="E78">
         <v>2</v>
       </c>
@@ -4382,6 +4773,9 @@
         <v/>
       </c>
       <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
         <v/>
       </c>
       <c r="P78" t="str">
@@ -4404,6 +4798,9 @@
       <c r="C79" t="str">
         <v/>
       </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
       <c r="E79">
         <v>1</v>
       </c>
@@ -4432,6 +4829,9 @@
         <v/>
       </c>
       <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
         <v/>
       </c>
       <c r="P79" t="str">
@@ -4454,6 +4854,9 @@
       <c r="C80" t="str">
         <v/>
       </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
       <c r="E80">
         <v>1</v>
       </c>
@@ -4482,6 +4885,9 @@
         <v/>
       </c>
       <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
         <v/>
       </c>
       <c r="P80" t="str">
@@ -4560,6 +4966,9 @@
       <c r="C82" t="str">
         <v/>
       </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
       <c r="E82">
         <v>3</v>
       </c>
@@ -4588,6 +4997,9 @@
         <v/>
       </c>
       <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
         <v/>
       </c>
       <c r="P82" t="str">
@@ -4610,6 +5022,9 @@
       <c r="C83" t="str">
         <v/>
       </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
       <c r="E83">
         <v>2</v>
       </c>
@@ -4638,6 +5053,9 @@
         <v/>
       </c>
       <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
         <v/>
       </c>
       <c r="P83" t="str">
@@ -4660,6 +5078,9 @@
       <c r="C84" t="str">
         <v/>
       </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
       <c r="E84">
         <v>2</v>
       </c>
@@ -4688,6 +5109,9 @@
         <v/>
       </c>
       <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
         <v/>
       </c>
       <c r="P84" t="str">
@@ -4710,6 +5134,9 @@
       <c r="C85" t="str">
         <v/>
       </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
       <c r="E85">
         <v>3</v>
       </c>
@@ -4738,6 +5165,9 @@
         <v/>
       </c>
       <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
         <v/>
       </c>
       <c r="P85" t="str">
@@ -4760,6 +5190,9 @@
       <c r="C86" t="str">
         <v/>
       </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
       <c r="E86">
         <v>2</v>
       </c>
@@ -4788,6 +5221,9 @@
         <v/>
       </c>
       <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
         <v/>
       </c>
       <c r="P86" t="str">
@@ -4810,6 +5246,9 @@
       <c r="C87" t="str">
         <v/>
       </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
       <c r="E87">
         <v>1</v>
       </c>
@@ -4838,6 +5277,9 @@
         <v/>
       </c>
       <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
         <v/>
       </c>
       <c r="P87" t="str">
@@ -4860,6 +5302,9 @@
       <c r="C88" t="str">
         <v/>
       </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
       <c r="E88">
         <v>1</v>
       </c>
@@ -4888,6 +5333,9 @@
         <v/>
       </c>
       <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
         <v/>
       </c>
       <c r="P88" t="str">
@@ -4966,6 +5414,9 @@
       <c r="C90" t="str">
         <v/>
       </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
       <c r="E90">
         <v>3</v>
       </c>
@@ -4994,6 +5445,9 @@
         <v/>
       </c>
       <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
         <v/>
       </c>
       <c r="P90" t="str">
@@ -5016,6 +5470,9 @@
       <c r="C91" t="str">
         <v/>
       </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
       <c r="E91">
         <v>2</v>
       </c>
@@ -5044,6 +5501,9 @@
         <v/>
       </c>
       <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
         <v/>
       </c>
       <c r="P91" t="str">
@@ -5066,6 +5526,9 @@
       <c r="C92" t="str">
         <v/>
       </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
       <c r="E92">
         <v>2</v>
       </c>
@@ -5094,6 +5557,9 @@
         <v/>
       </c>
       <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
         <v/>
       </c>
       <c r="P92" t="str">
@@ -5116,6 +5582,9 @@
       <c r="C93" t="str">
         <v/>
       </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
       <c r="E93">
         <v>3</v>
       </c>
@@ -5144,6 +5613,9 @@
         <v/>
       </c>
       <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
         <v/>
       </c>
       <c r="P93" t="str">
@@ -5166,6 +5638,9 @@
       <c r="C94" t="str">
         <v/>
       </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
       <c r="E94">
         <v>2</v>
       </c>
@@ -5194,6 +5669,9 @@
         <v/>
       </c>
       <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
         <v/>
       </c>
       <c r="P94" t="str">
@@ -5216,6 +5694,9 @@
       <c r="C95" t="str">
         <v/>
       </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
       <c r="E95">
         <v>1</v>
       </c>
@@ -5244,6 +5725,9 @@
         <v/>
       </c>
       <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
         <v/>
       </c>
       <c r="P95" t="str">
@@ -5266,6 +5750,9 @@
       <c r="C96" t="str">
         <v/>
       </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
       <c r="E96">
         <v>1</v>
       </c>
@@ -5294,6 +5781,9 @@
         <v/>
       </c>
       <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
         <v/>
       </c>
       <c r="P96" t="str">
@@ -5372,6 +5862,9 @@
       <c r="C98" t="str">
         <v/>
       </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
       <c r="E98">
         <v>3</v>
       </c>
@@ -5400,6 +5893,9 @@
         <v/>
       </c>
       <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
         <v/>
       </c>
       <c r="P98" t="str">
@@ -5422,6 +5918,9 @@
       <c r="C99" t="str">
         <v/>
       </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
       <c r="E99">
         <v>2</v>
       </c>
@@ -5450,6 +5949,9 @@
         <v/>
       </c>
       <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
         <v/>
       </c>
       <c r="P99" t="str">
@@ -5472,6 +5974,9 @@
       <c r="C100" t="str">
         <v/>
       </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
       <c r="E100">
         <v>2</v>
       </c>
@@ -5500,6 +6005,9 @@
         <v/>
       </c>
       <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
         <v/>
       </c>
       <c r="P100" t="str">
@@ -5522,6 +6030,9 @@
       <c r="C101" t="str">
         <v/>
       </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
       <c r="E101">
         <v>3</v>
       </c>
@@ -5550,6 +6061,9 @@
         <v/>
       </c>
       <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
         <v/>
       </c>
       <c r="P101" t="str">
@@ -5572,6 +6086,9 @@
       <c r="C102" t="str">
         <v/>
       </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
       <c r="E102">
         <v>2</v>
       </c>
@@ -5600,6 +6117,9 @@
         <v/>
       </c>
       <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
         <v/>
       </c>
       <c r="P102" t="str">
@@ -5622,6 +6142,9 @@
       <c r="C103" t="str">
         <v/>
       </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
       <c r="E103">
         <v>1</v>
       </c>
@@ -5650,6 +6173,9 @@
         <v/>
       </c>
       <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
         <v/>
       </c>
       <c r="P103" t="str">
@@ -5672,6 +6198,9 @@
       <c r="C104" t="str">
         <v/>
       </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
       <c r="E104">
         <v>1</v>
       </c>
@@ -5700,6 +6229,9 @@
         <v/>
       </c>
       <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
         <v/>
       </c>
       <c r="P104" t="str">
@@ -5778,6 +6310,9 @@
       <c r="C106" t="str">
         <v/>
       </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
       <c r="E106">
         <v>3</v>
       </c>
@@ -5806,6 +6341,9 @@
         <v/>
       </c>
       <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
         <v/>
       </c>
       <c r="P106" t="str">
@@ -5828,6 +6366,9 @@
       <c r="C107" t="str">
         <v/>
       </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
       <c r="E107">
         <v>2</v>
       </c>
@@ -5856,6 +6397,9 @@
         <v/>
       </c>
       <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
         <v/>
       </c>
       <c r="P107" t="str">
@@ -5878,6 +6422,9 @@
       <c r="C108" t="str">
         <v/>
       </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
       <c r="E108">
         <v>2</v>
       </c>
@@ -5906,6 +6453,9 @@
         <v/>
       </c>
       <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
         <v/>
       </c>
       <c r="P108" t="str">
@@ -5928,6 +6478,9 @@
       <c r="C109" t="str">
         <v/>
       </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
       <c r="E109">
         <v>3</v>
       </c>
@@ -5956,6 +6509,9 @@
         <v/>
       </c>
       <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
         <v/>
       </c>
       <c r="P109" t="str">
@@ -5978,6 +6534,9 @@
       <c r="C110" t="str">
         <v/>
       </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
       <c r="E110">
         <v>2</v>
       </c>
@@ -6006,6 +6565,9 @@
         <v/>
       </c>
       <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
         <v/>
       </c>
       <c r="P110" t="str">
@@ -6028,6 +6590,9 @@
       <c r="C111" t="str">
         <v/>
       </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
       <c r="E111">
         <v>1</v>
       </c>
@@ -6056,6 +6621,9 @@
         <v/>
       </c>
       <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
         <v/>
       </c>
       <c r="P111" t="str">
@@ -6078,6 +6646,9 @@
       <c r="C112" t="str">
         <v/>
       </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
       <c r="E112">
         <v>1</v>
       </c>
@@ -6106,6 +6677,9 @@
         <v/>
       </c>
       <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
         <v/>
       </c>
       <c r="P112" t="str">
@@ -6184,6 +6758,9 @@
       <c r="C114" t="str">
         <v/>
       </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
       <c r="E114">
         <v>3</v>
       </c>
@@ -6212,6 +6789,9 @@
         <v/>
       </c>
       <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
         <v/>
       </c>
       <c r="P114" t="str">
@@ -6234,6 +6814,9 @@
       <c r="C115" t="str">
         <v/>
       </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
       <c r="E115">
         <v>2</v>
       </c>
@@ -6262,6 +6845,9 @@
         <v/>
       </c>
       <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
         <v/>
       </c>
       <c r="P115" t="str">
@@ -6284,6 +6870,9 @@
       <c r="C116" t="str">
         <v/>
       </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
       <c r="E116">
         <v>2</v>
       </c>
@@ -6312,6 +6901,9 @@
         <v/>
       </c>
       <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
         <v/>
       </c>
       <c r="P116" t="str">
@@ -6334,6 +6926,9 @@
       <c r="C117" t="str">
         <v/>
       </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
       <c r="E117">
         <v>3</v>
       </c>
@@ -6362,6 +6957,9 @@
         <v/>
       </c>
       <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
         <v/>
       </c>
       <c r="P117" t="str">
@@ -6384,6 +6982,9 @@
       <c r="C118" t="str">
         <v/>
       </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
       <c r="E118">
         <v>2</v>
       </c>
@@ -6412,6 +7013,9 @@
         <v/>
       </c>
       <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
         <v/>
       </c>
       <c r="P118" t="str">
@@ -6434,6 +7038,9 @@
       <c r="C119" t="str">
         <v/>
       </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
       <c r="E119">
         <v>1</v>
       </c>
@@ -6462,6 +7069,9 @@
         <v/>
       </c>
       <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
         <v/>
       </c>
       <c r="P119" t="str">
@@ -6484,6 +7094,9 @@
       <c r="C120" t="str">
         <v/>
       </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
       <c r="E120">
         <v>1</v>
       </c>
@@ -6512,6 +7125,9 @@
         <v/>
       </c>
       <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
         <v/>
       </c>
       <c r="P120" t="str">
@@ -6590,6 +7206,9 @@
       <c r="C122" t="str">
         <v/>
       </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
       <c r="E122">
         <v>3</v>
       </c>
@@ -6618,6 +7237,9 @@
         <v/>
       </c>
       <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
         <v/>
       </c>
       <c r="P122" t="str">
@@ -6640,6 +7262,9 @@
       <c r="C123" t="str">
         <v/>
       </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
       <c r="E123">
         <v>2</v>
       </c>
@@ -6668,6 +7293,9 @@
         <v/>
       </c>
       <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
         <v/>
       </c>
       <c r="P123" t="str">
@@ -6690,6 +7318,9 @@
       <c r="C124" t="str">
         <v/>
       </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
       <c r="E124">
         <v>2</v>
       </c>
@@ -6718,6 +7349,9 @@
         <v/>
       </c>
       <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
         <v/>
       </c>
       <c r="P124" t="str">
@@ -6740,6 +7374,9 @@
       <c r="C125" t="str">
         <v/>
       </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
       <c r="E125">
         <v>3</v>
       </c>
@@ -6768,6 +7405,9 @@
         <v/>
       </c>
       <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
         <v/>
       </c>
       <c r="P125" t="str">
@@ -6790,6 +7430,9 @@
       <c r="C126" t="str">
         <v/>
       </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
       <c r="E126">
         <v>2</v>
       </c>
@@ -6818,6 +7461,9 @@
         <v/>
       </c>
       <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
         <v/>
       </c>
       <c r="P126" t="str">
@@ -6840,6 +7486,9 @@
       <c r="C127" t="str">
         <v/>
       </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
       <c r="E127">
         <v>1</v>
       </c>
@@ -6868,6 +7517,9 @@
         <v/>
       </c>
       <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
         <v/>
       </c>
       <c r="P127" t="str">
@@ -6890,6 +7542,9 @@
       <c r="C128" t="str">
         <v/>
       </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
       <c r="E128">
         <v>1</v>
       </c>
@@ -6918,6 +7573,9 @@
         <v/>
       </c>
       <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
         <v/>
       </c>
       <c r="P128" t="str">
@@ -6996,6 +7654,9 @@
       <c r="C130" t="str">
         <v/>
       </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
       <c r="E130">
         <v>3</v>
       </c>
@@ -7024,6 +7685,9 @@
         <v/>
       </c>
       <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
         <v/>
       </c>
       <c r="P130" t="str">
@@ -7046,6 +7710,9 @@
       <c r="C131" t="str">
         <v/>
       </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
       <c r="E131">
         <v>2</v>
       </c>
@@ -7074,6 +7741,9 @@
         <v/>
       </c>
       <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
         <v/>
       </c>
       <c r="P131" t="str">
@@ -7096,6 +7766,9 @@
       <c r="C132" t="str">
         <v/>
       </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
       <c r="E132">
         <v>2</v>
       </c>
@@ -7124,6 +7797,9 @@
         <v/>
       </c>
       <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
         <v/>
       </c>
       <c r="P132" t="str">
@@ -7146,6 +7822,9 @@
       <c r="C133" t="str">
         <v/>
       </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
       <c r="E133">
         <v>3</v>
       </c>
@@ -7174,6 +7853,9 @@
         <v/>
       </c>
       <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
         <v/>
       </c>
       <c r="P133" t="str">
@@ -7196,6 +7878,9 @@
       <c r="C134" t="str">
         <v/>
       </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
       <c r="E134">
         <v>2</v>
       </c>
@@ -7224,6 +7909,9 @@
         <v/>
       </c>
       <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
         <v/>
       </c>
       <c r="P134" t="str">
@@ -7246,6 +7934,9 @@
       <c r="C135" t="str">
         <v/>
       </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
       <c r="E135">
         <v>1</v>
       </c>
@@ -7274,6 +7965,9 @@
         <v/>
       </c>
       <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
         <v/>
       </c>
       <c r="P135" t="str">
@@ -7296,6 +7990,9 @@
       <c r="C136" t="str">
         <v/>
       </c>
+      <c r="D136" t="str">
+        <v/>
+      </c>
       <c r="E136">
         <v>1</v>
       </c>
@@ -7324,6 +8021,9 @@
         <v/>
       </c>
       <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
         <v/>
       </c>
       <c r="P136" t="str">
@@ -7458,6 +8158,9 @@
       <c r="C139" t="str">
         <v/>
       </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
       <c r="E139">
         <v>2</v>
       </c>
@@ -7486,6 +8189,9 @@
         <v/>
       </c>
       <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
         <v/>
       </c>
       <c r="P139" t="str">
@@ -7508,6 +8214,9 @@
       <c r="C140" t="str">
         <v/>
       </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
       <c r="E140">
         <v>7</v>
       </c>
@@ -7536,6 +8245,9 @@
         <v/>
       </c>
       <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
         <v/>
       </c>
       <c r="P140" t="str">
@@ -7558,6 +8270,9 @@
       <c r="C141" t="str">
         <v/>
       </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
       <c r="E141">
         <v>1</v>
       </c>
@@ -7586,6 +8301,9 @@
         <v/>
       </c>
       <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
         <v/>
       </c>
       <c r="P141" t="str">
@@ -7608,6 +8326,9 @@
       <c r="C142" t="str">
         <v/>
       </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
       <c r="E142">
         <v>5</v>
       </c>
@@ -7636,6 +8357,9 @@
         <v/>
       </c>
       <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
         <v/>
       </c>
       <c r="P142" t="str">
@@ -7658,6 +8382,9 @@
       <c r="C143" t="str">
         <v/>
       </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
       <c r="E143">
         <v>2</v>
       </c>
@@ -7686,6 +8413,9 @@
         <v/>
       </c>
       <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
         <v/>
       </c>
       <c r="P143" t="str">
@@ -7764,6 +8494,9 @@
       <c r="C145" t="str">
         <v/>
       </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
       <c r="E145">
         <v>2</v>
       </c>
@@ -7792,6 +8525,9 @@
         <v/>
       </c>
       <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
         <v/>
       </c>
       <c r="P145" t="str">
@@ -7814,6 +8550,9 @@
       <c r="C146" t="str">
         <v/>
       </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
       <c r="E146">
         <v>7</v>
       </c>
@@ -7842,6 +8581,9 @@
         <v/>
       </c>
       <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
         <v/>
       </c>
       <c r="P146" t="str">
@@ -7864,6 +8606,9 @@
       <c r="C147" t="str">
         <v/>
       </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
       <c r="E147">
         <v>1</v>
       </c>
@@ -7892,6 +8637,9 @@
         <v/>
       </c>
       <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
         <v/>
       </c>
       <c r="P147" t="str">
@@ -7914,6 +8662,9 @@
       <c r="C148" t="str">
         <v/>
       </c>
+      <c r="D148" t="str">
+        <v/>
+      </c>
       <c r="E148">
         <v>5</v>
       </c>
@@ -7942,6 +8693,9 @@
         <v/>
       </c>
       <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
         <v/>
       </c>
       <c r="P148" t="str">
@@ -7964,6 +8718,9 @@
       <c r="C149" t="str">
         <v/>
       </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
       <c r="E149">
         <v>2</v>
       </c>
@@ -7992,6 +8749,9 @@
         <v/>
       </c>
       <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
         <v/>
       </c>
       <c r="P149" t="str">
@@ -8070,6 +8830,9 @@
       <c r="C151" t="str">
         <v/>
       </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
       <c r="E151">
         <v>2</v>
       </c>
@@ -8098,6 +8861,9 @@
         <v/>
       </c>
       <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
         <v/>
       </c>
       <c r="P151" t="str">
@@ -8120,6 +8886,9 @@
       <c r="C152" t="str">
         <v/>
       </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
       <c r="E152">
         <v>7</v>
       </c>
@@ -8148,6 +8917,9 @@
         <v/>
       </c>
       <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
         <v/>
       </c>
       <c r="P152" t="str">
@@ -8170,6 +8942,9 @@
       <c r="C153" t="str">
         <v/>
       </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
       <c r="E153">
         <v>1</v>
       </c>
@@ -8198,6 +8973,9 @@
         <v/>
       </c>
       <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
         <v/>
       </c>
       <c r="P153" t="str">
@@ -8220,6 +8998,9 @@
       <c r="C154" t="str">
         <v/>
       </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
       <c r="E154">
         <v>5</v>
       </c>
@@ -8248,6 +9029,9 @@
         <v/>
       </c>
       <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
         <v/>
       </c>
       <c r="P154" t="str">
@@ -8270,6 +9054,9 @@
       <c r="C155" t="str">
         <v/>
       </c>
+      <c r="D155" t="str">
+        <v/>
+      </c>
       <c r="E155">
         <v>2</v>
       </c>
@@ -8298,6 +9085,9 @@
         <v/>
       </c>
       <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
         <v/>
       </c>
       <c r="P155" t="str">
@@ -8376,6 +9166,9 @@
       <c r="C157" t="str">
         <v/>
       </c>
+      <c r="D157" t="str">
+        <v/>
+      </c>
       <c r="E157">
         <v>2</v>
       </c>
@@ -8404,6 +9197,9 @@
         <v/>
       </c>
       <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
         <v/>
       </c>
       <c r="P157" t="str">
@@ -8426,6 +9222,9 @@
       <c r="C158" t="str">
         <v/>
       </c>
+      <c r="D158" t="str">
+        <v/>
+      </c>
       <c r="E158">
         <v>7</v>
       </c>
@@ -8454,6 +9253,9 @@
         <v/>
       </c>
       <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
         <v/>
       </c>
       <c r="P158" t="str">
@@ -8476,6 +9278,9 @@
       <c r="C159" t="str">
         <v/>
       </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
       <c r="E159">
         <v>1</v>
       </c>
@@ -8504,6 +9309,9 @@
         <v/>
       </c>
       <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
         <v/>
       </c>
       <c r="P159" t="str">
@@ -8526,6 +9334,9 @@
       <c r="C160" t="str">
         <v/>
       </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
       <c r="E160">
         <v>5</v>
       </c>
@@ -8554,6 +9365,9 @@
         <v/>
       </c>
       <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
         <v/>
       </c>
       <c r="P160" t="str">
@@ -8576,6 +9390,9 @@
       <c r="C161" t="str">
         <v/>
       </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
       <c r="E161">
         <v>2</v>
       </c>
@@ -8604,6 +9421,9 @@
         <v/>
       </c>
       <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
         <v/>
       </c>
       <c r="P161" t="str">
@@ -8682,6 +9502,9 @@
       <c r="C163" t="str">
         <v/>
       </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
       <c r="E163">
         <v>2</v>
       </c>
@@ -8710,6 +9533,9 @@
         <v/>
       </c>
       <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
         <v/>
       </c>
       <c r="P163" t="str">
@@ -8732,6 +9558,9 @@
       <c r="C164" t="str">
         <v/>
       </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
       <c r="E164">
         <v>7</v>
       </c>
@@ -8760,6 +9589,9 @@
         <v/>
       </c>
       <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
         <v/>
       </c>
       <c r="P164" t="str">
@@ -8782,6 +9614,9 @@
       <c r="C165" t="str">
         <v/>
       </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
       <c r="E165">
         <v>1</v>
       </c>
@@ -8810,6 +9645,9 @@
         <v/>
       </c>
       <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
         <v/>
       </c>
       <c r="P165" t="str">
@@ -8832,6 +9670,9 @@
       <c r="C166" t="str">
         <v/>
       </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
       <c r="E166">
         <v>5</v>
       </c>
@@ -8860,6 +9701,9 @@
         <v/>
       </c>
       <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
         <v/>
       </c>
       <c r="P166" t="str">
@@ -8882,6 +9726,9 @@
       <c r="C167" t="str">
         <v/>
       </c>
+      <c r="D167" t="str">
+        <v/>
+      </c>
       <c r="E167">
         <v>2</v>
       </c>
@@ -8910,6 +9757,9 @@
         <v/>
       </c>
       <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
         <v/>
       </c>
       <c r="P167" t="str">
@@ -8988,6 +9838,9 @@
       <c r="C169" t="str">
         <v/>
       </c>
+      <c r="D169" t="str">
+        <v/>
+      </c>
       <c r="E169">
         <v>2</v>
       </c>
@@ -9016,6 +9869,9 @@
         <v/>
       </c>
       <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
         <v/>
       </c>
       <c r="P169" t="str">
@@ -9038,6 +9894,9 @@
       <c r="C170" t="str">
         <v/>
       </c>
+      <c r="D170" t="str">
+        <v/>
+      </c>
       <c r="E170">
         <v>7</v>
       </c>
@@ -9066,6 +9925,9 @@
         <v/>
       </c>
       <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
         <v/>
       </c>
       <c r="P170" t="str">
@@ -9088,6 +9950,9 @@
       <c r="C171" t="str">
         <v/>
       </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
       <c r="E171">
         <v>1</v>
       </c>
@@ -9116,6 +9981,9 @@
         <v/>
       </c>
       <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
         <v/>
       </c>
       <c r="P171" t="str">
@@ -9138,6 +10006,9 @@
       <c r="C172" t="str">
         <v/>
       </c>
+      <c r="D172" t="str">
+        <v/>
+      </c>
       <c r="E172">
         <v>5</v>
       </c>
@@ -9166,6 +10037,9 @@
         <v/>
       </c>
       <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
         <v/>
       </c>
       <c r="P172" t="str">
@@ -9188,6 +10062,9 @@
       <c r="C173" t="str">
         <v/>
       </c>
+      <c r="D173" t="str">
+        <v/>
+      </c>
       <c r="E173">
         <v>2</v>
       </c>
@@ -9216,6 +10093,9 @@
         <v/>
       </c>
       <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
         <v/>
       </c>
       <c r="P173" t="str">
@@ -9294,6 +10174,9 @@
       <c r="C175" t="str">
         <v/>
       </c>
+      <c r="D175" t="str">
+        <v/>
+      </c>
       <c r="E175">
         <v>2</v>
       </c>
@@ -9322,6 +10205,9 @@
         <v/>
       </c>
       <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
         <v/>
       </c>
       <c r="P175" t="str">
@@ -9344,6 +10230,9 @@
       <c r="C176" t="str">
         <v/>
       </c>
+      <c r="D176" t="str">
+        <v/>
+      </c>
       <c r="E176">
         <v>7</v>
       </c>
@@ -9372,6 +10261,9 @@
         <v/>
       </c>
       <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
         <v/>
       </c>
       <c r="P176" t="str">
@@ -9394,6 +10286,9 @@
       <c r="C177" t="str">
         <v/>
       </c>
+      <c r="D177" t="str">
+        <v/>
+      </c>
       <c r="E177">
         <v>1</v>
       </c>
@@ -9422,6 +10317,9 @@
         <v/>
       </c>
       <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
         <v/>
       </c>
       <c r="P177" t="str">
@@ -9444,6 +10342,9 @@
       <c r="C178" t="str">
         <v/>
       </c>
+      <c r="D178" t="str">
+        <v/>
+      </c>
       <c r="E178">
         <v>5</v>
       </c>
@@ -9472,6 +10373,9 @@
         <v/>
       </c>
       <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
         <v/>
       </c>
       <c r="P178" t="str">
@@ -9494,6 +10398,9 @@
       <c r="C179" t="str">
         <v/>
       </c>
+      <c r="D179" t="str">
+        <v/>
+      </c>
       <c r="E179">
         <v>2</v>
       </c>
@@ -9522,6 +10429,9 @@
         <v/>
       </c>
       <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
         <v/>
       </c>
       <c r="P179" t="str">
@@ -9600,6 +10510,9 @@
       <c r="C181" t="str">
         <v/>
       </c>
+      <c r="D181" t="str">
+        <v/>
+      </c>
       <c r="E181">
         <v>2</v>
       </c>
@@ -9628,6 +10541,9 @@
         <v/>
       </c>
       <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
         <v/>
       </c>
       <c r="P181" t="str">
@@ -9650,6 +10566,9 @@
       <c r="C182" t="str">
         <v/>
       </c>
+      <c r="D182" t="str">
+        <v/>
+      </c>
       <c r="E182">
         <v>7</v>
       </c>
@@ -9678,6 +10597,9 @@
         <v/>
       </c>
       <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
         <v/>
       </c>
       <c r="P182" t="str">
@@ -9700,6 +10622,9 @@
       <c r="C183" t="str">
         <v/>
       </c>
+      <c r="D183" t="str">
+        <v/>
+      </c>
       <c r="E183">
         <v>1</v>
       </c>
@@ -9728,6 +10653,9 @@
         <v/>
       </c>
       <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
         <v/>
       </c>
       <c r="P183" t="str">
@@ -9750,6 +10678,9 @@
       <c r="C184" t="str">
         <v/>
       </c>
+      <c r="D184" t="str">
+        <v/>
+      </c>
       <c r="E184">
         <v>5</v>
       </c>
@@ -9778,6 +10709,9 @@
         <v/>
       </c>
       <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
         <v/>
       </c>
       <c r="P184" t="str">
@@ -9800,6 +10734,9 @@
       <c r="C185" t="str">
         <v/>
       </c>
+      <c r="D185" t="str">
+        <v/>
+      </c>
       <c r="E185">
         <v>2</v>
       </c>
@@ -9828,6 +10765,9 @@
         <v/>
       </c>
       <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
         <v/>
       </c>
       <c r="P185" t="str">
@@ -9906,6 +10846,9 @@
       <c r="C187" t="str">
         <v/>
       </c>
+      <c r="D187" t="str">
+        <v/>
+      </c>
       <c r="E187">
         <v>2</v>
       </c>
@@ -9934,6 +10877,9 @@
         <v/>
       </c>
       <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
         <v/>
       </c>
       <c r="P187" t="str">
@@ -9956,6 +10902,9 @@
       <c r="C188" t="str">
         <v/>
       </c>
+      <c r="D188" t="str">
+        <v/>
+      </c>
       <c r="E188">
         <v>7</v>
       </c>
@@ -9984,6 +10933,9 @@
         <v/>
       </c>
       <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
         <v/>
       </c>
       <c r="P188" t="str">
@@ -10006,6 +10958,9 @@
       <c r="C189" t="str">
         <v/>
       </c>
+      <c r="D189" t="str">
+        <v/>
+      </c>
       <c r="E189">
         <v>1</v>
       </c>
@@ -10034,6 +10989,9 @@
         <v/>
       </c>
       <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
         <v/>
       </c>
       <c r="P189" t="str">
@@ -10056,6 +11014,9 @@
       <c r="C190" t="str">
         <v/>
       </c>
+      <c r="D190" t="str">
+        <v/>
+      </c>
       <c r="E190">
         <v>5</v>
       </c>
@@ -10084,6 +11045,9 @@
         <v/>
       </c>
       <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
         <v/>
       </c>
       <c r="P190" t="str">
@@ -10106,6 +11070,9 @@
       <c r="C191" t="str">
         <v/>
       </c>
+      <c r="D191" t="str">
+        <v/>
+      </c>
       <c r="E191">
         <v>2</v>
       </c>
@@ -10134,6 +11101,9 @@
         <v/>
       </c>
       <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
         <v/>
       </c>
       <c r="P191" t="str">
@@ -10212,6 +11182,9 @@
       <c r="C193" t="str">
         <v/>
       </c>
+      <c r="D193" t="str">
+        <v/>
+      </c>
       <c r="E193">
         <v>2</v>
       </c>
@@ -10240,6 +11213,9 @@
         <v/>
       </c>
       <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
         <v/>
       </c>
       <c r="P193" t="str">
@@ -10262,6 +11238,9 @@
       <c r="C194" t="str">
         <v/>
       </c>
+      <c r="D194" t="str">
+        <v/>
+      </c>
       <c r="E194">
         <v>7</v>
       </c>
@@ -10290,6 +11269,9 @@
         <v/>
       </c>
       <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
         <v/>
       </c>
       <c r="P194" t="str">
@@ -10312,6 +11294,9 @@
       <c r="C195" t="str">
         <v/>
       </c>
+      <c r="D195" t="str">
+        <v/>
+      </c>
       <c r="E195">
         <v>1</v>
       </c>
@@ -10340,6 +11325,9 @@
         <v/>
       </c>
       <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
         <v/>
       </c>
       <c r="P195" t="str">
@@ -10362,6 +11350,9 @@
       <c r="C196" t="str">
         <v/>
       </c>
+      <c r="D196" t="str">
+        <v/>
+      </c>
       <c r="E196">
         <v>5</v>
       </c>
@@ -10390,6 +11381,9 @@
         <v/>
       </c>
       <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
         <v/>
       </c>
       <c r="P196" t="str">
@@ -10412,6 +11406,9 @@
       <c r="C197" t="str">
         <v/>
       </c>
+      <c r="D197" t="str">
+        <v/>
+      </c>
       <c r="E197">
         <v>2</v>
       </c>
@@ -10440,6 +11437,9 @@
         <v/>
       </c>
       <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
         <v/>
       </c>
       <c r="P197" t="str">
@@ -10518,6 +11518,9 @@
       <c r="C199" t="str">
         <v/>
       </c>
+      <c r="D199" t="str">
+        <v/>
+      </c>
       <c r="E199">
         <v>2</v>
       </c>
@@ -10546,6 +11549,9 @@
         <v/>
       </c>
       <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
         <v/>
       </c>
       <c r="P199" t="str">
@@ -10568,6 +11574,9 @@
       <c r="C200" t="str">
         <v/>
       </c>
+      <c r="D200" t="str">
+        <v/>
+      </c>
       <c r="E200">
         <v>7</v>
       </c>
@@ -10596,6 +11605,9 @@
         <v/>
       </c>
       <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
         <v/>
       </c>
       <c r="P200" t="str">
@@ -10618,6 +11630,9 @@
       <c r="C201" t="str">
         <v/>
       </c>
+      <c r="D201" t="str">
+        <v/>
+      </c>
       <c r="E201">
         <v>1</v>
       </c>
@@ -10646,6 +11661,9 @@
         <v/>
       </c>
       <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
         <v/>
       </c>
       <c r="P201" t="str">
@@ -10668,6 +11686,9 @@
       <c r="C202" t="str">
         <v/>
       </c>
+      <c r="D202" t="str">
+        <v/>
+      </c>
       <c r="E202">
         <v>5</v>
       </c>
@@ -10696,6 +11717,9 @@
         <v/>
       </c>
       <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
         <v/>
       </c>
       <c r="P202" t="str">
@@ -10718,6 +11742,9 @@
       <c r="C203" t="str">
         <v/>
       </c>
+      <c r="D203" t="str">
+        <v/>
+      </c>
       <c r="E203">
         <v>2</v>
       </c>
@@ -10746,6 +11773,9 @@
         <v/>
       </c>
       <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
         <v/>
       </c>
       <c r="P203" t="str">
@@ -10824,6 +11854,9 @@
       <c r="C205" t="str">
         <v/>
       </c>
+      <c r="D205" t="str">
+        <v/>
+      </c>
       <c r="E205">
         <v>2</v>
       </c>
@@ -10852,6 +11885,9 @@
         <v/>
       </c>
       <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
         <v/>
       </c>
       <c r="P205" t="str">
@@ -10874,6 +11910,9 @@
       <c r="C206" t="str">
         <v/>
       </c>
+      <c r="D206" t="str">
+        <v/>
+      </c>
       <c r="E206">
         <v>7</v>
       </c>
@@ -10902,6 +11941,9 @@
         <v/>
       </c>
       <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
         <v/>
       </c>
       <c r="P206" t="str">
@@ -10924,6 +11966,9 @@
       <c r="C207" t="str">
         <v/>
       </c>
+      <c r="D207" t="str">
+        <v/>
+      </c>
       <c r="E207">
         <v>1</v>
       </c>
@@ -10952,6 +11997,9 @@
         <v/>
       </c>
       <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
         <v/>
       </c>
       <c r="P207" t="str">
@@ -10974,6 +12022,9 @@
       <c r="C208" t="str">
         <v/>
       </c>
+      <c r="D208" t="str">
+        <v/>
+      </c>
       <c r="E208">
         <v>5</v>
       </c>
@@ -11002,6 +12053,9 @@
         <v/>
       </c>
       <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
         <v/>
       </c>
       <c r="P208" t="str">
@@ -11024,6 +12078,9 @@
       <c r="C209" t="str">
         <v/>
       </c>
+      <c r="D209" t="str">
+        <v/>
+      </c>
       <c r="E209">
         <v>2</v>
       </c>
@@ -11052,6 +12109,9 @@
         <v/>
       </c>
       <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
         <v/>
       </c>
       <c r="P209" t="str">
@@ -11130,6 +12190,9 @@
       <c r="C211" t="str">
         <v/>
       </c>
+      <c r="D211" t="str">
+        <v/>
+      </c>
       <c r="E211">
         <v>2</v>
       </c>
@@ -11158,6 +12221,9 @@
         <v/>
       </c>
       <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
         <v/>
       </c>
       <c r="P211" t="str">
@@ -11180,6 +12246,9 @@
       <c r="C212" t="str">
         <v/>
       </c>
+      <c r="D212" t="str">
+        <v/>
+      </c>
       <c r="E212">
         <v>7</v>
       </c>
@@ -11208,6 +12277,9 @@
         <v/>
       </c>
       <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
         <v/>
       </c>
       <c r="P212" t="str">
@@ -11230,6 +12302,9 @@
       <c r="C213" t="str">
         <v/>
       </c>
+      <c r="D213" t="str">
+        <v/>
+      </c>
       <c r="E213">
         <v>1</v>
       </c>
@@ -11258,6 +12333,9 @@
         <v/>
       </c>
       <c r="N213" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
         <v/>
       </c>
       <c r="P213" t="str">
@@ -11280,6 +12358,9 @@
       <c r="C214" t="str">
         <v/>
       </c>
+      <c r="D214" t="str">
+        <v/>
+      </c>
       <c r="E214">
         <v>5</v>
       </c>
@@ -11308,6 +12389,9 @@
         <v/>
       </c>
       <c r="N214" t="str">
+        <v/>
+      </c>
+      <c r="O214" t="str">
         <v/>
       </c>
       <c r="P214" t="str">
@@ -11330,6 +12414,9 @@
       <c r="C215" t="str">
         <v/>
       </c>
+      <c r="D215" t="str">
+        <v/>
+      </c>
       <c r="E215">
         <v>2</v>
       </c>
@@ -11358,6 +12445,9 @@
         <v/>
       </c>
       <c r="N215" t="str">
+        <v/>
+      </c>
+      <c r="O215" t="str">
         <v/>
       </c>
       <c r="P215" t="str">
@@ -11436,6 +12526,9 @@
       <c r="C217" t="str">
         <v/>
       </c>
+      <c r="D217" t="str">
+        <v/>
+      </c>
       <c r="E217">
         <v>2</v>
       </c>
@@ -11464,6 +12557,9 @@
         <v/>
       </c>
       <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
         <v/>
       </c>
       <c r="P217" t="str">
@@ -11486,6 +12582,9 @@
       <c r="C218" t="str">
         <v/>
       </c>
+      <c r="D218" t="str">
+        <v/>
+      </c>
       <c r="E218">
         <v>7</v>
       </c>
@@ -11514,6 +12613,9 @@
         <v/>
       </c>
       <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
         <v/>
       </c>
       <c r="P218" t="str">
@@ -11536,6 +12638,9 @@
       <c r="C219" t="str">
         <v/>
       </c>
+      <c r="D219" t="str">
+        <v/>
+      </c>
       <c r="E219">
         <v>1</v>
       </c>
@@ -11564,6 +12669,9 @@
         <v/>
       </c>
       <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
         <v/>
       </c>
       <c r="P219" t="str">
@@ -11586,6 +12694,9 @@
       <c r="C220" t="str">
         <v/>
       </c>
+      <c r="D220" t="str">
+        <v/>
+      </c>
       <c r="E220">
         <v>5</v>
       </c>
@@ -11614,6 +12725,9 @@
         <v/>
       </c>
       <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
         <v/>
       </c>
       <c r="P220" t="str">
@@ -11636,6 +12750,9 @@
       <c r="C221" t="str">
         <v/>
       </c>
+      <c r="D221" t="str">
+        <v/>
+      </c>
       <c r="E221">
         <v>2</v>
       </c>
@@ -11664,6 +12781,9 @@
         <v/>
       </c>
       <c r="N221" t="str">
+        <v/>
+      </c>
+      <c r="O221" t="str">
         <v/>
       </c>
       <c r="P221" t="str">
@@ -11742,6 +12862,9 @@
       <c r="C223" t="str">
         <v/>
       </c>
+      <c r="D223" t="str">
+        <v/>
+      </c>
       <c r="E223">
         <v>2</v>
       </c>
@@ -11770,6 +12893,9 @@
         <v/>
       </c>
       <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
         <v/>
       </c>
       <c r="P223" t="str">
@@ -11792,6 +12918,9 @@
       <c r="C224" t="str">
         <v/>
       </c>
+      <c r="D224" t="str">
+        <v/>
+      </c>
       <c r="E224">
         <v>7</v>
       </c>
@@ -11820,6 +12949,9 @@
         <v/>
       </c>
       <c r="N224" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
         <v/>
       </c>
       <c r="P224" t="str">
@@ -11842,6 +12974,9 @@
       <c r="C225" t="str">
         <v/>
       </c>
+      <c r="D225" t="str">
+        <v/>
+      </c>
       <c r="E225">
         <v>1</v>
       </c>
@@ -11870,6 +13005,9 @@
         <v/>
       </c>
       <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
         <v/>
       </c>
       <c r="P225" t="str">
@@ -11892,6 +13030,9 @@
       <c r="C226" t="str">
         <v/>
       </c>
+      <c r="D226" t="str">
+        <v/>
+      </c>
       <c r="E226">
         <v>5</v>
       </c>
@@ -11920,6 +13061,9 @@
         <v/>
       </c>
       <c r="N226" t="str">
+        <v/>
+      </c>
+      <c r="O226" t="str">
         <v/>
       </c>
       <c r="P226" t="str">
@@ -11942,6 +13086,9 @@
       <c r="C227" t="str">
         <v/>
       </c>
+      <c r="D227" t="str">
+        <v/>
+      </c>
       <c r="E227">
         <v>2</v>
       </c>
@@ -11970,6 +13117,9 @@
         <v/>
       </c>
       <c r="N227" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
         <v/>
       </c>
       <c r="P227" t="str">
@@ -12048,6 +13198,9 @@
       <c r="C229" t="str">
         <v/>
       </c>
+      <c r="D229" t="str">
+        <v/>
+      </c>
       <c r="E229">
         <v>2</v>
       </c>
@@ -12076,6 +13229,9 @@
         <v/>
       </c>
       <c r="N229" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
         <v/>
       </c>
       <c r="P229" t="str">
@@ -12098,6 +13254,9 @@
       <c r="C230" t="str">
         <v/>
       </c>
+      <c r="D230" t="str">
+        <v/>
+      </c>
       <c r="E230">
         <v>7</v>
       </c>
@@ -12126,6 +13285,9 @@
         <v/>
       </c>
       <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
         <v/>
       </c>
       <c r="P230" t="str">
@@ -12148,6 +13310,9 @@
       <c r="C231" t="str">
         <v/>
       </c>
+      <c r="D231" t="str">
+        <v/>
+      </c>
       <c r="E231">
         <v>1</v>
       </c>
@@ -12176,6 +13341,9 @@
         <v/>
       </c>
       <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
         <v/>
       </c>
       <c r="P231" t="str">
@@ -12198,6 +13366,9 @@
       <c r="C232" t="str">
         <v/>
       </c>
+      <c r="D232" t="str">
+        <v/>
+      </c>
       <c r="E232">
         <v>5</v>
       </c>
@@ -12226,6 +13397,9 @@
         <v/>
       </c>
       <c r="N232" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
         <v/>
       </c>
       <c r="P232" t="str">
@@ -12248,6 +13422,9 @@
       <c r="C233" t="str">
         <v/>
       </c>
+      <c r="D233" t="str">
+        <v/>
+      </c>
       <c r="E233">
         <v>2</v>
       </c>
@@ -12276,6 +13453,9 @@
         <v/>
       </c>
       <c r="N233" t="str">
+        <v/>
+      </c>
+      <c r="O233" t="str">
         <v/>
       </c>
       <c r="P233" t="str">
@@ -12970,6 +14150,9 @@
       <c r="C246" t="str">
         <v/>
       </c>
+      <c r="D246" t="str">
+        <v/>
+      </c>
       <c r="E246">
         <v>3</v>
       </c>
@@ -12998,6 +14181,9 @@
         <v/>
       </c>
       <c r="N246" t="str">
+        <v/>
+      </c>
+      <c r="O246" t="str">
         <v/>
       </c>
       <c r="P246" t="str">
@@ -13020,6 +14206,9 @@
       <c r="C247" t="str">
         <v/>
       </c>
+      <c r="D247" t="str">
+        <v/>
+      </c>
       <c r="E247">
         <v>5</v>
       </c>
@@ -13048,6 +14237,9 @@
         <v/>
       </c>
       <c r="N247" t="str">
+        <v/>
+      </c>
+      <c r="O247" t="str">
         <v/>
       </c>
       <c r="P247" t="str">
@@ -13070,6 +14262,9 @@
       <c r="C248" t="str">
         <v/>
       </c>
+      <c r="D248" t="str">
+        <v/>
+      </c>
       <c r="E248">
         <v>1</v>
       </c>
@@ -13098,6 +14293,9 @@
         <v/>
       </c>
       <c r="N248" t="str">
+        <v/>
+      </c>
+      <c r="O248" t="str">
         <v/>
       </c>
       <c r="P248" t="str">
@@ -13120,6 +14318,9 @@
       <c r="C249" t="str">
         <v/>
       </c>
+      <c r="D249" t="str">
+        <v/>
+      </c>
       <c r="E249">
         <v>1</v>
       </c>
@@ -13148,6 +14349,9 @@
         <v/>
       </c>
       <c r="N249" t="str">
+        <v/>
+      </c>
+      <c r="O249" t="str">
         <v/>
       </c>
       <c r="P249" t="str">
@@ -13170,6 +14374,9 @@
       <c r="C250" t="str">
         <v/>
       </c>
+      <c r="D250" t="str">
+        <v/>
+      </c>
       <c r="E250">
         <v>5</v>
       </c>
@@ -13198,6 +14405,9 @@
         <v/>
       </c>
       <c r="N250" t="str">
+        <v/>
+      </c>
+      <c r="O250" t="str">
         <v/>
       </c>
       <c r="P250" t="str">
@@ -13219,7 +14429,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:C50"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13243,7 +14458,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. Enter Start Date in column C - see "DATE ENTRY METHODS" below for calendar options</v>
+        <v>2. Enter Start Date in column C (format: YYYY-MM-DD or use Ctrl+; for today)</v>
       </c>
     </row>
     <row r="6">
@@ -13253,1214 +14468,383 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. Finish Date (column D) will auto-calculate = Start Date + Duration - 1</v>
+        <v>4. Dependencies (column G) are pre-configured in format: TaskID(Type)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5. Dependencies (column G) are pre-configured in format: TaskID(Type)</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>TASK ORGANIZATION</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+        <v>• PHASE • Design &amp; Approvals - Initial design phase (6 tasks)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DATE ENTRY METHODS - CHOOSE YOUR PREFERRED OPTION</v>
+        <v>• PHASE • Vendor Evaluation → Quotes → Finalisation → Work Orders</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+        <v>• 20 PACKAGE categories: Civil, Electricals, Plumbing, Kitchens, Bathrooms, etc.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>• Each package has 7 sequential tasks: Evaluation → Meetings → RFQs → Quotes → Comparison → Finalisation → Work Order</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OPTION 1: KEYBOARD ENTRY (Built-in, Works Everywhere)</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>• Click any date cell and type: 2024-01-15 (YYYY-MM-DD format)</v>
+        <v>COLUMN REFERENCE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>• Or press Ctrl+; to insert today's date</v>
+        <v>Column</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Description</v>
+      </c>
+      <c r="C16" t="str">
+        <v>How to Use</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>• Simple and fast for experienced users</v>
+        <v>ID</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Task identifier (1-249)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Pre-filled, do not change</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Name</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Task name</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Pre-filled with real project tasks</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>OPTION 2: VISUAL CALENDAR PICKER - RECOMMENDED ⭐</v>
+        <v>Start</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Start date</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Enter as YYYY-MM-DD (e.g., 2024-01-15)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>For the best experience, install a free calendar add-in:</v>
+        <v>Finish</v>
+      </c>
+      <c r="B20" t="str">
+        <v>End date</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Leave blank - will calculate when imported</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Duration</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Working days</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Pre-filled, adjust as needed</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>METHOD A: Randy's Date Picker (Works in Excel 2016/2019/2021/365, 32-bit &amp; 64-bit)</v>
+        <v>% Complete</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Progress (0-100)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Update as work progresses</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Step 1: Download the add-in</v>
+        <v>Predecessors</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Dependencies</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Pre-configured: TaskID(Type) format</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">        • Google search: "Randy Austin date picker Excel download"</v>
+        <v>Resource Names</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Assigned team</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Designer, Client, Vendor, etc.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">        • Or visit: https://bettersolutions.com/excel/date-picker/ (trusted source)</v>
+        <v>Status</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Current status</v>
+      </c>
+      <c r="C25" t="str">
+        <v>not_started, in_progress, completed, blocked</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">        • Download the .xlam file (Excel add-in)</v>
+        <v>Priority</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Task priority</v>
+      </c>
+      <c r="C26" t="str">
+        <v>low, medium, high</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v/>
+        <v>Approval Required</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Needs approval?</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Y or N</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Step 2: Install the add-in</v>
+        <v>Materials</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Required materials</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Optional</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">        • Open Excel</v>
+        <v>Owner</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Task owner</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Optional</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">        • File → Options → Add-ins</v>
+        <v>Target Start</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Planned start</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Optional - for planning</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">        • At bottom, select "Excel Add-ins" → Click "Go..."</v>
+        <v>Target Finish</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Planned finish</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Optional - for planning</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">        • Click "Browse..." → Find your downloaded .xlam file</v>
+        <v>Remarks</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Additional information</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">        • Check the box next to "Randy's Date Picker" → Click OK</v>
+        <v>Outline Level</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Hierarchy</v>
+      </c>
+      <c r="C33" t="str">
+        <v>1=Phase/Package, 2=Task</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Color</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Task color</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Optional hex code</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Step 3: Use the calendar</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">        • Click any date cell in your template</v>
+        <v>DEPENDENCY TYPES</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">        • A floating calendar popup appears automatically</v>
+        <v>Format</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Meaning</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">        • Click a date to insert it</v>
+        <v>TaskID(FS)</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Finish-to-Start</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Task finishes before this starts</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">        • Works for all date columns (no configuration needed)</v>
+        <v>TaskID(SS)</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Start-to-Start</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Task starts before this starts</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>TaskID(FF)</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Finish-to-Finish</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Task finishes before this finishes</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>METHOD B: Kutools Date Picker (Commercial, Full-Featured)</v>
+        <v>TaskID(SF)</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Start-to-Finish</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Task starts before this finishes</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">        • Visit: https://www.extendoffice.com/product/kutools-for-excel.html</v>
+        <v>With lag</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Add delay</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2(FS)+3 = Wait 3 days after Task 2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">        • Free trial available, then $49 for permanent license</v>
+        <v>Multiple</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Comma-separated</v>
+      </c>
+      <c r="C43" t="str">
+        <v>4(FS),5(FS) = Wait for both tasks</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">        • Includes 300+ Excel tools beyond just date picking</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">        • Calendar appears when clicking any date cell</v>
+        <v>AFTER IMPORT TO PIXELCRAFT DESIGNER</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>• System calculates Finish dates automatically (Start + Duration - 1)</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>METHOD C: Built-in ActiveX Control (Legacy, 32-bit Excel Only)</v>
+        <v>• Critical Path Analysis identifies tasks that cannot be delayed</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">        ⚠️ Not recommended - doesn't work in 64-bit Excel</v>
+        <v>• Project duration and critical percentage are displayed</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">        • Enable Developer tab: File → Options → Customize Ribbon → Check "Developer"</v>
+        <v>• Circular dependencies are detected and prevented</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">        • Developer → Insert → More Controls</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">        • Select "Microsoft Date and Time Picker Control 6.0"</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">        • Manually link to each cell (time-consuming for 249 tasks)</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>COMPARISON: Which Method Should You Choose?</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Method</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Ease of Use</v>
-      </c>
-      <c r="C55" t="str">
-        <v>64-bit Compatible</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Cost</v>
-      </c>
-      <c r="E55" t="str">
-        <v>Recommendation</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Keyboard Entry</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Easy</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Free</v>
-      </c>
-      <c r="E56" t="str">
-        <v>Good for quick edits</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Randy's Picker</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Very Easy</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D57" t="str">
-        <v>Free</v>
-      </c>
-      <c r="E57" t="str">
-        <v>⭐ BEST for most users</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Kutools</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Very Easy</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D58" t="str">
-        <v>$49</v>
-      </c>
-      <c r="E58" t="str">
-        <v>Best for power users</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>ActiveX Control</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Difficult</v>
-      </c>
-      <c r="C59" t="str">
-        <v>No</v>
-      </c>
-      <c r="D59" t="str">
-        <v>Free</v>
-      </c>
-      <c r="E59" t="str">
-        <v>Avoid - outdated</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>TASK ORGANIZATION</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>PHASES INCLUDED</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>1. Design &amp; Approvals - Initial design phase with client approvals</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>2. Vendor Evaluation → Quotes → Finalisation → Work Orders</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>PACKAGES INCLUDED (20 Categories)</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>• Civil, Electricals, Plumbing, Kitchens, Bathrooms, Audio, Automation</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>• Lighting, HVAC, Curtains, Furniture, Wardrobes, Flooring, Painting</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>• False Ceiling, Mirrors, Soft Furnishings, Décor, Upholstery, Storage</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Each package follows the same 7-step workflow:</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">  1. Vendor Evaluation (shortlist) → 2. Vendor Meetings / Site Survey</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">  3. RFQs Issued → 4. Quotes Received &amp; Clarifications</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">  5. Quote Comparison &amp; Negotiation → 6. Vendor Finalisation</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">  7. Work Order / PO Release</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>HIERARCHY</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>• PHASE headers: Outline Level 1 (major project phases)</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>• PACKAGE headers: Outline Level 1 (vendor categories)</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>• Individual tasks: Outline Level 2 (specific activities)</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>AUTOMATIC DATE CALCULATIONS</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>• When you enter Start Date + Duration, Finish Date calculates automatically</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>• Formula: Finish = Start + Duration - 1 day</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>• Example: Start = Jan 1, Duration = 5 → Finish = Jan 5</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>• Works for both Actual dates (C, D) and Target dates (N, O)</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>• You can override auto-calculated dates if needed</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>COLUMN REFERENCE (18 Columns)</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Column</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Description</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B100" t="str">
-        <v>Task identifier (1-249)</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Pre-filled, do not change</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Task name</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Pre-filled with your project tasks</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Start</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Start date</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Use calendar picker or type YYYY-MM-DD</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Finish</v>
-      </c>
-      <c r="B103" t="str">
-        <v>End date (AUTO-CALC)</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Auto: Start + Duration - 1, can override</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Working days</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Pre-filled, adjust as needed</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>% Complete</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Progress (0-100)</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Update as work progresses</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Predecessors</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Dependencies</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Pre-configured: TaskID(Type)</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Resource Names</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Assigned team</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Designer, Client, Vendor, etc.</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Status</v>
-      </c>
-      <c r="B108" t="str">
-        <v>Current status</v>
-      </c>
-      <c r="C108" t="str">
-        <v>not_started, in_progress, completed, blocked</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="B109" t="str">
-        <v>Task priority</v>
-      </c>
-      <c r="C109" t="str">
-        <v>low, medium, high (auto-set for key tasks)</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>Approval Required</v>
-      </c>
-      <c r="B110" t="str">
-        <v>Needs approval? (Y/N)</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Pre-set for approval tasks</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Materials</v>
-      </c>
-      <c r="B111" t="str">
-        <v>Required materials</v>
-      </c>
-      <c r="C111" t="str">
-        <v>Optional - add as needed</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="B112" t="str">
-        <v>Task owner name</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Optional - assign task owner</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Target Start</v>
-      </c>
-      <c r="B113" t="str">
-        <v>Planned start</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Optional planning dates</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Target Finish</v>
-      </c>
-      <c r="B114" t="str">
-        <v>Planned finish (AUTO-CALC)</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Auto: Target Start + Duration - 1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Remarks</v>
-      </c>
-      <c r="B115" t="str">
-        <v>Notes</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Milestones and special notes</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>Outline Level</v>
-      </c>
-      <c r="B116" t="str">
-        <v>Hierarchy (1 or 2)</v>
-      </c>
-      <c r="C116" t="str">
-        <v>1=Phase/Package, 2=Task</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Color</v>
-      </c>
-      <c r="B117" t="str">
-        <v>Task color</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Optional hex code: #4A90E2</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>DEPENDENCY TYPES (Critical Path Analysis)</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>Format</v>
-      </c>
-      <c r="B123" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C123" t="str">
-        <v>Meaning</v>
-      </c>
-      <c r="D123" t="str">
-        <v>Example</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>TaskID(FS)</v>
-      </c>
-      <c r="B124" t="str">
-        <v>Finish-to-Start</v>
-      </c>
-      <c r="C124" t="str">
-        <v>Task finishes before this starts</v>
-      </c>
-      <c r="D124" t="str">
-        <v>2(FS) = Wait for Task 2 to finish</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>TaskID(SS)</v>
-      </c>
-      <c r="B125" t="str">
-        <v>Start-to-Start</v>
-      </c>
-      <c r="C125" t="str">
-        <v>Task starts before this starts</v>
-      </c>
-      <c r="D125" t="str">
-        <v>3(SS) = Wait for Task 3 to start</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>TaskID(FF)</v>
-      </c>
-      <c r="B126" t="str">
-        <v>Finish-to-Finish</v>
-      </c>
-      <c r="C126" t="str">
-        <v>Task finishes before this finishes</v>
-      </c>
-      <c r="D126" t="str">
-        <v>4(FF) = Must finish with Task 4</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>TaskID(SF)</v>
-      </c>
-      <c r="B127" t="str">
-        <v>Start-to-Finish</v>
-      </c>
-      <c r="C127" t="str">
-        <v>Task starts before this finishes</v>
-      </c>
-      <c r="D127" t="str">
-        <v>5(SF) = Rare, special cases</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>With lag</v>
-      </c>
-      <c r="B128" t="str">
-        <v>Add delay</v>
-      </c>
-      <c r="C128" t="str">
-        <v>Wait extra days after dependency</v>
-      </c>
-      <c r="D128" t="str">
-        <v>2(FS)+3 = 3 days after Task 2</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Multiple</v>
-      </c>
-      <c r="B129" t="str">
-        <v>Comma-separated</v>
-      </c>
-      <c r="C129" t="str">
-        <v>Wait for multiple tasks</v>
-      </c>
-      <c r="D129" t="str">
-        <v>4(FS),5(FS) = Wait for both</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>PRE-CONFIGURED DEPENDENCIES</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>All task dependencies are pre-configured based on typical interior design workflow:</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>• Design phase tasks flow sequentially (Client Brief → Schematics → Working Drawings)</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>• Each package starts after Client Sign-off on drawings</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>• Within each package, tasks follow the 7-step workflow sequentially</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>• You can modify dependencies if your project workflow differs</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>CRITICAL PATH ANALYSIS (After Importing to PixelCraft Designer)</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>After importing this template into PixelCraft Designer, the system will:</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>✓ Calculate Early Start (ES) and Early Finish (EF) for all tasks</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>✓ Calculate Late Start (LS) and Late Finish (LF) for all tasks</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>✓ Identify critical tasks (zero float - must complete on time)</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>✓ Show total project duration in working days</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>✓ Display critical path percentage (% of tasks on critical path)</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>✓ Detect circular dependencies and prevent import errors</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>✓ Highlight critical tasks with visual badges</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>WHAT IS THE CRITICAL PATH?</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>The critical path is the longest sequence of dependent tasks that determines</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>the minimum project duration. Any delay in critical path tasks delays the</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>entire project. Tasks not on the critical path have "float" (slack time).</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>KEY METRICS:</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>• Total Float: How many days a task can be delayed without affecting project end</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>• Critical Tasks: Tasks with zero float (must complete on schedule)</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>• Project Duration: Earliest possible project completion date</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>TIPS FOR BEST RESULTS</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>1. Install Randy's Date Picker first for easiest date entry</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>2. Start by filling in Start dates for the first few tasks</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>3. Let the Finish dates auto-calculate (they use the formula)</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>4. Adjust Duration values based on your project needs</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>5. Review pre-configured dependencies - modify if your workflow differs</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>6. Use Status column to track progress: not_started → in_progress → completed</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>7. Set Priority to "high" for time-sensitive or client-facing tasks</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>8. Import into PixelCraft Designer to see Critical Path Analysis</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>9. Download updated schedule from PixelCraft to get latest progress</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>10. Keep Approval Required tasks visible - they often become bottlenecks</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>TROUBLESHOOTING</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>Problem: Date validation message appears but no calendar</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>Solution: You need to install a calendar add-in (see OPTION 2 above)</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>Problem: Finish date not calculating automatically</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>Solution: Make sure Start date AND Duration are both filled in</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v>Problem: Import fails with "circular dependency" error</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
-        <v>Solution: Check Predecessors column - a task cannot depend on itself or</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v xml:space="preserve">         create a loop (e.g., Task 5 → Task 10 → Task 5)</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Problem: Critical path shows 100% of tasks as critical</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>Solution: Dependencies may be too strict - some packages could start in</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v xml:space="preserve">         parallel instead of sequentially</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>Problem: Excel shows "####" in date columns</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Solution: Column is too narrow - double-click column border to auto-fit</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>For support with PixelCraft Designer system, contact your administrator</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━━</v>
+        <v>• Download updated schedule anytime with current progress</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/attached_assets/gantt_template.xlsx
+++ b/attached_assets/gantt_template.xlsx
@@ -6,6 +6,9 @@
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Tasks'!A1:R250</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -33,8 +36,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -65,8 +69,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,26 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R250"/>
-  <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="25.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="30.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -483,10 +468,10 @@
       <c r="B2" t="str">
         <v>PHASE • Design &amp; Approvals</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
+      <c r="C2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D2" s="1" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
@@ -516,10 +501,10 @@
       <c r="M2" t="str">
         <v/>
       </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
+      <c r="N2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O2" s="1" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
@@ -539,10 +524,10 @@
       <c r="B3" t="str">
         <v>Client Brief &amp; Scope</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
+      <c r="C3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D3" s="1" t="str">
         <v/>
       </c>
       <c r="E3">
@@ -572,10 +557,10 @@
       <c r="M3" t="str">
         <v/>
       </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
+      <c r="N3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O3" s="1" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
@@ -595,10 +580,10 @@
       <c r="B4" t="str">
         <v>Schematic Drawings (Overall)</v>
       </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
+      <c r="C4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D4" s="1" t="str">
         <v/>
       </c>
       <c r="E4">
@@ -628,10 +613,10 @@
       <c r="M4" t="str">
         <v/>
       </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
+      <c r="N4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O4" s="1" t="str">
         <v/>
       </c>
       <c r="P4" t="str">
@@ -651,10 +636,10 @@
       <c r="B5" t="str">
         <v>Working Drawings (Overall)</v>
       </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
+      <c r="C5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D5" s="1" t="str">
         <v/>
       </c>
       <c r="E5">
@@ -684,10 +669,10 @@
       <c r="M5" t="str">
         <v/>
       </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
+      <c r="N5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O5" s="1" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
@@ -707,10 +692,10 @@
       <c r="B6" t="str">
         <v>Finishes Board &amp; Samples (Overall)</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
+      <c r="C6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D6" s="1" t="str">
         <v/>
       </c>
       <c r="E6">
@@ -740,10 +725,10 @@
       <c r="M6" t="str">
         <v/>
       </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
+      <c r="N6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O6" s="1" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
@@ -763,10 +748,10 @@
       <c r="B7" t="str">
         <v>Client Sign‑off (Drawings &amp; Finishes)</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
+      <c r="C7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="1" t="str">
         <v/>
       </c>
       <c r="E7">
@@ -796,10 +781,10 @@
       <c r="M7" t="str">
         <v/>
       </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
+      <c r="N7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O7" s="1" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
@@ -819,10 +804,10 @@
       <c r="B8" t="str">
         <v>PHASE • Vendor Evaluation → Quotes → Finalisation → Work Orders</v>
       </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
+      <c r="C8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D8" s="1" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
@@ -852,10 +837,10 @@
       <c r="M8" t="str">
         <v/>
       </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
+      <c r="N8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O8" s="1" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
@@ -875,10 +860,10 @@
       <c r="B9" t="str">
         <v>PACKAGE • Civil</v>
       </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
+      <c r="C9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D9" s="1" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
@@ -908,10 +893,10 @@
       <c r="M9" t="str">
         <v/>
       </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
+      <c r="N9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O9" s="1" t="str">
         <v/>
       </c>
       <c r="P9" t="str">
@@ -931,10 +916,10 @@
       <c r="B10" t="str">
         <v>Civil: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
+      <c r="C10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D10" s="1" t="str">
         <v/>
       </c>
       <c r="E10">
@@ -964,10 +949,10 @@
       <c r="M10" t="str">
         <v/>
       </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
+      <c r="N10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O10" s="1" t="str">
         <v/>
       </c>
       <c r="P10" t="str">
@@ -987,10 +972,10 @@
       <c r="B11" t="str">
         <v>Civil: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
+      <c r="C11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D11" s="1" t="str">
         <v/>
       </c>
       <c r="E11">
@@ -1020,10 +1005,10 @@
       <c r="M11" t="str">
         <v/>
       </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
+      <c r="N11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O11" s="1" t="str">
         <v/>
       </c>
       <c r="P11" t="str">
@@ -1043,10 +1028,10 @@
       <c r="B12" t="str">
         <v>Civil: RFQs Issued</v>
       </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
+      <c r="C12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D12" s="1" t="str">
         <v/>
       </c>
       <c r="E12">
@@ -1076,10 +1061,10 @@
       <c r="M12" t="str">
         <v/>
       </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
+      <c r="N12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O12" s="1" t="str">
         <v/>
       </c>
       <c r="P12" t="str">
@@ -1099,10 +1084,10 @@
       <c r="B13" t="str">
         <v>Civil: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
+      <c r="C13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D13" s="1" t="str">
         <v/>
       </c>
       <c r="E13">
@@ -1132,10 +1117,10 @@
       <c r="M13" t="str">
         <v/>
       </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
+      <c r="N13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O13" s="1" t="str">
         <v/>
       </c>
       <c r="P13" t="str">
@@ -1155,10 +1140,10 @@
       <c r="B14" t="str">
         <v>Civil: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
+      <c r="C14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D14" s="1" t="str">
         <v/>
       </c>
       <c r="E14">
@@ -1188,10 +1173,10 @@
       <c r="M14" t="str">
         <v/>
       </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
+      <c r="N14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O14" s="1" t="str">
         <v/>
       </c>
       <c r="P14" t="str">
@@ -1211,10 +1196,10 @@
       <c r="B15" t="str">
         <v>Civil: Vendor Finalisation</v>
       </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
+      <c r="C15" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D15" s="1" t="str">
         <v/>
       </c>
       <c r="E15">
@@ -1244,10 +1229,10 @@
       <c r="M15" t="str">
         <v/>
       </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
+      <c r="N15" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O15" s="1" t="str">
         <v/>
       </c>
       <c r="P15" t="str">
@@ -1267,10 +1252,10 @@
       <c r="B16" t="str">
         <v>Civil: Work Order / PO Release</v>
       </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
+      <c r="C16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="1" t="str">
         <v/>
       </c>
       <c r="E16">
@@ -1300,10 +1285,10 @@
       <c r="M16" t="str">
         <v/>
       </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
+      <c r="N16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O16" s="1" t="str">
         <v/>
       </c>
       <c r="P16" t="str">
@@ -1323,10 +1308,10 @@
       <c r="B17" t="str">
         <v>PACKAGE • Electricals</v>
       </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
+      <c r="C17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D17" s="1" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
@@ -1356,10 +1341,10 @@
       <c r="M17" t="str">
         <v/>
       </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
+      <c r="N17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O17" s="1" t="str">
         <v/>
       </c>
       <c r="P17" t="str">
@@ -1379,10 +1364,10 @@
       <c r="B18" t="str">
         <v>Electricals: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
+      <c r="C18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D18" s="1" t="str">
         <v/>
       </c>
       <c r="E18">
@@ -1412,10 +1397,10 @@
       <c r="M18" t="str">
         <v/>
       </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
+      <c r="N18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O18" s="1" t="str">
         <v/>
       </c>
       <c r="P18" t="str">
@@ -1435,10 +1420,10 @@
       <c r="B19" t="str">
         <v>Electricals: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
+      <c r="C19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D19" s="1" t="str">
         <v/>
       </c>
       <c r="E19">
@@ -1468,10 +1453,10 @@
       <c r="M19" t="str">
         <v/>
       </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
+      <c r="N19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O19" s="1" t="str">
         <v/>
       </c>
       <c r="P19" t="str">
@@ -1491,10 +1476,10 @@
       <c r="B20" t="str">
         <v>Electricals: RFQs Issued</v>
       </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
+      <c r="C20" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D20" s="1" t="str">
         <v/>
       </c>
       <c r="E20">
@@ -1524,10 +1509,10 @@
       <c r="M20" t="str">
         <v/>
       </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
+      <c r="N20" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O20" s="1" t="str">
         <v/>
       </c>
       <c r="P20" t="str">
@@ -1547,10 +1532,10 @@
       <c r="B21" t="str">
         <v>Electricals: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
+      <c r="C21" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D21" s="1" t="str">
         <v/>
       </c>
       <c r="E21">
@@ -1580,10 +1565,10 @@
       <c r="M21" t="str">
         <v/>
       </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
+      <c r="N21" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O21" s="1" t="str">
         <v/>
       </c>
       <c r="P21" t="str">
@@ -1603,10 +1588,10 @@
       <c r="B22" t="str">
         <v>Electricals: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
+      <c r="C22" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D22" s="1" t="str">
         <v/>
       </c>
       <c r="E22">
@@ -1636,10 +1621,10 @@
       <c r="M22" t="str">
         <v/>
       </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
+      <c r="N22" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O22" s="1" t="str">
         <v/>
       </c>
       <c r="P22" t="str">
@@ -1659,10 +1644,10 @@
       <c r="B23" t="str">
         <v>Electricals: Vendor Finalisation</v>
       </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
+      <c r="C23" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D23" s="1" t="str">
         <v/>
       </c>
       <c r="E23">
@@ -1692,10 +1677,10 @@
       <c r="M23" t="str">
         <v/>
       </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
+      <c r="N23" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O23" s="1" t="str">
         <v/>
       </c>
       <c r="P23" t="str">
@@ -1715,10 +1700,10 @@
       <c r="B24" t="str">
         <v>Electricals: Work Order / PO Release</v>
       </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
+      <c r="C24" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D24" s="1" t="str">
         <v/>
       </c>
       <c r="E24">
@@ -1748,10 +1733,10 @@
       <c r="M24" t="str">
         <v/>
       </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
+      <c r="N24" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O24" s="1" t="str">
         <v/>
       </c>
       <c r="P24" t="str">
@@ -1771,10 +1756,10 @@
       <c r="B25" t="str">
         <v>PACKAGE • Plumbing</v>
       </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
+      <c r="C25" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D25" s="1" t="str">
         <v/>
       </c>
       <c r="E25" t="str">
@@ -1804,10 +1789,10 @@
       <c r="M25" t="str">
         <v/>
       </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
+      <c r="N25" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O25" s="1" t="str">
         <v/>
       </c>
       <c r="P25" t="str">
@@ -1827,10 +1812,10 @@
       <c r="B26" t="str">
         <v>Plumbing: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
+      <c r="C26" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D26" s="1" t="str">
         <v/>
       </c>
       <c r="E26">
@@ -1860,10 +1845,10 @@
       <c r="M26" t="str">
         <v/>
       </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
+      <c r="N26" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O26" s="1" t="str">
         <v/>
       </c>
       <c r="P26" t="str">
@@ -1883,10 +1868,10 @@
       <c r="B27" t="str">
         <v>Plumbing: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27" t="str">
+      <c r="C27" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D27" s="1" t="str">
         <v/>
       </c>
       <c r="E27">
@@ -1916,10 +1901,10 @@
       <c r="M27" t="str">
         <v/>
       </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
+      <c r="N27" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O27" s="1" t="str">
         <v/>
       </c>
       <c r="P27" t="str">
@@ -1939,10 +1924,10 @@
       <c r="B28" t="str">
         <v>Plumbing: RFQs Issued</v>
       </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
+      <c r="C28" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="1" t="str">
         <v/>
       </c>
       <c r="E28">
@@ -1972,10 +1957,10 @@
       <c r="M28" t="str">
         <v/>
       </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
+      <c r="N28" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O28" s="1" t="str">
         <v/>
       </c>
       <c r="P28" t="str">
@@ -1995,10 +1980,10 @@
       <c r="B29" t="str">
         <v>Plumbing: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
+      <c r="C29" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D29" s="1" t="str">
         <v/>
       </c>
       <c r="E29">
@@ -2028,10 +2013,10 @@
       <c r="M29" t="str">
         <v/>
       </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
+      <c r="N29" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O29" s="1" t="str">
         <v/>
       </c>
       <c r="P29" t="str">
@@ -2051,10 +2036,10 @@
       <c r="B30" t="str">
         <v>Plumbing: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C30" t="str">
-        <v/>
-      </c>
-      <c r="D30" t="str">
+      <c r="C30" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D30" s="1" t="str">
         <v/>
       </c>
       <c r="E30">
@@ -2084,10 +2069,10 @@
       <c r="M30" t="str">
         <v/>
       </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
+      <c r="N30" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O30" s="1" t="str">
         <v/>
       </c>
       <c r="P30" t="str">
@@ -2107,10 +2092,10 @@
       <c r="B31" t="str">
         <v>Plumbing: Vendor Finalisation</v>
       </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
+      <c r="C31" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D31" s="1" t="str">
         <v/>
       </c>
       <c r="E31">
@@ -2140,10 +2125,10 @@
       <c r="M31" t="str">
         <v/>
       </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
+      <c r="N31" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O31" s="1" t="str">
         <v/>
       </c>
       <c r="P31" t="str">
@@ -2163,10 +2148,10 @@
       <c r="B32" t="str">
         <v>Plumbing: Work Order / PO Release</v>
       </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
+      <c r="C32" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D32" s="1" t="str">
         <v/>
       </c>
       <c r="E32">
@@ -2196,10 +2181,10 @@
       <c r="M32" t="str">
         <v/>
       </c>
-      <c r="N32" t="str">
-        <v/>
-      </c>
-      <c r="O32" t="str">
+      <c r="N32" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O32" s="1" t="str">
         <v/>
       </c>
       <c r="P32" t="str">
@@ -2219,10 +2204,10 @@
       <c r="B33" t="str">
         <v>PACKAGE • Kitchens</v>
       </c>
-      <c r="C33" t="str">
-        <v/>
-      </c>
-      <c r="D33" t="str">
+      <c r="C33" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D33" s="1" t="str">
         <v/>
       </c>
       <c r="E33" t="str">
@@ -2252,10 +2237,10 @@
       <c r="M33" t="str">
         <v/>
       </c>
-      <c r="N33" t="str">
-        <v/>
-      </c>
-      <c r="O33" t="str">
+      <c r="N33" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O33" s="1" t="str">
         <v/>
       </c>
       <c r="P33" t="str">
@@ -2275,10 +2260,10 @@
       <c r="B34" t="str">
         <v>Kitchens: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C34" t="str">
-        <v/>
-      </c>
-      <c r="D34" t="str">
+      <c r="C34" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="1" t="str">
         <v/>
       </c>
       <c r="E34">
@@ -2308,10 +2293,10 @@
       <c r="M34" t="str">
         <v/>
       </c>
-      <c r="N34" t="str">
-        <v/>
-      </c>
-      <c r="O34" t="str">
+      <c r="N34" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O34" s="1" t="str">
         <v/>
       </c>
       <c r="P34" t="str">
@@ -2331,10 +2316,10 @@
       <c r="B35" t="str">
         <v>Kitchens: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C35" t="str">
-        <v/>
-      </c>
-      <c r="D35" t="str">
+      <c r="C35" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D35" s="1" t="str">
         <v/>
       </c>
       <c r="E35">
@@ -2364,10 +2349,10 @@
       <c r="M35" t="str">
         <v/>
       </c>
-      <c r="N35" t="str">
-        <v/>
-      </c>
-      <c r="O35" t="str">
+      <c r="N35" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O35" s="1" t="str">
         <v/>
       </c>
       <c r="P35" t="str">
@@ -2387,10 +2372,10 @@
       <c r="B36" t="str">
         <v>Kitchens: RFQs Issued</v>
       </c>
-      <c r="C36" t="str">
-        <v/>
-      </c>
-      <c r="D36" t="str">
+      <c r="C36" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D36" s="1" t="str">
         <v/>
       </c>
       <c r="E36">
@@ -2420,10 +2405,10 @@
       <c r="M36" t="str">
         <v/>
       </c>
-      <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="O36" t="str">
+      <c r="N36" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O36" s="1" t="str">
         <v/>
       </c>
       <c r="P36" t="str">
@@ -2443,10 +2428,10 @@
       <c r="B37" t="str">
         <v>Kitchens: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C37" t="str">
-        <v/>
-      </c>
-      <c r="D37" t="str">
+      <c r="C37" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D37" s="1" t="str">
         <v/>
       </c>
       <c r="E37">
@@ -2476,10 +2461,10 @@
       <c r="M37" t="str">
         <v/>
       </c>
-      <c r="N37" t="str">
-        <v/>
-      </c>
-      <c r="O37" t="str">
+      <c r="N37" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O37" s="1" t="str">
         <v/>
       </c>
       <c r="P37" t="str">
@@ -2499,10 +2484,10 @@
       <c r="B38" t="str">
         <v>Kitchens: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
-      <c r="D38" t="str">
+      <c r="C38" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D38" s="1" t="str">
         <v/>
       </c>
       <c r="E38">
@@ -2532,10 +2517,10 @@
       <c r="M38" t="str">
         <v/>
       </c>
-      <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="O38" t="str">
+      <c r="N38" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O38" s="1" t="str">
         <v/>
       </c>
       <c r="P38" t="str">
@@ -2555,10 +2540,10 @@
       <c r="B39" t="str">
         <v>Kitchens: Vendor Finalisation</v>
       </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39" t="str">
+      <c r="C39" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D39" s="1" t="str">
         <v/>
       </c>
       <c r="E39">
@@ -2588,10 +2573,10 @@
       <c r="M39" t="str">
         <v/>
       </c>
-      <c r="N39" t="str">
-        <v/>
-      </c>
-      <c r="O39" t="str">
+      <c r="N39" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O39" s="1" t="str">
         <v/>
       </c>
       <c r="P39" t="str">
@@ -2611,10 +2596,10 @@
       <c r="B40" t="str">
         <v>Kitchens: Work Order / PO Release</v>
       </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="D40" t="str">
+      <c r="C40" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D40" s="1" t="str">
         <v/>
       </c>
       <c r="E40">
@@ -2644,10 +2629,10 @@
       <c r="M40" t="str">
         <v/>
       </c>
-      <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="O40" t="str">
+      <c r="N40" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O40" s="1" t="str">
         <v/>
       </c>
       <c r="P40" t="str">
@@ -2667,10 +2652,10 @@
       <c r="B41" t="str">
         <v>PACKAGE • Bathrooms</v>
       </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
+      <c r="C41" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D41" s="1" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
@@ -2700,10 +2685,10 @@
       <c r="M41" t="str">
         <v/>
       </c>
-      <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
+      <c r="N41" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O41" s="1" t="str">
         <v/>
       </c>
       <c r="P41" t="str">
@@ -2723,10 +2708,10 @@
       <c r="B42" t="str">
         <v>Bathrooms: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C42" t="str">
-        <v/>
-      </c>
-      <c r="D42" t="str">
+      <c r="C42" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D42" s="1" t="str">
         <v/>
       </c>
       <c r="E42">
@@ -2756,10 +2741,10 @@
       <c r="M42" t="str">
         <v/>
       </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
+      <c r="N42" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O42" s="1" t="str">
         <v/>
       </c>
       <c r="P42" t="str">
@@ -2779,10 +2764,10 @@
       <c r="B43" t="str">
         <v>Bathrooms: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43" t="str">
+      <c r="C43" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D43" s="1" t="str">
         <v/>
       </c>
       <c r="E43">
@@ -2812,10 +2797,10 @@
       <c r="M43" t="str">
         <v/>
       </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
+      <c r="N43" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O43" s="1" t="str">
         <v/>
       </c>
       <c r="P43" t="str">
@@ -2835,10 +2820,10 @@
       <c r="B44" t="str">
         <v>Bathrooms: RFQs Issued</v>
       </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
+      <c r="C44" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D44" s="1" t="str">
         <v/>
       </c>
       <c r="E44">
@@ -2868,10 +2853,10 @@
       <c r="M44" t="str">
         <v/>
       </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
+      <c r="N44" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O44" s="1" t="str">
         <v/>
       </c>
       <c r="P44" t="str">
@@ -2891,10 +2876,10 @@
       <c r="B45" t="str">
         <v>Bathrooms: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C45" t="str">
-        <v/>
-      </c>
-      <c r="D45" t="str">
+      <c r="C45" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D45" s="1" t="str">
         <v/>
       </c>
       <c r="E45">
@@ -2924,10 +2909,10 @@
       <c r="M45" t="str">
         <v/>
       </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
+      <c r="N45" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O45" s="1" t="str">
         <v/>
       </c>
       <c r="P45" t="str">
@@ -2947,10 +2932,10 @@
       <c r="B46" t="str">
         <v>Bathrooms: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="D46" t="str">
+      <c r="C46" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D46" s="1" t="str">
         <v/>
       </c>
       <c r="E46">
@@ -2980,10 +2965,10 @@
       <c r="M46" t="str">
         <v/>
       </c>
-      <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="O46" t="str">
+      <c r="N46" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O46" s="1" t="str">
         <v/>
       </c>
       <c r="P46" t="str">
@@ -3003,10 +2988,10 @@
       <c r="B47" t="str">
         <v>Bathrooms: Vendor Finalisation</v>
       </c>
-      <c r="C47" t="str">
-        <v/>
-      </c>
-      <c r="D47" t="str">
+      <c r="C47" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D47" s="1" t="str">
         <v/>
       </c>
       <c r="E47">
@@ -3036,10 +3021,10 @@
       <c r="M47" t="str">
         <v/>
       </c>
-      <c r="N47" t="str">
-        <v/>
-      </c>
-      <c r="O47" t="str">
+      <c r="N47" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O47" s="1" t="str">
         <v/>
       </c>
       <c r="P47" t="str">
@@ -3059,10 +3044,10 @@
       <c r="B48" t="str">
         <v>Bathrooms: Work Order / PO Release</v>
       </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="D48" t="str">
+      <c r="C48" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D48" s="1" t="str">
         <v/>
       </c>
       <c r="E48">
@@ -3092,10 +3077,10 @@
       <c r="M48" t="str">
         <v/>
       </c>
-      <c r="N48" t="str">
-        <v/>
-      </c>
-      <c r="O48" t="str">
+      <c r="N48" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O48" s="1" t="str">
         <v/>
       </c>
       <c r="P48" t="str">
@@ -3115,10 +3100,10 @@
       <c r="B49" t="str">
         <v>PACKAGE • Audio</v>
       </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
+      <c r="C49" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D49" s="1" t="str">
         <v/>
       </c>
       <c r="E49" t="str">
@@ -3148,10 +3133,10 @@
       <c r="M49" t="str">
         <v/>
       </c>
-      <c r="N49" t="str">
-        <v/>
-      </c>
-      <c r="O49" t="str">
+      <c r="N49" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O49" s="1" t="str">
         <v/>
       </c>
       <c r="P49" t="str">
@@ -3171,10 +3156,10 @@
       <c r="B50" t="str">
         <v>Audio: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" t="str">
+      <c r="C50" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D50" s="1" t="str">
         <v/>
       </c>
       <c r="E50">
@@ -3204,10 +3189,10 @@
       <c r="M50" t="str">
         <v/>
       </c>
-      <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="O50" t="str">
+      <c r="N50" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O50" s="1" t="str">
         <v/>
       </c>
       <c r="P50" t="str">
@@ -3227,10 +3212,10 @@
       <c r="B51" t="str">
         <v>Audio: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C51" t="str">
-        <v/>
-      </c>
-      <c r="D51" t="str">
+      <c r="C51" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D51" s="1" t="str">
         <v/>
       </c>
       <c r="E51">
@@ -3260,10 +3245,10 @@
       <c r="M51" t="str">
         <v/>
       </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-      <c r="O51" t="str">
+      <c r="N51" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O51" s="1" t="str">
         <v/>
       </c>
       <c r="P51" t="str">
@@ -3283,10 +3268,10 @@
       <c r="B52" t="str">
         <v>Audio: RFQs Issued</v>
       </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
+      <c r="C52" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D52" s="1" t="str">
         <v/>
       </c>
       <c r="E52">
@@ -3316,10 +3301,10 @@
       <c r="M52" t="str">
         <v/>
       </c>
-      <c r="N52" t="str">
-        <v/>
-      </c>
-      <c r="O52" t="str">
+      <c r="N52" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O52" s="1" t="str">
         <v/>
       </c>
       <c r="P52" t="str">
@@ -3339,10 +3324,10 @@
       <c r="B53" t="str">
         <v>Audio: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
+      <c r="C53" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D53" s="1" t="str">
         <v/>
       </c>
       <c r="E53">
@@ -3372,10 +3357,10 @@
       <c r="M53" t="str">
         <v/>
       </c>
-      <c r="N53" t="str">
-        <v/>
-      </c>
-      <c r="O53" t="str">
+      <c r="N53" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O53" s="1" t="str">
         <v/>
       </c>
       <c r="P53" t="str">
@@ -3395,10 +3380,10 @@
       <c r="B54" t="str">
         <v>Audio: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
+      <c r="C54" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D54" s="1" t="str">
         <v/>
       </c>
       <c r="E54">
@@ -3428,10 +3413,10 @@
       <c r="M54" t="str">
         <v/>
       </c>
-      <c r="N54" t="str">
-        <v/>
-      </c>
-      <c r="O54" t="str">
+      <c r="N54" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O54" s="1" t="str">
         <v/>
       </c>
       <c r="P54" t="str">
@@ -3451,10 +3436,10 @@
       <c r="B55" t="str">
         <v>Audio: Vendor Finalisation</v>
       </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
+      <c r="C55" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D55" s="1" t="str">
         <v/>
       </c>
       <c r="E55">
@@ -3484,10 +3469,10 @@
       <c r="M55" t="str">
         <v/>
       </c>
-      <c r="N55" t="str">
-        <v/>
-      </c>
-      <c r="O55" t="str">
+      <c r="N55" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O55" s="1" t="str">
         <v/>
       </c>
       <c r="P55" t="str">
@@ -3507,10 +3492,10 @@
       <c r="B56" t="str">
         <v>Audio: Work Order / PO Release</v>
       </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
+      <c r="C56" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D56" s="1" t="str">
         <v/>
       </c>
       <c r="E56">
@@ -3540,10 +3525,10 @@
       <c r="M56" t="str">
         <v/>
       </c>
-      <c r="N56" t="str">
-        <v/>
-      </c>
-      <c r="O56" t="str">
+      <c r="N56" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O56" s="1" t="str">
         <v/>
       </c>
       <c r="P56" t="str">
@@ -3563,10 +3548,10 @@
       <c r="B57" t="str">
         <v>PACKAGE • Automation</v>
       </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
+      <c r="C57" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D57" s="1" t="str">
         <v/>
       </c>
       <c r="E57" t="str">
@@ -3596,10 +3581,10 @@
       <c r="M57" t="str">
         <v/>
       </c>
-      <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57" t="str">
+      <c r="N57" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O57" s="1" t="str">
         <v/>
       </c>
       <c r="P57" t="str">
@@ -3619,10 +3604,10 @@
       <c r="B58" t="str">
         <v>Automation: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
+      <c r="C58" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D58" s="1" t="str">
         <v/>
       </c>
       <c r="E58">
@@ -3652,10 +3637,10 @@
       <c r="M58" t="str">
         <v/>
       </c>
-      <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
+      <c r="N58" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O58" s="1" t="str">
         <v/>
       </c>
       <c r="P58" t="str">
@@ -3675,10 +3660,10 @@
       <c r="B59" t="str">
         <v>Automation: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
+      <c r="C59" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D59" s="1" t="str">
         <v/>
       </c>
       <c r="E59">
@@ -3708,10 +3693,10 @@
       <c r="M59" t="str">
         <v/>
       </c>
-      <c r="N59" t="str">
-        <v/>
-      </c>
-      <c r="O59" t="str">
+      <c r="N59" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O59" s="1" t="str">
         <v/>
       </c>
       <c r="P59" t="str">
@@ -3731,10 +3716,10 @@
       <c r="B60" t="str">
         <v>Automation: RFQs Issued</v>
       </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
+      <c r="C60" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D60" s="1" t="str">
         <v/>
       </c>
       <c r="E60">
@@ -3764,10 +3749,10 @@
       <c r="M60" t="str">
         <v/>
       </c>
-      <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60" t="str">
+      <c r="N60" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O60" s="1" t="str">
         <v/>
       </c>
       <c r="P60" t="str">
@@ -3787,10 +3772,10 @@
       <c r="B61" t="str">
         <v>Automation: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
+      <c r="C61" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D61" s="1" t="str">
         <v/>
       </c>
       <c r="E61">
@@ -3820,10 +3805,10 @@
       <c r="M61" t="str">
         <v/>
       </c>
-      <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61" t="str">
+      <c r="N61" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O61" s="1" t="str">
         <v/>
       </c>
       <c r="P61" t="str">
@@ -3843,10 +3828,10 @@
       <c r="B62" t="str">
         <v>Automation: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="D62" t="str">
+      <c r="C62" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D62" s="1" t="str">
         <v/>
       </c>
       <c r="E62">
@@ -3876,10 +3861,10 @@
       <c r="M62" t="str">
         <v/>
       </c>
-      <c r="N62" t="str">
-        <v/>
-      </c>
-      <c r="O62" t="str">
+      <c r="N62" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O62" s="1" t="str">
         <v/>
       </c>
       <c r="P62" t="str">
@@ -3899,10 +3884,10 @@
       <c r="B63" t="str">
         <v>Automation: Vendor Finalisation</v>
       </c>
-      <c r="C63" t="str">
-        <v/>
-      </c>
-      <c r="D63" t="str">
+      <c r="C63" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D63" s="1" t="str">
         <v/>
       </c>
       <c r="E63">
@@ -3932,10 +3917,10 @@
       <c r="M63" t="str">
         <v/>
       </c>
-      <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
+      <c r="N63" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O63" s="1" t="str">
         <v/>
       </c>
       <c r="P63" t="str">
@@ -3955,10 +3940,10 @@
       <c r="B64" t="str">
         <v>Automation: Work Order / PO Release</v>
       </c>
-      <c r="C64" t="str">
-        <v/>
-      </c>
-      <c r="D64" t="str">
+      <c r="C64" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D64" s="1" t="str">
         <v/>
       </c>
       <c r="E64">
@@ -3988,10 +3973,10 @@
       <c r="M64" t="str">
         <v/>
       </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
+      <c r="N64" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O64" s="1" t="str">
         <v/>
       </c>
       <c r="P64" t="str">
@@ -4011,10 +3996,10 @@
       <c r="B65" t="str">
         <v>PACKAGE • Lighting</v>
       </c>
-      <c r="C65" t="str">
-        <v/>
-      </c>
-      <c r="D65" t="str">
+      <c r="C65" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D65" s="1" t="str">
         <v/>
       </c>
       <c r="E65" t="str">
@@ -4044,10 +4029,10 @@
       <c r="M65" t="str">
         <v/>
       </c>
-      <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="O65" t="str">
+      <c r="N65" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O65" s="1" t="str">
         <v/>
       </c>
       <c r="P65" t="str">
@@ -4067,10 +4052,10 @@
       <c r="B66" t="str">
         <v>Lighting: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="D66" t="str">
+      <c r="C66" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D66" s="1" t="str">
         <v/>
       </c>
       <c r="E66">
@@ -4100,10 +4085,10 @@
       <c r="M66" t="str">
         <v/>
       </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
+      <c r="N66" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O66" s="1" t="str">
         <v/>
       </c>
       <c r="P66" t="str">
@@ -4123,10 +4108,10 @@
       <c r="B67" t="str">
         <v>Lighting: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="D67" t="str">
+      <c r="C67" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D67" s="1" t="str">
         <v/>
       </c>
       <c r="E67">
@@ -4156,10 +4141,10 @@
       <c r="M67" t="str">
         <v/>
       </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
+      <c r="N67" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O67" s="1" t="str">
         <v/>
       </c>
       <c r="P67" t="str">
@@ -4179,10 +4164,10 @@
       <c r="B68" t="str">
         <v>Lighting: RFQs Issued</v>
       </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
+      <c r="C68" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D68" s="1" t="str">
         <v/>
       </c>
       <c r="E68">
@@ -4212,10 +4197,10 @@
       <c r="M68" t="str">
         <v/>
       </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
+      <c r="N68" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O68" s="1" t="str">
         <v/>
       </c>
       <c r="P68" t="str">
@@ -4235,10 +4220,10 @@
       <c r="B69" t="str">
         <v>Lighting: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="D69" t="str">
+      <c r="C69" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D69" s="1" t="str">
         <v/>
       </c>
       <c r="E69">
@@ -4268,10 +4253,10 @@
       <c r="M69" t="str">
         <v/>
       </c>
-      <c r="N69" t="str">
-        <v/>
-      </c>
-      <c r="O69" t="str">
+      <c r="N69" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O69" s="1" t="str">
         <v/>
       </c>
       <c r="P69" t="str">
@@ -4291,10 +4276,10 @@
       <c r="B70" t="str">
         <v>Lighting: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
+      <c r="C70" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D70" s="1" t="str">
         <v/>
       </c>
       <c r="E70">
@@ -4324,10 +4309,10 @@
       <c r="M70" t="str">
         <v/>
       </c>
-      <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
+      <c r="N70" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O70" s="1" t="str">
         <v/>
       </c>
       <c r="P70" t="str">
@@ -4347,10 +4332,10 @@
       <c r="B71" t="str">
         <v>Lighting: Vendor Finalisation</v>
       </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
+      <c r="C71" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D71" s="1" t="str">
         <v/>
       </c>
       <c r="E71">
@@ -4380,10 +4365,10 @@
       <c r="M71" t="str">
         <v/>
       </c>
-      <c r="N71" t="str">
-        <v/>
-      </c>
-      <c r="O71" t="str">
+      <c r="N71" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O71" s="1" t="str">
         <v/>
       </c>
       <c r="P71" t="str">
@@ -4403,10 +4388,10 @@
       <c r="B72" t="str">
         <v>Lighting: Work Order / PO Release</v>
       </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
+      <c r="C72" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D72" s="1" t="str">
         <v/>
       </c>
       <c r="E72">
@@ -4436,10 +4421,10 @@
       <c r="M72" t="str">
         <v/>
       </c>
-      <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72" t="str">
+      <c r="N72" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O72" s="1" t="str">
         <v/>
       </c>
       <c r="P72" t="str">
@@ -4459,10 +4444,10 @@
       <c r="B73" t="str">
         <v>PACKAGE • HVAC</v>
       </c>
-      <c r="C73" t="str">
-        <v/>
-      </c>
-      <c r="D73" t="str">
+      <c r="C73" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D73" s="1" t="str">
         <v/>
       </c>
       <c r="E73" t="str">
@@ -4492,10 +4477,10 @@
       <c r="M73" t="str">
         <v/>
       </c>
-      <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73" t="str">
+      <c r="N73" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O73" s="1" t="str">
         <v/>
       </c>
       <c r="P73" t="str">
@@ -4515,10 +4500,10 @@
       <c r="B74" t="str">
         <v>HVAC: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C74" t="str">
-        <v/>
-      </c>
-      <c r="D74" t="str">
+      <c r="C74" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D74" s="1" t="str">
         <v/>
       </c>
       <c r="E74">
@@ -4548,10 +4533,10 @@
       <c r="M74" t="str">
         <v/>
       </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
+      <c r="N74" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O74" s="1" t="str">
         <v/>
       </c>
       <c r="P74" t="str">
@@ -4571,10 +4556,10 @@
       <c r="B75" t="str">
         <v>HVAC: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
+      <c r="C75" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D75" s="1" t="str">
         <v/>
       </c>
       <c r="E75">
@@ -4604,10 +4589,10 @@
       <c r="M75" t="str">
         <v/>
       </c>
-      <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75" t="str">
+      <c r="N75" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O75" s="1" t="str">
         <v/>
       </c>
       <c r="P75" t="str">
@@ -4627,10 +4612,10 @@
       <c r="B76" t="str">
         <v>HVAC: RFQs Issued</v>
       </c>
-      <c r="C76" t="str">
-        <v/>
-      </c>
-      <c r="D76" t="str">
+      <c r="C76" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D76" s="1" t="str">
         <v/>
       </c>
       <c r="E76">
@@ -4660,10 +4645,10 @@
       <c r="M76" t="str">
         <v/>
       </c>
-      <c r="N76" t="str">
-        <v/>
-      </c>
-      <c r="O76" t="str">
+      <c r="N76" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O76" s="1" t="str">
         <v/>
       </c>
       <c r="P76" t="str">
@@ -4683,10 +4668,10 @@
       <c r="B77" t="str">
         <v>HVAC: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
+      <c r="C77" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D77" s="1" t="str">
         <v/>
       </c>
       <c r="E77">
@@ -4716,10 +4701,10 @@
       <c r="M77" t="str">
         <v/>
       </c>
-      <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77" t="str">
+      <c r="N77" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O77" s="1" t="str">
         <v/>
       </c>
       <c r="P77" t="str">
@@ -4739,10 +4724,10 @@
       <c r="B78" t="str">
         <v>HVAC: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
+      <c r="C78" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D78" s="1" t="str">
         <v/>
       </c>
       <c r="E78">
@@ -4772,10 +4757,10 @@
       <c r="M78" t="str">
         <v/>
       </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78" t="str">
+      <c r="N78" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O78" s="1" t="str">
         <v/>
       </c>
       <c r="P78" t="str">
@@ -4795,10 +4780,10 @@
       <c r="B79" t="str">
         <v>HVAC: Vendor Finalisation</v>
       </c>
-      <c r="C79" t="str">
-        <v/>
-      </c>
-      <c r="D79" t="str">
+      <c r="C79" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D79" s="1" t="str">
         <v/>
       </c>
       <c r="E79">
@@ -4828,10 +4813,10 @@
       <c r="M79" t="str">
         <v/>
       </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
+      <c r="N79" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O79" s="1" t="str">
         <v/>
       </c>
       <c r="P79" t="str">
@@ -4851,10 +4836,10 @@
       <c r="B80" t="str">
         <v>HVAC: Work Order / PO Release</v>
       </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
+      <c r="C80" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D80" s="1" t="str">
         <v/>
       </c>
       <c r="E80">
@@ -4884,10 +4869,10 @@
       <c r="M80" t="str">
         <v/>
       </c>
-      <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="O80" t="str">
+      <c r="N80" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O80" s="1" t="str">
         <v/>
       </c>
       <c r="P80" t="str">
@@ -4907,10 +4892,10 @@
       <c r="B81" t="str">
         <v>PACKAGE • Doors &amp; Windows</v>
       </c>
-      <c r="C81" t="str">
-        <v/>
-      </c>
-      <c r="D81" t="str">
+      <c r="C81" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D81" s="1" t="str">
         <v/>
       </c>
       <c r="E81" t="str">
@@ -4940,10 +4925,10 @@
       <c r="M81" t="str">
         <v/>
       </c>
-      <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="O81" t="str">
+      <c r="N81" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O81" s="1" t="str">
         <v/>
       </c>
       <c r="P81" t="str">
@@ -4963,10 +4948,10 @@
       <c r="B82" t="str">
         <v>Doors &amp; Windows: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C82" t="str">
-        <v/>
-      </c>
-      <c r="D82" t="str">
+      <c r="C82" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D82" s="1" t="str">
         <v/>
       </c>
       <c r="E82">
@@ -4996,10 +4981,10 @@
       <c r="M82" t="str">
         <v/>
       </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82" t="str">
+      <c r="N82" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O82" s="1" t="str">
         <v/>
       </c>
       <c r="P82" t="str">
@@ -5019,10 +5004,10 @@
       <c r="B83" t="str">
         <v>Doors &amp; Windows: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C83" t="str">
-        <v/>
-      </c>
-      <c r="D83" t="str">
+      <c r="C83" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D83" s="1" t="str">
         <v/>
       </c>
       <c r="E83">
@@ -5052,10 +5037,10 @@
       <c r="M83" t="str">
         <v/>
       </c>
-      <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="O83" t="str">
+      <c r="N83" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O83" s="1" t="str">
         <v/>
       </c>
       <c r="P83" t="str">
@@ -5075,10 +5060,10 @@
       <c r="B84" t="str">
         <v>Doors &amp; Windows: RFQs Issued</v>
       </c>
-      <c r="C84" t="str">
-        <v/>
-      </c>
-      <c r="D84" t="str">
+      <c r="C84" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D84" s="1" t="str">
         <v/>
       </c>
       <c r="E84">
@@ -5108,10 +5093,10 @@
       <c r="M84" t="str">
         <v/>
       </c>
-      <c r="N84" t="str">
-        <v/>
-      </c>
-      <c r="O84" t="str">
+      <c r="N84" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O84" s="1" t="str">
         <v/>
       </c>
       <c r="P84" t="str">
@@ -5131,10 +5116,10 @@
       <c r="B85" t="str">
         <v>Doors &amp; Windows: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C85" t="str">
-        <v/>
-      </c>
-      <c r="D85" t="str">
+      <c r="C85" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D85" s="1" t="str">
         <v/>
       </c>
       <c r="E85">
@@ -5164,10 +5149,10 @@
       <c r="M85" t="str">
         <v/>
       </c>
-      <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85" t="str">
+      <c r="N85" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O85" s="1" t="str">
         <v/>
       </c>
       <c r="P85" t="str">
@@ -5187,10 +5172,10 @@
       <c r="B86" t="str">
         <v>Doors &amp; Windows: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C86" t="str">
-        <v/>
-      </c>
-      <c r="D86" t="str">
+      <c r="C86" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D86" s="1" t="str">
         <v/>
       </c>
       <c r="E86">
@@ -5220,10 +5205,10 @@
       <c r="M86" t="str">
         <v/>
       </c>
-      <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="O86" t="str">
+      <c r="N86" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O86" s="1" t="str">
         <v/>
       </c>
       <c r="P86" t="str">
@@ -5243,10 +5228,10 @@
       <c r="B87" t="str">
         <v>Doors &amp; Windows: Vendor Finalisation</v>
       </c>
-      <c r="C87" t="str">
-        <v/>
-      </c>
-      <c r="D87" t="str">
+      <c r="C87" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D87" s="1" t="str">
         <v/>
       </c>
       <c r="E87">
@@ -5276,10 +5261,10 @@
       <c r="M87" t="str">
         <v/>
       </c>
-      <c r="N87" t="str">
-        <v/>
-      </c>
-      <c r="O87" t="str">
+      <c r="N87" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O87" s="1" t="str">
         <v/>
       </c>
       <c r="P87" t="str">
@@ -5299,10 +5284,10 @@
       <c r="B88" t="str">
         <v>Doors &amp; Windows: Work Order / PO Release</v>
       </c>
-      <c r="C88" t="str">
-        <v/>
-      </c>
-      <c r="D88" t="str">
+      <c r="C88" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D88" s="1" t="str">
         <v/>
       </c>
       <c r="E88">
@@ -5332,10 +5317,10 @@
       <c r="M88" t="str">
         <v/>
       </c>
-      <c r="N88" t="str">
-        <v/>
-      </c>
-      <c r="O88" t="str">
+      <c r="N88" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O88" s="1" t="str">
         <v/>
       </c>
       <c r="P88" t="str">
@@ -5355,10 +5340,10 @@
       <c r="B89" t="str">
         <v>PACKAGE • Wall Finishes</v>
       </c>
-      <c r="C89" t="str">
-        <v/>
-      </c>
-      <c r="D89" t="str">
+      <c r="C89" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D89" s="1" t="str">
         <v/>
       </c>
       <c r="E89" t="str">
@@ -5388,10 +5373,10 @@
       <c r="M89" t="str">
         <v/>
       </c>
-      <c r="N89" t="str">
-        <v/>
-      </c>
-      <c r="O89" t="str">
+      <c r="N89" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O89" s="1" t="str">
         <v/>
       </c>
       <c r="P89" t="str">
@@ -5411,10 +5396,10 @@
       <c r="B90" t="str">
         <v>Wall Finishes: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C90" t="str">
-        <v/>
-      </c>
-      <c r="D90" t="str">
+      <c r="C90" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D90" s="1" t="str">
         <v/>
       </c>
       <c r="E90">
@@ -5444,10 +5429,10 @@
       <c r="M90" t="str">
         <v/>
       </c>
-      <c r="N90" t="str">
-        <v/>
-      </c>
-      <c r="O90" t="str">
+      <c r="N90" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O90" s="1" t="str">
         <v/>
       </c>
       <c r="P90" t="str">
@@ -5467,10 +5452,10 @@
       <c r="B91" t="str">
         <v>Wall Finishes: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C91" t="str">
-        <v/>
-      </c>
-      <c r="D91" t="str">
+      <c r="C91" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D91" s="1" t="str">
         <v/>
       </c>
       <c r="E91">
@@ -5500,10 +5485,10 @@
       <c r="M91" t="str">
         <v/>
       </c>
-      <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="O91" t="str">
+      <c r="N91" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O91" s="1" t="str">
         <v/>
       </c>
       <c r="P91" t="str">
@@ -5523,10 +5508,10 @@
       <c r="B92" t="str">
         <v>Wall Finishes: RFQs Issued</v>
       </c>
-      <c r="C92" t="str">
-        <v/>
-      </c>
-      <c r="D92" t="str">
+      <c r="C92" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D92" s="1" t="str">
         <v/>
       </c>
       <c r="E92">
@@ -5556,10 +5541,10 @@
       <c r="M92" t="str">
         <v/>
       </c>
-      <c r="N92" t="str">
-        <v/>
-      </c>
-      <c r="O92" t="str">
+      <c r="N92" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O92" s="1" t="str">
         <v/>
       </c>
       <c r="P92" t="str">
@@ -5579,10 +5564,10 @@
       <c r="B93" t="str">
         <v>Wall Finishes: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C93" t="str">
-        <v/>
-      </c>
-      <c r="D93" t="str">
+      <c r="C93" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D93" s="1" t="str">
         <v/>
       </c>
       <c r="E93">
@@ -5612,10 +5597,10 @@
       <c r="M93" t="str">
         <v/>
       </c>
-      <c r="N93" t="str">
-        <v/>
-      </c>
-      <c r="O93" t="str">
+      <c r="N93" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O93" s="1" t="str">
         <v/>
       </c>
       <c r="P93" t="str">
@@ -5635,10 +5620,10 @@
       <c r="B94" t="str">
         <v>Wall Finishes: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C94" t="str">
-        <v/>
-      </c>
-      <c r="D94" t="str">
+      <c r="C94" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D94" s="1" t="str">
         <v/>
       </c>
       <c r="E94">
@@ -5668,10 +5653,10 @@
       <c r="M94" t="str">
         <v/>
       </c>
-      <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="O94" t="str">
+      <c r="N94" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O94" s="1" t="str">
         <v/>
       </c>
       <c r="P94" t="str">
@@ -5691,10 +5676,10 @@
       <c r="B95" t="str">
         <v>Wall Finishes: Vendor Finalisation</v>
       </c>
-      <c r="C95" t="str">
-        <v/>
-      </c>
-      <c r="D95" t="str">
+      <c r="C95" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D95" s="1" t="str">
         <v/>
       </c>
       <c r="E95">
@@ -5724,10 +5709,10 @@
       <c r="M95" t="str">
         <v/>
       </c>
-      <c r="N95" t="str">
-        <v/>
-      </c>
-      <c r="O95" t="str">
+      <c r="N95" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O95" s="1" t="str">
         <v/>
       </c>
       <c r="P95" t="str">
@@ -5747,10 +5732,10 @@
       <c r="B96" t="str">
         <v>Wall Finishes: Work Order / PO Release</v>
       </c>
-      <c r="C96" t="str">
-        <v/>
-      </c>
-      <c r="D96" t="str">
+      <c r="C96" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D96" s="1" t="str">
         <v/>
       </c>
       <c r="E96">
@@ -5780,10 +5765,10 @@
       <c r="M96" t="str">
         <v/>
       </c>
-      <c r="N96" t="str">
-        <v/>
-      </c>
-      <c r="O96" t="str">
+      <c r="N96" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O96" s="1" t="str">
         <v/>
       </c>
       <c r="P96" t="str">
@@ -5803,10 +5788,10 @@
       <c r="B97" t="str">
         <v>PACKAGE • Furnishing</v>
       </c>
-      <c r="C97" t="str">
-        <v/>
-      </c>
-      <c r="D97" t="str">
+      <c r="C97" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D97" s="1" t="str">
         <v/>
       </c>
       <c r="E97" t="str">
@@ -5836,10 +5821,10 @@
       <c r="M97" t="str">
         <v/>
       </c>
-      <c r="N97" t="str">
-        <v/>
-      </c>
-      <c r="O97" t="str">
+      <c r="N97" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O97" s="1" t="str">
         <v/>
       </c>
       <c r="P97" t="str">
@@ -5859,10 +5844,10 @@
       <c r="B98" t="str">
         <v>Furnishing: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C98" t="str">
-        <v/>
-      </c>
-      <c r="D98" t="str">
+      <c r="C98" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D98" s="1" t="str">
         <v/>
       </c>
       <c r="E98">
@@ -5892,10 +5877,10 @@
       <c r="M98" t="str">
         <v/>
       </c>
-      <c r="N98" t="str">
-        <v/>
-      </c>
-      <c r="O98" t="str">
+      <c r="N98" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O98" s="1" t="str">
         <v/>
       </c>
       <c r="P98" t="str">
@@ -5915,10 +5900,10 @@
       <c r="B99" t="str">
         <v>Furnishing: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C99" t="str">
-        <v/>
-      </c>
-      <c r="D99" t="str">
+      <c r="C99" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D99" s="1" t="str">
         <v/>
       </c>
       <c r="E99">
@@ -5948,10 +5933,10 @@
       <c r="M99" t="str">
         <v/>
       </c>
-      <c r="N99" t="str">
-        <v/>
-      </c>
-      <c r="O99" t="str">
+      <c r="N99" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O99" s="1" t="str">
         <v/>
       </c>
       <c r="P99" t="str">
@@ -5971,10 +5956,10 @@
       <c r="B100" t="str">
         <v>Furnishing: RFQs Issued</v>
       </c>
-      <c r="C100" t="str">
-        <v/>
-      </c>
-      <c r="D100" t="str">
+      <c r="C100" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D100" s="1" t="str">
         <v/>
       </c>
       <c r="E100">
@@ -6004,10 +5989,10 @@
       <c r="M100" t="str">
         <v/>
       </c>
-      <c r="N100" t="str">
-        <v/>
-      </c>
-      <c r="O100" t="str">
+      <c r="N100" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O100" s="1" t="str">
         <v/>
       </c>
       <c r="P100" t="str">
@@ -6027,10 +6012,10 @@
       <c r="B101" t="str">
         <v>Furnishing: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C101" t="str">
-        <v/>
-      </c>
-      <c r="D101" t="str">
+      <c r="C101" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D101" s="1" t="str">
         <v/>
       </c>
       <c r="E101">
@@ -6060,10 +6045,10 @@
       <c r="M101" t="str">
         <v/>
       </c>
-      <c r="N101" t="str">
-        <v/>
-      </c>
-      <c r="O101" t="str">
+      <c r="N101" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O101" s="1" t="str">
         <v/>
       </c>
       <c r="P101" t="str">
@@ -6083,10 +6068,10 @@
       <c r="B102" t="str">
         <v>Furnishing: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C102" t="str">
-        <v/>
-      </c>
-      <c r="D102" t="str">
+      <c r="C102" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D102" s="1" t="str">
         <v/>
       </c>
       <c r="E102">
@@ -6116,10 +6101,10 @@
       <c r="M102" t="str">
         <v/>
       </c>
-      <c r="N102" t="str">
-        <v/>
-      </c>
-      <c r="O102" t="str">
+      <c r="N102" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O102" s="1" t="str">
         <v/>
       </c>
       <c r="P102" t="str">
@@ -6139,10 +6124,10 @@
       <c r="B103" t="str">
         <v>Furnishing: Vendor Finalisation</v>
       </c>
-      <c r="C103" t="str">
-        <v/>
-      </c>
-      <c r="D103" t="str">
+      <c r="C103" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D103" s="1" t="str">
         <v/>
       </c>
       <c r="E103">
@@ -6172,10 +6157,10 @@
       <c r="M103" t="str">
         <v/>
       </c>
-      <c r="N103" t="str">
-        <v/>
-      </c>
-      <c r="O103" t="str">
+      <c r="N103" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O103" s="1" t="str">
         <v/>
       </c>
       <c r="P103" t="str">
@@ -6195,10 +6180,10 @@
       <c r="B104" t="str">
         <v>Furnishing: Work Order / PO Release</v>
       </c>
-      <c r="C104" t="str">
-        <v/>
-      </c>
-      <c r="D104" t="str">
+      <c r="C104" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D104" s="1" t="str">
         <v/>
       </c>
       <c r="E104">
@@ -6228,10 +6213,10 @@
       <c r="M104" t="str">
         <v/>
       </c>
-      <c r="N104" t="str">
-        <v/>
-      </c>
-      <c r="O104" t="str">
+      <c r="N104" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O104" s="1" t="str">
         <v/>
       </c>
       <c r="P104" t="str">
@@ -6251,10 +6236,10 @@
       <c r="B105" t="str">
         <v>PACKAGE • Soft Furnishing</v>
       </c>
-      <c r="C105" t="str">
-        <v/>
-      </c>
-      <c r="D105" t="str">
+      <c r="C105" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D105" s="1" t="str">
         <v/>
       </c>
       <c r="E105" t="str">
@@ -6284,10 +6269,10 @@
       <c r="M105" t="str">
         <v/>
       </c>
-      <c r="N105" t="str">
-        <v/>
-      </c>
-      <c r="O105" t="str">
+      <c r="N105" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O105" s="1" t="str">
         <v/>
       </c>
       <c r="P105" t="str">
@@ -6307,10 +6292,10 @@
       <c r="B106" t="str">
         <v>Soft Furnishing: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C106" t="str">
-        <v/>
-      </c>
-      <c r="D106" t="str">
+      <c r="C106" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D106" s="1" t="str">
         <v/>
       </c>
       <c r="E106">
@@ -6340,10 +6325,10 @@
       <c r="M106" t="str">
         <v/>
       </c>
-      <c r="N106" t="str">
-        <v/>
-      </c>
-      <c r="O106" t="str">
+      <c r="N106" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O106" s="1" t="str">
         <v/>
       </c>
       <c r="P106" t="str">
@@ -6363,10 +6348,10 @@
       <c r="B107" t="str">
         <v>Soft Furnishing: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C107" t="str">
-        <v/>
-      </c>
-      <c r="D107" t="str">
+      <c r="C107" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D107" s="1" t="str">
         <v/>
       </c>
       <c r="E107">
@@ -6396,10 +6381,10 @@
       <c r="M107" t="str">
         <v/>
       </c>
-      <c r="N107" t="str">
-        <v/>
-      </c>
-      <c r="O107" t="str">
+      <c r="N107" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O107" s="1" t="str">
         <v/>
       </c>
       <c r="P107" t="str">
@@ -6419,10 +6404,10 @@
       <c r="B108" t="str">
         <v>Soft Furnishing: RFQs Issued</v>
       </c>
-      <c r="C108" t="str">
-        <v/>
-      </c>
-      <c r="D108" t="str">
+      <c r="C108" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D108" s="1" t="str">
         <v/>
       </c>
       <c r="E108">
@@ -6452,10 +6437,10 @@
       <c r="M108" t="str">
         <v/>
       </c>
-      <c r="N108" t="str">
-        <v/>
-      </c>
-      <c r="O108" t="str">
+      <c r="N108" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O108" s="1" t="str">
         <v/>
       </c>
       <c r="P108" t="str">
@@ -6475,10 +6460,10 @@
       <c r="B109" t="str">
         <v>Soft Furnishing: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C109" t="str">
-        <v/>
-      </c>
-      <c r="D109" t="str">
+      <c r="C109" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D109" s="1" t="str">
         <v/>
       </c>
       <c r="E109">
@@ -6508,10 +6493,10 @@
       <c r="M109" t="str">
         <v/>
       </c>
-      <c r="N109" t="str">
-        <v/>
-      </c>
-      <c r="O109" t="str">
+      <c r="N109" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O109" s="1" t="str">
         <v/>
       </c>
       <c r="P109" t="str">
@@ -6531,10 +6516,10 @@
       <c r="B110" t="str">
         <v>Soft Furnishing: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C110" t="str">
-        <v/>
-      </c>
-      <c r="D110" t="str">
+      <c r="C110" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D110" s="1" t="str">
         <v/>
       </c>
       <c r="E110">
@@ -6564,10 +6549,10 @@
       <c r="M110" t="str">
         <v/>
       </c>
-      <c r="N110" t="str">
-        <v/>
-      </c>
-      <c r="O110" t="str">
+      <c r="N110" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O110" s="1" t="str">
         <v/>
       </c>
       <c r="P110" t="str">
@@ -6587,10 +6572,10 @@
       <c r="B111" t="str">
         <v>Soft Furnishing: Vendor Finalisation</v>
       </c>
-      <c r="C111" t="str">
-        <v/>
-      </c>
-      <c r="D111" t="str">
+      <c r="C111" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D111" s="1" t="str">
         <v/>
       </c>
       <c r="E111">
@@ -6620,10 +6605,10 @@
       <c r="M111" t="str">
         <v/>
       </c>
-      <c r="N111" t="str">
-        <v/>
-      </c>
-      <c r="O111" t="str">
+      <c r="N111" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O111" s="1" t="str">
         <v/>
       </c>
       <c r="P111" t="str">
@@ -6643,10 +6628,10 @@
       <c r="B112" t="str">
         <v>Soft Furnishing: Work Order / PO Release</v>
       </c>
-      <c r="C112" t="str">
-        <v/>
-      </c>
-      <c r="D112" t="str">
+      <c r="C112" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D112" s="1" t="str">
         <v/>
       </c>
       <c r="E112">
@@ -6676,10 +6661,10 @@
       <c r="M112" t="str">
         <v/>
       </c>
-      <c r="N112" t="str">
-        <v/>
-      </c>
-      <c r="O112" t="str">
+      <c r="N112" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O112" s="1" t="str">
         <v/>
       </c>
       <c r="P112" t="str">
@@ -6699,10 +6684,10 @@
       <c r="B113" t="str">
         <v>PACKAGE • Appliances</v>
       </c>
-      <c r="C113" t="str">
-        <v/>
-      </c>
-      <c r="D113" t="str">
+      <c r="C113" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D113" s="1" t="str">
         <v/>
       </c>
       <c r="E113" t="str">
@@ -6732,10 +6717,10 @@
       <c r="M113" t="str">
         <v/>
       </c>
-      <c r="N113" t="str">
-        <v/>
-      </c>
-      <c r="O113" t="str">
+      <c r="N113" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O113" s="1" t="str">
         <v/>
       </c>
       <c r="P113" t="str">
@@ -6755,10 +6740,10 @@
       <c r="B114" t="str">
         <v>Appliances: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C114" t="str">
-        <v/>
-      </c>
-      <c r="D114" t="str">
+      <c r="C114" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D114" s="1" t="str">
         <v/>
       </c>
       <c r="E114">
@@ -6788,10 +6773,10 @@
       <c r="M114" t="str">
         <v/>
       </c>
-      <c r="N114" t="str">
-        <v/>
-      </c>
-      <c r="O114" t="str">
+      <c r="N114" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O114" s="1" t="str">
         <v/>
       </c>
       <c r="P114" t="str">
@@ -6811,10 +6796,10 @@
       <c r="B115" t="str">
         <v>Appliances: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C115" t="str">
-        <v/>
-      </c>
-      <c r="D115" t="str">
+      <c r="C115" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D115" s="1" t="str">
         <v/>
       </c>
       <c r="E115">
@@ -6844,10 +6829,10 @@
       <c r="M115" t="str">
         <v/>
       </c>
-      <c r="N115" t="str">
-        <v/>
-      </c>
-      <c r="O115" t="str">
+      <c r="N115" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O115" s="1" t="str">
         <v/>
       </c>
       <c r="P115" t="str">
@@ -6867,10 +6852,10 @@
       <c r="B116" t="str">
         <v>Appliances: RFQs Issued</v>
       </c>
-      <c r="C116" t="str">
-        <v/>
-      </c>
-      <c r="D116" t="str">
+      <c r="C116" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D116" s="1" t="str">
         <v/>
       </c>
       <c r="E116">
@@ -6900,10 +6885,10 @@
       <c r="M116" t="str">
         <v/>
       </c>
-      <c r="N116" t="str">
-        <v/>
-      </c>
-      <c r="O116" t="str">
+      <c r="N116" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O116" s="1" t="str">
         <v/>
       </c>
       <c r="P116" t="str">
@@ -6923,10 +6908,10 @@
       <c r="B117" t="str">
         <v>Appliances: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C117" t="str">
-        <v/>
-      </c>
-      <c r="D117" t="str">
+      <c r="C117" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D117" s="1" t="str">
         <v/>
       </c>
       <c r="E117">
@@ -6956,10 +6941,10 @@
       <c r="M117" t="str">
         <v/>
       </c>
-      <c r="N117" t="str">
-        <v/>
-      </c>
-      <c r="O117" t="str">
+      <c r="N117" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O117" s="1" t="str">
         <v/>
       </c>
       <c r="P117" t="str">
@@ -6979,10 +6964,10 @@
       <c r="B118" t="str">
         <v>Appliances: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C118" t="str">
-        <v/>
-      </c>
-      <c r="D118" t="str">
+      <c r="C118" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D118" s="1" t="str">
         <v/>
       </c>
       <c r="E118">
@@ -7012,10 +6997,10 @@
       <c r="M118" t="str">
         <v/>
       </c>
-      <c r="N118" t="str">
-        <v/>
-      </c>
-      <c r="O118" t="str">
+      <c r="N118" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O118" s="1" t="str">
         <v/>
       </c>
       <c r="P118" t="str">
@@ -7035,10 +7020,10 @@
       <c r="B119" t="str">
         <v>Appliances: Vendor Finalisation</v>
       </c>
-      <c r="C119" t="str">
-        <v/>
-      </c>
-      <c r="D119" t="str">
+      <c r="C119" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D119" s="1" t="str">
         <v/>
       </c>
       <c r="E119">
@@ -7068,10 +7053,10 @@
       <c r="M119" t="str">
         <v/>
       </c>
-      <c r="N119" t="str">
-        <v/>
-      </c>
-      <c r="O119" t="str">
+      <c r="N119" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O119" s="1" t="str">
         <v/>
       </c>
       <c r="P119" t="str">
@@ -7091,10 +7076,10 @@
       <c r="B120" t="str">
         <v>Appliances: Work Order / PO Release</v>
       </c>
-      <c r="C120" t="str">
-        <v/>
-      </c>
-      <c r="D120" t="str">
+      <c r="C120" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D120" s="1" t="str">
         <v/>
       </c>
       <c r="E120">
@@ -7124,10 +7109,10 @@
       <c r="M120" t="str">
         <v/>
       </c>
-      <c r="N120" t="str">
-        <v/>
-      </c>
-      <c r="O120" t="str">
+      <c r="N120" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O120" s="1" t="str">
         <v/>
       </c>
       <c r="P120" t="str">
@@ -7147,10 +7132,10 @@
       <c r="B121" t="str">
         <v>PACKAGE • Flooring</v>
       </c>
-      <c r="C121" t="str">
-        <v/>
-      </c>
-      <c r="D121" t="str">
+      <c r="C121" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D121" s="1" t="str">
         <v/>
       </c>
       <c r="E121" t="str">
@@ -7180,10 +7165,10 @@
       <c r="M121" t="str">
         <v/>
       </c>
-      <c r="N121" t="str">
-        <v/>
-      </c>
-      <c r="O121" t="str">
+      <c r="N121" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O121" s="1" t="str">
         <v/>
       </c>
       <c r="P121" t="str">
@@ -7203,10 +7188,10 @@
       <c r="B122" t="str">
         <v>Flooring: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C122" t="str">
-        <v/>
-      </c>
-      <c r="D122" t="str">
+      <c r="C122" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D122" s="1" t="str">
         <v/>
       </c>
       <c r="E122">
@@ -7236,10 +7221,10 @@
       <c r="M122" t="str">
         <v/>
       </c>
-      <c r="N122" t="str">
-        <v/>
-      </c>
-      <c r="O122" t="str">
+      <c r="N122" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O122" s="1" t="str">
         <v/>
       </c>
       <c r="P122" t="str">
@@ -7259,10 +7244,10 @@
       <c r="B123" t="str">
         <v>Flooring: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C123" t="str">
-        <v/>
-      </c>
-      <c r="D123" t="str">
+      <c r="C123" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D123" s="1" t="str">
         <v/>
       </c>
       <c r="E123">
@@ -7292,10 +7277,10 @@
       <c r="M123" t="str">
         <v/>
       </c>
-      <c r="N123" t="str">
-        <v/>
-      </c>
-      <c r="O123" t="str">
+      <c r="N123" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O123" s="1" t="str">
         <v/>
       </c>
       <c r="P123" t="str">
@@ -7315,10 +7300,10 @@
       <c r="B124" t="str">
         <v>Flooring: RFQs Issued</v>
       </c>
-      <c r="C124" t="str">
-        <v/>
-      </c>
-      <c r="D124" t="str">
+      <c r="C124" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D124" s="1" t="str">
         <v/>
       </c>
       <c r="E124">
@@ -7348,10 +7333,10 @@
       <c r="M124" t="str">
         <v/>
       </c>
-      <c r="N124" t="str">
-        <v/>
-      </c>
-      <c r="O124" t="str">
+      <c r="N124" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O124" s="1" t="str">
         <v/>
       </c>
       <c r="P124" t="str">
@@ -7371,10 +7356,10 @@
       <c r="B125" t="str">
         <v>Flooring: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C125" t="str">
-        <v/>
-      </c>
-      <c r="D125" t="str">
+      <c r="C125" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D125" s="1" t="str">
         <v/>
       </c>
       <c r="E125">
@@ -7404,10 +7389,10 @@
       <c r="M125" t="str">
         <v/>
       </c>
-      <c r="N125" t="str">
-        <v/>
-      </c>
-      <c r="O125" t="str">
+      <c r="N125" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O125" s="1" t="str">
         <v/>
       </c>
       <c r="P125" t="str">
@@ -7427,10 +7412,10 @@
       <c r="B126" t="str">
         <v>Flooring: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C126" t="str">
-        <v/>
-      </c>
-      <c r="D126" t="str">
+      <c r="C126" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D126" s="1" t="str">
         <v/>
       </c>
       <c r="E126">
@@ -7460,10 +7445,10 @@
       <c r="M126" t="str">
         <v/>
       </c>
-      <c r="N126" t="str">
-        <v/>
-      </c>
-      <c r="O126" t="str">
+      <c r="N126" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O126" s="1" t="str">
         <v/>
       </c>
       <c r="P126" t="str">
@@ -7483,10 +7468,10 @@
       <c r="B127" t="str">
         <v>Flooring: Vendor Finalisation</v>
       </c>
-      <c r="C127" t="str">
-        <v/>
-      </c>
-      <c r="D127" t="str">
+      <c r="C127" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D127" s="1" t="str">
         <v/>
       </c>
       <c r="E127">
@@ -7516,10 +7501,10 @@
       <c r="M127" t="str">
         <v/>
       </c>
-      <c r="N127" t="str">
-        <v/>
-      </c>
-      <c r="O127" t="str">
+      <c r="N127" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O127" s="1" t="str">
         <v/>
       </c>
       <c r="P127" t="str">
@@ -7539,10 +7524,10 @@
       <c r="B128" t="str">
         <v>Flooring: Work Order / PO Release</v>
       </c>
-      <c r="C128" t="str">
-        <v/>
-      </c>
-      <c r="D128" t="str">
+      <c r="C128" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D128" s="1" t="str">
         <v/>
       </c>
       <c r="E128">
@@ -7572,10 +7557,10 @@
       <c r="M128" t="str">
         <v/>
       </c>
-      <c r="N128" t="str">
-        <v/>
-      </c>
-      <c r="O128" t="str">
+      <c r="N128" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O128" s="1" t="str">
         <v/>
       </c>
       <c r="P128" t="str">
@@ -7595,10 +7580,10 @@
       <c r="B129" t="str">
         <v>PACKAGE • Carpentry</v>
       </c>
-      <c r="C129" t="str">
-        <v/>
-      </c>
-      <c r="D129" t="str">
+      <c r="C129" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D129" s="1" t="str">
         <v/>
       </c>
       <c r="E129" t="str">
@@ -7628,10 +7613,10 @@
       <c r="M129" t="str">
         <v/>
       </c>
-      <c r="N129" t="str">
-        <v/>
-      </c>
-      <c r="O129" t="str">
+      <c r="N129" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O129" s="1" t="str">
         <v/>
       </c>
       <c r="P129" t="str">
@@ -7651,10 +7636,10 @@
       <c r="B130" t="str">
         <v>Carpentry: Vendor Evaluation (shortlist)</v>
       </c>
-      <c r="C130" t="str">
-        <v/>
-      </c>
-      <c r="D130" t="str">
+      <c r="C130" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D130" s="1" t="str">
         <v/>
       </c>
       <c r="E130">
@@ -7684,10 +7669,10 @@
       <c r="M130" t="str">
         <v/>
       </c>
-      <c r="N130" t="str">
-        <v/>
-      </c>
-      <c r="O130" t="str">
+      <c r="N130" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O130" s="1" t="str">
         <v/>
       </c>
       <c r="P130" t="str">
@@ -7707,10 +7692,10 @@
       <c r="B131" t="str">
         <v>Carpentry: Vendor Meetings / Site Survey</v>
       </c>
-      <c r="C131" t="str">
-        <v/>
-      </c>
-      <c r="D131" t="str">
+      <c r="C131" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D131" s="1" t="str">
         <v/>
       </c>
       <c r="E131">
@@ -7740,10 +7725,10 @@
       <c r="M131" t="str">
         <v/>
       </c>
-      <c r="N131" t="str">
-        <v/>
-      </c>
-      <c r="O131" t="str">
+      <c r="N131" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O131" s="1" t="str">
         <v/>
       </c>
       <c r="P131" t="str">
@@ -7763,10 +7748,10 @@
       <c r="B132" t="str">
         <v>Carpentry: RFQs Issued</v>
       </c>
-      <c r="C132" t="str">
-        <v/>
-      </c>
-      <c r="D132" t="str">
+      <c r="C132" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D132" s="1" t="str">
         <v/>
       </c>
       <c r="E132">
@@ -7796,10 +7781,10 @@
       <c r="M132" t="str">
         <v/>
       </c>
-      <c r="N132" t="str">
-        <v/>
-      </c>
-      <c r="O132" t="str">
+      <c r="N132" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O132" s="1" t="str">
         <v/>
       </c>
       <c r="P132" t="str">
@@ -7819,10 +7804,10 @@
       <c r="B133" t="str">
         <v>Carpentry: Quotes Received &amp; Clarifications</v>
       </c>
-      <c r="C133" t="str">
-        <v/>
-      </c>
-      <c r="D133" t="str">
+      <c r="C133" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D133" s="1" t="str">
         <v/>
       </c>
       <c r="E133">
@@ -7852,10 +7837,10 @@
       <c r="M133" t="str">
         <v/>
       </c>
-      <c r="N133" t="str">
-        <v/>
-      </c>
-      <c r="O133" t="str">
+      <c r="N133" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O133" s="1" t="str">
         <v/>
       </c>
       <c r="P133" t="str">
@@ -7875,10 +7860,10 @@
       <c r="B134" t="str">
         <v>Carpentry: Quote Comparison &amp; Negotiation</v>
       </c>
-      <c r="C134" t="str">
-        <v/>
-      </c>
-      <c r="D134" t="str">
+      <c r="C134" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D134" s="1" t="str">
         <v/>
       </c>
       <c r="E134">
@@ -7908,10 +7893,10 @@
       <c r="M134" t="str">
         <v/>
       </c>
-      <c r="N134" t="str">
-        <v/>
-      </c>
-      <c r="O134" t="str">
+      <c r="N134" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O134" s="1" t="str">
         <v/>
       </c>
       <c r="P134" t="str">
@@ -7931,10 +7916,10 @@
       <c r="B135" t="str">
         <v>Carpentry: Vendor Finalisation</v>
       </c>
-      <c r="C135" t="str">
-        <v/>
-      </c>
-      <c r="D135" t="str">
+      <c r="C135" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D135" s="1" t="str">
         <v/>
       </c>
       <c r="E135">
@@ -7964,10 +7949,10 @@
       <c r="M135" t="str">
         <v/>
       </c>
-      <c r="N135" t="str">
-        <v/>
-      </c>
-      <c r="O135" t="str">
+      <c r="N135" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O135" s="1" t="str">
         <v/>
       </c>
       <c r="P135" t="str">
@@ -7987,10 +7972,10 @@
       <c r="B136" t="str">
         <v>Carpentry: Work Order / PO Release</v>
       </c>
-      <c r="C136" t="str">
-        <v/>
-      </c>
-      <c r="D136" t="str">
+      <c r="C136" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D136" s="1" t="str">
         <v/>
       </c>
       <c r="E136">
@@ -8020,10 +8005,10 @@
       <c r="M136" t="str">
         <v/>
       </c>
-      <c r="N136" t="str">
-        <v/>
-      </c>
-      <c r="O136" t="str">
+      <c r="N136" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O136" s="1" t="str">
         <v/>
       </c>
       <c r="P136" t="str">
@@ -8043,10 +8028,10 @@
       <c r="B137" t="str">
         <v>PHASE • Execution (Category-wise)</v>
       </c>
-      <c r="C137" t="str">
-        <v/>
-      </c>
-      <c r="D137" t="str">
+      <c r="C137" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D137" s="1" t="str">
         <v/>
       </c>
       <c r="E137" t="str">
@@ -8076,10 +8061,10 @@
       <c r="M137" t="str">
         <v/>
       </c>
-      <c r="N137" t="str">
-        <v/>
-      </c>
-      <c r="O137" t="str">
+      <c r="N137" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O137" s="1" t="str">
         <v/>
       </c>
       <c r="P137" t="str">
@@ -8099,10 +8084,10 @@
       <c r="B138" t="str">
         <v>EXECUTE • Civil</v>
       </c>
-      <c r="C138" t="str">
-        <v/>
-      </c>
-      <c r="D138" t="str">
+      <c r="C138" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D138" s="1" t="str">
         <v/>
       </c>
       <c r="E138" t="str">
@@ -8132,10 +8117,10 @@
       <c r="M138" t="str">
         <v/>
       </c>
-      <c r="N138" t="str">
-        <v/>
-      </c>
-      <c r="O138" t="str">
+      <c r="N138" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O138" s="1" t="str">
         <v/>
       </c>
       <c r="P138" t="str">
@@ -8155,10 +8140,10 @@
       <c r="B139" t="str">
         <v>Civil: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C139" t="str">
-        <v/>
-      </c>
-      <c r="D139" t="str">
+      <c r="C139" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D139" s="1" t="str">
         <v/>
       </c>
       <c r="E139">
@@ -8188,10 +8173,10 @@
       <c r="M139" t="str">
         <v/>
       </c>
-      <c r="N139" t="str">
-        <v/>
-      </c>
-      <c r="O139" t="str">
+      <c r="N139" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O139" s="1" t="str">
         <v/>
       </c>
       <c r="P139" t="str">
@@ -8211,10 +8196,10 @@
       <c r="B140" t="str">
         <v>Civil: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C140" t="str">
-        <v/>
-      </c>
-      <c r="D140" t="str">
+      <c r="C140" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D140" s="1" t="str">
         <v/>
       </c>
       <c r="E140">
@@ -8244,10 +8229,10 @@
       <c r="M140" t="str">
         <v/>
       </c>
-      <c r="N140" t="str">
-        <v/>
-      </c>
-      <c r="O140" t="str">
+      <c r="N140" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O140" s="1" t="str">
         <v/>
       </c>
       <c r="P140" t="str">
@@ -8267,10 +8252,10 @@
       <c r="B141" t="str">
         <v>Civil: Delivery to Site</v>
       </c>
-      <c r="C141" t="str">
-        <v/>
-      </c>
-      <c r="D141" t="str">
+      <c r="C141" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D141" s="1" t="str">
         <v/>
       </c>
       <c r="E141">
@@ -8300,10 +8285,10 @@
       <c r="M141" t="str">
         <v/>
       </c>
-      <c r="N141" t="str">
-        <v/>
-      </c>
-      <c r="O141" t="str">
+      <c r="N141" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O141" s="1" t="str">
         <v/>
       </c>
       <c r="P141" t="str">
@@ -8323,10 +8308,10 @@
       <c r="B142" t="str">
         <v>Civil: Installation / Execution</v>
       </c>
-      <c r="C142" t="str">
-        <v/>
-      </c>
-      <c r="D142" t="str">
+      <c r="C142" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D142" s="1" t="str">
         <v/>
       </c>
       <c r="E142">
@@ -8356,10 +8341,10 @@
       <c r="M142" t="str">
         <v/>
       </c>
-      <c r="N142" t="str">
-        <v/>
-      </c>
-      <c r="O142" t="str">
+      <c r="N142" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O142" s="1" t="str">
         <v/>
       </c>
       <c r="P142" t="str">
@@ -8379,10 +8364,10 @@
       <c r="B143" t="str">
         <v>Civil: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C143" t="str">
-        <v/>
-      </c>
-      <c r="D143" t="str">
+      <c r="C143" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D143" s="1" t="str">
         <v/>
       </c>
       <c r="E143">
@@ -8412,10 +8397,10 @@
       <c r="M143" t="str">
         <v/>
       </c>
-      <c r="N143" t="str">
-        <v/>
-      </c>
-      <c r="O143" t="str">
+      <c r="N143" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O143" s="1" t="str">
         <v/>
       </c>
       <c r="P143" t="str">
@@ -8435,10 +8420,10 @@
       <c r="B144" t="str">
         <v>EXECUTE • Electricals</v>
       </c>
-      <c r="C144" t="str">
-        <v/>
-      </c>
-      <c r="D144" t="str">
+      <c r="C144" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D144" s="1" t="str">
         <v/>
       </c>
       <c r="E144" t="str">
@@ -8468,10 +8453,10 @@
       <c r="M144" t="str">
         <v/>
       </c>
-      <c r="N144" t="str">
-        <v/>
-      </c>
-      <c r="O144" t="str">
+      <c r="N144" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O144" s="1" t="str">
         <v/>
       </c>
       <c r="P144" t="str">
@@ -8491,10 +8476,10 @@
       <c r="B145" t="str">
         <v>Electricals: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C145" t="str">
-        <v/>
-      </c>
-      <c r="D145" t="str">
+      <c r="C145" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D145" s="1" t="str">
         <v/>
       </c>
       <c r="E145">
@@ -8524,10 +8509,10 @@
       <c r="M145" t="str">
         <v/>
       </c>
-      <c r="N145" t="str">
-        <v/>
-      </c>
-      <c r="O145" t="str">
+      <c r="N145" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O145" s="1" t="str">
         <v/>
       </c>
       <c r="P145" t="str">
@@ -8547,10 +8532,10 @@
       <c r="B146" t="str">
         <v>Electricals: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C146" t="str">
-        <v/>
-      </c>
-      <c r="D146" t="str">
+      <c r="C146" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D146" s="1" t="str">
         <v/>
       </c>
       <c r="E146">
@@ -8580,10 +8565,10 @@
       <c r="M146" t="str">
         <v/>
       </c>
-      <c r="N146" t="str">
-        <v/>
-      </c>
-      <c r="O146" t="str">
+      <c r="N146" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O146" s="1" t="str">
         <v/>
       </c>
       <c r="P146" t="str">
@@ -8603,10 +8588,10 @@
       <c r="B147" t="str">
         <v>Electricals: Delivery to Site</v>
       </c>
-      <c r="C147" t="str">
-        <v/>
-      </c>
-      <c r="D147" t="str">
+      <c r="C147" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D147" s="1" t="str">
         <v/>
       </c>
       <c r="E147">
@@ -8636,10 +8621,10 @@
       <c r="M147" t="str">
         <v/>
       </c>
-      <c r="N147" t="str">
-        <v/>
-      </c>
-      <c r="O147" t="str">
+      <c r="N147" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O147" s="1" t="str">
         <v/>
       </c>
       <c r="P147" t="str">
@@ -8659,10 +8644,10 @@
       <c r="B148" t="str">
         <v>Electricals: Installation / Execution</v>
       </c>
-      <c r="C148" t="str">
-        <v/>
-      </c>
-      <c r="D148" t="str">
+      <c r="C148" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D148" s="1" t="str">
         <v/>
       </c>
       <c r="E148">
@@ -8692,10 +8677,10 @@
       <c r="M148" t="str">
         <v/>
       </c>
-      <c r="N148" t="str">
-        <v/>
-      </c>
-      <c r="O148" t="str">
+      <c r="N148" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O148" s="1" t="str">
         <v/>
       </c>
       <c r="P148" t="str">
@@ -8715,10 +8700,10 @@
       <c r="B149" t="str">
         <v>Electricals: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C149" t="str">
-        <v/>
-      </c>
-      <c r="D149" t="str">
+      <c r="C149" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D149" s="1" t="str">
         <v/>
       </c>
       <c r="E149">
@@ -8748,10 +8733,10 @@
       <c r="M149" t="str">
         <v/>
       </c>
-      <c r="N149" t="str">
-        <v/>
-      </c>
-      <c r="O149" t="str">
+      <c r="N149" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O149" s="1" t="str">
         <v/>
       </c>
       <c r="P149" t="str">
@@ -8771,10 +8756,10 @@
       <c r="B150" t="str">
         <v>EXECUTE • Plumbing</v>
       </c>
-      <c r="C150" t="str">
-        <v/>
-      </c>
-      <c r="D150" t="str">
+      <c r="C150" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D150" s="1" t="str">
         <v/>
       </c>
       <c r="E150" t="str">
@@ -8804,10 +8789,10 @@
       <c r="M150" t="str">
         <v/>
       </c>
-      <c r="N150" t="str">
-        <v/>
-      </c>
-      <c r="O150" t="str">
+      <c r="N150" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O150" s="1" t="str">
         <v/>
       </c>
       <c r="P150" t="str">
@@ -8827,10 +8812,10 @@
       <c r="B151" t="str">
         <v>Plumbing: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C151" t="str">
-        <v/>
-      </c>
-      <c r="D151" t="str">
+      <c r="C151" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D151" s="1" t="str">
         <v/>
       </c>
       <c r="E151">
@@ -8860,10 +8845,10 @@
       <c r="M151" t="str">
         <v/>
       </c>
-      <c r="N151" t="str">
-        <v/>
-      </c>
-      <c r="O151" t="str">
+      <c r="N151" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O151" s="1" t="str">
         <v/>
       </c>
       <c r="P151" t="str">
@@ -8883,10 +8868,10 @@
       <c r="B152" t="str">
         <v>Plumbing: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C152" t="str">
-        <v/>
-      </c>
-      <c r="D152" t="str">
+      <c r="C152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D152" s="1" t="str">
         <v/>
       </c>
       <c r="E152">
@@ -8916,10 +8901,10 @@
       <c r="M152" t="str">
         <v/>
       </c>
-      <c r="N152" t="str">
-        <v/>
-      </c>
-      <c r="O152" t="str">
+      <c r="N152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O152" s="1" t="str">
         <v/>
       </c>
       <c r="P152" t="str">
@@ -8939,10 +8924,10 @@
       <c r="B153" t="str">
         <v>Plumbing: Delivery to Site</v>
       </c>
-      <c r="C153" t="str">
-        <v/>
-      </c>
-      <c r="D153" t="str">
+      <c r="C153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D153" s="1" t="str">
         <v/>
       </c>
       <c r="E153">
@@ -8972,10 +8957,10 @@
       <c r="M153" t="str">
         <v/>
       </c>
-      <c r="N153" t="str">
-        <v/>
-      </c>
-      <c r="O153" t="str">
+      <c r="N153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O153" s="1" t="str">
         <v/>
       </c>
       <c r="P153" t="str">
@@ -8995,10 +8980,10 @@
       <c r="B154" t="str">
         <v>Plumbing: Installation / Execution</v>
       </c>
-      <c r="C154" t="str">
-        <v/>
-      </c>
-      <c r="D154" t="str">
+      <c r="C154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D154" s="1" t="str">
         <v/>
       </c>
       <c r="E154">
@@ -9028,10 +9013,10 @@
       <c r="M154" t="str">
         <v/>
       </c>
-      <c r="N154" t="str">
-        <v/>
-      </c>
-      <c r="O154" t="str">
+      <c r="N154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O154" s="1" t="str">
         <v/>
       </c>
       <c r="P154" t="str">
@@ -9051,10 +9036,10 @@
       <c r="B155" t="str">
         <v>Plumbing: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C155" t="str">
-        <v/>
-      </c>
-      <c r="D155" t="str">
+      <c r="C155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D155" s="1" t="str">
         <v/>
       </c>
       <c r="E155">
@@ -9084,10 +9069,10 @@
       <c r="M155" t="str">
         <v/>
       </c>
-      <c r="N155" t="str">
-        <v/>
-      </c>
-      <c r="O155" t="str">
+      <c r="N155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O155" s="1" t="str">
         <v/>
       </c>
       <c r="P155" t="str">
@@ -9107,10 +9092,10 @@
       <c r="B156" t="str">
         <v>EXECUTE • Kitchens</v>
       </c>
-      <c r="C156" t="str">
-        <v/>
-      </c>
-      <c r="D156" t="str">
+      <c r="C156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D156" s="1" t="str">
         <v/>
       </c>
       <c r="E156" t="str">
@@ -9140,10 +9125,10 @@
       <c r="M156" t="str">
         <v/>
       </c>
-      <c r="N156" t="str">
-        <v/>
-      </c>
-      <c r="O156" t="str">
+      <c r="N156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O156" s="1" t="str">
         <v/>
       </c>
       <c r="P156" t="str">
@@ -9163,10 +9148,10 @@
       <c r="B157" t="str">
         <v>Kitchens: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C157" t="str">
-        <v/>
-      </c>
-      <c r="D157" t="str">
+      <c r="C157" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D157" s="1" t="str">
         <v/>
       </c>
       <c r="E157">
@@ -9196,10 +9181,10 @@
       <c r="M157" t="str">
         <v/>
       </c>
-      <c r="N157" t="str">
-        <v/>
-      </c>
-      <c r="O157" t="str">
+      <c r="N157" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O157" s="1" t="str">
         <v/>
       </c>
       <c r="P157" t="str">
@@ -9219,10 +9204,10 @@
       <c r="B158" t="str">
         <v>Kitchens: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C158" t="str">
-        <v/>
-      </c>
-      <c r="D158" t="str">
+      <c r="C158" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D158" s="1" t="str">
         <v/>
       </c>
       <c r="E158">
@@ -9252,10 +9237,10 @@
       <c r="M158" t="str">
         <v/>
       </c>
-      <c r="N158" t="str">
-        <v/>
-      </c>
-      <c r="O158" t="str">
+      <c r="N158" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O158" s="1" t="str">
         <v/>
       </c>
       <c r="P158" t="str">
@@ -9275,10 +9260,10 @@
       <c r="B159" t="str">
         <v>Kitchens: Delivery to Site</v>
       </c>
-      <c r="C159" t="str">
-        <v/>
-      </c>
-      <c r="D159" t="str">
+      <c r="C159" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D159" s="1" t="str">
         <v/>
       </c>
       <c r="E159">
@@ -9308,10 +9293,10 @@
       <c r="M159" t="str">
         <v/>
       </c>
-      <c r="N159" t="str">
-        <v/>
-      </c>
-      <c r="O159" t="str">
+      <c r="N159" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O159" s="1" t="str">
         <v/>
       </c>
       <c r="P159" t="str">
@@ -9331,10 +9316,10 @@
       <c r="B160" t="str">
         <v>Kitchens: Installation / Execution</v>
       </c>
-      <c r="C160" t="str">
-        <v/>
-      </c>
-      <c r="D160" t="str">
+      <c r="C160" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D160" s="1" t="str">
         <v/>
       </c>
       <c r="E160">
@@ -9364,10 +9349,10 @@
       <c r="M160" t="str">
         <v/>
       </c>
-      <c r="N160" t="str">
-        <v/>
-      </c>
-      <c r="O160" t="str">
+      <c r="N160" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O160" s="1" t="str">
         <v/>
       </c>
       <c r="P160" t="str">
@@ -9387,10 +9372,10 @@
       <c r="B161" t="str">
         <v>Kitchens: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C161" t="str">
-        <v/>
-      </c>
-      <c r="D161" t="str">
+      <c r="C161" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D161" s="1" t="str">
         <v/>
       </c>
       <c r="E161">
@@ -9420,10 +9405,10 @@
       <c r="M161" t="str">
         <v/>
       </c>
-      <c r="N161" t="str">
-        <v/>
-      </c>
-      <c r="O161" t="str">
+      <c r="N161" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O161" s="1" t="str">
         <v/>
       </c>
       <c r="P161" t="str">
@@ -9443,10 +9428,10 @@
       <c r="B162" t="str">
         <v>EXECUTE • Bathrooms</v>
       </c>
-      <c r="C162" t="str">
-        <v/>
-      </c>
-      <c r="D162" t="str">
+      <c r="C162" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D162" s="1" t="str">
         <v/>
       </c>
       <c r="E162" t="str">
@@ -9476,10 +9461,10 @@
       <c r="M162" t="str">
         <v/>
       </c>
-      <c r="N162" t="str">
-        <v/>
-      </c>
-      <c r="O162" t="str">
+      <c r="N162" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O162" s="1" t="str">
         <v/>
       </c>
       <c r="P162" t="str">
@@ -9499,10 +9484,10 @@
       <c r="B163" t="str">
         <v>Bathrooms: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C163" t="str">
-        <v/>
-      </c>
-      <c r="D163" t="str">
+      <c r="C163" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D163" s="1" t="str">
         <v/>
       </c>
       <c r="E163">
@@ -9532,10 +9517,10 @@
       <c r="M163" t="str">
         <v/>
       </c>
-      <c r="N163" t="str">
-        <v/>
-      </c>
-      <c r="O163" t="str">
+      <c r="N163" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O163" s="1" t="str">
         <v/>
       </c>
       <c r="P163" t="str">
@@ -9555,10 +9540,10 @@
       <c r="B164" t="str">
         <v>Bathrooms: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C164" t="str">
-        <v/>
-      </c>
-      <c r="D164" t="str">
+      <c r="C164" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D164" s="1" t="str">
         <v/>
       </c>
       <c r="E164">
@@ -9588,10 +9573,10 @@
       <c r="M164" t="str">
         <v/>
       </c>
-      <c r="N164" t="str">
-        <v/>
-      </c>
-      <c r="O164" t="str">
+      <c r="N164" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O164" s="1" t="str">
         <v/>
       </c>
       <c r="P164" t="str">
@@ -9611,10 +9596,10 @@
       <c r="B165" t="str">
         <v>Bathrooms: Delivery to Site</v>
       </c>
-      <c r="C165" t="str">
-        <v/>
-      </c>
-      <c r="D165" t="str">
+      <c r="C165" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D165" s="1" t="str">
         <v/>
       </c>
       <c r="E165">
@@ -9644,10 +9629,10 @@
       <c r="M165" t="str">
         <v/>
       </c>
-      <c r="N165" t="str">
-        <v/>
-      </c>
-      <c r="O165" t="str">
+      <c r="N165" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O165" s="1" t="str">
         <v/>
       </c>
       <c r="P165" t="str">
@@ -9667,10 +9652,10 @@
       <c r="B166" t="str">
         <v>Bathrooms: Installation / Execution</v>
       </c>
-      <c r="C166" t="str">
-        <v/>
-      </c>
-      <c r="D166" t="str">
+      <c r="C166" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D166" s="1" t="str">
         <v/>
       </c>
       <c r="E166">
@@ -9700,10 +9685,10 @@
       <c r="M166" t="str">
         <v/>
       </c>
-      <c r="N166" t="str">
-        <v/>
-      </c>
-      <c r="O166" t="str">
+      <c r="N166" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O166" s="1" t="str">
         <v/>
       </c>
       <c r="P166" t="str">
@@ -9723,10 +9708,10 @@
       <c r="B167" t="str">
         <v>Bathrooms: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C167" t="str">
-        <v/>
-      </c>
-      <c r="D167" t="str">
+      <c r="C167" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D167" s="1" t="str">
         <v/>
       </c>
       <c r="E167">
@@ -9756,10 +9741,10 @@
       <c r="M167" t="str">
         <v/>
       </c>
-      <c r="N167" t="str">
-        <v/>
-      </c>
-      <c r="O167" t="str">
+      <c r="N167" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O167" s="1" t="str">
         <v/>
       </c>
       <c r="P167" t="str">
@@ -9779,10 +9764,10 @@
       <c r="B168" t="str">
         <v>EXECUTE • Audio</v>
       </c>
-      <c r="C168" t="str">
-        <v/>
-      </c>
-      <c r="D168" t="str">
+      <c r="C168" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D168" s="1" t="str">
         <v/>
       </c>
       <c r="E168" t="str">
@@ -9812,10 +9797,10 @@
       <c r="M168" t="str">
         <v/>
       </c>
-      <c r="N168" t="str">
-        <v/>
-      </c>
-      <c r="O168" t="str">
+      <c r="N168" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O168" s="1" t="str">
         <v/>
       </c>
       <c r="P168" t="str">
@@ -9835,10 +9820,10 @@
       <c r="B169" t="str">
         <v>Audio: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C169" t="str">
-        <v/>
-      </c>
-      <c r="D169" t="str">
+      <c r="C169" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D169" s="1" t="str">
         <v/>
       </c>
       <c r="E169">
@@ -9868,10 +9853,10 @@
       <c r="M169" t="str">
         <v/>
       </c>
-      <c r="N169" t="str">
-        <v/>
-      </c>
-      <c r="O169" t="str">
+      <c r="N169" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O169" s="1" t="str">
         <v/>
       </c>
       <c r="P169" t="str">
@@ -9891,10 +9876,10 @@
       <c r="B170" t="str">
         <v>Audio: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C170" t="str">
-        <v/>
-      </c>
-      <c r="D170" t="str">
+      <c r="C170" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D170" s="1" t="str">
         <v/>
       </c>
       <c r="E170">
@@ -9924,10 +9909,10 @@
       <c r="M170" t="str">
         <v/>
       </c>
-      <c r="N170" t="str">
-        <v/>
-      </c>
-      <c r="O170" t="str">
+      <c r="N170" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O170" s="1" t="str">
         <v/>
       </c>
       <c r="P170" t="str">
@@ -9947,10 +9932,10 @@
       <c r="B171" t="str">
         <v>Audio: Delivery to Site</v>
       </c>
-      <c r="C171" t="str">
-        <v/>
-      </c>
-      <c r="D171" t="str">
+      <c r="C171" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D171" s="1" t="str">
         <v/>
       </c>
       <c r="E171">
@@ -9980,10 +9965,10 @@
       <c r="M171" t="str">
         <v/>
       </c>
-      <c r="N171" t="str">
-        <v/>
-      </c>
-      <c r="O171" t="str">
+      <c r="N171" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O171" s="1" t="str">
         <v/>
       </c>
       <c r="P171" t="str">
@@ -10003,10 +9988,10 @@
       <c r="B172" t="str">
         <v>Audio: Installation / Execution</v>
       </c>
-      <c r="C172" t="str">
-        <v/>
-      </c>
-      <c r="D172" t="str">
+      <c r="C172" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D172" s="1" t="str">
         <v/>
       </c>
       <c r="E172">
@@ -10036,10 +10021,10 @@
       <c r="M172" t="str">
         <v/>
       </c>
-      <c r="N172" t="str">
-        <v/>
-      </c>
-      <c r="O172" t="str">
+      <c r="N172" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O172" s="1" t="str">
         <v/>
       </c>
       <c r="P172" t="str">
@@ -10059,10 +10044,10 @@
       <c r="B173" t="str">
         <v>Audio: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C173" t="str">
-        <v/>
-      </c>
-      <c r="D173" t="str">
+      <c r="C173" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D173" s="1" t="str">
         <v/>
       </c>
       <c r="E173">
@@ -10092,10 +10077,10 @@
       <c r="M173" t="str">
         <v/>
       </c>
-      <c r="N173" t="str">
-        <v/>
-      </c>
-      <c r="O173" t="str">
+      <c r="N173" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O173" s="1" t="str">
         <v/>
       </c>
       <c r="P173" t="str">
@@ -10115,10 +10100,10 @@
       <c r="B174" t="str">
         <v>EXECUTE • Automation</v>
       </c>
-      <c r="C174" t="str">
-        <v/>
-      </c>
-      <c r="D174" t="str">
+      <c r="C174" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D174" s="1" t="str">
         <v/>
       </c>
       <c r="E174" t="str">
@@ -10148,10 +10133,10 @@
       <c r="M174" t="str">
         <v/>
       </c>
-      <c r="N174" t="str">
-        <v/>
-      </c>
-      <c r="O174" t="str">
+      <c r="N174" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O174" s="1" t="str">
         <v/>
       </c>
       <c r="P174" t="str">
@@ -10171,10 +10156,10 @@
       <c r="B175" t="str">
         <v>Automation: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C175" t="str">
-        <v/>
-      </c>
-      <c r="D175" t="str">
+      <c r="C175" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D175" s="1" t="str">
         <v/>
       </c>
       <c r="E175">
@@ -10204,10 +10189,10 @@
       <c r="M175" t="str">
         <v/>
       </c>
-      <c r="N175" t="str">
-        <v/>
-      </c>
-      <c r="O175" t="str">
+      <c r="N175" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O175" s="1" t="str">
         <v/>
       </c>
       <c r="P175" t="str">
@@ -10227,10 +10212,10 @@
       <c r="B176" t="str">
         <v>Automation: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C176" t="str">
-        <v/>
-      </c>
-      <c r="D176" t="str">
+      <c r="C176" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D176" s="1" t="str">
         <v/>
       </c>
       <c r="E176">
@@ -10260,10 +10245,10 @@
       <c r="M176" t="str">
         <v/>
       </c>
-      <c r="N176" t="str">
-        <v/>
-      </c>
-      <c r="O176" t="str">
+      <c r="N176" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O176" s="1" t="str">
         <v/>
       </c>
       <c r="P176" t="str">
@@ -10283,10 +10268,10 @@
       <c r="B177" t="str">
         <v>Automation: Delivery to Site</v>
       </c>
-      <c r="C177" t="str">
-        <v/>
-      </c>
-      <c r="D177" t="str">
+      <c r="C177" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D177" s="1" t="str">
         <v/>
       </c>
       <c r="E177">
@@ -10316,10 +10301,10 @@
       <c r="M177" t="str">
         <v/>
       </c>
-      <c r="N177" t="str">
-        <v/>
-      </c>
-      <c r="O177" t="str">
+      <c r="N177" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O177" s="1" t="str">
         <v/>
       </c>
       <c r="P177" t="str">
@@ -10339,10 +10324,10 @@
       <c r="B178" t="str">
         <v>Automation: Installation / Execution</v>
       </c>
-      <c r="C178" t="str">
-        <v/>
-      </c>
-      <c r="D178" t="str">
+      <c r="C178" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D178" s="1" t="str">
         <v/>
       </c>
       <c r="E178">
@@ -10372,10 +10357,10 @@
       <c r="M178" t="str">
         <v/>
       </c>
-      <c r="N178" t="str">
-        <v/>
-      </c>
-      <c r="O178" t="str">
+      <c r="N178" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O178" s="1" t="str">
         <v/>
       </c>
       <c r="P178" t="str">
@@ -10395,10 +10380,10 @@
       <c r="B179" t="str">
         <v>Automation: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C179" t="str">
-        <v/>
-      </c>
-      <c r="D179" t="str">
+      <c r="C179" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D179" s="1" t="str">
         <v/>
       </c>
       <c r="E179">
@@ -10428,10 +10413,10 @@
       <c r="M179" t="str">
         <v/>
       </c>
-      <c r="N179" t="str">
-        <v/>
-      </c>
-      <c r="O179" t="str">
+      <c r="N179" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O179" s="1" t="str">
         <v/>
       </c>
       <c r="P179" t="str">
@@ -10451,10 +10436,10 @@
       <c r="B180" t="str">
         <v>EXECUTE • Lighting</v>
       </c>
-      <c r="C180" t="str">
-        <v/>
-      </c>
-      <c r="D180" t="str">
+      <c r="C180" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D180" s="1" t="str">
         <v/>
       </c>
       <c r="E180" t="str">
@@ -10484,10 +10469,10 @@
       <c r="M180" t="str">
         <v/>
       </c>
-      <c r="N180" t="str">
-        <v/>
-      </c>
-      <c r="O180" t="str">
+      <c r="N180" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O180" s="1" t="str">
         <v/>
       </c>
       <c r="P180" t="str">
@@ -10507,10 +10492,10 @@
       <c r="B181" t="str">
         <v>Lighting: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C181" t="str">
-        <v/>
-      </c>
-      <c r="D181" t="str">
+      <c r="C181" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D181" s="1" t="str">
         <v/>
       </c>
       <c r="E181">
@@ -10540,10 +10525,10 @@
       <c r="M181" t="str">
         <v/>
       </c>
-      <c r="N181" t="str">
-        <v/>
-      </c>
-      <c r="O181" t="str">
+      <c r="N181" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O181" s="1" t="str">
         <v/>
       </c>
       <c r="P181" t="str">
@@ -10563,10 +10548,10 @@
       <c r="B182" t="str">
         <v>Lighting: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C182" t="str">
-        <v/>
-      </c>
-      <c r="D182" t="str">
+      <c r="C182" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D182" s="1" t="str">
         <v/>
       </c>
       <c r="E182">
@@ -10596,10 +10581,10 @@
       <c r="M182" t="str">
         <v/>
       </c>
-      <c r="N182" t="str">
-        <v/>
-      </c>
-      <c r="O182" t="str">
+      <c r="N182" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O182" s="1" t="str">
         <v/>
       </c>
       <c r="P182" t="str">
@@ -10619,10 +10604,10 @@
       <c r="B183" t="str">
         <v>Lighting: Delivery to Site</v>
       </c>
-      <c r="C183" t="str">
-        <v/>
-      </c>
-      <c r="D183" t="str">
+      <c r="C183" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D183" s="1" t="str">
         <v/>
       </c>
       <c r="E183">
@@ -10652,10 +10637,10 @@
       <c r="M183" t="str">
         <v/>
       </c>
-      <c r="N183" t="str">
-        <v/>
-      </c>
-      <c r="O183" t="str">
+      <c r="N183" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O183" s="1" t="str">
         <v/>
       </c>
       <c r="P183" t="str">
@@ -10675,10 +10660,10 @@
       <c r="B184" t="str">
         <v>Lighting: Installation / Execution</v>
       </c>
-      <c r="C184" t="str">
-        <v/>
-      </c>
-      <c r="D184" t="str">
+      <c r="C184" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D184" s="1" t="str">
         <v/>
       </c>
       <c r="E184">
@@ -10708,10 +10693,10 @@
       <c r="M184" t="str">
         <v/>
       </c>
-      <c r="N184" t="str">
-        <v/>
-      </c>
-      <c r="O184" t="str">
+      <c r="N184" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O184" s="1" t="str">
         <v/>
       </c>
       <c r="P184" t="str">
@@ -10731,10 +10716,10 @@
       <c r="B185" t="str">
         <v>Lighting: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C185" t="str">
-        <v/>
-      </c>
-      <c r="D185" t="str">
+      <c r="C185" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D185" s="1" t="str">
         <v/>
       </c>
       <c r="E185">
@@ -10764,10 +10749,10 @@
       <c r="M185" t="str">
         <v/>
       </c>
-      <c r="N185" t="str">
-        <v/>
-      </c>
-      <c r="O185" t="str">
+      <c r="N185" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O185" s="1" t="str">
         <v/>
       </c>
       <c r="P185" t="str">
@@ -10787,10 +10772,10 @@
       <c r="B186" t="str">
         <v>EXECUTE • HVAC</v>
       </c>
-      <c r="C186" t="str">
-        <v/>
-      </c>
-      <c r="D186" t="str">
+      <c r="C186" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D186" s="1" t="str">
         <v/>
       </c>
       <c r="E186" t="str">
@@ -10820,10 +10805,10 @@
       <c r="M186" t="str">
         <v/>
       </c>
-      <c r="N186" t="str">
-        <v/>
-      </c>
-      <c r="O186" t="str">
+      <c r="N186" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O186" s="1" t="str">
         <v/>
       </c>
       <c r="P186" t="str">
@@ -10843,10 +10828,10 @@
       <c r="B187" t="str">
         <v>HVAC: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C187" t="str">
-        <v/>
-      </c>
-      <c r="D187" t="str">
+      <c r="C187" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D187" s="1" t="str">
         <v/>
       </c>
       <c r="E187">
@@ -10876,10 +10861,10 @@
       <c r="M187" t="str">
         <v/>
       </c>
-      <c r="N187" t="str">
-        <v/>
-      </c>
-      <c r="O187" t="str">
+      <c r="N187" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O187" s="1" t="str">
         <v/>
       </c>
       <c r="P187" t="str">
@@ -10899,10 +10884,10 @@
       <c r="B188" t="str">
         <v>HVAC: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C188" t="str">
-        <v/>
-      </c>
-      <c r="D188" t="str">
+      <c r="C188" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D188" s="1" t="str">
         <v/>
       </c>
       <c r="E188">
@@ -10932,10 +10917,10 @@
       <c r="M188" t="str">
         <v/>
       </c>
-      <c r="N188" t="str">
-        <v/>
-      </c>
-      <c r="O188" t="str">
+      <c r="N188" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O188" s="1" t="str">
         <v/>
       </c>
       <c r="P188" t="str">
@@ -10955,10 +10940,10 @@
       <c r="B189" t="str">
         <v>HVAC: Delivery to Site</v>
       </c>
-      <c r="C189" t="str">
-        <v/>
-      </c>
-      <c r="D189" t="str">
+      <c r="C189" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D189" s="1" t="str">
         <v/>
       </c>
       <c r="E189">
@@ -10988,10 +10973,10 @@
       <c r="M189" t="str">
         <v/>
       </c>
-      <c r="N189" t="str">
-        <v/>
-      </c>
-      <c r="O189" t="str">
+      <c r="N189" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O189" s="1" t="str">
         <v/>
       </c>
       <c r="P189" t="str">
@@ -11011,10 +10996,10 @@
       <c r="B190" t="str">
         <v>HVAC: Installation / Execution</v>
       </c>
-      <c r="C190" t="str">
-        <v/>
-      </c>
-      <c r="D190" t="str">
+      <c r="C190" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D190" s="1" t="str">
         <v/>
       </c>
       <c r="E190">
@@ -11044,10 +11029,10 @@
       <c r="M190" t="str">
         <v/>
       </c>
-      <c r="N190" t="str">
-        <v/>
-      </c>
-      <c r="O190" t="str">
+      <c r="N190" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O190" s="1" t="str">
         <v/>
       </c>
       <c r="P190" t="str">
@@ -11067,10 +11052,10 @@
       <c r="B191" t="str">
         <v>HVAC: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C191" t="str">
-        <v/>
-      </c>
-      <c r="D191" t="str">
+      <c r="C191" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D191" s="1" t="str">
         <v/>
       </c>
       <c r="E191">
@@ -11100,10 +11085,10 @@
       <c r="M191" t="str">
         <v/>
       </c>
-      <c r="N191" t="str">
-        <v/>
-      </c>
-      <c r="O191" t="str">
+      <c r="N191" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O191" s="1" t="str">
         <v/>
       </c>
       <c r="P191" t="str">
@@ -11123,10 +11108,10 @@
       <c r="B192" t="str">
         <v>EXECUTE • Doors &amp; Windows</v>
       </c>
-      <c r="C192" t="str">
-        <v/>
-      </c>
-      <c r="D192" t="str">
+      <c r="C192" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D192" s="1" t="str">
         <v/>
       </c>
       <c r="E192" t="str">
@@ -11156,10 +11141,10 @@
       <c r="M192" t="str">
         <v/>
       </c>
-      <c r="N192" t="str">
-        <v/>
-      </c>
-      <c r="O192" t="str">
+      <c r="N192" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O192" s="1" t="str">
         <v/>
       </c>
       <c r="P192" t="str">
@@ -11179,10 +11164,10 @@
       <c r="B193" t="str">
         <v>Doors &amp; Windows: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C193" t="str">
-        <v/>
-      </c>
-      <c r="D193" t="str">
+      <c r="C193" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D193" s="1" t="str">
         <v/>
       </c>
       <c r="E193">
@@ -11212,10 +11197,10 @@
       <c r="M193" t="str">
         <v/>
       </c>
-      <c r="N193" t="str">
-        <v/>
-      </c>
-      <c r="O193" t="str">
+      <c r="N193" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O193" s="1" t="str">
         <v/>
       </c>
       <c r="P193" t="str">
@@ -11235,10 +11220,10 @@
       <c r="B194" t="str">
         <v>Doors &amp; Windows: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C194" t="str">
-        <v/>
-      </c>
-      <c r="D194" t="str">
+      <c r="C194" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D194" s="1" t="str">
         <v/>
       </c>
       <c r="E194">
@@ -11268,10 +11253,10 @@
       <c r="M194" t="str">
         <v/>
       </c>
-      <c r="N194" t="str">
-        <v/>
-      </c>
-      <c r="O194" t="str">
+      <c r="N194" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O194" s="1" t="str">
         <v/>
       </c>
       <c r="P194" t="str">
@@ -11291,10 +11276,10 @@
       <c r="B195" t="str">
         <v>Doors &amp; Windows: Delivery to Site</v>
       </c>
-      <c r="C195" t="str">
-        <v/>
-      </c>
-      <c r="D195" t="str">
+      <c r="C195" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D195" s="1" t="str">
         <v/>
       </c>
       <c r="E195">
@@ -11324,10 +11309,10 @@
       <c r="M195" t="str">
         <v/>
       </c>
-      <c r="N195" t="str">
-        <v/>
-      </c>
-      <c r="O195" t="str">
+      <c r="N195" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O195" s="1" t="str">
         <v/>
       </c>
       <c r="P195" t="str">
@@ -11347,10 +11332,10 @@
       <c r="B196" t="str">
         <v>Doors &amp; Windows: Installation / Execution</v>
       </c>
-      <c r="C196" t="str">
-        <v/>
-      </c>
-      <c r="D196" t="str">
+      <c r="C196" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D196" s="1" t="str">
         <v/>
       </c>
       <c r="E196">
@@ -11380,10 +11365,10 @@
       <c r="M196" t="str">
         <v/>
       </c>
-      <c r="N196" t="str">
-        <v/>
-      </c>
-      <c r="O196" t="str">
+      <c r="N196" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O196" s="1" t="str">
         <v/>
       </c>
       <c r="P196" t="str">
@@ -11403,10 +11388,10 @@
       <c r="B197" t="str">
         <v>Doors &amp; Windows: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C197" t="str">
-        <v/>
-      </c>
-      <c r="D197" t="str">
+      <c r="C197" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D197" s="1" t="str">
         <v/>
       </c>
       <c r="E197">
@@ -11436,10 +11421,10 @@
       <c r="M197" t="str">
         <v/>
       </c>
-      <c r="N197" t="str">
-        <v/>
-      </c>
-      <c r="O197" t="str">
+      <c r="N197" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O197" s="1" t="str">
         <v/>
       </c>
       <c r="P197" t="str">
@@ -11459,10 +11444,10 @@
       <c r="B198" t="str">
         <v>EXECUTE • Wall Finishes</v>
       </c>
-      <c r="C198" t="str">
-        <v/>
-      </c>
-      <c r="D198" t="str">
+      <c r="C198" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D198" s="1" t="str">
         <v/>
       </c>
       <c r="E198" t="str">
@@ -11492,10 +11477,10 @@
       <c r="M198" t="str">
         <v/>
       </c>
-      <c r="N198" t="str">
-        <v/>
-      </c>
-      <c r="O198" t="str">
+      <c r="N198" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O198" s="1" t="str">
         <v/>
       </c>
       <c r="P198" t="str">
@@ -11515,10 +11500,10 @@
       <c r="B199" t="str">
         <v>Wall Finishes: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C199" t="str">
-        <v/>
-      </c>
-      <c r="D199" t="str">
+      <c r="C199" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D199" s="1" t="str">
         <v/>
       </c>
       <c r="E199">
@@ -11548,10 +11533,10 @@
       <c r="M199" t="str">
         <v/>
       </c>
-      <c r="N199" t="str">
-        <v/>
-      </c>
-      <c r="O199" t="str">
+      <c r="N199" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O199" s="1" t="str">
         <v/>
       </c>
       <c r="P199" t="str">
@@ -11571,10 +11556,10 @@
       <c r="B200" t="str">
         <v>Wall Finishes: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C200" t="str">
-        <v/>
-      </c>
-      <c r="D200" t="str">
+      <c r="C200" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D200" s="1" t="str">
         <v/>
       </c>
       <c r="E200">
@@ -11604,10 +11589,10 @@
       <c r="M200" t="str">
         <v/>
       </c>
-      <c r="N200" t="str">
-        <v/>
-      </c>
-      <c r="O200" t="str">
+      <c r="N200" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O200" s="1" t="str">
         <v/>
       </c>
       <c r="P200" t="str">
@@ -11627,10 +11612,10 @@
       <c r="B201" t="str">
         <v>Wall Finishes: Delivery to Site</v>
       </c>
-      <c r="C201" t="str">
-        <v/>
-      </c>
-      <c r="D201" t="str">
+      <c r="C201" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D201" s="1" t="str">
         <v/>
       </c>
       <c r="E201">
@@ -11660,10 +11645,10 @@
       <c r="M201" t="str">
         <v/>
       </c>
-      <c r="N201" t="str">
-        <v/>
-      </c>
-      <c r="O201" t="str">
+      <c r="N201" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O201" s="1" t="str">
         <v/>
       </c>
       <c r="P201" t="str">
@@ -11683,10 +11668,10 @@
       <c r="B202" t="str">
         <v>Wall Finishes: Installation / Execution</v>
       </c>
-      <c r="C202" t="str">
-        <v/>
-      </c>
-      <c r="D202" t="str">
+      <c r="C202" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D202" s="1" t="str">
         <v/>
       </c>
       <c r="E202">
@@ -11716,10 +11701,10 @@
       <c r="M202" t="str">
         <v/>
       </c>
-      <c r="N202" t="str">
-        <v/>
-      </c>
-      <c r="O202" t="str">
+      <c r="N202" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O202" s="1" t="str">
         <v/>
       </c>
       <c r="P202" t="str">
@@ -11739,10 +11724,10 @@
       <c r="B203" t="str">
         <v>Wall Finishes: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C203" t="str">
-        <v/>
-      </c>
-      <c r="D203" t="str">
+      <c r="C203" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D203" s="1" t="str">
         <v/>
       </c>
       <c r="E203">
@@ -11772,10 +11757,10 @@
       <c r="M203" t="str">
         <v/>
       </c>
-      <c r="N203" t="str">
-        <v/>
-      </c>
-      <c r="O203" t="str">
+      <c r="N203" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O203" s="1" t="str">
         <v/>
       </c>
       <c r="P203" t="str">
@@ -11795,10 +11780,10 @@
       <c r="B204" t="str">
         <v>EXECUTE • Furnishing</v>
       </c>
-      <c r="C204" t="str">
-        <v/>
-      </c>
-      <c r="D204" t="str">
+      <c r="C204" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D204" s="1" t="str">
         <v/>
       </c>
       <c r="E204" t="str">
@@ -11828,10 +11813,10 @@
       <c r="M204" t="str">
         <v/>
       </c>
-      <c r="N204" t="str">
-        <v/>
-      </c>
-      <c r="O204" t="str">
+      <c r="N204" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O204" s="1" t="str">
         <v/>
       </c>
       <c r="P204" t="str">
@@ -11851,10 +11836,10 @@
       <c r="B205" t="str">
         <v>Furnishing: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C205" t="str">
-        <v/>
-      </c>
-      <c r="D205" t="str">
+      <c r="C205" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D205" s="1" t="str">
         <v/>
       </c>
       <c r="E205">
@@ -11884,10 +11869,10 @@
       <c r="M205" t="str">
         <v/>
       </c>
-      <c r="N205" t="str">
-        <v/>
-      </c>
-      <c r="O205" t="str">
+      <c r="N205" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O205" s="1" t="str">
         <v/>
       </c>
       <c r="P205" t="str">
@@ -11907,10 +11892,10 @@
       <c r="B206" t="str">
         <v>Furnishing: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C206" t="str">
-        <v/>
-      </c>
-      <c r="D206" t="str">
+      <c r="C206" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D206" s="1" t="str">
         <v/>
       </c>
       <c r="E206">
@@ -11940,10 +11925,10 @@
       <c r="M206" t="str">
         <v/>
       </c>
-      <c r="N206" t="str">
-        <v/>
-      </c>
-      <c r="O206" t="str">
+      <c r="N206" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O206" s="1" t="str">
         <v/>
       </c>
       <c r="P206" t="str">
@@ -11963,10 +11948,10 @@
       <c r="B207" t="str">
         <v>Furnishing: Delivery to Site</v>
       </c>
-      <c r="C207" t="str">
-        <v/>
-      </c>
-      <c r="D207" t="str">
+      <c r="C207" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D207" s="1" t="str">
         <v/>
       </c>
       <c r="E207">
@@ -11996,10 +11981,10 @@
       <c r="M207" t="str">
         <v/>
       </c>
-      <c r="N207" t="str">
-        <v/>
-      </c>
-      <c r="O207" t="str">
+      <c r="N207" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O207" s="1" t="str">
         <v/>
       </c>
       <c r="P207" t="str">
@@ -12019,10 +12004,10 @@
       <c r="B208" t="str">
         <v>Furnishing: Installation / Execution</v>
       </c>
-      <c r="C208" t="str">
-        <v/>
-      </c>
-      <c r="D208" t="str">
+      <c r="C208" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D208" s="1" t="str">
         <v/>
       </c>
       <c r="E208">
@@ -12052,10 +12037,10 @@
       <c r="M208" t="str">
         <v/>
       </c>
-      <c r="N208" t="str">
-        <v/>
-      </c>
-      <c r="O208" t="str">
+      <c r="N208" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O208" s="1" t="str">
         <v/>
       </c>
       <c r="P208" t="str">
@@ -12075,10 +12060,10 @@
       <c r="B209" t="str">
         <v>Furnishing: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C209" t="str">
-        <v/>
-      </c>
-      <c r="D209" t="str">
+      <c r="C209" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D209" s="1" t="str">
         <v/>
       </c>
       <c r="E209">
@@ -12108,10 +12093,10 @@
       <c r="M209" t="str">
         <v/>
       </c>
-      <c r="N209" t="str">
-        <v/>
-      </c>
-      <c r="O209" t="str">
+      <c r="N209" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O209" s="1" t="str">
         <v/>
       </c>
       <c r="P209" t="str">
@@ -12131,10 +12116,10 @@
       <c r="B210" t="str">
         <v>EXECUTE • Soft Furnishing</v>
       </c>
-      <c r="C210" t="str">
-        <v/>
-      </c>
-      <c r="D210" t="str">
+      <c r="C210" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D210" s="1" t="str">
         <v/>
       </c>
       <c r="E210" t="str">
@@ -12164,10 +12149,10 @@
       <c r="M210" t="str">
         <v/>
       </c>
-      <c r="N210" t="str">
-        <v/>
-      </c>
-      <c r="O210" t="str">
+      <c r="N210" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O210" s="1" t="str">
         <v/>
       </c>
       <c r="P210" t="str">
@@ -12187,10 +12172,10 @@
       <c r="B211" t="str">
         <v>Soft Furnishing: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C211" t="str">
-        <v/>
-      </c>
-      <c r="D211" t="str">
+      <c r="C211" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D211" s="1" t="str">
         <v/>
       </c>
       <c r="E211">
@@ -12220,10 +12205,10 @@
       <c r="M211" t="str">
         <v/>
       </c>
-      <c r="N211" t="str">
-        <v/>
-      </c>
-      <c r="O211" t="str">
+      <c r="N211" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O211" s="1" t="str">
         <v/>
       </c>
       <c r="P211" t="str">
@@ -12243,10 +12228,10 @@
       <c r="B212" t="str">
         <v>Soft Furnishing: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C212" t="str">
-        <v/>
-      </c>
-      <c r="D212" t="str">
+      <c r="C212" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D212" s="1" t="str">
         <v/>
       </c>
       <c r="E212">
@@ -12276,10 +12261,10 @@
       <c r="M212" t="str">
         <v/>
       </c>
-      <c r="N212" t="str">
-        <v/>
-      </c>
-      <c r="O212" t="str">
+      <c r="N212" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O212" s="1" t="str">
         <v/>
       </c>
       <c r="P212" t="str">
@@ -12299,10 +12284,10 @@
       <c r="B213" t="str">
         <v>Soft Furnishing: Delivery to Site</v>
       </c>
-      <c r="C213" t="str">
-        <v/>
-      </c>
-      <c r="D213" t="str">
+      <c r="C213" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D213" s="1" t="str">
         <v/>
       </c>
       <c r="E213">
@@ -12332,10 +12317,10 @@
       <c r="M213" t="str">
         <v/>
       </c>
-      <c r="N213" t="str">
-        <v/>
-      </c>
-      <c r="O213" t="str">
+      <c r="N213" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O213" s="1" t="str">
         <v/>
       </c>
       <c r="P213" t="str">
@@ -12355,10 +12340,10 @@
       <c r="B214" t="str">
         <v>Soft Furnishing: Installation / Execution</v>
       </c>
-      <c r="C214" t="str">
-        <v/>
-      </c>
-      <c r="D214" t="str">
+      <c r="C214" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D214" s="1" t="str">
         <v/>
       </c>
       <c r="E214">
@@ -12388,10 +12373,10 @@
       <c r="M214" t="str">
         <v/>
       </c>
-      <c r="N214" t="str">
-        <v/>
-      </c>
-      <c r="O214" t="str">
+      <c r="N214" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O214" s="1" t="str">
         <v/>
       </c>
       <c r="P214" t="str">
@@ -12411,10 +12396,10 @@
       <c r="B215" t="str">
         <v>Soft Furnishing: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C215" t="str">
-        <v/>
-      </c>
-      <c r="D215" t="str">
+      <c r="C215" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D215" s="1" t="str">
         <v/>
       </c>
       <c r="E215">
@@ -12444,10 +12429,10 @@
       <c r="M215" t="str">
         <v/>
       </c>
-      <c r="N215" t="str">
-        <v/>
-      </c>
-      <c r="O215" t="str">
+      <c r="N215" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O215" s="1" t="str">
         <v/>
       </c>
       <c r="P215" t="str">
@@ -12467,10 +12452,10 @@
       <c r="B216" t="str">
         <v>EXECUTE • Appliances</v>
       </c>
-      <c r="C216" t="str">
-        <v/>
-      </c>
-      <c r="D216" t="str">
+      <c r="C216" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D216" s="1" t="str">
         <v/>
       </c>
       <c r="E216" t="str">
@@ -12500,10 +12485,10 @@
       <c r="M216" t="str">
         <v/>
       </c>
-      <c r="N216" t="str">
-        <v/>
-      </c>
-      <c r="O216" t="str">
+      <c r="N216" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O216" s="1" t="str">
         <v/>
       </c>
       <c r="P216" t="str">
@@ -12523,10 +12508,10 @@
       <c r="B217" t="str">
         <v>Appliances: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C217" t="str">
-        <v/>
-      </c>
-      <c r="D217" t="str">
+      <c r="C217" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D217" s="1" t="str">
         <v/>
       </c>
       <c r="E217">
@@ -12556,10 +12541,10 @@
       <c r="M217" t="str">
         <v/>
       </c>
-      <c r="N217" t="str">
-        <v/>
-      </c>
-      <c r="O217" t="str">
+      <c r="N217" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O217" s="1" t="str">
         <v/>
       </c>
       <c r="P217" t="str">
@@ -12579,10 +12564,10 @@
       <c r="B218" t="str">
         <v>Appliances: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C218" t="str">
-        <v/>
-      </c>
-      <c r="D218" t="str">
+      <c r="C218" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D218" s="1" t="str">
         <v/>
       </c>
       <c r="E218">
@@ -12612,10 +12597,10 @@
       <c r="M218" t="str">
         <v/>
       </c>
-      <c r="N218" t="str">
-        <v/>
-      </c>
-      <c r="O218" t="str">
+      <c r="N218" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O218" s="1" t="str">
         <v/>
       </c>
       <c r="P218" t="str">
@@ -12635,10 +12620,10 @@
       <c r="B219" t="str">
         <v>Appliances: Delivery to Site</v>
       </c>
-      <c r="C219" t="str">
-        <v/>
-      </c>
-      <c r="D219" t="str">
+      <c r="C219" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D219" s="1" t="str">
         <v/>
       </c>
       <c r="E219">
@@ -12668,10 +12653,10 @@
       <c r="M219" t="str">
         <v/>
       </c>
-      <c r="N219" t="str">
-        <v/>
-      </c>
-      <c r="O219" t="str">
+      <c r="N219" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O219" s="1" t="str">
         <v/>
       </c>
       <c r="P219" t="str">
@@ -12691,10 +12676,10 @@
       <c r="B220" t="str">
         <v>Appliances: Installation / Execution</v>
       </c>
-      <c r="C220" t="str">
-        <v/>
-      </c>
-      <c r="D220" t="str">
+      <c r="C220" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D220" s="1" t="str">
         <v/>
       </c>
       <c r="E220">
@@ -12724,10 +12709,10 @@
       <c r="M220" t="str">
         <v/>
       </c>
-      <c r="N220" t="str">
-        <v/>
-      </c>
-      <c r="O220" t="str">
+      <c r="N220" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O220" s="1" t="str">
         <v/>
       </c>
       <c r="P220" t="str">
@@ -12747,10 +12732,10 @@
       <c r="B221" t="str">
         <v>Appliances: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C221" t="str">
-        <v/>
-      </c>
-      <c r="D221" t="str">
+      <c r="C221" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D221" s="1" t="str">
         <v/>
       </c>
       <c r="E221">
@@ -12780,10 +12765,10 @@
       <c r="M221" t="str">
         <v/>
       </c>
-      <c r="N221" t="str">
-        <v/>
-      </c>
-      <c r="O221" t="str">
+      <c r="N221" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O221" s="1" t="str">
         <v/>
       </c>
       <c r="P221" t="str">
@@ -12803,10 +12788,10 @@
       <c r="B222" t="str">
         <v>EXECUTE • Flooring</v>
       </c>
-      <c r="C222" t="str">
-        <v/>
-      </c>
-      <c r="D222" t="str">
+      <c r="C222" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D222" s="1" t="str">
         <v/>
       </c>
       <c r="E222" t="str">
@@ -12836,10 +12821,10 @@
       <c r="M222" t="str">
         <v/>
       </c>
-      <c r="N222" t="str">
-        <v/>
-      </c>
-      <c r="O222" t="str">
+      <c r="N222" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O222" s="1" t="str">
         <v/>
       </c>
       <c r="P222" t="str">
@@ -12859,10 +12844,10 @@
       <c r="B223" t="str">
         <v>Flooring: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C223" t="str">
-        <v/>
-      </c>
-      <c r="D223" t="str">
+      <c r="C223" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D223" s="1" t="str">
         <v/>
       </c>
       <c r="E223">
@@ -12892,10 +12877,10 @@
       <c r="M223" t="str">
         <v/>
       </c>
-      <c r="N223" t="str">
-        <v/>
-      </c>
-      <c r="O223" t="str">
+      <c r="N223" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O223" s="1" t="str">
         <v/>
       </c>
       <c r="P223" t="str">
@@ -12915,10 +12900,10 @@
       <c r="B224" t="str">
         <v>Flooring: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C224" t="str">
-        <v/>
-      </c>
-      <c r="D224" t="str">
+      <c r="C224" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D224" s="1" t="str">
         <v/>
       </c>
       <c r="E224">
@@ -12948,10 +12933,10 @@
       <c r="M224" t="str">
         <v/>
       </c>
-      <c r="N224" t="str">
-        <v/>
-      </c>
-      <c r="O224" t="str">
+      <c r="N224" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O224" s="1" t="str">
         <v/>
       </c>
       <c r="P224" t="str">
@@ -12971,10 +12956,10 @@
       <c r="B225" t="str">
         <v>Flooring: Delivery to Site</v>
       </c>
-      <c r="C225" t="str">
-        <v/>
-      </c>
-      <c r="D225" t="str">
+      <c r="C225" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D225" s="1" t="str">
         <v/>
       </c>
       <c r="E225">
@@ -13004,10 +12989,10 @@
       <c r="M225" t="str">
         <v/>
       </c>
-      <c r="N225" t="str">
-        <v/>
-      </c>
-      <c r="O225" t="str">
+      <c r="N225" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O225" s="1" t="str">
         <v/>
       </c>
       <c r="P225" t="str">
@@ -13027,10 +13012,10 @@
       <c r="B226" t="str">
         <v>Flooring: Installation / Execution</v>
       </c>
-      <c r="C226" t="str">
-        <v/>
-      </c>
-      <c r="D226" t="str">
+      <c r="C226" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D226" s="1" t="str">
         <v/>
       </c>
       <c r="E226">
@@ -13060,10 +13045,10 @@
       <c r="M226" t="str">
         <v/>
       </c>
-      <c r="N226" t="str">
-        <v/>
-      </c>
-      <c r="O226" t="str">
+      <c r="N226" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O226" s="1" t="str">
         <v/>
       </c>
       <c r="P226" t="str">
@@ -13083,10 +13068,10 @@
       <c r="B227" t="str">
         <v>Flooring: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C227" t="str">
-        <v/>
-      </c>
-      <c r="D227" t="str">
+      <c r="C227" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D227" s="1" t="str">
         <v/>
       </c>
       <c r="E227">
@@ -13116,10 +13101,10 @@
       <c r="M227" t="str">
         <v/>
       </c>
-      <c r="N227" t="str">
-        <v/>
-      </c>
-      <c r="O227" t="str">
+      <c r="N227" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O227" s="1" t="str">
         <v/>
       </c>
       <c r="P227" t="str">
@@ -13139,10 +13124,10 @@
       <c r="B228" t="str">
         <v>EXECUTE • Carpentry</v>
       </c>
-      <c r="C228" t="str">
-        <v/>
-      </c>
-      <c r="D228" t="str">
+      <c r="C228" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D228" s="1" t="str">
         <v/>
       </c>
       <c r="E228" t="str">
@@ -13172,10 +13157,10 @@
       <c r="M228" t="str">
         <v/>
       </c>
-      <c r="N228" t="str">
-        <v/>
-      </c>
-      <c r="O228" t="str">
+      <c r="N228" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O228" s="1" t="str">
         <v/>
       </c>
       <c r="P228" t="str">
@@ -13195,10 +13180,10 @@
       <c r="B229" t="str">
         <v>Carpentry: Mobilization &amp; Material Submittals</v>
       </c>
-      <c r="C229" t="str">
-        <v/>
-      </c>
-      <c r="D229" t="str">
+      <c r="C229" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D229" s="1" t="str">
         <v/>
       </c>
       <c r="E229">
@@ -13228,10 +13213,10 @@
       <c r="M229" t="str">
         <v/>
       </c>
-      <c r="N229" t="str">
-        <v/>
-      </c>
-      <c r="O229" t="str">
+      <c r="N229" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O229" s="1" t="str">
         <v/>
       </c>
       <c r="P229" t="str">
@@ -13251,10 +13236,10 @@
       <c r="B230" t="str">
         <v>Carpentry: Fabrication / Off‑site Prep (if applicable)</v>
       </c>
-      <c r="C230" t="str">
-        <v/>
-      </c>
-      <c r="D230" t="str">
+      <c r="C230" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D230" s="1" t="str">
         <v/>
       </c>
       <c r="E230">
@@ -13284,10 +13269,10 @@
       <c r="M230" t="str">
         <v/>
       </c>
-      <c r="N230" t="str">
-        <v/>
-      </c>
-      <c r="O230" t="str">
+      <c r="N230" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O230" s="1" t="str">
         <v/>
       </c>
       <c r="P230" t="str">
@@ -13307,10 +13292,10 @@
       <c r="B231" t="str">
         <v>Carpentry: Delivery to Site</v>
       </c>
-      <c r="C231" t="str">
-        <v/>
-      </c>
-      <c r="D231" t="str">
+      <c r="C231" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D231" s="1" t="str">
         <v/>
       </c>
       <c r="E231">
@@ -13340,10 +13325,10 @@
       <c r="M231" t="str">
         <v/>
       </c>
-      <c r="N231" t="str">
-        <v/>
-      </c>
-      <c r="O231" t="str">
+      <c r="N231" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O231" s="1" t="str">
         <v/>
       </c>
       <c r="P231" t="str">
@@ -13363,10 +13348,10 @@
       <c r="B232" t="str">
         <v>Carpentry: Installation / Execution</v>
       </c>
-      <c r="C232" t="str">
-        <v/>
-      </c>
-      <c r="D232" t="str">
+      <c r="C232" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D232" s="1" t="str">
         <v/>
       </c>
       <c r="E232">
@@ -13396,10 +13381,10 @@
       <c r="M232" t="str">
         <v/>
       </c>
-      <c r="N232" t="str">
-        <v/>
-      </c>
-      <c r="O232" t="str">
+      <c r="N232" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O232" s="1" t="str">
         <v/>
       </c>
       <c r="P232" t="str">
@@ -13419,10 +13404,10 @@
       <c r="B233" t="str">
         <v>Carpentry: Testing &amp; Commissioning / QA‑QC</v>
       </c>
-      <c r="C233" t="str">
-        <v/>
-      </c>
-      <c r="D233" t="str">
+      <c r="C233" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D233" s="1" t="str">
         <v/>
       </c>
       <c r="E233">
@@ -13452,10 +13437,10 @@
       <c r="M233" t="str">
         <v/>
       </c>
-      <c r="N233" t="str">
-        <v/>
-      </c>
-      <c r="O233" t="str">
+      <c r="N233" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O233" s="1" t="str">
         <v/>
       </c>
       <c r="P233" t="str">
@@ -13475,10 +13460,10 @@
       <c r="B234" t="str">
         <v>LINK • Flooring waits for Civil</v>
       </c>
-      <c r="C234" t="str">
-        <v/>
-      </c>
-      <c r="D234" t="str">
+      <c r="C234" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D234" s="1" t="str">
         <v/>
       </c>
       <c r="E234" t="str">
@@ -13508,10 +13493,10 @@
       <c r="M234" t="str">
         <v/>
       </c>
-      <c r="N234" t="str">
-        <v/>
-      </c>
-      <c r="O234" t="str">
+      <c r="N234" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O234" s="1" t="str">
         <v/>
       </c>
       <c r="P234" t="str">
@@ -13531,10 +13516,10 @@
       <c r="B235" t="str">
         <v>LINK • Wall Finishes wait for Civil</v>
       </c>
-      <c r="C235" t="str">
-        <v/>
-      </c>
-      <c r="D235" t="str">
+      <c r="C235" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D235" s="1" t="str">
         <v/>
       </c>
       <c r="E235" t="str">
@@ -13564,10 +13549,10 @@
       <c r="M235" t="str">
         <v/>
       </c>
-      <c r="N235" t="str">
-        <v/>
-      </c>
-      <c r="O235" t="str">
+      <c r="N235" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O235" s="1" t="str">
         <v/>
       </c>
       <c r="P235" t="str">
@@ -13587,10 +13572,10 @@
       <c r="B236" t="str">
         <v>LINK • Doors &amp; Windows wait for Civil</v>
       </c>
-      <c r="C236" t="str">
-        <v/>
-      </c>
-      <c r="D236" t="str">
+      <c r="C236" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D236" s="1" t="str">
         <v/>
       </c>
       <c r="E236" t="str">
@@ -13620,10 +13605,10 @@
       <c r="M236" t="str">
         <v/>
       </c>
-      <c r="N236" t="str">
-        <v/>
-      </c>
-      <c r="O236" t="str">
+      <c r="N236" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O236" s="1" t="str">
         <v/>
       </c>
       <c r="P236" t="str">
@@ -13643,10 +13628,10 @@
       <c r="B237" t="str">
         <v>LINK • Carpentry waits for Civil</v>
       </c>
-      <c r="C237" t="str">
-        <v/>
-      </c>
-      <c r="D237" t="str">
+      <c r="C237" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D237" s="1" t="str">
         <v/>
       </c>
       <c r="E237" t="str">
@@ -13676,10 +13661,10 @@
       <c r="M237" t="str">
         <v/>
       </c>
-      <c r="N237" t="str">
-        <v/>
-      </c>
-      <c r="O237" t="str">
+      <c r="N237" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O237" s="1" t="str">
         <v/>
       </c>
       <c r="P237" t="str">
@@ -13699,10 +13684,10 @@
       <c r="B238" t="str">
         <v>LINK • Lighting after Electricals</v>
       </c>
-      <c r="C238" t="str">
-        <v/>
-      </c>
-      <c r="D238" t="str">
+      <c r="C238" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D238" s="1" t="str">
         <v/>
       </c>
       <c r="E238" t="str">
@@ -13732,10 +13717,10 @@
       <c r="M238" t="str">
         <v/>
       </c>
-      <c r="N238" t="str">
-        <v/>
-      </c>
-      <c r="O238" t="str">
+      <c r="N238" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O238" s="1" t="str">
         <v/>
       </c>
       <c r="P238" t="str">
@@ -13755,10 +13740,10 @@
       <c r="B239" t="str">
         <v>LINK • Automation after Electricals</v>
       </c>
-      <c r="C239" t="str">
-        <v/>
-      </c>
-      <c r="D239" t="str">
+      <c r="C239" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D239" s="1" t="str">
         <v/>
       </c>
       <c r="E239" t="str">
@@ -13788,10 +13773,10 @@
       <c r="M239" t="str">
         <v/>
       </c>
-      <c r="N239" t="str">
-        <v/>
-      </c>
-      <c r="O239" t="str">
+      <c r="N239" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O239" s="1" t="str">
         <v/>
       </c>
       <c r="P239" t="str">
@@ -13811,10 +13796,10 @@
       <c r="B240" t="str">
         <v>LINK • Audio after Electricals</v>
       </c>
-      <c r="C240" t="str">
-        <v/>
-      </c>
-      <c r="D240" t="str">
+      <c r="C240" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D240" s="1" t="str">
         <v/>
       </c>
       <c r="E240" t="str">
@@ -13844,10 +13829,10 @@
       <c r="M240" t="str">
         <v/>
       </c>
-      <c r="N240" t="str">
-        <v/>
-      </c>
-      <c r="O240" t="str">
+      <c r="N240" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O240" s="1" t="str">
         <v/>
       </c>
       <c r="P240" t="str">
@@ -13867,10 +13852,10 @@
       <c r="B241" t="str">
         <v>LINK • Kitchens after Plumbing</v>
       </c>
-      <c r="C241" t="str">
-        <v/>
-      </c>
-      <c r="D241" t="str">
+      <c r="C241" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D241" s="1" t="str">
         <v/>
       </c>
       <c r="E241" t="str">
@@ -13900,10 +13885,10 @@
       <c r="M241" t="str">
         <v/>
       </c>
-      <c r="N241" t="str">
-        <v/>
-      </c>
-      <c r="O241" t="str">
+      <c r="N241" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O241" s="1" t="str">
         <v/>
       </c>
       <c r="P241" t="str">
@@ -13923,10 +13908,10 @@
       <c r="B242" t="str">
         <v>LINK • Bathrooms after Plumbing</v>
       </c>
-      <c r="C242" t="str">
-        <v/>
-      </c>
-      <c r="D242" t="str">
+      <c r="C242" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D242" s="1" t="str">
         <v/>
       </c>
       <c r="E242" t="str">
@@ -13956,10 +13941,10 @@
       <c r="M242" t="str">
         <v/>
       </c>
-      <c r="N242" t="str">
-        <v/>
-      </c>
-      <c r="O242" t="str">
+      <c r="N242" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O242" s="1" t="str">
         <v/>
       </c>
       <c r="P242" t="str">
@@ -13979,10 +13964,10 @@
       <c r="B243" t="str">
         <v>LINK • Appliances after Kitchens &amp; Electricals</v>
       </c>
-      <c r="C243" t="str">
-        <v/>
-      </c>
-      <c r="D243" t="str">
+      <c r="C243" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D243" s="1" t="str">
         <v/>
       </c>
       <c r="E243" t="str">
@@ -14012,10 +13997,10 @@
       <c r="M243" t="str">
         <v/>
       </c>
-      <c r="N243" t="str">
-        <v/>
-      </c>
-      <c r="O243" t="str">
+      <c r="N243" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O243" s="1" t="str">
         <v/>
       </c>
       <c r="P243" t="str">
@@ -14035,10 +14020,10 @@
       <c r="B244" t="str">
         <v>PHASE • Closeout &amp; Handover</v>
       </c>
-      <c r="C244" t="str">
-        <v/>
-      </c>
-      <c r="D244" t="str">
+      <c r="C244" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D244" s="1" t="str">
         <v/>
       </c>
       <c r="E244" t="str">
@@ -14068,10 +14053,10 @@
       <c r="M244" t="str">
         <v/>
       </c>
-      <c r="N244" t="str">
-        <v/>
-      </c>
-      <c r="O244" t="str">
+      <c r="N244" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O244" s="1" t="str">
         <v/>
       </c>
       <c r="P244" t="str">
@@ -14091,10 +14076,10 @@
       <c r="B245" t="str">
         <v>All Trades Complete – Declaration</v>
       </c>
-      <c r="C245" t="str">
-        <v/>
-      </c>
-      <c r="D245" t="str">
+      <c r="C245" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D245" s="1" t="str">
         <v/>
       </c>
       <c r="E245">
@@ -14124,10 +14109,10 @@
       <c r="M245" t="str">
         <v/>
       </c>
-      <c r="N245" t="str">
-        <v/>
-      </c>
-      <c r="O245" t="str">
+      <c r="N245" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O245" s="1" t="str">
         <v/>
       </c>
       <c r="P245" t="str">
@@ -14147,10 +14132,10 @@
       <c r="B246" t="str">
         <v>Snagging / Punch List</v>
       </c>
-      <c r="C246" t="str">
-        <v/>
-      </c>
-      <c r="D246" t="str">
+      <c r="C246" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D246" s="1" t="str">
         <v/>
       </c>
       <c r="E246">
@@ -14180,10 +14165,10 @@
       <c r="M246" t="str">
         <v/>
       </c>
-      <c r="N246" t="str">
-        <v/>
-      </c>
-      <c r="O246" t="str">
+      <c r="N246" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O246" s="1" t="str">
         <v/>
       </c>
       <c r="P246" t="str">
@@ -14203,10 +14188,10 @@
       <c r="B247" t="str">
         <v>Rectification of Snags</v>
       </c>
-      <c r="C247" t="str">
-        <v/>
-      </c>
-      <c r="D247" t="str">
+      <c r="C247" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D247" s="1" t="str">
         <v/>
       </c>
       <c r="E247">
@@ -14236,10 +14221,10 @@
       <c r="M247" t="str">
         <v/>
       </c>
-      <c r="N247" t="str">
-        <v/>
-      </c>
-      <c r="O247" t="str">
+      <c r="N247" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O247" s="1" t="str">
         <v/>
       </c>
       <c r="P247" t="str">
@@ -14259,10 +14244,10 @@
       <c r="B248" t="str">
         <v>Client Demo &amp; Acceptance</v>
       </c>
-      <c r="C248" t="str">
-        <v/>
-      </c>
-      <c r="D248" t="str">
+      <c r="C248" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D248" s="1" t="str">
         <v/>
       </c>
       <c r="E248">
@@ -14292,10 +14277,10 @@
       <c r="M248" t="str">
         <v/>
       </c>
-      <c r="N248" t="str">
-        <v/>
-      </c>
-      <c r="O248" t="str">
+      <c r="N248" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O248" s="1" t="str">
         <v/>
       </c>
       <c r="P248" t="str">
@@ -14315,10 +14300,10 @@
       <c r="B249" t="str">
         <v>Practical Completion / Handover</v>
       </c>
-      <c r="C249" t="str">
-        <v/>
-      </c>
-      <c r="D249" t="str">
+      <c r="C249" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D249" s="1" t="str">
         <v/>
       </c>
       <c r="E249">
@@ -14348,10 +14333,10 @@
       <c r="M249" t="str">
         <v/>
       </c>
-      <c r="N249" t="str">
-        <v/>
-      </c>
-      <c r="O249" t="str">
+      <c r="N249" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O249" s="1" t="str">
         <v/>
       </c>
       <c r="P249" t="str">
@@ -14371,10 +14356,10 @@
       <c r="B250" t="str">
         <v>As‑Built Docs &amp; O&amp;M Manuals</v>
       </c>
-      <c r="C250" t="str">
-        <v/>
-      </c>
-      <c r="D250" t="str">
+      <c r="C250" s="1" t="str">
+        <v/>
+      </c>
+      <c r="D250" s="1" t="str">
         <v/>
       </c>
       <c r="E250">
@@ -14404,10 +14389,10 @@
       <c r="M250" t="str">
         <v/>
       </c>
-      <c r="N250" t="str">
-        <v/>
-      </c>
-      <c r="O250" t="str">
+      <c r="N250" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O250" s="1" t="str">
         <v/>
       </c>
       <c r="P250" t="str">
@@ -14421,6 +14406,8 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R250"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:R250"/>
   </ignoredErrors>
@@ -14430,11 +14417,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C50"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
